--- a/results/metrics_modelling3.xlsx
+++ b/results/metrics_modelling3.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Logit_test</t>
+          <t>Logit_splashing_test</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.006796121597290039, 0.005709648132324219, 0.009855985641479492, 0.0030870437622070312, 0.008744001388549805</t>
+          <t>0.0074918270111083984, 0.0032570362091064453, 0.003041982650756836, 0.0076830387115478516, 0.004441261291503906</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.0317230224609375, 0.004549264907836914, 0.010825872421264648, 0.0075531005859375, 0.007467031478881836</t>
+          <t>0.01373600959777832, 0.004681110382080078, 0.006099224090576172, 0.009279966354370117, 0.004483699798583984</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">

--- a/results/metrics_modelling3.xlsx
+++ b/results/metrics_modelling3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,6 +669,800 @@
       <c r="Z2" t="inlineStr">
         <is>
           <t>0.8862599206349207, 0.8992807539682539, 0.8969388757861635, 0.8968406053459119, 0.9042354559748428</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LogisticRegression_splashing_test</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>{'estimator': LogisticRegression(), 'source_features': ['init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'], 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': None, 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8035714285714286</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.8653846153846154</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8912037037037037</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.8407960199004975</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.8802083333333334</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.8600508905852416</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.9132688492063492</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.018549442291259766, 0.0, 0.01028299331665039, 0.007892370223999023, 0.0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.004538774490356445, 0.013784646987915039, 0.008110523223876953, 0.008096694946289062, 0.02117133140563965</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0.84, 0.8133333333333334, 0.7837837837837838, 0.7972972972972973, 0.7702702702702703</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.8080808080808081, 0.8181818181818182, 0.8154362416107382, 0.8389261744966443, 0.8221476510067114</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.8461538461538461, 0.8269230769230769, 0.8636363636363636, 0.8235294117647058, 0.7818181818181819</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.8292682926829268, 0.8415841584158416, 0.8309178743961353, 0.86, 0.8390243902439024</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.9166666666666666, 0.8958333333333334, 0.7916666666666666, 0.875, 0.8958333333333334</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.8854166666666666, 0.8854166666666666, 0.8958333333333334, 0.8958333333333334, 0.8958333333333334</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.8799999999999999, 0.86, 0.8260869565217391, 0.8484848484848485, 0.8349514563106797</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.8564231738035264, 0.8629441624365483, 0.862155388471178, 0.8775510204081632, 0.8664987405541561</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.9436728395061728, 0.8935185185185186, 0.889423076923077, 0.9046474358974359, 0.8509615384615384</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.8981150793650794, 0.9085565476190476, 0.9093700864779874, 0.9061271619496855, 0.9170106132075472</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>KNeighborsClassifier_splashing_test</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{'estimator': KNeighborsClassifier(), 'source_features': ['init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'], 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': None, 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8269230769230769</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.880787037037037</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.9158249158249159</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.9282051282051282</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.9427083333333334</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.9354005167958657</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.9661954365079365</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.013483047485351562, 0.008872747421264648, 0.0, 0.00803828239440918, 0.015599966049194336</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0.0032334327697753906, 0.008018970489501953, 0.02013373374938965, 0.00797891616821289, 0.0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0.9333333333333333, 0.7733333333333333, 0.8108108108108109, 0.8648648648648649, 0.7297297297297297</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.898989898989899, 0.8888888888888888, 0.889261744966443, 0.8993288590604027, 0.8859060402684564</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.9387755102040817, 0.8444444444444444, 0.8541666666666666, 0.9318181818181818, 0.7916666666666666</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.9263157894736842, 0.9206349206349206, 0.9035532994923858, 0.9263157894736842, 0.9157894736842105</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0.9583333333333334, 0.7916666666666666, 0.8541666666666666, 0.8541666666666666, 0.7916666666666666</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.9166666666666666, 0.90625, 0.9270833333333334, 0.9166666666666666, 0.90625</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.9484536082474228, 0.8172043010752689, 0.8541666666666666, 0.8913043478260869, 0.7916666666666666</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.9214659685863874, 0.9133858267716536, 0.9151670951156814, 0.9214659685863874, 0.9109947643979057</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.970679012345679, 0.8873456790123456, 0.923477564102564, 0.938301282051282, 0.8257211538461537</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0.9578869047619047, 0.9656250000000001, 0.9632468553459119, 0.9583824685534591, 0.9681603773584906</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SVC_splashing_test</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>{'estimator': SVC(probability=True), 'source_features': ['init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'], 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': None, 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.8214285714285714</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8846153846153847</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.8855218855218855</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.9030612244897959</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.921875</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.9123711340206186</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.9497271825396826</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0.02239513397216797, 0.014011144638061523, 0.011605024337768555, 0.008462667465209961, 0.015657901763916016</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.014072656631469727, 0.008000850677490234, 0.012187957763671875, 0.013071537017822266, 0.0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0.88, 0.7733333333333333, 0.8513513513513513, 0.8648648648648649, 0.8378378378378378</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0.8754208754208754, 0.8821548821548821, 0.8791946308724832, 0.8590604026845637, 0.8993288590604027</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.8545454545454545, 0.8297872340425532, 0.9302325581395349, 0.9523809523809523, 0.875</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.8743961352657005, 0.943502824858757, 0.9333333333333333, 0.9261363636363636, 0.9175257731958762</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0.9791666666666666, 0.8125, 0.8333333333333334, 0.8333333333333334, 0.875</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.9427083333333334, 0.8697916666666666, 0.875, 0.8489583333333334, 0.9270833333333334</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.912621359223301, 0.8210526315789474, 0.8791208791208791, 0.888888888888889, 0.875</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.9072681704260651, 0.9051490514905148, 0.9032258064516129, 0.8858695652173912, 0.9222797927461139</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.9606481481481481, 0.8966049382716049, 0.9350961538461539, 0.9663461538461539, 0.8669871794871795</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.9385416666666667, 0.9472966269841271, 0.946221501572327, 0.9348221305031447, 0.9523142688679246</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_splashing_test</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x000001FA077EBB20&gt;, 'source_features': ['init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'], 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': None, 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.910891089108911</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.9483024691358024</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.9988343253968255</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1.8345623016357422, 1.5924808979034424, 1.5990405082702637, 1.5497426986694336, 1.6355464458465576</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.0, 0.011824607849121094, 0.011261940002441406, 0.015034914016723633, 0.013416528701782227</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0.9333333333333333, 0.8933333333333333, 0.8648648648648649, 0.9459459459459459, 0.8648648648648649</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0.98989898989899, 0.98989898989899, 0.9932885906040269, 0.9865771812080537, 0.9966442953020134</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.9387755102040817, 0.8846153846153846, 0.9318181818181818, 0.9583333333333334, 0.8958333333333334</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0.9896373056994818, 0.9896373056994818, 0.9947916666666666, 0.9845360824742269, 0.9948186528497409</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0.9583333333333334, 0.9583333333333334, 0.8541666666666666, 0.9583333333333334, 0.8958333333333334</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.9947916666666666, 0.9947916666666666, 0.9947916666666666, 0.9947916666666666, 1.0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.9484536082474228, 0.9199999999999999, 0.8913043478260869, 0.9583333333333334, 0.8958333333333334</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.9922077922077923, 0.9922077922077923, 0.9947916666666666, 0.9896373056994819, 0.9974025974025974</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.9814814814814814, 0.9722222222222222, 0.9455128205128205, 0.969551282051282, 0.905448717948718</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.9982638888888888, 0.9980406746031746, 0.9985996462264151, 0.9984522405660378, 1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_splashing_test</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x000001FA077E87F0&gt;, 'source_features': ['init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'], 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': None, 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.910891089108911</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9483024691358024</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.9988343253968255</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.5326519012451172, 1.561889886856079, 1.562685251235962, 1.514699935913086, 1.5161700248718262</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.010239601135253906, 0.009035110473632812, 0.00038623809814453125, 0.008512496948242188, 0.01370692253112793</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0.9333333333333333, 0.8933333333333333, 0.8648648648648649, 0.9459459459459459, 0.8648648648648649</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0.98989898989899, 0.98989898989899, 0.9932885906040269, 0.9865771812080537, 0.9966442953020134</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.9387755102040817, 0.8846153846153846, 0.9318181818181818, 0.9583333333333334, 0.8958333333333334</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0.9896373056994818, 0.9896373056994818, 0.9947916666666666, 0.9845360824742269, 0.9948186528497409</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>0.9583333333333334, 0.9583333333333334, 0.8541666666666666, 0.9583333333333334, 0.8958333333333334</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.9947916666666666, 0.9947916666666666, 0.9947916666666666, 0.9947916666666666, 1.0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.9484536082474228, 0.9199999999999999, 0.8913043478260869, 0.9583333333333334, 0.8958333333333334</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.9922077922077923, 0.9922077922077923, 0.9947916666666666, 0.9896373056994819, 0.9974025974025974</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.9814814814814814, 0.9722222222222222, 0.9455128205128205, 0.969551282051282, 0.905448717948718</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.9982638888888888, 0.9980406746031746, 0.9985996462264151, 0.9984522405660378, 1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_splashing_test</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x000001FA05B67970&gt;, 'source_features': ['init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'], 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': None, 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.910891089108911</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9483024691358024</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.9988343253968255</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.5839686393737793, 1.4876301288604736, 1.5380446910858154, 1.614840030670166, 1.587310791015625</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0.01909041404724121, 0.01392221450805664, 0.016156911849975586, 0.014037370681762695, 0.008305072784423828</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0.9333333333333333, 0.8933333333333333, 0.8648648648648649, 0.9459459459459459, 0.8648648648648649</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0.98989898989899, 0.98989898989899, 0.9932885906040269, 0.9865771812080537, 0.9966442953020134</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.9387755102040817, 0.8846153846153846, 0.9318181818181818, 0.9583333333333334, 0.8958333333333334</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0.9896373056994818, 0.9896373056994818, 0.9947916666666666, 0.9845360824742269, 0.9948186528497409</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0.9583333333333334, 0.9583333333333334, 0.8541666666666666, 0.9583333333333334, 0.8958333333333334</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.9947916666666666, 0.9947916666666666, 0.9947916666666666, 0.9947916666666666, 1.0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.9484536082474228, 0.9199999999999999, 0.8913043478260869, 0.9583333333333334, 0.8958333333333334</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.9922077922077923, 0.9922077922077923, 0.9947916666666666, 0.9896373056994819, 0.9974025974025974</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.9814814814814814, 0.9722222222222222, 0.9455128205128205, 0.969551282051282, 0.905448717948718</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0.9982638888888888, 0.9980406746031746, 0.9985996462264151, 0.9984522405660378, 1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>XGBClassifier_splashing_test</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{'estimator': XGBClassifier(base_score=None, booster=None, callbacks=None,
+              colsample_bylevel=None, colsample_bynode=None,
+              colsample_bytree=None, early_stopping_rounds=None,
+              enable_categorical=False, eval_metric=None, feature_types=None,
+              gamma=None, gpu_id=None, grow_policy=None, importance_type=None,
+              interaction_constraints=None, learning_rate=None, max_bin=None,
+              max_cat_threshold=None, max_cat_to_onehot=None,
+              max_delta_step=None, max_depth=None, max_leaves=None,
+              min_child_weight=None, missing=nan, monotone_constraints=None,
+              n_estimators=100, n_jobs=None, num_parallel_tree=None,
+              predictor=None, random_state=None, ...), 'source_features': ['init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'], 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': None, 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.910891089108911</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.9513888888888888</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.9999751984126984</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.09089159965515137, 0.059160709381103516, 0.08683967590332031, 0.10107588768005371, 0.06659388542175293</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0.016202449798583984, 0.007999658584594727, 0.01626896858215332, 0.01671314239501953, 0.014142274856567383</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0.9466666666666667, 0.8933333333333333, 0.8378378378378378, 0.9324324324324325, 0.8108108108108109</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1.0, 0.9966329966329966, 0.9966442953020134, 0.9966442953020134, 1.0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.94, 0.9, 0.9090909090909091, 0.9574468085106383, 0.84</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1.0, 0.9948186528497409, 0.9948186528497409, 0.9948186528497409, 1.0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0.9791666666666666, 0.9375, 0.8333333333333334, 0.9375, 0.875</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.9591836734693877, 0.9183673469387755, 0.8695652173913043, 0.9473684210526315, 0.8571428571428572</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>1.0, 0.9974025974025974, 0.9974025974025974, 0.9974025974025974, 1.0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.9822530864197532, 0.9737654320987654, 0.9174679487179487, 0.9599358974358974, 0.8870192307692307</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>1.0, 0.9999751984126984, 0.9999754323899371, 0.9999754323899371, 1.0</t>
         </is>
       </c>
     </row>

--- a/results/metrics_modelling3.xlsx
+++ b/results/metrics_modelling3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,12 +573,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Logit_splashing_test</t>
+          <t>Logit_splashing_base</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{'estimator': StatsModelsEstimator(model_class=&lt;class 'statsmodels.discrete.discrete_model.Logit'&gt;), 'source_features': ['init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'], 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': None, 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': StatsModelsEstimator(model_class=&lt;class 'statsmodels.discrete.discrete_model.Logit'&gt;), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -613,62 +613,62 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.0074918270111083984, 0.0032570362091064453, 0.003041982650756836, 0.0076830387115478516, 0.004441261291503906</t>
+          <t>0.005369901657104492, 0.012936115264892578, 0.006644010543823242, 0.008224010467529297, 0.0029840469360351562, 0.002872943878173828, 0.007586956024169922</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.01373600959777832, 0.004681110382080078, 0.006099224090576172, 0.009279966354370117, 0.004483699798583984</t>
+          <t>0.004912137985229492, 0.01417398452758789, 0.004354000091552734, 0.006852865219116211, 0.004110813140869141, 0.004078865051269531, 0.009239912033081055</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.84, 0.7866666666666666, 0.7567567567567568, 0.7432432432432432, 0.8108108108108109</t>
+          <t>0.9074074074074074, 0.6981132075471698, 0.8301886792452831, 0.7547169811320755, 0.8113207547169812, 0.7169811320754716, 0.7547169811320755</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.7946127946127947, 0.8080808080808081, 0.802013422818792, 0.802013422818792, 0.8087248322147651</t>
+          <t>0.7861635220125787, 0.7962382445141066, 0.7931034482758621, 0.8056426332288401, 0.7899686520376176, 0.8150470219435737, 0.8087774294670846</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.875, 0.8333333333333334, 0.8947368421052632, 0.8372093023255814, 0.84</t>
+          <t>0.8947368421052632, 0.8518518518518519, 0.8787878787878788, 0.8888888888888888, 0.9, 0.7878787878787878, 0.7837837837837838</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.8540540540540541, 0.8770949720670391, 0.8674033149171271, 0.8674033149171271, 0.8688524590163934</t>
+          <t>0.8512820512820513, 0.8645833333333334, 0.868421052631579, 0.8673469387755102, 0.8527918781725888, 0.8769230769230769, 0.8717948717948718</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.875, 0.8333333333333334, 0.7083333333333334, 0.75, 0.875</t>
+          <t>0.9714285714285714, 0.6571428571428571, 0.8529411764705882, 0.7058823529411765, 0.7941176470588235, 0.7647058823529411, 0.8529411764705882</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.8229166666666666, 0.8177083333333334, 0.8177083333333334, 0.8177083333333334, 0.828125</t>
+          <t>0.8097560975609757, 0.8097560975609757, 0.8009708737864077, 0.8252427184466019, 0.8155339805825242, 0.8300970873786407, 0.8252427184466019</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.875, 0.8333333333333334, 0.7906976744186046, 0.7912087912087912, 0.8571428571428572</t>
+          <t>0.9315068493150684, 0.7419354838709677, 0.8656716417910447, 0.7868852459016393, 0.84375, 0.7761194029850745, 0.8169014084507041</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.8381962864721485, 0.8463611859838276, 0.8418230563002681, 0.8418230563002681, 0.8480000000000001</t>
+          <t>0.8300000000000001, 0.8362720403022671, 0.8333333333333333, 0.8457711442786069, 0.8337468982630273, 0.8528678304239402, 0.8478802992518701</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.9220679012345678, 0.8641975308641975, 0.8878205128205128, 0.8830128205128205, 0.8557692307692307</t>
+          <t>0.9503759398496241, 0.8269841269841269, 0.9040247678018576, 0.9040247678018576, 0.9349845201238389, 0.8126934984520123, 0.8436532507739938</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.8862599206349207, 0.8992807539682539, 0.8969388757861635, 0.8968406053459119, 0.9042354559748428</t>
+          <t>0.8876537880423052, 0.9035515618314078, 0.8926239367643268, 0.8959747400979465, 0.8880702809519718, 0.9072085230689921, 0.8982086089870264</t>
         </is>
       </c>
     </row>
@@ -685,12 +685,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LogisticRegression_splashing_test</t>
+          <t>LogisticRegression_splashing_base</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'estimator': LogisticRegression(), 'source_features': ['init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'], 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': None, 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': LogisticRegression(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -725,62 +725,62 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.018549442291259766, 0.0, 0.01028299331665039, 0.007892370223999023, 0.0</t>
+          <t>0.006107807159423828, 0.0034821033477783203, 0.003284931182861328, 0.003621816635131836, 0.003426074981689453, 0.003782033920288086, 0.003475189208984375</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.004538774490356445, 0.013784646987915039, 0.008110523223876953, 0.008096694946289062, 0.02117133140563965</t>
+          <t>0.00541996955871582, 0.004540920257568359, 0.0042972564697265625, 0.004637241363525391, 0.0045320987701416016, 0.0045931339263916016, 0.004570960998535156</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.84, 0.8133333333333334, 0.7837837837837838, 0.7972972972972973, 0.7702702702702703</t>
+          <t>0.8703703703703703, 0.7924528301886793, 0.8490566037735849, 0.7735849056603774, 0.8301886792452831, 0.7547169811320755, 0.7735849056603774</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.8080808080808081, 0.8181818181818182, 0.8154362416107382, 0.8389261744966443, 0.8221476510067114</t>
+          <t>0.8113207547169812, 0.8119122257053292, 0.8119122257053292, 0.8150470219435737, 0.8119122257053292, 0.8463949843260188, 0.8181818181818182</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.8461538461538461, 0.8269230769230769, 0.8636363636363636, 0.8235294117647058, 0.7818181818181819</t>
+          <t>0.8333333333333334, 0.8529411764705882, 0.8611111111111112, 0.8235294117647058, 0.8571428571428571, 0.8, 0.7894736842105263</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.8292682926829268, 0.8415841584158416, 0.8309178743961353, 0.86, 0.8390243902439024</t>
+          <t>0.8341013824884793, 0.8310502283105022, 0.8348623853211009, 0.832579185520362, 0.8318181818181818, 0.8685446009389671, 0.8394495412844036</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.9166666666666666, 0.8958333333333334, 0.7916666666666666, 0.875, 0.8958333333333334</t>
+          <t>1.0, 0.8285714285714286, 0.9117647058823529, 0.8235294117647058, 0.8823529411764706, 0.8235294117647058, 0.8823529411764706</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.8854166666666666, 0.8854166666666666, 0.8958333333333334, 0.8958333333333334, 0.8958333333333334</t>
+          <t>0.8829268292682927, 0.8878048780487805, 0.883495145631068, 0.8932038834951457, 0.8883495145631068, 0.8980582524271845, 0.8883495145631068</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.8799999999999999, 0.86, 0.8260869565217391, 0.8484848484848485, 0.8349514563106797</t>
+          <t>0.9090909090909091, 0.8405797101449276, 0.8857142857142858, 0.8235294117647058, 0.8695652173913043, 0.8115942028985507, 0.8333333333333333</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.8564231738035264, 0.8629441624365483, 0.862155388471178, 0.8775510204081632, 0.8664987405541561</t>
+          <t>0.8578199052132701, 0.8584905660377359, 0.8584905660377358, 0.8618266978922716, 0.8591549295774649, 0.883054892601432, 0.8632075471698114</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.9436728395061728, 0.8935185185185186, 0.889423076923077, 0.9046474358974359, 0.8509615384615384</t>
+          <t>0.9578947368421054, 0.8571428571428572, 0.9504643962848297, 0.8869969040247677, 0.9411764705882353, 0.8126934984520124, 0.8606811145510836</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.8981150793650794, 0.9085565476190476, 0.9093700864779874, 0.9061271619496855, 0.9170106132075472</t>
+          <t>0.8975825598963955, 0.9145485665382971, 0.9012586992009622, 0.9084328550562764, 0.8984234040725149, 0.9190652117879542, 0.9092061173640348</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KNeighborsClassifier_splashing_test</t>
+          <t>KNeighborsClassifier_splashing_base</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{'estimator': KNeighborsClassifier(), 'source_features': ['init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'], 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': None, 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': KNeighborsClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -837,62 +837,62 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.013483047485351562, 0.008872747421264648, 0.0, 0.00803828239440918, 0.015599966049194336</t>
+          <t>0.003818988800048828, 0.003165006637573242, 0.002794981002807617, 0.002596139907836914, 0.002512693405151367, 0.002949953079223633, 0.0029401779174804688</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.0032334327697753906, 0.008018970489501953, 0.02013373374938965, 0.00797891616821289, 0.0</t>
+          <t>0.008829116821289062, 0.005921125411987305, 0.0054149627685546875, 0.0054569244384765625, 0.006937265396118164, 0.006503105163574219, 0.006007194519042969</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.9333333333333333, 0.7733333333333333, 0.8108108108108109, 0.8648648648648649, 0.7297297297297297</t>
+          <t>0.8888888888888888, 0.8301886792452831, 0.8679245283018868, 0.8113207547169812, 0.8490566037735849, 0.8113207547169812, 0.7735849056603774</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.898989898989899, 0.8888888888888888, 0.889261744966443, 0.8993288590604027, 0.8859060402684564</t>
+          <t>0.8962264150943396, 0.896551724137931, 0.8808777429467085, 0.8934169278996865, 0.8934169278996865, 0.890282131661442, 0.8934169278996865</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.9387755102040817, 0.8444444444444444, 0.8541666666666666, 0.9318181818181818, 0.7916666666666666</t>
+          <t>0.8918918918918919, 0.8823529411764706, 0.9090909090909091, 0.875, 0.8611111111111112, 0.9, 0.7894736842105263</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.9263157894736842, 0.9206349206349206, 0.9035532994923858, 0.9263157894736842, 0.9157894736842105</t>
+          <t>0.9174757281553398, 0.9215686274509803, 0.9158415841584159, 0.9174757281553398, 0.9215686274509803, 0.9130434782608695, 0.9215686274509803</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.9583333333333334, 0.7916666666666666, 0.8541666666666666, 0.8541666666666666, 0.7916666666666666</t>
+          <t>0.9428571428571428, 0.8571428571428571, 0.8823529411764706, 0.8235294117647058, 0.9117647058823529, 0.7941176470588235, 0.8823529411764706</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.9166666666666666, 0.90625, 0.9270833333333334, 0.9166666666666666, 0.90625</t>
+          <t>0.9219512195121952, 0.9170731707317074, 0.8980582524271845, 0.9174757281553398, 0.912621359223301, 0.9174757281553398, 0.912621359223301</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.9484536082474228, 0.8172043010752689, 0.8541666666666666, 0.8913043478260869, 0.7916666666666666</t>
+          <t>0.9166666666666667, 0.8695652173913043, 0.8955223880597014, 0.8484848484848485, 0.8857142857142858, 0.84375, 0.8333333333333333</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.9214659685863874, 0.9133858267716536, 0.9151670951156814, 0.9214659685863874, 0.9109947643979057</t>
+          <t>0.9197080291970803, 0.9193154034229828, 0.9068627450980392, 0.9174757281553398, 0.9170731707317074, 0.9152542372881356, 0.9170731707317074</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.970679012345679, 0.8873456790123456, 0.923477564102564, 0.938301282051282, 0.8257211538461537</t>
+          <t>0.9624060150375939, 0.8849206349206349, 0.9272445820433436, 0.914860681114551, 0.8924148606811145, 0.923374613003096, 0.846749226006192</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.9578869047619047, 0.9656250000000001, 0.9632468553459119, 0.9583824685534591, 0.9681603773584906</t>
+          <t>0.9620332398014245, 0.9660034231921266, 0.9626256551250107, 0.9647521264713463, 0.9616805567488615, 0.9633774379242204, 0.967694819142538</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SVC_splashing_test</t>
+          <t>SVC_splashing_base</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'estimator': SVC(probability=True), 'source_features': ['init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'], 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': None, 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': SVC(probability=True), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -949,62 +949,62 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.02239513397216797, 0.014011144638061523, 0.011605024337768555, 0.008462667465209961, 0.015657901763916016</t>
+          <t>0.009522199630737305, 0.007333993911743164, 0.008442878723144531, 0.007794857025146484, 0.008556842803955078, 0.0076141357421875, 0.0077898502349853516</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.014072656631469727, 0.008000850677490234, 0.012187957763671875, 0.013071537017822266, 0.0</t>
+          <t>0.005955934524536133, 0.00539708137512207, 0.006314992904663086, 0.0053369998931884766, 0.005982160568237305, 0.0050771236419677734, 0.005279064178466797</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.88, 0.7733333333333333, 0.8513513513513513, 0.8648648648648649, 0.8378378378378378</t>
+          <t>0.9074074074074074, 0.7547169811320755, 0.8679245283018868, 0.8679245283018868, 0.8867924528301887, 0.8490566037735849, 0.8490566037735849</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.8754208754208754, 0.8821548821548821, 0.8791946308724832, 0.8590604026845637, 0.8993288590604027</t>
+          <t>0.8710691823899371, 0.8746081504702194, 0.8683385579937304, 0.877742946708464, 0.8746081504702194, 0.877742946708464, 0.890282131661442</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.8545454545454545, 0.8297872340425532, 0.9302325581395349, 0.9523809523809523, 0.875</t>
+          <t>0.875, 0.84375, 0.9354838709677419, 0.9354838709677419, 0.9666666666666667, 0.9333333333333333, 0.8611111111111112</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.8743961352657005, 0.943502824858757, 0.9333333333333333, 0.9261363636363636, 0.9175257731958762</t>
+          <t>0.8660714285714286, 0.9365079365079365, 0.9361702127659575, 0.9154228855721394, 0.923469387755102, 0.9282051282051282, 0.934010152284264</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.9791666666666666, 0.8125, 0.8333333333333334, 0.8333333333333334, 0.875</t>
+          <t>1.0, 0.7714285714285715, 0.8529411764705882, 0.8529411764705882, 0.8529411764705882, 0.8235294117647058, 0.9117647058823529</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.9427083333333334, 0.8697916666666666, 0.875, 0.8489583333333334, 0.9270833333333334</t>
+          <t>0.9463414634146341, 0.8634146341463415, 0.8543689320388349, 0.8932038834951457, 0.8786407766990292, 0.8786407766990292, 0.8932038834951457</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.912621359223301, 0.8210526315789474, 0.8791208791208791, 0.888888888888889, 0.875</t>
+          <t>0.9333333333333333, 0.8059701492537314, 0.8923076923076922, 0.8923076923076922, 0.90625, 0.8749999999999999, 0.8857142857142858</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.9072681704260651, 0.9051490514905148, 0.9032258064516129, 0.8858695652173912, 0.9222797927461139</t>
+          <t>0.9044289044289044, 0.898477157360406, 0.8934010152284263, 0.9041769041769042, 0.900497512437811, 0.9027431421446385, 0.913151364764268</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.9606481481481481, 0.8966049382716049, 0.9350961538461539, 0.9663461538461539, 0.8669871794871795</t>
+          <t>0.9699248120300752, 0.8333333333333334, 0.9705882352941176, 0.9303405572755418, 0.9504643962848297, 0.9055727554179567, 0.8839009287925697</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.9385416666666667, 0.9472966269841271, 0.946221501572327, 0.9348221305031447, 0.9523142688679246</t>
+          <t>0.9373839844593136, 0.9515618314077879, 0.9390626342469285, 0.9434229744823438, 0.9364850932210671, 0.9465375032219263, 0.9486854540768108</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CatBoostClassifier_splashing_test</t>
+          <t>CatBoostClassifier_splashing_base</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x000001FA077EBB20&gt;, 'source_features': ['init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'], 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': None, 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x177d4ee50&gt;, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1042,7 +1042,7 @@
         <v>0.910891089108911</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9483024691358024</v>
+        <v>0.9467592592592593</v>
       </c>
       <c r="J6" t="n">
         <v>0.9966329966329966</v>
@@ -1057,66 +1057,66 @@
         <v>0.9974025974025974</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9988343253968255</v>
+        <v>0.9988839285714286</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>1.8345623016357422, 1.5924808979034424, 1.5990405082702637, 1.5497426986694336, 1.6355464458465576</t>
+          <t>0.65146803855896, 0.5669980049133301, 0.5646288394927979, 0.5705621242523193, 0.5885837078094482, 0.5664160251617432, 0.5634949207305908</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.0, 0.011824607849121094, 0.011261940002441406, 0.015034914016723633, 0.013416528701782227</t>
+          <t>0.006080150604248047, 0.005192756652832031, 0.006352901458740234, 0.005527019500732422, 0.005827188491821289, 0.006092071533203125, 0.0054569244384765625</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.9333333333333333, 0.8933333333333333, 0.8648648648648649, 0.9459459459459459, 0.8648648648648649</t>
+          <t>0.9629629629629629, 0.8679245283018868, 0.9056603773584906, 0.8301886792452831, 0.8867924528301887, 0.8867924528301887, 0.8679245283018868</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0.98989898989899, 0.98989898989899, 0.9932885906040269, 0.9865771812080537, 0.9966442953020134</t>
+          <t>0.9874213836477987, 0.9937304075235109, 0.9905956112852664, 0.9905956112852664, 0.987460815047022, 0.9937304075235109, 0.9905956112852664</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.9387755102040817, 0.8846153846153846, 0.9318181818181818, 0.9583333333333334, 0.8958333333333334</t>
+          <t>0.9459459459459459, 0.9117647058823529, 0.9142857142857143, 0.8787878787878788, 0.9375, 0.9375, 0.8857142857142857</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0.9896373056994818, 0.9896373056994818, 0.9947916666666666, 0.9845360824742269, 0.9948186528497409</t>
+          <t>0.9855072463768116, 0.9903381642512077, 0.9903381642512077, 0.9951219512195122, 0.9902912621359223, 0.9951456310679612, 0.9903381642512077</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.9583333333333334, 0.9583333333333334, 0.8541666666666666, 0.9583333333333334, 0.8958333333333334</t>
+          <t>1.0, 0.8857142857142857, 0.9411764705882353, 0.8529411764705882, 0.8823529411764706, 0.8823529411764706, 0.9117647058823529</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.9947916666666666, 0.9947916666666666, 0.9947916666666666, 0.9947916666666666, 1.0</t>
+          <t>0.9951219512195122, 1.0, 0.9951456310679612, 0.9902912621359223, 0.9902912621359223, 0.9951456310679612, 0.9951456310679612</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.9484536082474228, 0.9199999999999999, 0.8913043478260869, 0.9583333333333334, 0.8958333333333334</t>
+          <t>0.9722222222222222, 0.8985507246376812, 0.9275362318840579, 0.8656716417910447, 0.9090909090909091, 0.9090909090909091, 0.8985507246376812</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.9922077922077923, 0.9922077922077923, 0.9947916666666666, 0.9896373056994819, 0.9974025974025974</t>
+          <t>0.9902912621359223, 0.9951456310679612, 0.9927360774818401, 0.9927007299270073, 0.9902912621359223, 0.9951456310679612, 0.9927360774818401</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.9814814814814814, 0.9722222222222222, 0.9455128205128205, 0.969551282051282, 0.905448717948718</t>
+          <t>1.0, 0.9396825396825397, 0.9736842105263158, 0.93343653250774, 0.9705882352941176, 0.9504643962848298, 0.9226006191950464</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.9982638888888888, 0.9980406746031746, 0.9985996462264151, 0.9984522405660378, 1.0</t>
+          <t>0.9979063241959854, 0.9986307231493367, 0.9984319958759343, 0.9985179139101297, 0.9984319958759343, 0.9999570409829023, 0.9984319958759343</t>
         </is>
       </c>
     </row>
@@ -1133,336 +1133,112 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CatBoostClassifier_splashing_test</t>
+          <t>XGBClassifier_splashing_base</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
-        <is>
-          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x000001FA077E87F0&gt;, 'source_features': ['init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'], 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': None, 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.8679245283018868</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.9583333333333334</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.910891089108911</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.9483024691358024</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.9966329966329966</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.9948186528497409</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.9974025974025974</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.9988343253968255</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1.5326519012451172, 1.561889886856079, 1.562685251235962, 1.514699935913086, 1.5161700248718262</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0.010239601135253906, 0.009035110473632812, 0.00038623809814453125, 0.008512496948242188, 0.01370692253112793</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0.9333333333333333, 0.8933333333333333, 0.8648648648648649, 0.9459459459459459, 0.8648648648648649</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0.98989898989899, 0.98989898989899, 0.9932885906040269, 0.9865771812080537, 0.9966442953020134</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0.9387755102040817, 0.8846153846153846, 0.9318181818181818, 0.9583333333333334, 0.8958333333333334</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>0.9896373056994818, 0.9896373056994818, 0.9947916666666666, 0.9845360824742269, 0.9948186528497409</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>0.9583333333333334, 0.9583333333333334, 0.8541666666666666, 0.9583333333333334, 0.8958333333333334</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0.9947916666666666, 0.9947916666666666, 0.9947916666666666, 0.9947916666666666, 1.0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0.9484536082474228, 0.9199999999999999, 0.8913043478260869, 0.9583333333333334, 0.8958333333333334</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0.9922077922077923, 0.9922077922077923, 0.9947916666666666, 0.9896373056994819, 0.9974025974025974</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0.9814814814814814, 0.9722222222222222, 0.9455128205128205, 0.969551282051282, 0.905448717948718</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>0.9982638888888888, 0.9980406746031746, 0.9985996462264151, 0.9984522405660378, 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>df_dimless</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>splashing</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>CatBoostClassifier_splashing_test</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x000001FA05B67970&gt;, 'source_features': ['init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'], 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': None, 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.8679245283018868</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.9583333333333334</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.910891089108911</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.9483024691358024</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.9966329966329966</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.9948186528497409</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.9974025974025974</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.9988343253968255</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>1.5839686393737793, 1.4876301288604736, 1.5380446910858154, 1.614840030670166, 1.587310791015625</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0.01909041404724121, 0.01392221450805664, 0.016156911849975586, 0.014037370681762695, 0.008305072784423828</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0.9333333333333333, 0.8933333333333333, 0.8648648648648649, 0.9459459459459459, 0.8648648648648649</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>0.98989898989899, 0.98989898989899, 0.9932885906040269, 0.9865771812080537, 0.9966442953020134</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0.9387755102040817, 0.8846153846153846, 0.9318181818181818, 0.9583333333333334, 0.8958333333333334</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>0.9896373056994818, 0.9896373056994818, 0.9947916666666666, 0.9845360824742269, 0.9948186528497409</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>0.9583333333333334, 0.9583333333333334, 0.8541666666666666, 0.9583333333333334, 0.8958333333333334</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0.9947916666666666, 0.9947916666666666, 0.9947916666666666, 0.9947916666666666, 1.0</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0.9484536082474228, 0.9199999999999999, 0.8913043478260869, 0.9583333333333334, 0.8958333333333334</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0.9922077922077923, 0.9922077922077923, 0.9947916666666666, 0.9896373056994819, 0.9974025974025974</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0.9814814814814814, 0.9722222222222222, 0.9455128205128205, 0.969551282051282, 0.905448717948718</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0.9982638888888888, 0.9980406746031746, 0.9985996462264151, 0.9984522405660378, 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>df_dimless</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>splashing</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>XGBClassifier_splashing_test</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
         <is>
           <t>{'estimator': XGBClassifier(base_score=None, booster=None, callbacks=None,
               colsample_bylevel=None, colsample_bynode=None,
-              colsample_bytree=None, early_stopping_rounds=None,
+              colsample_bytree=None, device=None, early_stopping_rounds=None,
               enable_categorical=False, eval_metric=None, feature_types=None,
-              gamma=None, gpu_id=None, grow_policy=None, importance_type=None,
+              gamma=None, grow_policy=None, importance_type=None,
               interaction_constraints=None, learning_rate=None, max_bin=None,
               max_cat_threshold=None, max_cat_to_onehot=None,
               max_delta_step=None, max_depth=None, max_leaves=None,
               min_child_weight=None, missing=nan, monotone_constraints=None,
-              n_estimators=100, n_jobs=None, num_parallel_tree=None,
-              predictor=None, random_state=None, ...), 'source_features': ['init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'], 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': None, 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.8679245283018868</v>
-      </c>
-      <c r="G9" t="n">
+              multi_strategy=None, n_estimators=None, n_jobs=None,
+              num_parallel_tree=None, random_state=None, ...), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="G7" t="n">
         <v>0.9583333333333334</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.910891089108911</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.9513888888888888</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="H7" t="n">
+        <v>0.9019607843137256</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9440586419753086</v>
+      </c>
+      <c r="J7" t="n">
         <v>0.9966329966329966</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K7" t="n">
         <v>0.9948186528497409</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M7" t="n">
         <v>0.9974025974025974</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N7" t="n">
         <v>0.9999751984126984</v>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0.09089159965515137, 0.059160709381103516, 0.08683967590332031, 0.10107588768005371, 0.06659388542175293</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0.016202449798583984, 0.007999658584594727, 0.01626896858215332, 0.01671314239501953, 0.014142274856567383</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0.9466666666666667, 0.8933333333333333, 0.8378378378378378, 0.9324324324324325, 0.8108108108108109</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>1.0, 0.9966329966329966, 0.9966442953020134, 0.9966442953020134, 1.0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0.94, 0.9, 0.9090909090909091, 0.9574468085106383, 0.84</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>1.0, 0.9948186528497409, 0.9948186528497409, 0.9948186528497409, 1.0</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>0.9791666666666666, 0.9375, 0.8333333333333334, 0.9375, 0.875</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1.0, 1.0, 1.0, 1.0, 1.0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0.9591836734693877, 0.9183673469387755, 0.8695652173913043, 0.9473684210526315, 0.8571428571428572</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1.0, 0.9974025974025974, 0.9974025974025974, 0.9974025974025974, 1.0</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0.9822530864197532, 0.9737654320987654, 0.9174679487179487, 0.9599358974358974, 0.8870192307692307</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>1.0, 0.9999751984126984, 0.9999754323899371, 0.9999754323899371, 1.0</t>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0.08306121826171875, 0.08234429359436035, 0.08005213737487793, 0.08477997779846191, 0.09169220924377441, 0.08149409294128418, 0.0740668773651123</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.0071909427642822266, 0.007078886032104492, 0.006330966949462891, 0.006796121597290039, 0.007634162902832031, 0.007539987564086914, 0.005554914474487305</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.8490566037735849, 0.9056603773584906, 0.8301886792452831, 0.8867924528301887, 0.8867924528301887, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.8857142857142857, 0.9393939393939394, 0.8571428571428571, 0.9375, 0.9666666666666667, 0.8611111111111112</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>1.0, 0.8857142857142857, 0.9117647058823529, 0.8823529411764706, 0.8823529411764706, 0.8529411764705882, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8857142857142857, 0.9253731343283583, 0.8695652173913043, 0.9090909090909091, 0.90625, 0.8857142857142858</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.9984962406015038, 0.9333333333333333, 0.9520123839009289, 0.8978328173374612, 0.9659442724458205, 0.9342105263157896, 0.9256965944272446</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.9999784157133608, 1.0, 0.9999355614743535, 0.9999785204914512, 0.9999785204914512, 1.0, 0.9999785204914512</t>
         </is>
       </c>
     </row>

--- a/results/metrics_modelling3.xlsx
+++ b/results/metrics_modelling3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:BJ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,57 +506,237 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>cv_fit_time_mean</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>cv_fit_time_median</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>cv_fit_time_std</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>cv_score_time</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>cv_score_time_mean</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cv_score_time_median</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>cv_score_time_std</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>cv_test_accuracy</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_accuracy_mean</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_accuracy_median</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_accuracy_std</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_f1</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_f1_mean</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_f1_median</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_f1_std</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_precision</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_precision_mean</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_precision_median</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_precision_std</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_recall</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_recall_mean</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_recall_median</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_recall_std</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_roc_auc</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_roc_auc_mean</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_roc_auc_median</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_roc_auc_std</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>cv_train_accuracy</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>cv_test_precision</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_accuracy_mean</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_accuracy_median</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_accuracy_std</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_f1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_f1_mean</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_f1_median</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_f1_std</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>cv_train_precision</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>cv_test_recall</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_precision_mean</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_precision_median</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_precision_std</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>cv_train_recall</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>cv_test_f1</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>cv_train_f1</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>cv_test_roc_auc</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_recall_mean</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_recall_median</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_recall_std</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>cv_train_roc_auc</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_roc_auc_mean</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_roc_auc_median</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_roc_auc_std</t>
         </is>
       </c>
     </row>
@@ -613,63 +793,171 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.005369901657104492, 0.012936115264892578, 0.006644010543823242, 0.008224010467529297, 0.0029840469360351562, 0.002872943878173828, 0.007586956024169922</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0.004912137985229492, 0.01417398452758789, 0.004354000091552734, 0.006852865219116211, 0.004110813140869141, 0.004078865051269531, 0.009239912033081055</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+          <t>0.005934715270996094, 0.007602214813232422, 0.0031249523162841797, 0.002904176712036133, 0.007550954818725586, 0.006783962249755859, 0.0040090084075927734</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.005415712084089007</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.005934715270996094</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.001890416961435114</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.01199793815612793, 0.008247852325439453, 0.00414586067199707, 0.004086971282958984, 0.0044286251068115234, 0.006849050521850586, 0.009813070297241211</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>0.007081338337489537</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.006849050521850586</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.002870295566065284</v>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>0.9074074074074074, 0.6981132075471698, 0.8301886792452831, 0.7547169811320755, 0.8113207547169812, 0.7169811320754716, 0.7547169811320755</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="X2" t="n">
+        <v>0.7819207347509234</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.7547169811320755</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.06725431763906545</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.9315068493150684, 0.7419354838709677, 0.8656716417910447, 0.7868852459016393, 0.84375, 0.7761194029850745, 0.8169014084507041</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8232528617592141</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.8169014084507041</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.05871898539669561</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8518518518518519, 0.8787878787878788, 0.8888888888888888, 0.9, 0.7878787878787878, 0.7837837837837838</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.8551325761852079</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.04614438668581942</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.9714285714285714, 0.6571428571428571, 0.8529411764705882, 0.7058823529411765, 0.7941176470588235, 0.7647058823529411, 0.8529411764705882</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.7998799519807923</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.7941176470588235</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.0967616822945771</v>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.9503759398496241, 0.8269841269841269, 0.9040247678018576, 0.9040247678018576, 0.9349845201238389, 0.8126934984520123, 0.8436532507739938</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.8823915531124731</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.9040247678018576</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.0503592050549525</v>
+      </c>
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>0.7861635220125787, 0.7962382445141066, 0.7931034482758621, 0.8056426332288401, 0.7899686520376176, 0.8150470219435737, 0.8087774294670846</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.8947368421052632, 0.8518518518518519, 0.8787878787878788, 0.8888888888888888, 0.9, 0.7878787878787878, 0.7837837837837838</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
+      <c r="AR2" t="n">
+        <v>0.7992772787828092</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.7962382445141066</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.009895370205512033</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.8300000000000001, 0.8362720403022671, 0.8333333333333333, 0.8457711442786069, 0.8337468982630273, 0.8528678304239402, 0.8478802992518701</t>
+        </is>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.8399816494075779</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.8362720403022671</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0.008092565675433257</v>
+      </c>
+      <c r="AY2" t="inlineStr">
         <is>
           <t>0.8512820512820513, 0.8645833333333334, 0.868421052631579, 0.8673469387755102, 0.8527918781725888, 0.8769230769230769, 0.8717948717948718</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0.9714285714285714, 0.6571428571428571, 0.8529411764705882, 0.7058823529411765, 0.7941176470588235, 0.7647058823529411, 0.8529411764705882</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
+      <c r="AZ2" t="n">
+        <v>0.8647347432732874</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0.8673469387755102</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0.008802947619334362</v>
+      </c>
+      <c r="BC2" t="inlineStr">
         <is>
           <t>0.8097560975609757, 0.8097560975609757, 0.8009708737864077, 0.8252427184466019, 0.8155339805825242, 0.8300970873786407, 0.8252427184466019</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.9315068493150684, 0.7419354838709677, 0.8656716417910447, 0.7868852459016393, 0.84375, 0.7761194029850745, 0.8169014084507041</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0.8300000000000001, 0.8362720403022671, 0.8333333333333333, 0.8457711442786069, 0.8337468982630273, 0.8528678304239402, 0.8478802992518701</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0.9503759398496241, 0.8269841269841269, 0.9040247678018576, 0.9040247678018576, 0.9349845201238389, 0.8126934984520123, 0.8436532507739938</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BD2" t="n">
+        <v>0.816657081966104</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0.8155339805825242</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0.009787935053886839</v>
+      </c>
+      <c r="BG2" t="inlineStr">
         <is>
           <t>0.8876537880423052, 0.9035515618314078, 0.8926239367643268, 0.8959747400979465, 0.8880702809519718, 0.9072085230689921, 0.8982086089870264</t>
         </is>
+      </c>
+      <c r="BH2" t="n">
+        <v>0.8961844913919966</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0.8959747400979465</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.006878900544216725</v>
       </c>
     </row>
     <row r="3">
@@ -725,63 +1013,171 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.006107807159423828, 0.0034821033477783203, 0.003284931182861328, 0.003621816635131836, 0.003426074981689453, 0.003782033920288086, 0.003475189208984375</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0.00541996955871582, 0.004540920257568359, 0.0042972564697265625, 0.004637241363525391, 0.0045320987701416016, 0.0045931339263916016, 0.004570960998535156</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+          <t>0.0062160491943359375, 0.0036652088165283203, 0.003248929977416992, 0.0033130645751953125, 0.003133058547973633, 0.0037260055541992188, 0.003981113433837891</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.003897632871355329</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.00366520881652832</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.0009865241696905742</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.005682945251464844, 0.005716085433959961, 0.0047760009765625, 0.004233121871948242, 0.004353046417236328, 0.004647970199584961, 0.005806922912597656</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>0.00503087043762207</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.0047760009765625</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.000632952019066935</v>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>0.8703703703703703, 0.7924528301886793, 0.8490566037735849, 0.7735849056603774, 0.8301886792452831, 0.7547169811320755, 0.7735849056603774</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="X3" t="n">
+        <v>0.8062793251472496</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.7924528301886793</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.04052673239832488</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.9090909090909091, 0.8405797101449276, 0.8857142857142858, 0.8235294117647058, 0.8695652173913043, 0.8115942028985507, 0.8333333333333333</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8533438671911453</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.8405797101449276</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.03298049265322964</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.8333333333333334, 0.8529411764705882, 0.8611111111111112, 0.8235294117647058, 0.8571428571428571, 0.8, 0.7894736842105263</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.8310759391475887</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.02623572233655289</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>1.0, 0.8285714285714286, 0.9117647058823529, 0.8235294117647058, 0.8823529411764706, 0.8235294117647058, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.8788715486194477</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.05908094691303778</v>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.9578947368421054, 0.8571428571428572, 0.9504643962848297, 0.8869969040247677, 0.9411764705882353, 0.8126934984520124, 0.8606811145510836</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.8952928539836987</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.8869969040247677</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.05156559231488393</v>
+      </c>
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>0.8113207547169812, 0.8119122257053292, 0.8119122257053292, 0.8150470219435737, 0.8119122257053292, 0.8463949843260188, 0.8181818181818182</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.8333333333333334, 0.8529411764705882, 0.8611111111111112, 0.8235294117647058, 0.8571428571428571, 0.8, 0.7894736842105263</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
+      <c r="AR3" t="n">
+        <v>0.8180973223263399</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0.8119122257053292</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.01177623075655056</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.8578199052132701, 0.8584905660377359, 0.8584905660377358, 0.8618266978922716, 0.8591549295774649, 0.883054892601432, 0.8632075471698114</t>
+        </is>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.8631493006471033</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.8591549295774649</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0.008330240384199985</v>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>0.8341013824884793, 0.8310502283105022, 0.8348623853211009, 0.832579185520362, 0.8318181818181818, 0.8685446009389671, 0.8394495412844036</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>1.0, 0.8285714285714286, 0.9117647058823529, 0.8235294117647058, 0.8823529411764706, 0.8235294117647058, 0.8823529411764706</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
+      <c r="AZ3" t="n">
+        <v>0.8389150722402852</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0.8341013824884793</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0.01236443975154782</v>
+      </c>
+      <c r="BC3" t="inlineStr">
         <is>
           <t>0.8829268292682927, 0.8878048780487805, 0.883495145631068, 0.8932038834951457, 0.8883495145631068, 0.8980582524271845, 0.8883495145631068</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.9090909090909091, 0.8405797101449276, 0.8857142857142858, 0.8235294117647058, 0.8695652173913043, 0.8115942028985507, 0.8333333333333333</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.8578199052132701, 0.8584905660377359, 0.8584905660377358, 0.8618266978922716, 0.8591549295774649, 0.883054892601432, 0.8632075471698114</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.9578947368421054, 0.8571428571428572, 0.9504643962848297, 0.8869969040247677, 0.9411764705882353, 0.8126934984520124, 0.8606811145510836</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="BD3" t="n">
+        <v>0.888884002570955</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0.8883495145631068</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0.00491487231480214</v>
+      </c>
+      <c r="BG3" t="inlineStr">
         <is>
           <t>0.8975825598963955, 0.9145485665382971, 0.9012586992009622, 0.9084328550562764, 0.8984234040725149, 0.9190652117879542, 0.9092061173640348</t>
         </is>
+      </c>
+      <c r="BH3" t="n">
+        <v>0.9069310591309193</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0.9084328550562764</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.007603060102699606</v>
       </c>
     </row>
     <row r="4">
@@ -837,63 +1233,171 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.003818988800048828, 0.003165006637573242, 0.002794981002807617, 0.002596139907836914, 0.002512693405151367, 0.002949953079223633, 0.0029401779174804688</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0.008829116821289062, 0.005921125411987305, 0.0054149627685546875, 0.0054569244384765625, 0.006937265396118164, 0.006503105163574219, 0.006007194519042969</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+          <t>0.0046231746673583984, 0.004214763641357422, 0.0031578540802001953, 0.0028798580169677734, 0.002457141876220703, 0.0027239322662353516, 0.0028579235076904297</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.003273521150861468</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.002879858016967773</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.0007575426473526852</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.009921073913574219, 0.0070078372955322266, 0.0054683685302734375, 0.006150245666503906, 0.005865812301635742, 0.0057811737060546875, 0.005489826202392578</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>0.006526333945138114</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.005865812301635742</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.001467881810458844</v>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>0.8888888888888888, 0.8301886792452831, 0.8679245283018868, 0.8113207547169812, 0.8490566037735849, 0.8113207547169812, 0.7735849056603774</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="X4" t="n">
+        <v>0.833183587900569</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.8301886792452831</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.03601369874946368</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>0.9166666666666667, 0.8695652173913043, 0.8955223880597014, 0.8484848484848485, 0.8857142857142858, 0.84375, 0.8333333333333333</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.87043381995002</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.02821192547334734</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>0.8918918918918919, 0.8823529411764706, 0.9090909090909091, 0.875, 0.8611111111111112, 0.9, 0.7894736842105263</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.8727029339258443</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.03702761166157346</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8571428571428571, 0.8823529411764706, 0.8235294117647058, 0.9117647058823529, 0.7941176470588235, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.8705882352941176</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.04696225729259014</v>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0.9624060150375939, 0.8849206349206349, 0.9272445820433436, 0.914860681114551, 0.8924148606811145, 0.923374613003096, 0.846749226006192</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.9074243732580752</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.914860681114551</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.03409798408896362</v>
+      </c>
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>0.8962264150943396, 0.896551724137931, 0.8808777429467085, 0.8934169278996865, 0.8934169278996865, 0.890282131661442, 0.8934169278996865</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0.8918918918918919, 0.8823529411764706, 0.9090909090909091, 0.875, 0.8611111111111112, 0.9, 0.7894736842105263</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
+      <c r="AR4" t="n">
+        <v>0.8920269710770686</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.8934169278996865</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.004946202189722954</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.9197080291970803, 0.9193154034229828, 0.9068627450980392, 0.9174757281553398, 0.9170731707317074, 0.9152542372881356, 0.9170731707317074</t>
+        </is>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.916108926374999</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.9170731707317074</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.004021106444933429</v>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>0.9174757281553398, 0.9215686274509803, 0.9158415841584159, 0.9174757281553398, 0.9215686274509803, 0.9130434782608695, 0.9215686274509803</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>0.9428571428571428, 0.8571428571428571, 0.8823529411764706, 0.8235294117647058, 0.9117647058823529, 0.7941176470588235, 0.8823529411764706</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
+      <c r="AZ4" t="n">
+        <v>0.918363200154701</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.9174757281553398</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.003095099671022134</v>
+      </c>
+      <c r="BC4" t="inlineStr">
         <is>
           <t>0.9219512195121952, 0.9170731707317074, 0.8980582524271845, 0.9174757281553398, 0.912621359223301, 0.9174757281553398, 0.912621359223301</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0.9166666666666667, 0.8695652173913043, 0.8955223880597014, 0.8484848484848485, 0.8857142857142858, 0.84375, 0.8333333333333333</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0.9197080291970803, 0.9193154034229828, 0.9068627450980392, 0.9174757281553398, 0.9170731707317074, 0.9152542372881356, 0.9170731707317074</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0.9624060150375939, 0.8849206349206349, 0.9272445820433436, 0.914860681114551, 0.8924148606811145, 0.923374613003096, 0.846749226006192</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
+      <c r="BD4" t="n">
+        <v>0.9138966882040529</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.9170731707317074</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0.007118321889567089</v>
+      </c>
+      <c r="BG4" t="inlineStr">
         <is>
           <t>0.9620332398014245, 0.9660034231921266, 0.9626256551250107, 0.9647521264713463, 0.9616805567488615, 0.9633774379242204, 0.967694819142538</t>
         </is>
+      </c>
+      <c r="BH4" t="n">
+        <v>0.9640238940579325</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0.9633774379242204</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.002061603425119283</v>
       </c>
     </row>
     <row r="5">
@@ -945,67 +1449,175 @@
         <v>0.9123711340206186</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9497271825396826</v>
+        <v>0.9496775793650793</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.009522199630737305, 0.007333993911743164, 0.008442878723144531, 0.007794857025146484, 0.008556842803955078, 0.0076141357421875, 0.0077898502349853516</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0.005955934524536133, 0.00539708137512207, 0.006314992904663086, 0.0053369998931884766, 0.005982160568237305, 0.0050771236419677734, 0.005279064178466797</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+          <t>0.009666204452514648, 0.007354259490966797, 0.0077362060546875, 0.007951021194458008, 0.008820056915283203, 0.007756948471069336, 0.007589817047119141</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.008124930518014091</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.007756948471069336</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.0007611803105418836</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.006411075592041016, 0.005286693572998047, 0.00494694709777832, 0.0054471492767333984, 0.005460023880004883, 0.005702972412109375, 0.004817008972167969</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>0.005438838686261859</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.005447149276733398</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.0004880437287313565</v>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>0.9074074074074074, 0.7547169811320755, 0.8679245283018868, 0.8679245283018868, 0.8867924528301887, 0.8490566037735849, 0.8490566037735849</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="X5" t="n">
+        <v>0.8546970150743736</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.0450683171313999</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0.9333333333333333, 0.8059701492537314, 0.8923076923076922, 0.8923076923076922, 0.90625, 0.8749999999999999, 0.8857142857142858</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8844118789881049</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.8923076923076922</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.03632843171013504</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>0.875, 0.84375, 0.9354838709677419, 0.9354838709677419, 0.9666666666666667, 0.9333333333333333, 0.8611111111111112</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.9072612647209422</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.04310467686730826</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>1.0, 0.7714285714285715, 0.8529411764705882, 0.8529411764705882, 0.8529411764705882, 0.8235294117647058, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.8665066026410564</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.8529411764705882</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.06687698340327823</v>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>0.9699248120300752, 0.8333333333333334, 0.9705882352941176, 0.9303405572755418, 0.9504643962848297, 0.9055727554179567, 0.8839009287925697</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.9205892883469178</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.9303405572755418</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.04645524972067035</v>
+      </c>
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>0.8710691823899371, 0.8746081504702194, 0.8683385579937304, 0.877742946708464, 0.8746081504702194, 0.877742946708464, 0.890282131661442</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0.875, 0.84375, 0.9354838709677419, 0.9354838709677419, 0.9666666666666667, 0.9333333333333333, 0.8611111111111112</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
+      <c r="AR5" t="n">
+        <v>0.8763417237717823</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.8746081504702194</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.006504094660230648</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.9044289044289044, 0.898477157360406, 0.8934010152284263, 0.9041769041769042, 0.900497512437811, 0.9027431421446385, 0.913151364764268</t>
+        </is>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.902410857220194</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.9027431421446385</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.005643865032366699</v>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>0.8660714285714286, 0.9365079365079365, 0.9361702127659575, 0.9154228855721394, 0.923469387755102, 0.9282051282051282, 0.934010152284264</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>1.0, 0.7714285714285715, 0.8529411764705882, 0.8529411764705882, 0.8529411764705882, 0.8235294117647058, 0.9117647058823529</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
+      <c r="AZ5" t="n">
+        <v>0.9199795902374223</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.9282051282051282</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.02311113143313012</v>
+      </c>
+      <c r="BC5" t="inlineStr">
         <is>
           <t>0.9463414634146341, 0.8634146341463415, 0.8543689320388349, 0.8932038834951457, 0.8786407766990292, 0.8786407766990292, 0.8932038834951457</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0.9333333333333333, 0.8059701492537314, 0.8923076923076922, 0.8923076923076922, 0.90625, 0.8749999999999999, 0.8857142857142858</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0.9044289044289044, 0.898477157360406, 0.8934010152284263, 0.9041769041769042, 0.900497512437811, 0.9027431421446385, 0.913151364764268</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0.9699248120300752, 0.8333333333333334, 0.9705882352941176, 0.9303405572755418, 0.9504643962848297, 0.9055727554179567, 0.8839009287925697</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0.9373839844593136, 0.9515618314077879, 0.9390626342469285, 0.9434229744823438, 0.9364850932210671, 0.9465375032219263, 0.9486854540768108</t>
-        </is>
+      <c r="BD5" t="n">
+        <v>0.8868306214268801</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.8786407766990292</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0.02766894624575639</v>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>0.9373839844593136, 0.9515618314077879, 0.9390196752298307, 0.943401494973795, 0.936485093221067, 0.9465589827304751, 0.9486854540768108</t>
+        </is>
+      </c>
+      <c r="BH5" t="n">
+        <v>0.9432995022998687</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0.943401494973795</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.00544656662729267</v>
       </c>
     </row>
     <row r="6">
@@ -1026,7 +1638,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x177d4ee50&gt;, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x31b740510&gt;, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1061,63 +1673,171 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.65146803855896, 0.5669980049133301, 0.5646288394927979, 0.5705621242523193, 0.5885837078094482, 0.5664160251617432, 0.5634949207305908</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0.006080150604248047, 0.005192756652832031, 0.006352901458740234, 0.005527019500732422, 0.005827188491821289, 0.006092071533203125, 0.0054569244384765625</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+          <t>0.6742079257965088, 0.5923383235931396, 0.576941967010498, 0.5896830558776855, 0.5711178779602051, 0.6020679473876953, 0.6565041542053223</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.6089801788330078</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.5923383235931396</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.03716814553393157</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.005761146545410156, 0.006316661834716797, 0.006231069564819336, 0.00539398193359375, 0.006084918975830078, 0.0055921077728271484, 0.005114078521728516</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>0.005784852164132255</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.005761146545410156</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.0004161731712175744</v>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>0.9629629629629629, 0.8679245283018868, 0.9056603773584906, 0.8301886792452831, 0.8867924528301887, 0.8867924528301887, 0.8679245283018868</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="X6" t="n">
+        <v>0.8868922831186982</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.03793577234399872</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8985507246376812, 0.9275362318840579, 0.8656716417910447, 0.9090909090909091, 0.9090909090909091, 0.8985507246376812</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9115304804792151</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.03021720375687164</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.9117647058823529, 0.9142857142857143, 0.8787878787878788, 0.9375, 0.9375, 0.8857142857142857</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.915928361516597</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.02433124593359062</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>1.0, 0.8857142857142857, 0.9411764705882353, 0.8529411764705882, 0.8823529411764706, 0.8823529411764706, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.9080432172869148</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.04539117047431458</v>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>1.0, 0.9396825396825397, 0.9736842105263158, 0.93343653250774, 0.9705882352941176, 0.9504643962848298, 0.9226006191950464</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.9557795047843699</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.9504643962848298</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.02502210082274886</v>
+      </c>
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>0.9874213836477987, 0.9937304075235109, 0.9905956112852664, 0.9905956112852664, 0.987460815047022, 0.9937304075235109, 0.9905956112852664</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0.9459459459459459, 0.9117647058823529, 0.9142857142857143, 0.8787878787878788, 0.9375, 0.9375, 0.8857142857142857</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
+      <c r="AR6" t="n">
+        <v>0.9905899782282346</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.9905956112852664</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.002377163415894737</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.9902912621359223, 0.9951456310679612, 0.9927360774818401, 0.9927007299270073, 0.9902912621359223, 0.9951456310679612, 0.9927360774818401</t>
+        </is>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.9927209530426364</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.9927360774818401</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.001834813705181454</v>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>0.9855072463768116, 0.9903381642512077, 0.9903381642512077, 0.9951219512195122, 0.9902912621359223, 0.9951456310679612, 0.9903381642512077</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>1.0, 0.8857142857142857, 0.9411764705882353, 0.8529411764705882, 0.8823529411764706, 0.8823529411764706, 0.9117647058823529</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
+      <c r="AZ6" t="n">
+        <v>0.9910115119362616</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.9903381642512077</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0.003074376650758704</v>
+      </c>
+      <c r="BC6" t="inlineStr">
         <is>
           <t>0.9951219512195122, 1.0, 0.9951456310679612, 0.9902912621359223, 0.9902912621359223, 0.9951456310679612, 0.9951456310679612</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0.9722222222222222, 0.8985507246376812, 0.9275362318840579, 0.8656716417910447, 0.9090909090909091, 0.9090909090909091, 0.8985507246376812</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0.9902912621359223, 0.9951456310679612, 0.9927360774818401, 0.9927007299270073, 0.9902912621359223, 0.9951456310679612, 0.9927360774818401</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>1.0, 0.9396825396825397, 0.9736842105263158, 0.93343653250774, 0.9705882352941176, 0.9504643962848298, 0.9226006191950464</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
+      <c r="BD6" t="n">
+        <v>0.994448766956463</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.9951456310679612</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0.003100597103577546</v>
+      </c>
+      <c r="BG6" t="inlineStr">
         <is>
           <t>0.9979063241959854, 0.9986307231493367, 0.9984319958759343, 0.9985179139101297, 0.9984319958759343, 0.9999570409829023, 0.9984319958759343</t>
         </is>
+      </c>
+      <c r="BH6" t="n">
+        <v>0.9986154271237367</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0.9984319958759343</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.0005871770933261723</v>
       </c>
     </row>
     <row r="7">
@@ -1183,63 +1903,171 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.08306121826171875, 0.08234429359436035, 0.08005213737487793, 0.08477997779846191, 0.09169220924377441, 0.08149409294128418, 0.0740668773651123</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0.0071909427642822266, 0.007078886032104492, 0.006330966949462891, 0.006796121597290039, 0.007634162902832031, 0.007539987564086914, 0.005554914474487305</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+          <t>0.09037303924560547, 0.09052681922912598, 0.09748506546020508, 0.08583807945251465, 0.09505724906921387, 0.08665800094604492, 0.11919617652893066</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0.09501920427594866</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.09052681922912598</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.01060039792483113</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.009242057800292969, 0.013006925582885742, 0.00894308090209961, 0.006383180618286133, 0.010007858276367188, 0.009367704391479492, 0.013145923614501953</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>0.01001381874084473</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.009367704391479492</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.002207451550437751</v>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>0.9629629629629629, 0.8490566037735849, 0.9056603773584906, 0.8301886792452831, 0.8867924528301887, 0.8867924528301887, 0.8490566037735849</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="X7" t="n">
+        <v>0.8815014475391835</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.04142800609502062</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8857142857142857, 0.9253731343283583, 0.8695652173913043, 0.9090909090909091, 0.90625, 0.8857142857142858</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9077042934944808</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.90625</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.03139722177532166</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.8857142857142857, 0.9393939393939394, 0.8571428571428571, 0.9375, 0.9666666666666667, 0.8611111111111112</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.9133535437106867</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.0410897083958572</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>1.0, 0.8857142857142857, 0.9117647058823529, 0.8823529411764706, 0.8823529411764706, 0.8529411764705882, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.9038415366146458</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.04344942323952641</v>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>0.9984962406015038, 0.9333333333333333, 0.9520123839009289, 0.8978328173374612, 0.9659442724458205, 0.9342105263157896, 0.9256965944272446</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.9439323097660115</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.9342105263157896</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.02974076696634106</v>
+      </c>
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0.9459459459459459, 0.8857142857142857, 0.9393939393939394, 0.8571428571428571, 0.9375, 0.9666666666666667, 0.8611111111111112</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
+      <c r="AR7" t="n">
+        <v>0.9977594515655674</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.001417051170840857</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.9982688114216364</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.001094907038779773</v>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1.0, 0.8857142857142857, 0.9117647058823529, 0.8823529411764706, 0.8823529411764706, 0.8529411764705882, 0.9117647058823529</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
+      <c r="AZ7" t="n">
+        <v>0.9965459942243395</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.002184519446236978</v>
+      </c>
+      <c r="BC7" t="inlineStr">
         <is>
           <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0.9722222222222222, 0.8857142857142857, 0.9253731343283583, 0.8695652173913043, 0.9090909090909091, 0.90625, 0.8857142857142858</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0.9984962406015038, 0.9333333333333333, 0.9520123839009289, 0.8978328173374612, 0.9659442724458205, 0.9342105263157896, 0.9256965944272446</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="BD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="inlineStr">
         <is>
           <t>0.9999784157133608, 1.0, 0.9999355614743535, 0.9999785204914512, 0.9999785204914512, 1.0, 0.9999785204914512</t>
         </is>
+      </c>
+      <c r="BH7" t="n">
+        <v>0.9999785055231526</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0.9999785204914512</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1.988619454760789e-05</v>
       </c>
     </row>
   </sheetData>

--- a/results/metrics_modelling3.xlsx
+++ b/results/metrics_modelling3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1242,6 +1242,118 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_no_fragmentation_base</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x0000029003465F50&gt;, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8292682926829269</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9781818181818182</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.3808012008666992, 1.0942845344543457, 1.1142067909240723, 1.0898537635803223, 1.101231575012207, 1.0872023105621338, 1.101468563079834</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0.008841991424560547, 0.008999824523925781, 0.008000373840332031, 0.007999897003173828, 0.00800180435180664, 0.007001399993896484, 0.008001089096069336</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.8301886792452831, 0.9622641509433962, 0.8867924528301887, 0.9056603773584906, 0.9433962264150944, 0.8867924528301887</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0.9937106918238994, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9937304075235109, 0.9968652037617555, 0.9905956112852664</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.9166666666666666, 0.6470588235294118, 0.9285714285714286, 0.75, 1.0, 0.9230769230769231, 0.7857142857142857</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 0.9883720930232558, 1.0, 0.9882352941176471, 0.9883720930232558, 0.9880952380952381</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.7857142857142857, 0.9285714285714286, 0.8571428571428571, 0.6428571428571429, 0.8571428571428571, 0.7857142857142857</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 1.0, 0.9882352941176471, 0.9882352941176471, 1.0, 0.9764705882352941</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.8148148148148148, 0.7096774193548386, 0.9285714285714286, 0.7999999999999999, 0.782608695652174, 0.888888888888889, 0.7857142857142857</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 0.9941520467836257, 0.9940828402366864, 0.9882352941176471, 0.9941520467836257, 0.9822485207100591</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.9641025641025642, 0.9084249084249085, 0.9908424908424909, 0.9084249084249084, 0.989010989010989, 0.9688644688644689, 0.9761904761904763</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0.999949124949125, 1.0, 0.9998994469582705, 1.0, 0.9998491704374057, 0.9998994469582704, 0.9998994469582705</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/metrics_modelling3.xlsx
+++ b/results/metrics_modelling3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ8"/>
+  <dimension ref="A1:BJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2290,6 +2290,896 @@
         <v>1.988619454760789e-05</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LogisticRegression_no_fragmentation_base</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{'estimator': LogisticRegression(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.717948717948718</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.9254545454545455</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.8754208754208754</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.6835443037974683</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.7448275862068965</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.9316571826733249</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.00896906852722168, 0.013093233108520508, 0.0, 0.008106708526611328, 0.010124683380126953, 0.0, 0.0</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>0.005756241934640067</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.008106708526611328</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.005184656369554661</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.007524251937866211, 0.005464315414428711, 0.010611295700073242, 0.0, 0.0, 0.0, 0.010504722595214844</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>0.00487208366394043</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.005464315414428711</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.004523928583663451</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.8148148148148148, 0.7924528301886793, 0.9245283018867925, 0.8490566037735849, 0.8490566037735849, 0.8490566037735849, 0.8867924528301887</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>0.85225117300589</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.04039982656823135</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0.5833333333333334, 0.6206896551724138, 0.8571428571428571, 0.7333333333333334, 0.6363636363636364, 0.6666666666666666, 0.7999999999999999</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.6996470688588915</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.09324779318350135</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>0.7777777777777778, 0.6, 0.8571428571428571, 0.6875, 0.875, 0.8, 0.75</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.7639172335600907</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.08898364299549143</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.4666666666666667, 0.6428571428571429, 0.8571428571428571, 0.7857142857142857, 0.5, 0.5714285714285714, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.6687074829931972</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.1531201700556019</v>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>0.9418803418803419, 0.8498168498168499, 0.9578754578754578, 0.8864468864468865, 0.9560439560439561, 0.9212454212454212, 0.9633699633699634</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.9252398395255538</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.9418803418803419</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.03955875522584676</v>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.8773584905660378, 0.877742946708464, 0.8589341692789969, 0.877742946708464, 0.8746081504702194, 0.8714733542319749, 0.8526645768025078</t>
+        </is>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.8700749478238093</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.8746081504702194</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.009414197796548299</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>0.7547169811320756, 0.7577639751552795, 0.7133757961783439, 0.751592356687898, 0.7468354430379747, 0.7453416149068324, 0.69281045751634</t>
+        </is>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.737490946373535</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.7468354430379747</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.02278289116899502</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.8, 0.8026315789473685, 0.7777777777777778, 0.8194444444444444, 0.8082191780821918, 0.7894736842105263, 0.7794117647058824</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.7967083468811701</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.014168514244079</v>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>0.7142857142857143, 0.7176470588235294, 0.6588235294117647, 0.6941176470588235, 0.6941176470588235, 0.7058823529411765, 0.6235294117647059</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.6869147659063627</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.6941176470588235</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.03154134629409137</v>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>0.9281135531135531, 0.9407742584213172, 0.9262443438914028, 0.9370035193564605, 0.9277526395173454, 0.9327300150829563, 0.9243841126194067</t>
+        </is>
+      </c>
+      <c r="BH9" t="n">
+        <v>0.9310003488574919</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0.9281135531135531</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.005604009792409489</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>KNeighborsClassifier_no_fragmentation_base</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{'estimator': KNeighborsClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.7692307692307692</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9495454545454545</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.8922558922558923</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.8309859154929577</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.7468354430379747</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.7866666666666666</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.9578155847172223</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.007361412048339844, 0.0034761428833007812, 0.0, 0.004326820373535156, 0.0, 0.01344752311706543, 0.00612187385559082</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0.004961967468261719</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.004326820373535156</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.00432535218434897</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0.010094881057739258, 0.002934694290161133, 0.013010263442993164, 0.004120349884033203, 0.0160982608795166, 0.0, 0.008006095886230469</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>0.007752077920096261</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.008006095886230469</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.005336556973224901</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.7735849056603774, 0.8679245283018868, 0.8301886792452831, 0.8490566037735849, 0.8490566037735849, 0.8867924528301887</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>0.8493560946391135</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.03667999015847824</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>0.8000000000000002, 0.5714285714285714, 0.7200000000000001, 0.6666666666666666, 0.6923076923076924, 0.6666666666666666, 0.8125000000000001</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.7042242281527996</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.6923076923076924</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.07722263485750151</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>0.8, 0.5714285714285714, 0.8181818181818182, 0.6923076923076923, 0.75, 0.8, 0.7222222222222222</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.7363057577343292</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.07957368269107451</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0.8, 0.5714285714285714, 0.6428571428571429, 0.6428571428571429, 0.6428571428571429, 0.5714285714285714, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.6857142857142857</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.1216983797214333</v>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.8772893772893773, 0.9487179487179488, 0.8946886446886448, 0.9010989010989011, 0.903846153846154, 0.9468864468864469</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.9167102738531312</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.903846153846154</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.02713046960614661</v>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0.89937106918239, 0.9059561128526645, 0.9122257053291536, 0.9028213166144201, 0.9059561128526645, 0.9028213166144201, 0.9028213166144201</t>
+        </is>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.9045675642943048</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.9028213166144201</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.003754139860286498</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>0.8117647058823529, 0.8255813953488372, 0.829268292682927, 0.8165680473372781, 0.8255813953488372, 0.822857142857143, 0.8143712574850299</t>
+        </is>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.820856033848915</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.822857142857143</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.00612395781888402</v>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>0.8023255813953488, 0.8160919540229885, 0.8607594936708861, 0.8214285714285714, 0.8160919540229885, 0.8, 0.8292682926829268</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.8208522638891014</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0.8160919540229885</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0.01884949652022786</v>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>0.8214285714285714, 0.8352941176470589, 0.8, 0.8117647058823529, 0.8352941176470589, 0.8470588235294118, 0.8</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.821548619447779</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.8214285714285714</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0.01712589238622703</v>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>0.9602920227920229, 0.9680744092508797, 0.9614379084967319, 0.9640020110608346, 0.9654600301659125, 0.9612116641528407, 0.9623428858722977</t>
+        </is>
+      </c>
+      <c r="BH10" t="n">
+        <v>0.9632601331130743</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0.9623428858722977</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.002556083322909469</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SVC_no_fragmentation_base</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{'estimator': SVC(probability=True), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6842105263157895</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9281818181818182</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.8194444444444444</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.7468354430379747</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.781456953642384</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.9624898385785624</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.008918046951293945, 0.015131235122680664, 0.00925302505493164, 0.005823373794555664, 0.015625, 0.015604257583618164, 0.026727914810180664</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0.01386897904532296</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.01513123512268066</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.006364980577914103</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0.029338359832763672, 0.008470535278320312, 0.011104106903076172, 0.010102987289428711, 0.0, 0.0, 0.0024471282958984375</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>0.00878044537135533</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.008470535278320312</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.009442879088229031</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0.8333333333333334, 0.7358490566037735, 0.8679245283018868, 0.8867924528301887, 0.8867924528301887, 0.8679245283018868, 0.8301886792452831</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>0.844115004492363</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.04900177617977858</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>0.6666666666666665, 0.5, 0.6956521739130435, 0.7857142857142857, 0.75, 0.7200000000000001, 0.689655172413793</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.6868126141011126</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.6956521739130435</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.08474045998405863</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>0.75, 0.5, 0.8888888888888888, 0.7857142857142857, 0.9, 0.8181818181818182, 0.6666666666666666</t>
+        </is>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.75849309420738</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.1290923865694569</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>0.6, 0.5, 0.5714285714285714, 0.7857142857142857, 0.6428571428571429, 0.6428571428571429, 0.7142857142857143</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.636734693877551</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.08668065543508287</v>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>0.9384615384615385, 0.8626373626373627, 0.9725274725274725, 0.9267399267399268, 0.9523809523809523, 0.9432234432234433, 0.9413919413919414</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.9339089481946626</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.9413919413919414</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.03190862001703766</v>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0.8805031446540881, 0.9028213166144201, 0.8683385579937304, 0.8840125391849529, 0.8808777429467085, 0.8840125391849529, 0.8746081504702194</t>
+        </is>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.8821677130070105</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.8808777429467085</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.009900977108437748</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>0.7532467532467533, 0.8248587570621468, 0.7272727272727274, 0.7836257309941521, 0.7790697674418604, 0.7784431137724551, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.7690512792933218</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.7784431137724551</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.03058507390673511</v>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>0.8285714285714286, 0.7934782608695652, 0.8115942028985508, 0.7790697674418605, 0.7701149425287356, 0.7926829268292683, 0.835820895522388</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.8016189178088281</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.7934782608695652</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.02281229712069013</v>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>0.6904761904761905, 0.8588235294117647, 0.6588235294117647, 0.788235294117647, 0.788235294117647, 0.7647058823529411, 0.6588235294117647</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.7440176070428172</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0.07061116591341229</v>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>0.9595543345543346, 0.9641025641025641, 0.9572146807440925, 0.9567621920563096, 0.9577677224736049, 0.956913021618904, 0.9638511814982402</t>
+        </is>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.9594522424354358</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0.9577677224736049</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.002988427262158618</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>XGBClassifier_no_fragmentation_base</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{'estimator': XGBClassifier(base_score=None, booster=None, callbacks=None,
+              colsample_bylevel=None, colsample_bynode=None,
+              colsample_bytree=None, early_stopping_rounds=None,
+              enable_categorical=False, eval_metric=None, feature_types=None,
+              gamma=None, gpu_id=None, grow_policy=None, importance_type=None,
+              interaction_constraints=None, learning_rate=None, max_bin=None,
+              max_cat_threshold=None, max_cat_to_onehot=None,
+              max_delta_step=None, max_depth=None, max_leaves=None,
+              min_child_weight=None, missing=nan, monotone_constraints=None,
+              n_estimators=100, n_jobs=None, num_parallel_tree=None,
+              predictor=None, random_state=None, ...), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7804878048780488</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.9654545454545455</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.07788205146789551, 0.05489039421081543, 0.06288433074951172, 0.057038068771362305, 0.04688525199890137, 0.07667183876037598, 0.0814962387084961</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0.0653925963810512</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.06288433074951172</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.01237187286775673</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0.019135475158691406, 0.01563429832458496, 0.016017913818359375, 0.01617717742919922, 0.015770435333251953, 0.015863656997680664, 0.013914346694946289</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>0.01607332910810198</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.01586365699768066</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.001433290613797244</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.8113207547169812, 0.9433962264150944, 0.8867924528301887, 0.9245283018867925, 0.8867924528301887, 0.9056603773584906</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>0.8951282819207348</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.03894782463392368</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>0.8, 0.6428571428571429, 0.88, 0.7999999999999999, 0.8571428571428571, 0.7857142857142857, 0.8275862068965518</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.7990429275158339</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.07103103165205046</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>1.0, 0.6428571428571429, 1.0, 0.75, 0.8571428571428571, 0.7857142857142857, 0.8</t>
+        </is>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.8336734693877551</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.1211409730861799</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>0.6666666666666666, 0.6428571428571429, 0.7857142857142857, 0.8571428571428571, 0.8571428571428571, 0.7857142857142857, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.7789115646258503</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.08414501276770733</v>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>0.9709401709401709, 0.8736263736263736, 0.9798534798534799, 0.9267399267399268, 0.9780219780219781, 0.967032967032967, 0.9780219780219781</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.9534624106052678</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.9709401709401709</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.03680129906862034</v>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="AR12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="AV12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 0.9999999999999999, 1.0, 0.9999999999999999, 1.0</t>
+        </is>
+      </c>
+      <c r="BH12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>5.934391687221749e-17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/metrics_modelling3.xlsx
+++ b/results/metrics_modelling3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ12"/>
+  <dimension ref="A1:BJ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,31 +793,31 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.005259990692138672, 0.00709986686706543, 0.008516073226928711, 0.0029969215393066406, 0.0077550411224365234, 0.0030901432037353516, 0.007534027099609375</t>
+          <t>0.02117919921875, 0.0032470226287841797, 0.003450155258178711, 0.0030150413513183594, 0.0029571056365966797, 0.003010988235473633, 0.0067059993743896484</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.006036009107317243</v>
+        <v>0.006223644529070173</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00709986686706543</v>
+        <v>0.00324702262878418</v>
       </c>
       <c r="R2" t="n">
-        <v>0.002104350055521584</v>
+        <v>0.006230574086080055</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.014683961868286133, 0.007281303405761719, 0.007439851760864258, 0.004224061965942383, 0.004151821136474609, 0.0070989131927490234, 0.00782012939453125</t>
+          <t>0.011981725692749023, 0.006932973861694336, 0.008883953094482422, 0.006124019622802734, 0.004461050033569336, 0.004125833511352539, 0.01243901252746582</t>
         </is>
       </c>
       <c r="T2" t="n">
-        <v>0.007528577532087054</v>
+        <v>0.007849795477730888</v>
       </c>
       <c r="U2" t="n">
-        <v>0.007281303405761719</v>
+        <v>0.006932973861694336</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003248306428409989</v>
+        <v>0.003125325011603613</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -968,216 +968,216 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>no_fragmentation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LogisticRegression_splashing_base</t>
+          <t>Logit_no_fragmentation_base</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'estimator': LogisticRegression(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': StatsModelsEstimator(model_class=&lt;class 'statsmodels.discrete.discrete_model.Logit'&gt;), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.84</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8035714285714286</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9375</v>
+        <v>0.8</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8653846153846154</v>
+        <v>0.7272727272727272</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8912037037037037</v>
+        <v>0.9081818181818181</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8148148148148148</v>
+        <v>0.8282828282828283</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8407960199004975</v>
+        <v>0.6555555555555556</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8802083333333334</v>
+        <v>0.7468354430379747</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8600508905852416</v>
+        <v>0.698224852071006</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9132688492063492</v>
+        <v>0.9099988386946928</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.00602412223815918, 0.0033731460571289062, 0.0034301280975341797, 0.003506898880004883, 0.003591775894165039, 0.004220008850097656, 0.0030460357666015625</t>
+          <t>0.0072820186614990234, 0.0034618377685546875, 0.005471229553222656, 0.0029850006103515625, 0.009046792984008789, 0.002930879592895508, 0.0034608840942382812</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.003884587969098772</v>
+        <v>0.00494837760925293</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003506898880004883</v>
+        <v>0.003461837768554688</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0009327209363421094</v>
+        <v>0.002231714537591837</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.00506901741027832, 0.004395723342895508, 0.00477290153503418, 0.004426002502441406, 0.004522085189819336, 0.004422187805175781, 0.004745006561279297</t>
+          <t>0.009822845458984375, 0.004209995269775391, 0.00435185432434082, 0.010168075561523438, 0.006246089935302734, 0.004252195358276367, 0.004079103469848633</t>
         </is>
       </c>
       <c r="T3" t="n">
-        <v>0.004621846335274833</v>
+        <v>0.00616145133972168</v>
       </c>
       <c r="U3" t="n">
-        <v>0.004522085189819336</v>
+        <v>0.00435185432434082</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0002321484482853146</v>
+        <v>0.0025221946636105</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.8703703703703703, 0.7924528301886793, 0.8490566037735849, 0.7735849056603774, 0.8301886792452831, 0.7547169811320755, 0.7735849056603774</t>
+          <t>0.8518518518518519, 0.8113207547169812, 0.8867924528301887, 0.7547169811320755, 0.8301886792452831, 0.8490566037735849, 0.8679245283018868</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>0.8062793251472496</v>
+        <v>0.835978835978836</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.7924528301886793</v>
+        <v>0.8490566037735849</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.04052673239832488</v>
+        <v>0.0401258155209778</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.9090909090909091, 0.8405797101449276, 0.8857142857142858, 0.8235294117647058, 0.8695652173913043, 0.8115942028985507, 0.8333333333333333</t>
+          <t>0.7142857142857142, 0.6428571428571429, 0.7999999999999999, 0.6285714285714286, 0.6666666666666666, 0.6923076923076924, 0.7878787878787878</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>0.8533438671911453</v>
+        <v>0.704652490366776</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8405797101449276</v>
+        <v>0.6923076923076924</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.03298049265322964</v>
+        <v>0.06246470200147004</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.8333333333333334, 0.8529411764705882, 0.8611111111111112, 0.8235294117647058, 0.8571428571428571, 0.8, 0.7894736842105263</t>
+          <t>0.7692307692307693, 0.6428571428571429, 0.75, 0.5238095238095238, 0.6923076923076923, 0.75, 0.6842105263157895</t>
         </is>
       </c>
       <c r="AF3" t="n">
-        <v>0.8310759391475887</v>
+        <v>0.6874879506458454</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.02623572233655289</v>
+        <v>0.07866194292625306</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.0, 0.8285714285714286, 0.9117647058823529, 0.8235294117647058, 0.8823529411764706, 0.8235294117647058, 0.8823529411764706</t>
+          <t>0.6666666666666666, 0.6428571428571429, 0.8571428571428571, 0.7857142857142857, 0.6428571428571429, 0.6428571428571429, 0.9285714285714286</t>
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0.8788715486194477</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.05908094691303778</v>
+        <v>0.1102166785443514</v>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.9578947368421054, 0.8571428571428572, 0.9504643962848297, 0.8869969040247677, 0.9411764705882353, 0.8126934984520124, 0.8606811145510836</t>
+          <t>0.9316239316239316, 0.8644688644688645, 0.9340659340659341, 0.86996336996337, 0.9102564102564102, 0.9065934065934067, 0.9578754578754578</t>
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>0.8952928539836987</v>
+        <v>0.9106924821210536</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8869969040247677</v>
+        <v>0.9102564102564102</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.05156559231488393</v>
+        <v>0.03167503077011312</v>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.8113207547169812, 0.8119122257053292, 0.8119122257053292, 0.8150470219435737, 0.8119122257053292, 0.8463949843260188, 0.8181818181818182</t>
+          <t>0.8333333333333334, 0.8338557993730408, 0.8338557993730408, 0.8495297805642633, 0.8275862068965517, 0.8463949843260188, 0.8369905956112853</t>
         </is>
       </c>
       <c r="AR3" t="n">
-        <v>0.8180973223263399</v>
+        <v>0.8373637856396476</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.8119122257053292</v>
+        <v>0.8338557993730408</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.01177623075655056</v>
+        <v>0.007232572948425511</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.8578199052132701, 0.8584905660377359, 0.8584905660377358, 0.8618266978922716, 0.8591549295774649, 0.883054892601432, 0.8632075471698114</t>
+          <t>0.6971428571428572, 0.707182320441989, 0.6971428571428572, 0.7303370786516853, 0.6892655367231638, 0.7134502923976608, 0.7078651685393259</t>
         </is>
       </c>
       <c r="AV3" t="n">
-        <v>0.8631493006471033</v>
+        <v>0.7060551587199342</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.8591549295774649</v>
+        <v>0.707182320441989</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.008330240384199985</v>
+        <v>0.01247623977448649</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>0.8341013824884793, 0.8310502283105022, 0.8348623853211009, 0.832579185520362, 0.8318181818181818, 0.8685446009389671, 0.8394495412844036</t>
+          <t>0.6703296703296703, 0.6666666666666666, 0.6777777777777778, 0.6989247311827957, 0.6630434782608695, 0.7093023255813954, 0.6774193548387096</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>0.8389150722402852</v>
+        <v>0.6804948578054122</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.8341013824884793</v>
+        <v>0.6774193548387096</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.01236443975154782</v>
+        <v>0.01597083157929664</v>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>0.8829268292682927, 0.8878048780487805, 0.883495145631068, 0.8932038834951457, 0.8883495145631068, 0.8980582524271845, 0.8883495145631068</t>
+          <t>0.7261904761904762, 0.7529411764705882, 0.7176470588235294, 0.7647058823529411, 0.7176470588235294, 0.7176470588235294, 0.7411764705882353</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.888884002570955</v>
+        <v>0.7339935974389756</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.8883495145631068</v>
+        <v>0.7261904761904762</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.00491487231480214</v>
+        <v>0.01779392166608651</v>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.8975825598963955, 0.9145485665382971, 0.9012586992009622, 0.9084328550562764, 0.8984234040725149, 0.9190652117879542, 0.9092061173640348</t>
+          <t>0.907967032967033, 0.9191050779286074, 0.9073906485671193, 0.9190548014077425, 0.9080945198592257, 0.9143790849673202, 0.9038712921065862</t>
         </is>
       </c>
       <c r="BH3" t="n">
-        <v>0.9069310591309193</v>
+        <v>0.9114089225433765</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.9084328550562764</v>
+        <v>0.9080945198592257</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.007603060102699606</v>
+        <v>0.005635428789683134</v>
       </c>
     </row>
     <row r="4">
@@ -1193,211 +1193,211 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KNeighborsClassifier_splashing_base</t>
+          <t>LogisticRegression_splashing_base</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{'estimator': KNeighborsClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': LogisticRegression(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>0.8133333333333334</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8269230769230769</v>
+        <v>0.8035714285714286</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.9375</v>
       </c>
       <c r="H4" t="n">
-        <v>0.86</v>
+        <v>0.8653846153846154</v>
       </c>
       <c r="I4" t="n">
-        <v>0.880787037037037</v>
+        <v>0.8912037037037037</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9158249158249159</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9282051282051282</v>
+        <v>0.8407960199004975</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9427083333333334</v>
+        <v>0.8802083333333334</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9354005167958657</v>
+        <v>0.8600508905852416</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9661954365079365</v>
+        <v>0.9132688492063492</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.0033121109008789062, 0.002633333206176758, 0.002763032913208008, 0.0028138160705566406, 0.0028731822967529297, 0.002604961395263672, 0.002413034439086914</t>
+          <t>0.0065839290618896484, 0.003679990768432617, 0.00339508056640625, 0.003592967987060547, 0.0034291744232177734, 0.004132270812988281, 0.003287076950073242</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.002773353031703404</v>
+        <v>0.004014355795724052</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002763032913208008</v>
+        <v>0.003592967987060547</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0002617961227112058</v>
+        <v>0.001079738853742046</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.009039878845214844, 0.006004810333251953, 0.006154060363769531, 0.005715131759643555, 0.005308866500854492, 0.005414009094238281, 0.00579380989074707</t>
+          <t>0.004926919937133789, 0.004796266555786133, 0.00476384162902832, 0.004468202590942383, 0.0047719478607177734, 0.004295825958251953, 0.004725933074951172</t>
         </is>
       </c>
       <c r="T4" t="n">
-        <v>0.006204366683959961</v>
+        <v>0.004678419658115932</v>
       </c>
       <c r="U4" t="n">
-        <v>0.00579380989074707</v>
+        <v>0.00476384162902832</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001190256639119724</v>
+        <v>0.0002016047749735491</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.8888888888888888, 0.8301886792452831, 0.8679245283018868, 0.8113207547169812, 0.8490566037735849, 0.8113207547169812, 0.7735849056603774</t>
+          <t>0.8703703703703703, 0.7924528301886793, 0.8490566037735849, 0.7735849056603774, 0.8301886792452831, 0.7547169811320755, 0.7735849056603774</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>0.833183587900569</v>
+        <v>0.8062793251472496</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.8301886792452831</v>
+        <v>0.7924528301886793</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03601369874946368</v>
+        <v>0.04052673239832488</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.9166666666666667, 0.8695652173913043, 0.8955223880597014, 0.8484848484848485, 0.8857142857142858, 0.84375, 0.8333333333333333</t>
+          <t>0.9090909090909091, 0.8405797101449276, 0.8857142857142858, 0.8235294117647058, 0.8695652173913043, 0.8115942028985507, 0.8333333333333333</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>0.87043381995002</v>
+        <v>0.8533438671911453</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8695652173913043</v>
+        <v>0.8405797101449276</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.02821192547334734</v>
+        <v>0.03298049265322964</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.8918918918918919, 0.8823529411764706, 0.9090909090909091, 0.875, 0.8611111111111112, 0.9, 0.7894736842105263</t>
+          <t>0.8333333333333334, 0.8529411764705882, 0.8611111111111112, 0.8235294117647058, 0.8571428571428571, 0.8, 0.7894736842105263</t>
         </is>
       </c>
       <c r="AF4" t="n">
-        <v>0.8727029339258443</v>
+        <v>0.8310759391475887</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.03702761166157346</v>
+        <v>0.02623572233655289</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.9428571428571428, 0.8571428571428571, 0.8823529411764706, 0.8235294117647058, 0.9117647058823529, 0.7941176470588235, 0.8823529411764706</t>
+          <t>1.0, 0.8285714285714286, 0.9117647058823529, 0.8235294117647058, 0.8823529411764706, 0.8235294117647058, 0.8823529411764706</t>
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0.8705882352941176</v>
+        <v>0.8788715486194477</v>
       </c>
       <c r="AK4" t="n">
         <v>0.8823529411764706</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.04696225729259014</v>
+        <v>0.05908094691303778</v>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.9624060150375939, 0.8849206349206349, 0.9272445820433436, 0.914860681114551, 0.8924148606811145, 0.923374613003096, 0.846749226006192</t>
+          <t>0.9578947368421054, 0.8571428571428572, 0.9504643962848297, 0.8869969040247677, 0.9411764705882353, 0.8126934984520124, 0.8606811145510836</t>
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>0.9074243732580752</v>
+        <v>0.8952928539836987</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.914860681114551</v>
+        <v>0.8869969040247677</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.03409798408896362</v>
+        <v>0.05156559231488393</v>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.8962264150943396, 0.896551724137931, 0.8808777429467085, 0.8934169278996865, 0.8934169278996865, 0.890282131661442, 0.8934169278996865</t>
+          <t>0.8113207547169812, 0.8119122257053292, 0.8119122257053292, 0.8150470219435737, 0.8119122257053292, 0.8463949843260188, 0.8181818181818182</t>
         </is>
       </c>
       <c r="AR4" t="n">
-        <v>0.8920269710770686</v>
+        <v>0.8180973223263399</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.8934169278996865</v>
+        <v>0.8119122257053292</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.004946202189722954</v>
+        <v>0.01177623075655056</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.9197080291970803, 0.9193154034229828, 0.9068627450980392, 0.9174757281553398, 0.9170731707317074, 0.9152542372881356, 0.9170731707317074</t>
+          <t>0.8578199052132701, 0.8584905660377359, 0.8584905660377358, 0.8618266978922716, 0.8591549295774649, 0.883054892601432, 0.8632075471698114</t>
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>0.916108926374999</v>
+        <v>0.8631493006471033</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.9170731707317074</v>
+        <v>0.8591549295774649</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.004021106444933429</v>
+        <v>0.008330240384199985</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.9174757281553398, 0.9215686274509803, 0.9158415841584159, 0.9174757281553398, 0.9215686274509803, 0.9130434782608695, 0.9215686274509803</t>
+          <t>0.8341013824884793, 0.8310502283105022, 0.8348623853211009, 0.832579185520362, 0.8318181818181818, 0.8685446009389671, 0.8394495412844036</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>0.918363200154701</v>
+        <v>0.8389150722402852</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.9174757281553398</v>
+        <v>0.8341013824884793</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.003095099671022134</v>
+        <v>0.01236443975154782</v>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.9219512195121952, 0.9170731707317074, 0.8980582524271845, 0.9174757281553398, 0.912621359223301, 0.9174757281553398, 0.912621359223301</t>
+          <t>0.8829268292682927, 0.8878048780487805, 0.883495145631068, 0.8932038834951457, 0.8883495145631068, 0.8980582524271845, 0.8883495145631068</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.9138966882040529</v>
+        <v>0.888884002570955</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.9170731707317074</v>
+        <v>0.8883495145631068</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.007118321889567089</v>
+        <v>0.00491487231480214</v>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.9620332398014245, 0.9660034231921266, 0.9626256551250107, 0.9647521264713463, 0.9616805567488615, 0.9633774379242204, 0.967694819142538</t>
+          <t>0.8975825598963955, 0.9145485665382971, 0.9012586992009622, 0.9084328550562764, 0.8984234040725149, 0.9190652117879542, 0.9092061173640348</t>
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>0.9640238940579325</v>
+        <v>0.9069310591309193</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.9633774379242204</v>
+        <v>0.9084328550562764</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.002061603425119283</v>
+        <v>0.007603060102699606</v>
       </c>
     </row>
     <row r="5">
@@ -1408,216 +1408,216 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>no_fragmentation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SVC_splashing_base</t>
+          <t>LogisticRegression_no_fragmentation_base</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'estimator': SVC(probability=True), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': LogisticRegression(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.84</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.7</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8846153846153847</v>
+        <v>0.717948717948718</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.9254545454545455</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8855218855218855</v>
+        <v>0.8754208754208754</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9030612244897959</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="L5" t="n">
-        <v>0.921875</v>
+        <v>0.6835443037974683</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9123711340206186</v>
+        <v>0.7448275862068965</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9497271825396826</v>
+        <v>0.9316571826733249</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.009903192520141602, 0.008059978485107422, 0.007985115051269531, 0.007807016372680664, 0.007658958435058594, 0.00767207145690918, 0.007129192352294922</t>
+          <t>0.0056149959564208984, 0.0036008358001708984, 0.003214120864868164, 0.0038242340087890625, 0.0033888816833496094, 0.0032241344451904297, 0.0030870437622070312</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.008030789239065987</v>
+        <v>0.003707749502999442</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.007807016372680664</v>
+        <v>0.003388881683349609</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0008140480879537349</v>
+        <v>0.0008130272595688407</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.005318880081176758, 0.004998207092285156, 0.005772113800048828, 0.005053997039794922, 0.005886077880859375, 0.0056569576263427734, 0.005222797393798828</t>
+          <t>0.005347013473510742, 0.004559040069580078, 0.004645824432373047, 0.004475831985473633, 0.004625797271728516, 0.004248857498168945, 0.004568815231323242</t>
         </is>
       </c>
       <c r="T5" t="n">
-        <v>0.005415575844900948</v>
+        <v>0.004638739994594029</v>
       </c>
       <c r="U5" t="n">
-        <v>0.005318880081176758</v>
+        <v>0.004568815231323242</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003291126931631227</v>
+        <v>0.0003143378426585304</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.9074074074074074, 0.7547169811320755, 0.8679245283018868, 0.8679245283018868, 0.8867924528301887, 0.8490566037735849, 0.8490566037735849</t>
+          <t>0.8148148148148148, 0.7924528301886793, 0.9245283018867925, 0.8490566037735849, 0.8490566037735849, 0.8490566037735849, 0.8867924528301887</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>0.8546970150743736</v>
+        <v>0.85225117300589</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.8679245283018868</v>
+        <v>0.8490566037735849</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0450683171313999</v>
+        <v>0.04039982656823135</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.9333333333333333, 0.8059701492537314, 0.8923076923076922, 0.8923076923076922, 0.90625, 0.8749999999999999, 0.8857142857142858</t>
+          <t>0.5833333333333334, 0.6206896551724138, 0.8571428571428571, 0.7333333333333334, 0.6363636363636364, 0.6666666666666666, 0.7999999999999999</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>0.8844118789881049</v>
+        <v>0.6996470688588915</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8923076923076922</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.03632843171013504</v>
+        <v>0.09324779318350135</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.875, 0.84375, 0.9354838709677419, 0.9354838709677419, 0.9666666666666667, 0.9333333333333333, 0.8611111111111112</t>
+          <t>0.7777777777777778, 0.6, 0.8571428571428571, 0.6875, 0.875, 0.8, 0.75</t>
         </is>
       </c>
       <c r="AF5" t="n">
-        <v>0.9072612647209422</v>
+        <v>0.7639172335600907</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.04310467686730826</v>
+        <v>0.08898364299549143</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.0, 0.7714285714285715, 0.8529411764705882, 0.8529411764705882, 0.8529411764705882, 0.8235294117647058, 0.9117647058823529</t>
+          <t>0.4666666666666667, 0.6428571428571429, 0.8571428571428571, 0.7857142857142857, 0.5, 0.5714285714285714, 0.8571428571428571</t>
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0.8665066026410564</v>
+        <v>0.6687074829931972</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8529411764705882</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.06687698340327823</v>
+        <v>0.1531201700556019</v>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.9699248120300752, 0.8333333333333334, 0.9705882352941176, 0.9303405572755418, 0.9504643962848297, 0.9055727554179567, 0.8839009287925697</t>
+          <t>0.9418803418803419, 0.8498168498168499, 0.9578754578754578, 0.8864468864468865, 0.9560439560439561, 0.9212454212454212, 0.9633699633699634</t>
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>0.9205892883469178</v>
+        <v>0.9252398395255538</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9303405572755418</v>
+        <v>0.9418803418803419</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.04645524972067035</v>
+        <v>0.03955875522584676</v>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.8710691823899371, 0.8746081504702194, 0.8683385579937304, 0.877742946708464, 0.8746081504702194, 0.877742946708464, 0.890282131661442</t>
+          <t>0.8773584905660378, 0.877742946708464, 0.8589341692789969, 0.877742946708464, 0.8746081504702194, 0.8714733542319749, 0.8526645768025078</t>
         </is>
       </c>
       <c r="AR5" t="n">
-        <v>0.8763417237717823</v>
+        <v>0.8700749478238093</v>
       </c>
       <c r="AS5" t="n">
         <v>0.8746081504702194</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.006504094660230648</v>
+        <v>0.009414197796548299</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.9044289044289044, 0.898477157360406, 0.8934010152284263, 0.9041769041769042, 0.900497512437811, 0.9027431421446385, 0.913151364764268</t>
+          <t>0.7547169811320756, 0.7577639751552795, 0.7133757961783439, 0.751592356687898, 0.7468354430379747, 0.7453416149068324, 0.69281045751634</t>
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>0.902410857220194</v>
+        <v>0.737490946373535</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.9027431421446385</v>
+        <v>0.7468354430379747</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.005643865032366699</v>
+        <v>0.02278289116899502</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.8660714285714286, 0.9365079365079365, 0.9361702127659575, 0.9154228855721394, 0.923469387755102, 0.9282051282051282, 0.934010152284264</t>
+          <t>0.8, 0.8026315789473685, 0.7777777777777778, 0.8194444444444444, 0.8082191780821918, 0.7894736842105263, 0.7794117647058824</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>0.9199795902374223</v>
+        <v>0.7967083468811701</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.9282051282051282</v>
+        <v>0.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.02311113143313012</v>
+        <v>0.014168514244079</v>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.9463414634146341, 0.8634146341463415, 0.8543689320388349, 0.8932038834951457, 0.8786407766990292, 0.8786407766990292, 0.8932038834951457</t>
+          <t>0.7142857142857143, 0.7176470588235294, 0.6588235294117647, 0.6941176470588235, 0.6941176470588235, 0.7058823529411765, 0.6235294117647059</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.8868306214268801</v>
+        <v>0.6869147659063627</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.8786407766990292</v>
+        <v>0.6941176470588235</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.02766894624575639</v>
+        <v>0.03154134629409137</v>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.9373839844593136, 0.9515618314077879, 0.9390196752298307, 0.9434444539908927, 0.936485093221067, 0.9465589827304751, 0.9486854540768108</t>
+          <t>0.9281135531135531, 0.9407742584213172, 0.9262443438914028, 0.9370035193564605, 0.9277526395173454, 0.9327300150829563, 0.9243841126194067</t>
         </is>
       </c>
       <c r="BH5" t="n">
-        <v>0.9433056393023111</v>
+        <v>0.9310003488574919</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.9434444539908927</v>
+        <v>0.9281135531135531</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.005446702292296702</v>
+        <v>0.005604009792409489</v>
       </c>
     </row>
     <row r="6">
@@ -1633,211 +1633,211 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CatBoostClassifier_splashing_base</t>
+          <t>KNeighborsClassifier_splashing_base</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x16a90c850&gt;, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': KNeighborsClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.88</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8679245283018868</v>
+        <v>0.8269230769230769</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H6" t="n">
-        <v>0.910891089108911</v>
+        <v>0.86</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9467592592592593</v>
+        <v>0.880787037037037</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9966329966329966</v>
+        <v>0.9158249158249159</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9948186528497409</v>
+        <v>0.9282051282051282</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0.9427083333333334</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9974025974025974</v>
+        <v>0.9354005167958657</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9988839285714286</v>
+        <v>0.9661954365079365</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.6268463134765625, 0.5556938648223877, 0.5717732906341553, 0.5568299293518066, 0.5568921566009521, 0.5782740116119385, 0.5516190528869629</t>
+          <t>0.0038111209869384766, 0.0026099681854248047, 0.002904653549194336, 0.0025260448455810547, 0.002437114715576172, 0.0027048587799072266, 0.0025479793548583984</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.5711326599121094</v>
+        <v>0.00279167720249721</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5568921566009521</v>
+        <v>0.002609968185424805</v>
       </c>
       <c r="R6" t="n">
-        <v>0.02444211176962691</v>
+        <v>0.00043887008117464</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.005814075469970703, 0.0051081180572509766, 0.005595684051513672, 0.0057680606842041016, 0.00548100471496582, 0.005693197250366211, 0.00574803352355957</t>
+          <t>0.03403282165527344, 0.006546974182128906, 0.005788326263427734, 0.005702018737792969, 0.005563974380493164, 0.0058040618896484375, 0.005694150924682617</t>
         </is>
       </c>
       <c r="T6" t="n">
-        <v>0.005601167678833008</v>
+        <v>0.009876046861921037</v>
       </c>
       <c r="U6" t="n">
-        <v>0.005693197250366211</v>
+        <v>0.005788326263427734</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0002270271093154386</v>
+        <v>0.009866449268142702</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.9629629629629629, 0.8679245283018868, 0.9056603773584906, 0.8301886792452831, 0.8867924528301887, 0.8867924528301887, 0.8679245283018868</t>
+          <t>0.8888888888888888, 0.8301886792452831, 0.8679245283018868, 0.8113207547169812, 0.8490566037735849, 0.8113207547169812, 0.7735849056603774</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>0.8868922831186982</v>
+        <v>0.833183587900569</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.8867924528301887</v>
+        <v>0.8301886792452831</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03793577234399872</v>
+        <v>0.03601369874946368</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.9722222222222222, 0.8985507246376812, 0.9275362318840579, 0.8656716417910447, 0.9090909090909091, 0.9090909090909091, 0.8985507246376812</t>
+          <t>0.9166666666666667, 0.8695652173913043, 0.8955223880597014, 0.8484848484848485, 0.8857142857142858, 0.84375, 0.8333333333333333</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>0.9115304804792151</v>
+        <v>0.87043381995002</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.8695652173913043</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.03021720375687164</v>
+        <v>0.02821192547334734</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>0.9459459459459459, 0.9117647058823529, 0.9142857142857143, 0.8787878787878788, 0.9375, 0.9375, 0.8857142857142857</t>
+          <t>0.8918918918918919, 0.8823529411764706, 0.9090909090909091, 0.875, 0.8611111111111112, 0.9, 0.7894736842105263</t>
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>0.915928361516597</v>
+        <v>0.8727029339258443</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.9142857142857143</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.02433124593359062</v>
+        <v>0.03702761166157346</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.0, 0.8857142857142857, 0.9411764705882353, 0.8529411764705882, 0.8823529411764706, 0.8823529411764706, 0.9117647058823529</t>
+          <t>0.9428571428571428, 0.8571428571428571, 0.8823529411764706, 0.8235294117647058, 0.9117647058823529, 0.7941176470588235, 0.8823529411764706</t>
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0.9080432172869148</v>
+        <v>0.8705882352941176</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.8857142857142857</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.04539117047431458</v>
+        <v>0.04696225729259014</v>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>1.0, 0.9396825396825397, 0.9736842105263158, 0.93343653250774, 0.9705882352941176, 0.9504643962848298, 0.9226006191950464</t>
+          <t>0.9624060150375939, 0.8849206349206349, 0.9272445820433436, 0.914860681114551, 0.8924148606811145, 0.923374613003096, 0.846749226006192</t>
         </is>
       </c>
       <c r="AN6" t="n">
-        <v>0.9557795047843699</v>
+        <v>0.9074243732580752</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.9504643962848298</v>
+        <v>0.914860681114551</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.02502210082274886</v>
+        <v>0.03409798408896362</v>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.9874213836477987, 0.9937304075235109, 0.9905956112852664, 0.9905956112852664, 0.987460815047022, 0.9937304075235109, 0.9905956112852664</t>
+          <t>0.8962264150943396, 0.896551724137931, 0.8808777429467085, 0.8934169278996865, 0.8934169278996865, 0.890282131661442, 0.8934169278996865</t>
         </is>
       </c>
       <c r="AR6" t="n">
-        <v>0.9905899782282346</v>
+        <v>0.8920269710770686</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.9905956112852664</v>
+        <v>0.8934169278996865</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.002377163415894737</v>
+        <v>0.004946202189722954</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.9902912621359223, 0.9951456310679612, 0.9927360774818401, 0.9927007299270073, 0.9902912621359223, 0.9951456310679612, 0.9927360774818401</t>
+          <t>0.9197080291970803, 0.9193154034229828, 0.9068627450980392, 0.9174757281553398, 0.9170731707317074, 0.9152542372881356, 0.9170731707317074</t>
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>0.9927209530426364</v>
+        <v>0.916108926374999</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.9927360774818401</v>
+        <v>0.9170731707317074</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.001834813705181454</v>
+        <v>0.004021106444933429</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>0.9855072463768116, 0.9903381642512077, 0.9903381642512077, 0.9951219512195122, 0.9902912621359223, 0.9951456310679612, 0.9903381642512077</t>
+          <t>0.9174757281553398, 0.9215686274509803, 0.9158415841584159, 0.9174757281553398, 0.9215686274509803, 0.9130434782608695, 0.9215686274509803</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>0.9910115119362616</v>
+        <v>0.918363200154701</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.9903381642512077</v>
+        <v>0.9174757281553398</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.003074376650758704</v>
+        <v>0.003095099671022134</v>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>0.9951219512195122, 1.0, 0.9951456310679612, 0.9902912621359223, 0.9902912621359223, 0.9951456310679612, 0.9951456310679612</t>
+          <t>0.9219512195121952, 0.9170731707317074, 0.8980582524271845, 0.9174757281553398, 0.912621359223301, 0.9174757281553398, 0.912621359223301</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.994448766956463</v>
+        <v>0.9138966882040529</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.9951456310679612</v>
+        <v>0.9170731707317074</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.003100597103577546</v>
+        <v>0.007118321889567089</v>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.9979063241959854, 0.9986307231493367, 0.9984319958759343, 0.9985179139101297, 0.9984319958759343, 0.9999570409829023, 0.9984319958759343</t>
+          <t>0.9620332398014245, 0.9660034231921266, 0.9626256551250107, 0.9647521264713463, 0.9616805567488615, 0.9633774379242204, 0.967694819142538</t>
         </is>
       </c>
       <c r="BH6" t="n">
-        <v>0.9986154271237367</v>
+        <v>0.9640238940579325</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.9984319958759343</v>
+        <v>0.9633774379242204</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.0005871770933261723</v>
+        <v>0.002061603425119283</v>
       </c>
     </row>
     <row r="7">
@@ -1853,211 +1853,211 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CatBoostClassifier_no_fragmentation_base</t>
+          <t>KNeighborsClassifier_no_fragmentation_base</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x14932f850&gt;, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': KNeighborsClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.88</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="G7" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8292682926829269</v>
+        <v>0.7692307692307692</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9781818181818182</v>
+        <v>0.9495454545454545</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0.8922558922558923</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0.8309859154929577</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0.7468354430379747</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0.9578155847172223</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.5788400173187256, 0.5555107593536377, 0.5553131103515625, 0.5709900856018066, 0.5529239177703857, 0.547766923904419, 0.5719518661499023</t>
+          <t>0.013814210891723633, 0.0026061534881591797, 0.0027799606323242188, 0.0025517940521240234, 0.0026178359985351562, 0.0024237632751464844, 0.0025777816772460938</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.5618995257786342</v>
+        <v>0.004195928573608398</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5555107593536377</v>
+        <v>0.00260615348815918</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01092282837470189</v>
+        <v>0.003927853439721885</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.005773782730102539, 0.005828142166137695, 0.0057828426361083984, 0.0059468746185302734, 0.005060911178588867, 0.005029201507568359, 0.005877971649169922</t>
+          <t>0.03016972541809082, 0.00638580322265625, 0.006022214889526367, 0.005488157272338867, 0.005755186080932617, 0.00590205192565918, 0.005587339401245117</t>
         </is>
       </c>
       <c r="T7" t="n">
-        <v>0.005614246640886579</v>
+        <v>0.009330068315778459</v>
       </c>
       <c r="U7" t="n">
-        <v>0.005782842636108398</v>
+        <v>0.00590205192565918</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0003641581019381846</v>
+        <v>0.008512186884758929</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9074074074074074, 0.8301886792452831, 0.9622641509433962, 0.8867924528301887, 0.8867924528301887, 0.9433962264150944, 0.8867924528301887</t>
+          <t>0.8888888888888888, 0.7735849056603774, 0.8679245283018868, 0.8301886792452831, 0.8490566037735849, 0.8490566037735849, 0.8867924528301887</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>0.9005191175002497</v>
+        <v>0.8493560946391135</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.8867924528301887</v>
+        <v>0.8490566037735849</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.04001781509646558</v>
+        <v>0.03667999015847824</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.8148148148148148, 0.7096774193548386, 0.9285714285714286, 0.7999999999999999, 0.7272727272727273, 0.888888888888889, 0.7857142857142857</t>
+          <t>0.8000000000000002, 0.5714285714285714, 0.7200000000000001, 0.6666666666666666, 0.6923076923076924, 0.6666666666666666, 0.8125000000000001</t>
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>0.8078485092309977</v>
+        <v>0.7042242281527996</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.6923076923076924</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.07355429314085414</v>
+        <v>0.07722263485750151</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>0.9166666666666666, 0.6470588235294118, 0.9285714285714286, 0.75, 1.0, 0.9230769230769231, 0.7857142857142857</t>
+          <t>0.8, 0.5714285714285714, 0.8181818181818182, 0.6923076923076923, 0.75, 0.8, 0.7222222222222222</t>
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>0.8501554467941023</v>
+        <v>0.7363057577343292</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.1157434080450252</v>
+        <v>0.07957368269107451</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.7333333333333333, 0.7857142857142857, 0.9285714285714286, 0.8571428571428571, 0.5714285714285714, 0.8571428571428571, 0.7857142857142857</t>
+          <t>0.8, 0.5714285714285714, 0.6428571428571429, 0.6428571428571429, 0.6428571428571429, 0.5714285714285714, 0.9285714285714286</t>
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0.7884353741496598</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.106383770352787</v>
+        <v>0.1216983797214333</v>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.9641025641025642, 0.9084249084249085, 0.9908424908424909, 0.9084249084249084, 0.989010989010989, 0.9688644688644689, 0.9761904761904763</t>
+          <t>0.9444444444444444, 0.8772893772893773, 0.9487179487179488, 0.8946886446886448, 0.9010989010989011, 0.903846153846154, 0.9468864468864469</t>
         </is>
       </c>
       <c r="AN7" t="n">
-        <v>0.9579801151229724</v>
+        <v>0.9167102738531312</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.9688644688644689</v>
+        <v>0.903846153846154</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.03260556193142309</v>
+        <v>0.02713046960614661</v>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.9937106918238994, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9937304075235109, 0.9968652037617555, 0.9905956112852664</t>
+          <t>0.89937106918239, 0.9059561128526645, 0.9122257053291536, 0.9028213166144201, 0.9059561128526645, 0.9028213166144201, 0.9028213166144201</t>
         </is>
       </c>
       <c r="AR7" t="n">
-        <v>0.9955189031311348</v>
+        <v>0.9045675642943048</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.9968652037617555</v>
+        <v>0.9028213166144201</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.002834102341681714</v>
+        <v>0.003754139860286498</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.9880952380952381, 1.0, 0.9941520467836257, 0.9940828402366864, 0.9882352941176471, 0.9941520467836257, 0.9822485207100591</t>
+          <t>0.8117647058823529, 0.8255813953488372, 0.829268292682927, 0.8165680473372781, 0.8255813953488372, 0.822857142857143, 0.8143712574850299</t>
         </is>
       </c>
       <c r="AV7" t="n">
-        <v>0.9915665695324117</v>
+        <v>0.820856033848915</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.9940828402366864</v>
+        <v>0.822857142857143</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.005355868938882427</v>
+        <v>0.00612395781888402</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>0.9880952380952381, 1.0, 0.9883720930232558, 1.0, 0.9882352941176471, 0.9883720930232558, 0.9880952380952381</t>
+          <t>0.8023255813953488, 0.8160919540229885, 0.8607594936708861, 0.8214285714285714, 0.8160919540229885, 0.8, 0.8292682926829268</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>0.9915957080506621</v>
+        <v>0.8208522638891014</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.9883720930232558</v>
+        <v>0.8160919540229885</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.005316370884193521</v>
+        <v>0.01884949652022786</v>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>0.9880952380952381, 1.0, 1.0, 0.9882352941176471, 0.9882352941176471, 1.0, 0.9764705882352941</t>
+          <t>0.8214285714285714, 0.8352941176470589, 0.8, 0.8117647058823529, 0.8352941176470589, 0.8470588235294118, 0.8</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.991576630652261</v>
+        <v>0.821548619447779</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.9882352941176471</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.008241888868281137</v>
+        <v>0.01712589238622703</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.999949124949125, 1.0, 0.9998994469582705, 1.0, 0.9998491704374057, 0.9998994469582704, 0.9998994469582704</t>
+          <t>0.9602920227920229, 0.9680744092508797, 0.9614379084967319, 0.9640020110608346, 0.9654600301659125, 0.9612116641528407, 0.9623428858722977</t>
         </is>
       </c>
       <c r="BH7" t="n">
-        <v>0.9999280908944774</v>
+        <v>0.9632601331130743</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.9998994469582705</v>
+        <v>0.9623428858722977</v>
       </c>
       <c r="BJ7" t="n">
-        <v>5.274484965747932e-05</v>
+        <v>0.002556083322909469</v>
       </c>
     </row>
     <row r="8">
@@ -2073,10 +2073,890 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>SVC_splashing_base</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{'estimator': SVC(probability=True), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8214285714285714</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8846153846153847</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.8855218855218855</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.9030612244897959</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.921875</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.9123711340206186</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.9497271825396826</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0.009201288223266602, 0.007555246353149414, 0.00789785385131836, 0.0074770450592041016, 0.007703065872192383, 0.007289886474609375, 0.007388114929199219</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0.007787500108991351</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.007555246353149414</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.0006065777440287308</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.0058438777923583984, 0.005338907241821289, 0.005315065383911133, 0.005349874496459961, 0.005384206771850586, 0.005096912384033203, 0.005342006683349609</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>0.005381550107683454</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.005342006683349609</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.0002082506178569593</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.7547169811320755, 0.8679245283018868, 0.8679245283018868, 0.8867924528301887, 0.8490566037735849, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>0.8546970150743736</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.0450683171313999</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>0.9333333333333333, 0.8059701492537314, 0.8923076923076922, 0.8923076923076922, 0.90625, 0.8749999999999999, 0.8857142857142858</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8844118789881049</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.8923076923076922</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.03632843171013504</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>0.875, 0.84375, 0.9354838709677419, 0.9354838709677419, 0.9666666666666667, 0.9333333333333333, 0.8611111111111112</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.9072612647209422</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.04310467686730826</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>1.0, 0.7714285714285715, 0.8529411764705882, 0.8529411764705882, 0.8529411764705882, 0.8235294117647058, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.8665066026410564</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.8529411764705882</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.06687698340327823</v>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>0.9699248120300752, 0.8317460317460317, 0.9705882352941176, 0.9303405572755418, 0.9504643962848297, 0.9055727554179567, 0.8839009287925697</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.9203625309773033</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.9303405572755418</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.04688251914863425</v>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.8710691823899371, 0.8746081504702194, 0.8683385579937304, 0.877742946708464, 0.8746081504702194, 0.877742946708464, 0.890282131661442</t>
+        </is>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.8763417237717823</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.8746081504702194</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0.006504094660230648</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.9044289044289044, 0.898477157360406, 0.8934010152284263, 0.9041769041769042, 0.900497512437811, 0.9027431421446385, 0.913151364764268</t>
+        </is>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.902410857220194</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.9027431421446385</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0.005643865032366699</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.8660714285714286, 0.9365079365079365, 0.9361702127659575, 0.9154228855721394, 0.923469387755102, 0.9282051282051282, 0.934010152284264</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.9199795902374223</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0.9282051282051282</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.02311113143313012</v>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>0.9463414634146341, 0.8634146341463415, 0.8543689320388349, 0.8932038834951457, 0.8786407766990292, 0.8786407766990292, 0.8932038834951457</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>0.8868306214268801</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0.8786407766990292</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0.02766894624575639</v>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>0.9372976473127563, 0.9515618314077879, 0.9390196752298307, 0.9434444539908927, 0.9364850932210671, 0.9465589827304751, 0.9486854540768108</t>
+        </is>
+      </c>
+      <c r="BH8" t="n">
+        <v>0.9432933054242316</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0.9434444539908927</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.005460178801644405</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SVC_no_fragmentation_base</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{'estimator': SVC(probability=True), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6842105263157895</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.9281818181818182</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.8194444444444444</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.7468354430379747</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.781456953642384</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.9624898385785624</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.008935928344726562, 0.006967067718505859, 0.007485151290893555, 0.0068700313568115234, 0.007204771041870117, 0.006928920745849609, 0.006788015365600586</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>0.007311412266322545</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.006967067718505859</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.0006983904395327948</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.005445241928100586, 0.005352973937988281, 0.0054247379302978516, 0.004976749420166016, 0.004960060119628906, 0.005160093307495117, 0.005090951919555664</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>0.005201544080461774</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.005160093307495117</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.0001908369058981177</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.8333333333333334, 0.7358490566037735, 0.8679245283018868, 0.8867924528301887, 0.8867924528301887, 0.8679245283018868, 0.8301886792452831</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>0.844115004492363</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.04900177617977858</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0.6666666666666665, 0.5, 0.6956521739130435, 0.7857142857142857, 0.75, 0.7200000000000001, 0.689655172413793</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.6868126141011126</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.6956521739130435</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.08474045998405863</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>0.75, 0.5, 0.8888888888888888, 0.7857142857142857, 0.9, 0.8181818181818182, 0.6666666666666666</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.75849309420738</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.1290923865694569</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.6, 0.5, 0.5714285714285714, 0.7857142857142857, 0.6428571428571429, 0.6428571428571429, 0.7142857142857143</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.636734693877551</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.08668065543508287</v>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>0.9384615384615385, 0.8626373626373627, 0.9725274725274725, 0.9267399267399268, 0.9523809523809523, 0.9432234432234433, 0.9413919413919414</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.9339089481946626</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.9413919413919414</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.03190862001703766</v>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.8805031446540881, 0.9028213166144201, 0.8683385579937304, 0.8840125391849529, 0.8808777429467085, 0.8840125391849529, 0.8746081504702194</t>
+        </is>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.8821677130070105</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.8808777429467085</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.009900977108437748</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>0.7532467532467533, 0.8248587570621468, 0.7272727272727274, 0.7836257309941521, 0.7790697674418604, 0.7784431137724551, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.7690512792933218</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.7784431137724551</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.03058507390673511</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.8285714285714286, 0.7934782608695652, 0.8115942028985508, 0.7790697674418605, 0.7701149425287356, 0.7926829268292683, 0.835820895522388</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.8016189178088281</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.7934782608695652</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.02281229712069013</v>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>0.6904761904761905, 0.8588235294117647, 0.6588235294117647, 0.788235294117647, 0.788235294117647, 0.7647058823529411, 0.6588235294117647</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.7440176070428172</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.07061116591341229</v>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>0.9595543345543346, 0.9641025641025641, 0.9572146807440925, 0.9567621920563096, 0.9577677224736049, 0.9569130216189041, 0.9638511814982402</t>
+        </is>
+      </c>
+      <c r="BH9" t="n">
+        <v>0.9594522424354358</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0.9577677224736049</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.002988427262158605</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_splashing_base</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x16fb7af50&gt;, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.910891089108911</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9467592592592593</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.9988839285714286</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.6066570281982422, 0.5708298683166504, 0.5453627109527588, 0.5702857971191406, 0.5615198612213135, 0.5314240455627441, 0.5659708976745605</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0.5645786012922015</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.5659708976745605</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.02178470571524163</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0.0053708553314208984, 0.0063610076904296875, 0.0051500797271728516, 0.005546092987060547, 0.004878997802734375, 0.005018711090087891, 0.005541801452636719</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>0.005409649440220424</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.005370855331420898</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.0004542606062731175</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.8679245283018868, 0.9056603773584906, 0.8301886792452831, 0.8867924528301887, 0.8867924528301887, 0.8679245283018868</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>0.8868922831186982</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.03793577234399872</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8985507246376812, 0.9275362318840579, 0.8656716417910447, 0.9090909090909091, 0.9090909090909091, 0.8985507246376812</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9115304804792151</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.03021720375687164</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.9117647058823529, 0.9142857142857143, 0.8787878787878788, 0.9375, 0.9375, 0.8857142857142857</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.915928361516597</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.02433124593359062</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>1.0, 0.8857142857142857, 0.9411764705882353, 0.8529411764705882, 0.8823529411764706, 0.8823529411764706, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.9080432172869148</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.04539117047431458</v>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>1.0, 0.9396825396825397, 0.9736842105263158, 0.93343653250774, 0.9705882352941176, 0.9504643962848298, 0.9226006191950464</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.9557795047843699</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.9504643962848298</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.02502210082274886</v>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0.9874213836477987, 0.9937304075235109, 0.9905956112852664, 0.9905956112852664, 0.987460815047022, 0.9937304075235109, 0.9905956112852664</t>
+        </is>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.9905899782282346</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.9905956112852664</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.002377163415894737</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>0.9902912621359223, 0.9951456310679612, 0.9927360774818401, 0.9927007299270073, 0.9902912621359223, 0.9951456310679612, 0.9927360774818401</t>
+        </is>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.9927209530426364</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.9927360774818401</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.001834813705181454</v>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>0.9855072463768116, 0.9903381642512077, 0.9903381642512077, 0.9951219512195122, 0.9902912621359223, 0.9951456310679612, 0.9903381642512077</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.9910115119362616</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0.9903381642512077</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0.003074376650758704</v>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>0.9951219512195122, 1.0, 0.9951456310679612, 0.9902912621359223, 0.9902912621359223, 0.9951456310679612, 0.9951456310679612</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.994448766956463</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.9951456310679612</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0.003100597103577546</v>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>0.9979063241959854, 0.9986307231493367, 0.9984319958759343, 0.9985179139101297, 0.9984319958759343, 0.9999570409829023, 0.9984319958759343</t>
+        </is>
+      </c>
+      <c r="BH10" t="n">
+        <v>0.9986154271237367</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0.9984319958759343</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.0005871770933261723</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_no_fragmentation_base</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x16fb27f10&gt;, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.8292682926829269</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9781818181818182</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.5642380714416504, 0.5649821758270264, 0.5700709819793701, 0.5433738231658936, 0.5416419506072998, 0.5433840751647949, 0.5672628879547119</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0.5564219951629639</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.5642380714416504</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.01193362240803832</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0.0054111480712890625, 0.00581812858581543, 0.005033016204833984, 0.00533604621887207, 0.005205631256103516, 0.0053369998931884766, 0.0055849552154541016</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>0.005389417920793805</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.005336999893188477</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.0002357043477349292</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.8301886792452831, 0.9622641509433962, 0.8867924528301887, 0.8867924528301887, 0.9433962264150944, 0.8867924528301887</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>0.9005191175002497</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.04001781509646558</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>0.8148148148148148, 0.7096774193548386, 0.9285714285714286, 0.7999999999999999, 0.7272727272727273, 0.888888888888889, 0.7857142857142857</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8078485092309977</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.07355429314085414</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>0.9166666666666666, 0.6470588235294118, 0.9285714285714286, 0.75, 1.0, 0.9230769230769231, 0.7857142857142857</t>
+        </is>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.8501554467941023</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.1157434080450252</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.7857142857142857, 0.9285714285714286, 0.8571428571428571, 0.5714285714285714, 0.8571428571428571, 0.7857142857142857</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.7884353741496598</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.106383770352787</v>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>0.9641025641025642, 0.9084249084249085, 0.9908424908424909, 0.9084249084249084, 0.989010989010989, 0.9688644688644689, 0.9761904761904763</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.9579801151229724</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.9688644688644689</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.03260556193142309</v>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0.9937106918238994, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9937304075235109, 0.9968652037617555, 0.9905956112852664</t>
+        </is>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.9955189031311348</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.002834102341681714</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 0.9941520467836257, 0.9940828402366864, 0.9882352941176471, 0.9941520467836257, 0.9822485207100591</t>
+        </is>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.9915665695324117</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.9940828402366864</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.005355868938882427</v>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 0.9883720930232558, 1.0, 0.9882352941176471, 0.9883720930232558, 0.9880952380952381</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.9915957080506621</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.9883720930232558</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.005316370884193521</v>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 1.0, 0.9882352941176471, 0.9882352941176471, 1.0, 0.9764705882352941</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.991576630652261</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.9882352941176471</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0.008241888868281137</v>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>0.999949124949125, 1.0, 0.9998994469582705, 1.0, 0.9998491704374057, 0.9998994469582704, 0.9998994469582704</t>
+        </is>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.9999280908944774</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0.9998994469582705</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>5.274484965747932e-05</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>XGBClassifier_splashing_base</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>{'estimator': XGBClassifier(base_score=None, booster=None, callbacks=None,
               colsample_bylevel=None, colsample_bynode=None,
@@ -2091,1093 +2971,433 @@
               num_parallel_tree=None, random_state=None, ...), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E12" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F12" t="n">
         <v>0.8518518518518519</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G12" t="n">
         <v>0.9583333333333334</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H12" t="n">
         <v>0.9019607843137256</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I12" t="n">
         <v>0.9440586419753086</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J12" t="n">
         <v>0.9966329966329966</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K12" t="n">
         <v>0.9948186528497409</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M12" t="n">
         <v>0.9974025974025974</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N12" t="n">
         <v>0.9999751984126984</v>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0.08282208442687988, 0.09463286399841309, 0.08095884323120117, 0.0952138900756836, 0.09817290306091309, 0.07666778564453125, 0.07187414169311523</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>0.08576321601867676</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.08282208442687988</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.009481950674350216</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0.009022951126098633, 0.007380962371826172, 0.008313179016113281, 0.009870052337646484, 0.008810043334960938, 0.006027936935424805, 0.00585174560546875</t>
-        </is>
-      </c>
-      <c r="T8" t="n">
-        <v>0.007896695818219866</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.008313179016113281</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.001419774178932221</v>
-      </c>
-      <c r="W8" t="inlineStr">
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.040197134017944336, 0.03922295570373535, 0.03351879119873047, 0.03398489952087402, 0.032292842864990234, 0.0335690975189209, 0.03051900863647461</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0.03475781849452427</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0335690975189209</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.003319054673175258</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0.006788015365600586, 0.005930900573730469, 0.006511211395263672, 0.005742073059082031, 0.006432056427001953, 0.005510807037353516, 0.005647897720336914</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>0.006080423082624163</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.005930900573730469</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.0004564286464750315</v>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>0.9629629629629629, 0.8490566037735849, 0.9056603773584906, 0.8301886792452831, 0.8867924528301887, 0.8867924528301887, 0.8490566037735849</t>
         </is>
       </c>
-      <c r="X8" t="n">
+      <c r="X12" t="n">
         <v>0.8815014475391835</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Y12" t="n">
         <v>0.8867924528301887</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="Z12" t="n">
         <v>0.04142800609502062</v>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>0.9722222222222222, 0.8857142857142857, 0.9253731343283583, 0.8695652173913043, 0.9090909090909091, 0.90625, 0.8857142857142858</t>
         </is>
       </c>
-      <c r="AB8" t="n">
+      <c r="AB12" t="n">
         <v>0.9077042934944808</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AC12" t="n">
         <v>0.90625</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AD12" t="n">
         <v>0.03139722177532166</v>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>0.9459459459459459, 0.8857142857142857, 0.9393939393939394, 0.8571428571428571, 0.9375, 0.9666666666666667, 0.8611111111111112</t>
         </is>
       </c>
-      <c r="AF8" t="n">
+      <c r="AF12" t="n">
         <v>0.9133535437106867</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AG12" t="n">
         <v>0.9375</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AH12" t="n">
         <v>0.0410897083958572</v>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AI12" t="inlineStr">
         <is>
           <t>1.0, 0.8857142857142857, 0.9117647058823529, 0.8823529411764706, 0.8823529411764706, 0.8529411764705882, 0.9117647058823529</t>
         </is>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AJ12" t="n">
         <v>0.9038415366146458</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AK12" t="n">
         <v>0.8857142857142857</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AL12" t="n">
         <v>0.04344942323952641</v>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>0.9984962406015038, 0.9333333333333333, 0.9520123839009289, 0.8978328173374612, 0.9659442724458205, 0.9342105263157896, 0.9256965944272446</t>
         </is>
       </c>
-      <c r="AN8" t="n">
+      <c r="AN12" t="n">
         <v>0.9439323097660115</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AO12" t="n">
         <v>0.9342105263157896</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AP12" t="n">
         <v>0.02974076696634106</v>
       </c>
-      <c r="AQ8" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
         </is>
       </c>
-      <c r="AR8" t="n">
+      <c r="AR12" t="n">
         <v>0.9977594515655674</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="AS12" t="n">
         <v>0.9968652037617555</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="AT12" t="n">
         <v>0.001417051170840857</v>
       </c>
-      <c r="AU8" t="inlineStr">
+      <c r="AU12" t="inlineStr">
         <is>
           <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
         </is>
       </c>
-      <c r="AV8" t="n">
+      <c r="AV12" t="n">
         <v>0.9982688114216364</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="AW12" t="n">
         <v>0.9975786924939467</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="AX12" t="n">
         <v>0.001094907038779773</v>
       </c>
-      <c r="AY8" t="inlineStr">
+      <c r="AY12" t="inlineStr">
         <is>
           <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
         </is>
       </c>
-      <c r="AZ8" t="n">
+      <c r="AZ12" t="n">
         <v>0.9965459942243395</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BA12" t="n">
         <v>0.9951690821256038</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BB12" t="n">
         <v>0.002184519446236978</v>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BC12" t="inlineStr">
         <is>
           <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
         </is>
       </c>
-      <c r="BD8" t="n">
+      <c r="BD12" t="n">
         <v>1</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BE12" t="n">
         <v>1</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="BF12" t="n">
         <v>0</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>0.9999784157133608, 1.0, 0.9999355614743535, 0.9999785204914512, 0.9999785204914512, 1.0, 0.9999785204914512</t>
         </is>
       </c>
-      <c r="BH8" t="n">
+      <c r="BH12" t="n">
         <v>0.9999785055231526</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BI12" t="n">
         <v>0.9999785204914512</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BJ12" t="n">
         <v>1.988619454760789e-05</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>df_dimless</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>no_fragmentation</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LogisticRegression_no_fragmentation_base</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>{'estimator': LogisticRegression(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.8533333333333334</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.7368421052631579</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.717948717948718</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.9254545454545455</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.8754208754208754</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.8181818181818182</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.6835443037974683</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.7448275862068965</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.9316571826733249</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0.00896906852722168, 0.013093233108520508, 0.0, 0.008106708526611328, 0.010124683380126953, 0.0, 0.0</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>0.005756241934640067</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.008106708526611328</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.005184656369554661</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0.007524251937866211, 0.005464315414428711, 0.010611295700073242, 0.0, 0.0, 0.0, 0.010504722595214844</t>
-        </is>
-      </c>
-      <c r="T9" t="n">
-        <v>0.00487208366394043</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.005464315414428711</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.004523928583663451</v>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0.8148148148148148, 0.7924528301886793, 0.9245283018867925, 0.8490566037735849, 0.8490566037735849, 0.8490566037735849, 0.8867924528301887</t>
-        </is>
-      </c>
-      <c r="X9" t="n">
-        <v>0.85225117300589</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.8490566037735849</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.04039982656823135</v>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>0.5833333333333334, 0.6206896551724138, 0.8571428571428571, 0.7333333333333334, 0.6363636363636364, 0.6666666666666666, 0.7999999999999999</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>0.6996470688588915</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.09324779318350135</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>0.7777777777777778, 0.6, 0.8571428571428571, 0.6875, 0.875, 0.8, 0.75</t>
-        </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.7639172335600907</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.08898364299549143</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0.4666666666666667, 0.6428571428571429, 0.8571428571428571, 0.7857142857142857, 0.5, 0.5714285714285714, 0.8571428571428571</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0.6687074829931972</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0.1531201700556019</v>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>0.9418803418803419, 0.8498168498168499, 0.9578754578754578, 0.8864468864468865, 0.9560439560439561, 0.9212454212454212, 0.9633699633699634</t>
-        </is>
-      </c>
-      <c r="AN9" t="n">
-        <v>0.9252398395255538</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0.9418803418803419</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0.03955875522584676</v>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>0.8773584905660378, 0.877742946708464, 0.8589341692789969, 0.877742946708464, 0.8746081504702194, 0.8714733542319749, 0.8526645768025078</t>
-        </is>
-      </c>
-      <c r="AR9" t="n">
-        <v>0.8700749478238093</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0.8746081504702194</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0.009414197796548299</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>0.7547169811320756, 0.7577639751552795, 0.7133757961783439, 0.751592356687898, 0.7468354430379747, 0.7453416149068324, 0.69281045751634</t>
-        </is>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.737490946373535</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.7468354430379747</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0.02278289116899502</v>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>0.8, 0.8026315789473685, 0.7777777777777778, 0.8194444444444444, 0.8082191780821918, 0.7894736842105263, 0.7794117647058824</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.7967083468811701</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0.014168514244079</v>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>0.7142857142857143, 0.7176470588235294, 0.6588235294117647, 0.6941176470588235, 0.6941176470588235, 0.7058823529411765, 0.6235294117647059</t>
-        </is>
-      </c>
-      <c r="BD9" t="n">
-        <v>0.6869147659063627</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0.6941176470588235</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>0.03154134629409137</v>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>0.9281135531135531, 0.9407742584213172, 0.9262443438914028, 0.9370035193564605, 0.9277526395173454, 0.9327300150829563, 0.9243841126194067</t>
-        </is>
-      </c>
-      <c r="BH9" t="n">
-        <v>0.9310003488574919</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>0.9281135531135531</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.005604009792409489</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>df_dimless</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>no_fragmentation</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>KNeighborsClassifier_no_fragmentation_base</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>{'estimator': KNeighborsClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.7894736842105263</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.7692307692307692</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.9495454545454545</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.8922558922558923</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.8309859154929577</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.7468354430379747</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.7866666666666666</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.9578155847172223</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0.007361412048339844, 0.0034761428833007812, 0.0, 0.004326820373535156, 0.0, 0.01344752311706543, 0.00612187385559082</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>0.004961967468261719</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.004326820373535156</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.00432535218434897</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0.010094881057739258, 0.002934694290161133, 0.013010263442993164, 0.004120349884033203, 0.0160982608795166, 0.0, 0.008006095886230469</t>
-        </is>
-      </c>
-      <c r="T10" t="n">
-        <v>0.007752077920096261</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.008006095886230469</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.005336556973224901</v>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0.8888888888888888, 0.7735849056603774, 0.8679245283018868, 0.8301886792452831, 0.8490566037735849, 0.8490566037735849, 0.8867924528301887</t>
-        </is>
-      </c>
-      <c r="X10" t="n">
-        <v>0.8493560946391135</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.8490566037735849</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0.03667999015847824</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>0.8000000000000002, 0.5714285714285714, 0.7200000000000001, 0.6666666666666666, 0.6923076923076924, 0.6666666666666666, 0.8125000000000001</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>0.7042242281527996</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0.6923076923076924</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.07722263485750151</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>0.8, 0.5714285714285714, 0.8181818181818182, 0.6923076923076923, 0.75, 0.8, 0.7222222222222222</t>
-        </is>
-      </c>
-      <c r="AF10" t="n">
-        <v>0.7363057577343292</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0.07957368269107451</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0.8, 0.5714285714285714, 0.6428571428571429, 0.6428571428571429, 0.6428571428571429, 0.5714285714285714, 0.9285714285714286</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0.6857142857142857</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0.1216983797214333</v>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>0.9444444444444444, 0.8772893772893773, 0.9487179487179488, 0.8946886446886448, 0.9010989010989011, 0.903846153846154, 0.9468864468864469</t>
-        </is>
-      </c>
-      <c r="AN10" t="n">
-        <v>0.9167102738531312</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0.903846153846154</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0.02713046960614661</v>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>0.89937106918239, 0.9059561128526645, 0.9122257053291536, 0.9028213166144201, 0.9059561128526645, 0.9028213166144201, 0.9028213166144201</t>
-        </is>
-      </c>
-      <c r="AR10" t="n">
-        <v>0.9045675642943048</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0.9028213166144201</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0.003754139860286498</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>0.8117647058823529, 0.8255813953488372, 0.829268292682927, 0.8165680473372781, 0.8255813953488372, 0.822857142857143, 0.8143712574850299</t>
-        </is>
-      </c>
-      <c r="AV10" t="n">
-        <v>0.820856033848915</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0.822857142857143</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0.00612395781888402</v>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>0.8023255813953488, 0.8160919540229885, 0.8607594936708861, 0.8214285714285714, 0.8160919540229885, 0.8, 0.8292682926829268</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0.8208522638891014</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0.8160919540229885</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0.01884949652022786</v>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>0.8214285714285714, 0.8352941176470589, 0.8, 0.8117647058823529, 0.8352941176470589, 0.8470588235294118, 0.8</t>
-        </is>
-      </c>
-      <c r="BD10" t="n">
-        <v>0.821548619447779</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0.8214285714285714</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>0.01712589238622703</v>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>0.9602920227920229, 0.9680744092508797, 0.9614379084967319, 0.9640020110608346, 0.9654600301659125, 0.9612116641528407, 0.9623428858722977</t>
-        </is>
-      </c>
-      <c r="BH10" t="n">
-        <v>0.9632601331130743</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>0.9623428858722977</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0.002556083322909469</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>df_dimless</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>no_fragmentation</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>SVC_no_fragmentation_base</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>{'estimator': SVC(probability=True), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.6842105263157895</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9281818181818182</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.8194444444444444</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.7468354430379747</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.781456953642384</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.9624898385785624</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.008918046951293945, 0.015131235122680664, 0.00925302505493164, 0.005823373794555664, 0.015625, 0.015604257583618164, 0.026727914810180664</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>0.01386897904532296</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.01513123512268066</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.006364980577914103</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0.029338359832763672, 0.008470535278320312, 0.011104106903076172, 0.010102987289428711, 0.0, 0.0, 0.0024471282958984375</t>
-        </is>
-      </c>
-      <c r="T11" t="n">
-        <v>0.00878044537135533</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.008470535278320312</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.009442879088229031</v>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0.8333333333333334, 0.7358490566037735, 0.8679245283018868, 0.8867924528301887, 0.8867924528301887, 0.8679245283018868, 0.8301886792452831</t>
-        </is>
-      </c>
-      <c r="X11" t="n">
-        <v>0.844115004492363</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.8679245283018868</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0.04900177617977858</v>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>0.6666666666666665, 0.5, 0.6956521739130435, 0.7857142857142857, 0.75, 0.7200000000000001, 0.689655172413793</t>
-        </is>
-      </c>
-      <c r="AB11" t="n">
-        <v>0.6868126141011126</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.6956521739130435</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0.08474045998405863</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>0.75, 0.5, 0.8888888888888888, 0.7857142857142857, 0.9, 0.8181818181818182, 0.6666666666666666</t>
-        </is>
-      </c>
-      <c r="AF11" t="n">
-        <v>0.75849309420738</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.1290923865694569</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>0.6, 0.5, 0.5714285714285714, 0.7857142857142857, 0.6428571428571429, 0.6428571428571429, 0.7142857142857143</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.636734693877551</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0.08668065543508287</v>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>0.9384615384615385, 0.8626373626373627, 0.9725274725274725, 0.9267399267399268, 0.9523809523809523, 0.9432234432234433, 0.9413919413919414</t>
-        </is>
-      </c>
-      <c r="AN11" t="n">
-        <v>0.9339089481946626</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0.9413919413919414</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0.03190862001703766</v>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>0.8805031446540881, 0.9028213166144201, 0.8683385579937304, 0.8840125391849529, 0.8808777429467085, 0.8840125391849529, 0.8746081504702194</t>
-        </is>
-      </c>
-      <c r="AR11" t="n">
-        <v>0.8821677130070105</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0.8808777429467085</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0.009900977108437748</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>0.7532467532467533, 0.8248587570621468, 0.7272727272727274, 0.7836257309941521, 0.7790697674418604, 0.7784431137724551, 0.7368421052631579</t>
-        </is>
-      </c>
-      <c r="AV11" t="n">
-        <v>0.7690512792933218</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0.7784431137724551</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0.03058507390673511</v>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>0.8285714285714286, 0.7934782608695652, 0.8115942028985508, 0.7790697674418605, 0.7701149425287356, 0.7926829268292683, 0.835820895522388</t>
-        </is>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.8016189178088281</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0.7934782608695652</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>0.02281229712069013</v>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>0.6904761904761905, 0.8588235294117647, 0.6588235294117647, 0.788235294117647, 0.788235294117647, 0.7647058823529411, 0.6588235294117647</t>
-        </is>
-      </c>
-      <c r="BD11" t="n">
-        <v>0.7440176070428172</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>0.07061116591341229</v>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>0.9595543345543346, 0.9641025641025641, 0.9572146807440925, 0.9567621920563096, 0.9577677224736049, 0.956913021618904, 0.9638511814982402</t>
-        </is>
-      </c>
-      <c r="BH11" t="n">
-        <v>0.9594522424354358</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>0.9577677224736049</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.002988427262158618</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>df_dimless</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>no_fragmentation</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>XGBClassifier_no_fragmentation_base</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>{'estimator': XGBClassifier(base_score=None, booster=None, callbacks=None,
               colsample_bylevel=None, colsample_bynode=None,
-              colsample_bytree=None, early_stopping_rounds=None,
+              colsample_bytree=None, device=None, early_stopping_rounds=None,
               enable_categorical=False, eval_metric=None, feature_types=None,
-              gamma=None, gpu_id=None, grow_policy=None, importance_type=None,
+              gamma=None, grow_policy=None, importance_type=None,
               interaction_constraints=None, learning_rate=None, max_bin=None,
               max_cat_threshold=None, max_cat_to_onehot=None,
               max_delta_step=None, max_depth=None, max_leaves=None,
               min_child_weight=None, missing=nan, monotone_constraints=None,
-              n_estimators=100, n_jobs=None, num_parallel_tree=None,
-              predictor=None, random_state=None, ...), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.7619047619047619</v>
-      </c>
-      <c r="G12" t="n">
+              multi_strategy=None, n_estimators=None, n_jobs=None,
+              num_parallel_tree=None, random_state=None, ...), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'particle_liquid_density_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="G13" t="n">
         <v>0.8</v>
       </c>
-      <c r="H12" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.9654545454545455</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="H13" t="n">
+        <v>0.761904761904762</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N13" t="n">
         <v>1</v>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0.07788205146789551, 0.05489039421081543, 0.06288433074951172, 0.057038068771362305, 0.04688525199890137, 0.07667183876037598, 0.0814962387084961</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>0.0653925963810512</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.06288433074951172</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.01237187286775673</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0.019135475158691406, 0.01563429832458496, 0.016017913818359375, 0.01617717742919922, 0.015770435333251953, 0.015863656997680664, 0.013914346694946289</t>
-        </is>
-      </c>
-      <c r="T12" t="n">
-        <v>0.01607332910810198</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.01586365699768066</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.001433290613797244</v>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>0.9074074074074074, 0.8113207547169812, 0.9433962264150944, 0.8867924528301887, 0.9245283018867925, 0.8867924528301887, 0.9056603773584906</t>
-        </is>
-      </c>
-      <c r="X12" t="n">
-        <v>0.8951282819207348</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.9056603773584906</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0.03894782463392368</v>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>0.8, 0.6428571428571429, 0.88, 0.7999999999999999, 0.8571428571428571, 0.7857142857142857, 0.8275862068965518</t>
-        </is>
-      </c>
-      <c r="AB12" t="n">
-        <v>0.7990429275158339</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0.07103103165205046</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>1.0, 0.6428571428571429, 1.0, 0.75, 0.8571428571428571, 0.7857142857142857, 0.8</t>
-        </is>
-      </c>
-      <c r="AF12" t="n">
-        <v>0.8336734693877551</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0.1211409730861799</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>0.6666666666666666, 0.6428571428571429, 0.7857142857142857, 0.8571428571428571, 0.8571428571428571, 0.7857142857142857, 0.8571428571428571</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0.7789115646258503</v>
-      </c>
-      <c r="AK12" t="n">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.04003310203552246, 0.030820131301879883, 0.033125877380371094, 0.026775121688842773, 0.029233932495117188, 0.028567075729370117, 0.028364181518554688</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0.0309884888785226</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.02923393249511719</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.004140099429056395</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0.0064640045166015625, 0.0062122344970703125, 0.005652904510498047, 0.005545854568481445, 0.0057070255279541016, 0.005602836608886719, 0.005322933197021484</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>0.005786827632359096</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.005652904510498047</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.0003724363939755224</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.8301886792452831, 0.9433962264150944, 0.8867924528301887, 0.9245283018867925, 0.9245283018867925, 0.9245283018867925</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>0.9059099530797644</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.9245283018867925</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.03494195579170031</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>0.8, 0.689655172413793, 0.88, 0.7999999999999999, 0.8571428571428571, 0.8461538461538461, 0.8666666666666666</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8199455060538803</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.06051109293167232</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>1.0, 0.6666666666666666, 1.0, 0.75, 0.8571428571428571, 0.9166666666666666, 0.8125</t>
+        </is>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.8575680272108844</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.1159506672885783</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>0.6666666666666666, 0.7142857142857143, 0.7857142857142857, 0.8571428571428571, 0.8571428571428571, 0.7857142857142857, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.7993197278911566</v>
+      </c>
+      <c r="AK13" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="AL12" t="n">
-        <v>0.08414501276770733</v>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>0.9709401709401709, 0.8736263736263736, 0.9798534798534799, 0.9267399267399268, 0.9780219780219781, 0.967032967032967, 0.9780219780219781</t>
-        </is>
-      </c>
-      <c r="AN12" t="n">
-        <v>0.9534624106052678</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0.9709401709401709</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0.03680129906862034</v>
-      </c>
-      <c r="AQ12" t="inlineStr">
+      <c r="AL13" t="n">
+        <v>0.08331597764568634</v>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>0.9675213675213675, 0.8937728937728937, 0.978021978021978, 0.9322344322344323, 0.9706959706959707, 0.9743589743589743, 0.9780219780219781</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.956375370661085</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.9706959706959707</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.02949994933279096</v>
+      </c>
+      <c r="AQ13" t="inlineStr">
         <is>
           <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
         </is>
       </c>
-      <c r="AR12" t="n">
+      <c r="AR13" t="n">
         <v>1</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="AS13" t="n">
         <v>1</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AT13" t="n">
         <v>0</v>
       </c>
-      <c r="AU12" t="inlineStr">
+      <c r="AU13" t="inlineStr">
         <is>
           <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
         </is>
       </c>
-      <c r="AV12" t="n">
+      <c r="AV13" t="n">
         <v>1</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="AW13" t="n">
         <v>1</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="AX13" t="n">
         <v>0</v>
       </c>
-      <c r="AY12" t="inlineStr">
+      <c r="AY13" t="inlineStr">
         <is>
           <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
         </is>
       </c>
-      <c r="AZ12" t="n">
+      <c r="AZ13" t="n">
         <v>1</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BA13" t="n">
         <v>1</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BB13" t="n">
         <v>0</v>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BC13" t="inlineStr">
         <is>
           <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
         </is>
       </c>
-      <c r="BD12" t="n">
+      <c r="BD13" t="n">
         <v>1</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BE13" t="n">
         <v>1</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BF13" t="n">
         <v>0</v>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>1.0, 1.0, 1.0, 0.9999999999999999, 1.0, 0.9999999999999999, 1.0</t>
-        </is>
-      </c>
-      <c r="BH12" t="n">
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 0.9999999999999999</t>
+        </is>
+      </c>
+      <c r="BH13" t="n">
         <v>1</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BI13" t="n">
         <v>1</v>
       </c>
-      <c r="BJ12" t="n">
-        <v>5.934391687221749e-17</v>
+      <c r="BJ13" t="n">
+        <v>4.196248604251576e-17</v>
       </c>
     </row>
   </sheetData>

--- a/results/metrics_modelling3.xlsx
+++ b/results/metrics_modelling3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ13"/>
+  <dimension ref="A1:BJ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3400,6 +3400,4886 @@
         <v>4.196248604251576e-17</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Logit_splashing_Stk</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{'estimator': StatsModelsEstimator(model_class=&lt;class 'statsmodels.discrete.discrete_model.Logit'&gt;), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'sedimentation_Stk', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.8269230769230769</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8842592592592593</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.8586387434554974</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.8563968668407309</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.9020585317460318</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0.004244804382324219, 0.009035110473632812, 0.008500099182128906, 0.008196115493774414, 0.003726959228515625, 0.006556987762451172, 0.006724834442138672</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0.00671213013785226</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.006724834442138672</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.001920507960266922</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0.005571126937866211, 0.005261898040771484, 0.012495756149291992, 0.00462794303894043, 0.010282039642333984, 0.005293130874633789, 0.005861997604370117</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>0.007056270326886859</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.005571126937866211</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.002824655173821637</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.7924528301886793, 0.8301886792452831, 0.7924528301886793, 0.8301886792452831, 0.7169811320754716, 0.7358490566037735</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>0.8007886592792254</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.7924528301886793</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.05913194145943818</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>0.9295774647887323, 0.8358208955223881, 0.8695652173913043, 0.8405797101449276, 0.8656716417910447, 0.7761194029850745, 0.8055555555555555</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8461271268827181</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.8405797101449276</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.04563741743181095</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>0.9166666666666666, 0.875, 0.8571428571428571, 0.8285714285714286, 0.8787878787878788, 0.7878787878787878, 0.7631578947368421</t>
+        </is>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.8438865019692088</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.05006761531871717</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8, 0.8823529411764706, 0.8529411764705882, 0.8529411764705882, 0.7647058823529411, 0.8529411764705882</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.8498199279711883</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.8529411764705882</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.05273921401317838</v>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>0.9473684210526315, 0.8365079365079364, 0.9040247678018576, 0.8591331269349844, 0.9458204334365325, 0.8390092879256966, 0.8560371517027864</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.8839858750517749</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.8591331269349844</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.04459060636904717</v>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>0.7987421383647799, 0.8087774294670846, 0.8025078369905956, 0.8275862068965517, 0.8025078369905956, 0.8181818181818182, 0.8181818181818182</t>
+        </is>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.8109264407247492</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0.8087774294670846</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.009839062557250047</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>0.8446601941747572, 0.851581508515815, 0.8467153284671532, 0.8674698795180722, 0.8474576271186439, 0.8592233009708737, 0.8578431372549019</t>
+        </is>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.8535644251457454</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.851581508515815</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.007663571614375176</v>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>0.8405797101449275, 0.8495145631067961, 0.848780487804878, 0.861244019138756, 0.8454106280193237, 0.8592233009708737, 0.8663366336633663</t>
+        </is>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.8530127632641317</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0.8495145631067961</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.008671568521364954</v>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>0.848780487804878, 0.8536585365853658, 0.8446601941747572, 0.8737864077669902, 0.8495145631067961, 0.8592233009708737, 0.8495145631067961</t>
+        </is>
+      </c>
+      <c r="BD14" t="n">
+        <v>0.8541625790737797</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0.8495145631067961</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0.00905088746702265</v>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>0.8867904165767322, 0.9069319640564827, 0.8970487155253888, 0.9031488959532605, 0.8919365924907638, 0.9071226050347968, 0.9029770598848699</t>
+        </is>
+      </c>
+      <c r="BH14" t="n">
+        <v>0.8994223213603278</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0.9029770598848699</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.007205630596929708</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Logit_no_fragmentation_Stk</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{'estimator': StatsModelsEstimator(model_class=&lt;class 'statsmodels.discrete.discrete_model.Logit'&gt;), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sign_sedimentation_Re', 'sedimentation_Stk', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.7391304347826086</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.7906976744186046</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9454545454545454</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.8552188552188552</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.7088607594936709</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.7225806451612904</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.9282893972825456</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0.008211851119995117, 0.0025637149810791016, 0.002723217010498047, 0.0024650096893310547, 0.002454042434692383, 0.002524852752685547, 0.0023632049560546875</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0.003329413277762277</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.002524852752685547</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.00199593554559883</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0.008605003356933594, 0.003763914108276367, 0.0038726329803466797, 0.004273891448974609, 0.005388975143432617, 0.0037622451782226562, 0.003857851028442383</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>0.00478921617780413</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.00387263298034668</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.001647464795048527</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0.8518518518518519, 0.7735849056603774, 0.9056603773584906, 0.8301886792452831, 0.8113207547169812, 0.8679245283018868, 0.9433962264150944</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>0.854846760507138</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.05306202874688164</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>0.6666666666666667, 0.6000000000000001, 0.8275862068965518, 0.689655172413793, 0.6666666666666666, 0.7200000000000001, 0.9032258064516129</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.7248286455850417</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.689655172413793</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.09709566327453666</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.5625, 0.8, 0.6666666666666666, 0.625, 0.8181818181818182, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.7406809693574399</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.1127343541893685</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>0.5333333333333333, 0.6428571428571429, 0.8571428571428571, 0.7142857142857143, 0.7142857142857143, 0.6428571428571429, 1.0</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.7292517006802722</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.1431386924281006</v>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>0.9299145299145299, 0.8772893772893772, 0.9615384615384617, 0.9047619047619047, 0.8846153846153846, 0.9175824175824177, 0.9963369963369964</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.924577010291296</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.9175824175824177</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.0393132985264237</v>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>0.8679245283018868, 0.8808777429467085, 0.8620689655172413, 0.8652037617554859, 0.8652037617554859, 0.8840125391849529, 0.8463949843260188</t>
+        </is>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.8673837548268258</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.8652037617554859</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0.01157075644324925</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>0.746987951807229, 0.7738095238095238, 0.7380952380952379, 0.7485380116959064, 0.7455621301775148, 0.7757575757575759, 0.7065868263473054</t>
+        </is>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.7479053225271848</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.746987951807229</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.02157036310782525</v>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>0.7560975609756098, 0.7831325301204819, 0.7469879518072289, 0.7441860465116279, 0.75, 0.8, 0.7195121951219512</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.7571308977909857</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.02464426219705408</v>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>0.7380952380952381, 0.7647058823529411, 0.7294117647058823, 0.7529411764705882, 0.7411764705882353, 0.7529411764705882, 0.6941176470588235</t>
+        </is>
+      </c>
+      <c r="BD15" t="n">
+        <v>0.7390556222488996</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0.7411764705882353</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0.02125155124888153</v>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>0.9314204314204315, 0.9385118149824032, 0.9252388134741075, 0.9362493715434892, 0.9338360985419809, 0.9341377576671694, 0.9190045248868778</t>
+        </is>
+      </c>
+      <c r="BH15" t="n">
+        <v>0.9311998303594944</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0.9338360985419809</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.006311578643324333</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LogisticRegression_splashing_Stk</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{'estimator': LogisticRegression(fit_intercept=False), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'sedimentation_Stk', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.8269230769230769</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8896604938271604</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.8047138047138047</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.8602150537634409</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.8465608465608465</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.9047867063492063</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0.011903047561645508, 0.0034902095794677734, 0.0034570693969726562, 0.003618955612182617, 0.0036039352416992188, 0.003425121307373047, 0.003443002700805664</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0.004705905914306641</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.003490209579467773</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.002939083729328645</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0.01099705696105957, 0.005799770355224609, 0.005082130432128906, 0.0053479671478271484, 0.0047380924224853516, 0.004704952239990234, 0.004775285720825195</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>0.005920750754220145</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.005082130432128906</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.002104546879173433</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.7924528301886793, 0.8301886792452831, 0.7735849056603774, 0.8301886792452831, 0.7169811320754716, 0.7169811320754716</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>0.7953978236997106</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.7924528301886793</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.06296233061159889</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>0.9295774647887323, 0.8358208955223881, 0.8695652173913043, 0.8181818181818182, 0.8656716417910447, 0.7692307692307693, 0.7887323943661971</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8395400287531791</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.8358208955223881</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.05026490658495797</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>0.9166666666666666, 0.875, 0.8571428571428571, 0.84375, 0.8787878787878788, 0.8064516129032258, 0.7567567567567568</t>
+        </is>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.8477936817510551</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.04861651522073106</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8, 0.8823529411764706, 0.7941176470588235, 0.8529411764705882, 0.7352941176470589, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.8330132052821128</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.06226547173882527</v>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>0.9518796992481204, 0.8396825396825397, 0.9117647058823529, 0.8544891640866872, 0.9458204334365325, 0.8343653250773994, 0.8544891640866874</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>0.884641575928617</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.8544891640866874</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0.04685362347870711</v>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>0.7861635220125787, 0.8025078369905956, 0.7962382445141066, 0.8087774294670846, 0.8087774294670846, 0.8213166144200627, 0.8213166144200627</t>
+        </is>
+      </c>
+      <c r="AR16" t="n">
+        <v>0.806442527327368</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0.8087774294670846</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0.01185765395986192</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>0.8333333333333333, 0.845965770171149, 0.8410757946210269, 0.8523002421307506, 0.85012285012285, 0.8599508599508598, 0.85785536159601</t>
+        </is>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.8486577445608541</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.85012285012285</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0.008677682439675007</v>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>0.8374384236453202, 0.8480392156862745, 0.8472906403940886, 0.8502415458937198, 0.8606965174129353, 0.8706467661691543, 0.882051282051282</t>
+        </is>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.8566291987503966</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0.8502415458937198</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0.0142898667201938</v>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>0.8292682926829268, 0.8439024390243902, 0.8349514563106796, 0.8543689320388349, 0.8398058252427184, 0.8495145631067961, 0.8349514563106796</t>
+        </is>
+      </c>
+      <c r="BD16" t="n">
+        <v>0.8409661378167179</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0.8398058252427184</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0.00821036823573305</v>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>0.8897258795596805, 0.9068463842533163, 0.8982515680041241, 0.9060701091159035, 0.8934831171062806, 0.9097431050777558, 0.9050390927055589</t>
+        </is>
+      </c>
+      <c r="BH16" t="n">
+        <v>0.9013084651175172</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0.9050390927055589</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.007001423478172876</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>LogisticRegression_no_fragmentation_Stk</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>{'estimator': LogisticRegression(fit_intercept=False), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sign_sedimentation_Re', 'sedimentation_Stk', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.7555555555555556</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9254545454545455</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.8417508417508418</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.6568627450980392</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.8481012658227848</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.7403314917127071</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.9297410289165022</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0.004661083221435547, 0.0030999183654785156, 0.002833843231201172, 0.0029659271240234375, 0.0027751922607421875, 0.002717733383178711, 0.002774953842163086</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0.003118378775460379</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.002833843231201172</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.0006415065054109721</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0.004563808441162109, 0.004396915435791016, 0.00404810905456543, 0.003935098648071289, 0.004174947738647461, 0.0039021968841552734, 0.003983259201049805</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>0.004143476486206055</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.00404810905456543</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.0002324719302644663</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>0.8703703703703703, 0.6981132075471698, 0.9056603773584906, 0.8301886792452831, 0.8490566037735849, 0.8867924528301887, 0.8867924528301887</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>0.8467105919936108</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.8703703703703703</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.06503585108022772</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>0.7407407407407408, 0.5555555555555556, 0.8484848484848484, 0.742857142857143, 0.75, 0.7857142857142857, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.7495545693024683</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.08809520611700794</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>0.8333333333333334, 0.45454545454545453, 0.7368421052631579, 0.6190476190476191, 0.6666666666666666, 0.7857142857142857, 0.7</t>
+        </is>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.6851642092243596</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.1151729664679592</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>0.6666666666666666, 0.7142857142857143, 1.0, 0.9285714285714286, 0.8571428571428571, 0.7857142857142857, 1.0</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.8503401360544217</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.1238581051430825</v>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>0.9418803418803419, 0.8864468864468864, 0.978021978021978, 0.9102564102564104, 0.8809523809523809, 0.9413919413919414, 0.9871794871794872</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>0.9323042037327751</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.9413919413919414</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0.03873298606319705</v>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>0.839622641509434, 0.8652037617554859, 0.8338557993730408, 0.8463949843260188, 0.8463949843260188, 0.8338557993730408, 0.8432601880877743</t>
+        </is>
+      </c>
+      <c r="AR17" t="n">
+        <v>0.8440840226786877</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0.8432601880877743</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0.009903391882826382</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>0.7411167512690356, 0.7748691099476439, 0.7309644670050762, 0.743455497382199, 0.743455497382199, 0.7309644670050762, 0.7395833333333333</t>
+        </is>
+      </c>
+      <c r="AV17" t="n">
+        <v>0.7434870176177947</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.7411167512690356</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0.01372861020592027</v>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>0.6460176991150443, 0.6981132075471698, 0.6428571428571429, 0.6698113207547169, 0.6698113207547169, 0.6428571428571429, 0.6635514018691588</t>
+        </is>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.6618598908221561</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0.6635514018691588</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0.01858109084011272</v>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>0.8690476190476191, 0.8705882352941177, 0.8470588235294118, 0.8352941176470589, 0.8352941176470589, 0.8470588235294118, 0.8352941176470589</t>
+        </is>
+      </c>
+      <c r="BD17" t="n">
+        <v>0.8485194077631052</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0.8470588235294118</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0.01432994923579595</v>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>0.9285205535205534, 0.9392659627953747, 0.9242332830568125, 0.9359477124183007, 0.9320261437908496, 0.9320261437908497, 0.9220211161387631</t>
+        </is>
+      </c>
+      <c r="BH17" t="n">
+        <v>0.9305772736445006</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0.9320261437908496</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.005684785794350271</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>KNeighborsClassifier_splashing_Stk</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>{'estimator': KNeighborsClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'sedimentation_Stk', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7866666666666666</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.8478260869565217</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.8297872340425533</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8595679012345679</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.8956228956228957</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.917098445595855</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.921875</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.9194805194805195</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.9642857142857142</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.00534510612487793, 0.002683877944946289, 0.003039121627807617, 0.0028562545776367188, 0.0029916763305664062, 0.002621889114379883, 0.002547025680541992</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0.003154993057250977</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.002856254577636719</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.0009103933265869021</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.0073201656341552734, 0.0060291290283203125, 0.006006956100463867, 0.00621795654296875, 0.0057830810546875, 0.006292104721069336, 0.005763053894042969</t>
+        </is>
+      </c>
+      <c r="T18" t="n">
+        <v>0.006201778139386859</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.006029129028320312</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.0004920454066076421</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.7547169811320755, 0.8490566037735849, 0.7735849056603774, 0.8867924528301887, 0.7924528301886793, 0.7924528301886793</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>0.819706498951782</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.7924528301886793</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.05068744653618453</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.9166666666666667, 0.8, 0.8823529411764706, 0.8285714285714286, 0.9117647058823528, 0.8405797101449276, 0.8450704225352113</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8607151249967224</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.8450704225352113</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.04066336554563011</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>0.8918918918918919, 0.8666666666666667, 0.8823529411764706, 0.8055555555555556, 0.9117647058823529, 0.8285714285714286, 0.8108108108108109</t>
+        </is>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.856802000079311</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.03880484967622251</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.7428571428571429, 0.8823529411764706, 0.8529411764705882, 0.9117647058823529, 0.8529411764705882, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.8668667466986795</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.05859819151679976</v>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.861904761904762, 0.9388544891640868, 0.8962848297213624, 0.9574303405572755, 0.8839009287925697, 0.8808049535603716</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.9088624923653672</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0.8962848297213624</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.03420009022422212</v>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>0.8867924528301887, 0.896551724137931, 0.9028213166144201, 0.8934169278996865, 0.890282131661442, 0.890282131661442, 0.8934169278996865</t>
+        </is>
+      </c>
+      <c r="AR18" t="n">
+        <v>0.8933662303863995</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0.8934169278996865</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0.004807569147339707</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>0.9126213592233011, 0.9204819277108435, 0.9260143198090693, 0.9174757281553398, 0.9152542372881356, 0.9152542372881356, 0.9174757281553398</t>
+        </is>
+      </c>
+      <c r="AV18" t="n">
+        <v>0.9177967910900237</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.9174757281553398</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.004047188696489415</v>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>0.9082125603864735, 0.9095238095238095, 0.9107981220657277, 0.9174757281553398, 0.9130434782608695, 0.9130434782608695, 0.9174757281553398</t>
+        </is>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.9127961292583471</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0.9130434782608695</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0.003372766298319967</v>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>0.9170731707317074, 0.9317073170731708, 0.941747572815534, 0.9174757281553398, 0.9174757281553398, 0.9174757281553398, 0.9174757281553398</t>
+        </is>
+      </c>
+      <c r="BD18" t="n">
+        <v>0.9229187104631104</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0.9174757281553398</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0.009137366172521151</v>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>0.9589898553852795, 0.9644629867351305, 0.9647306469627975, 0.9674585445485007, 0.9602843886931867, 0.9621745854454851, 0.9656113068133001</t>
+        </is>
+      </c>
+      <c r="BH18" t="n">
+        <v>0.9633874735119542</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0.9644629867351305</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0.002800999199045301</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>KNeighborsClassifier_no_fragmentation_Stk</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>{'estimator': KNeighborsClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sign_sedimentation_Re', 'sedimentation_Stk', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.7368421052631577</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9422727272727273</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.9057239057239057</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.8591549295774648</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.7721518987341772</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.8133333333333335</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.9669898966438276</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0.002947092056274414, 0.0021181106567382812, 0.002035856246948242, 0.002084970474243164, 0.0021390914916992188, 0.002025127410888672, 0.002021312713623047</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0.002195937292916434</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.002084970474243164</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.0003096383246274558</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0.007241964340209961, 0.005403995513916016, 0.0053501129150390625, 0.005082130432128906, 0.006201744079589844, 0.005455970764160156, 0.00567173957824707</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>0.005772522517613002</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.005455970764160156</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.0006808330914867516</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0.8333333333333334, 0.7169811320754716, 0.9433962264150944, 0.8113207547169812, 0.7924528301886793, 0.8867924528301887, 0.9056603773584906</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>0.8414195867026056</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.0711525630757197</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0.6666666666666665, 0.5161290322580646, 0.888888888888889, 0.6666666666666666, 0.5217391304347826, 0.7692307692307692, 0.8275862068965518</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.6938439087203415</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.1332519430809997</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>0.75, 0.47058823529411764, 0.9230769230769231, 0.625, 0.6666666666666666, 0.8333333333333334, 0.8</t>
+        </is>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.7240950226244344</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.1390493075325232</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>0.6, 0.5714285714285714, 0.8571428571428571, 0.7142857142857143, 0.42857142857142855, 0.7142857142857143, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.6775510204081633</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0.1446534297687294</v>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>0.8547008547008548, 0.8443223443223444, 0.9734432234432235, 0.9075091575091576, 0.9148351648351648, 0.8956043956043956, 0.9587912087912088</t>
+        </is>
+      </c>
+      <c r="AN19" t="n">
+        <v>0.90702947845805</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0.9075091575091576</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0.04464498553812639</v>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>0.9088050314465409, 0.9090909090909091, 0.890282131661442, 0.890282131661442, 0.9090909090909091, 0.9090909090909091, 0.8996865203761756</t>
+        </is>
+      </c>
+      <c r="AR19" t="n">
+        <v>0.902332648916904</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0.9088050314465409</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0.008249206938947097</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>0.8284023668639053, 0.8304093567251463, 0.7976878612716763, 0.7928994082840236, 0.8198757763975155, 0.8263473053892215, 0.8095238095238095</t>
+        </is>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.8150208406364712</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.8198757763975155</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0.01408006782990952</v>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>0.8235294117647058, 0.8255813953488372, 0.7840909090909091, 0.7976190476190477, 0.868421052631579, 0.8414634146341463, 0.8192771084337349</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.8228546199318514</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0.0255866473382321</v>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>0.8333333333333334, 0.8352941176470589, 0.8117647058823529, 0.788235294117647, 0.7764705882352941, 0.8117647058823529, 0.8</t>
+        </is>
+      </c>
+      <c r="BD19" t="n">
+        <v>0.8081232492997198</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0.8117647058823529</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0.02022633971824729</v>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>0.9679741554741554, 0.9736551030668678, 0.9592257415786828, 0.9600553041729512, 0.9659627953745601, 0.9675716440422324, 0.9659627953745601</t>
+        </is>
+      </c>
+      <c r="BH19" t="n">
+        <v>0.96577250558343</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0.9659627953745601</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0.004564434495284856</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SVC_splashing_Stk</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>{'estimator': SVC(probability=True), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'sedimentation_Stk', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.8431372549019608</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.8686868686868686</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9351851851851851</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.90625</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.90625</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.90625</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.9453621031746031</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0.01099395751953125, 0.007735013961791992, 0.007822036743164062, 0.007668018341064453, 0.00790715217590332, 0.007451772689819336, 0.007354021072387695</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0.008133138929094588</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.007735013961791992</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.001181902995038058</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0.0060520172119140625, 0.005255222320556641, 0.005505084991455078, 0.0055980682373046875, 0.005476713180541992, 0.005070209503173828, 0.005224943161010742</t>
+        </is>
+      </c>
+      <c r="T20" t="n">
+        <v>0.005454608372279576</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.005476713180541992</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.0002977961823694547</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.6981132075471698, 0.9056603773584906, 0.7735849056603774, 0.8490566037735849, 0.8301886792452831, 0.8113207547169812</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>0.8276929220325447</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.8301886792452831</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.07189070131602421</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>0.9444444444444445, 0.7575757575757576, 0.9295774647887325, 0.8235294117647058, 0.8709677419354839, 0.8656716417910447, 0.8529411764705882</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8635296626815367</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.8656716417910447</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.05844141546300533</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>0.918918918918919, 0.8064516129032258, 0.8918918918918919, 0.8235294117647058, 0.9642857142857143, 0.8787878787878788, 0.8529411764705882</t>
+        </is>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.8766866578604177</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0.05073076703977463</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>0.9714285714285714, 0.7142857142857143, 0.9705882352941176, 0.8235294117647058, 0.7941176470588235, 0.8529411764705882, 0.8529411764705882</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.8542617046818727</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.8529411764705882</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0.08570587857795191</v>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>0.9924812030075187, 0.8428571428571429, 0.9442724458204333, 0.9179566563467492, 0.9659442724458205, 0.8947368421052633, 0.8498452012383901</t>
+        </is>
+      </c>
+      <c r="AN20" t="n">
+        <v>0.9154419662601884</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0.9179566563467492</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0.05254010914479783</v>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>0.8584905660377359, 0.8683385579937304, 0.8714733542319749, 0.8808777429467085, 0.8652037617554859, 0.8620689655172413, 0.877742946708464</t>
+        </is>
+      </c>
+      <c r="AR20" t="n">
+        <v>0.8691708421701916</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0.8683385579937304</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0.007528701633722329</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>0.8936170212765958, 0.8923076923076924, 0.8992628992628993, 0.9082125603864736, 0.8916876574307304, 0.8937198067632851, 0.9041769041769042</t>
+        </is>
+      </c>
+      <c r="AV20" t="n">
+        <v>0.8975692202292258</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0.8937198067632851</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0.006006247261204087</v>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>0.8669724770642202, 0.9405405405405406, 0.9104477611940298, 0.9038461538461539, 0.9267015706806283, 0.8894230769230769, 0.9154228855721394</t>
+        </is>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0.9076220665458269</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0.9104477611940298</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0.02240644231632747</v>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>0.9219512195121952, 0.848780487804878, 0.8883495145631068, 0.912621359223301, 0.8592233009708737, 0.8980582524271845, 0.8932038834951457</t>
+        </is>
+      </c>
+      <c r="BD20" t="n">
+        <v>0.8888840025709551</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0.8932038834951457</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0.024634661881573</v>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>0.9384200302180012, 0.954813863928113, 0.9437022080934788, 0.9466234212561215, 0.9415972162556921, 0.9454635277944841, 0.9530672738207749</t>
+        </is>
+      </c>
+      <c r="BH20" t="n">
+        <v>0.946241077338095</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>0.9454635277944841</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0.005477492640031644</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SVC_no_fragmentation_Stk</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>{'estimator': SVC(probability=True), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sign_sedimentation_Re', 'sedimentation_Stk', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.7368421052631577</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9490909090909092</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.8754208754208754</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.6835443037974683</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.7448275862068965</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.9517477644872837</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0.007231950759887695, 0.00641322135925293, 0.006639003753662109, 0.006249904632568359, 0.006307125091552734, 0.006089925765991211, 0.00638890266418457</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0.006474290575299945</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.00638890266418457</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.0003460449161258601</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0.005120992660522461, 0.004752159118652344, 0.004922151565551758, 0.004518032073974609, 0.004743814468383789, 0.004865169525146484, 0.004729270935058594</t>
+        </is>
+      </c>
+      <c r="T21" t="n">
+        <v>0.004807370049612862</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.004752159118652344</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.0001739368573815722</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>0.8148148148148148, 0.7924528301886793, 0.9245283018867925, 0.8490566037735849, 0.8301886792452831, 0.8679245283018868, 0.9056603773584906</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>0.8549465907956474</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.04431317962196792</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>0.5454545454545455, 0.5925925925925927, 0.8571428571428571, 0.6666666666666666, 0.6086956521739131, 0.7200000000000001, 0.8148148148148148</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.6864810184064842</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.1081435705363146</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>0.8571428571428571, 0.6153846153846154, 0.8571428571428571, 0.8, 0.7777777777777778, 0.8181818181818182, 0.8461538461538461</t>
+        </is>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.7959691102548245</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0.07878932049124372</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>0.4, 0.5714285714285714, 0.8571428571428571, 0.5714285714285714, 0.5, 0.6428571428571429, 0.7857142857142857</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.6183673469387755</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0.1472219493622158</v>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>0.9487179487179487, 0.8608058608058609, 0.9798534798534799, 0.8992673992673993, 0.9413919413919414, 0.8901098901098902, 0.978021978021978</t>
+        </is>
+      </c>
+      <c r="AN21" t="n">
+        <v>0.9283097854526426</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0.9413919413919414</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0.04238457013157627</v>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>0.8742138364779874, 0.890282131661442, 0.8589341692789969, 0.8714733542319749, 0.8808777429467085, 0.8652037617554859, 0.8463949843260188</t>
+        </is>
+      </c>
+      <c r="AR21" t="n">
+        <v>0.8696257115255163</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0.8714733542319749</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0.01336995554902775</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>0.7183098591549295, 0.7770700636942675, 0.7058823529411765, 0.7388535031847134, 0.7564102564102564, 0.7152317880794701, 0.6423357664233578</t>
+        </is>
+      </c>
+      <c r="AV21" t="n">
+        <v>0.7220133699840244</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0.7183098591549295</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0.03993997544518949</v>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>0.8793103448275862, 0.8472222222222222, 0.7941176470588235, 0.8055555555555556, 0.8309859154929577, 0.8181818181818182, 0.8461538461538461</t>
+        </is>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0.8316467642132584</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0.8309859154929577</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0.0267148822405101</v>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>0.6071428571428571, 0.7176470588235294, 0.6352941176470588, 0.6823529411764706, 0.6941176470588235, 0.6352941176470588, 0.5176470588235295</t>
+        </is>
+      </c>
+      <c r="BD21" t="n">
+        <v>0.6413565426170468</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0.6352941176470588</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0.06191330384039277</v>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>0.949989824989825, 0.9563599798893917, 0.945952740070387, 0.9524886877828055, 0.951533433886375, 0.953192559074912, 0.9450226244343891</t>
+        </is>
+      </c>
+      <c r="BH21" t="n">
+        <v>0.950648550018298</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>0.951533433886375</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>0.003730130754326795</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_splashing_Stk</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x316f68510&gt;, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'sedimentation_Stk', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.9019607843137256</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.9498456790123456</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.9990823412698413</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0.6199281215667725, 0.5437040328979492, 0.5525357723236084, 0.5781040191650391, 0.5560300350189209, 0.5743870735168457, 0.6042511463165283</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0.5755628858293805</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.5743870735168457</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.02598322825080677</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>0.00580286979675293, 0.005880117416381836, 0.005866050720214844, 0.00542902946472168, 0.0054090023040771484, 0.0057659149169921875, 0.005793094635009766</t>
+        </is>
+      </c>
+      <c r="T22" t="n">
+        <v>0.005706582750592913</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.005793094635009766</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.0001857071694844416</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.8679245283018868, 0.9056603773584906, 0.8490566037735849, 0.9245283018867925, 0.9245283018867925, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>0.8976739542777279</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.04032204548687622</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8985507246376812, 0.9275362318840579, 0.8787878787878787, 0.9411764705882353, 0.9393939393939394, 0.8857142857142858</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9204831076040431</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.9275362318840579</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.03148902275483324</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.9117647058823529, 0.9142857142857143, 0.90625, 0.9411764705882353, 0.96875, 0.8611111111111112</t>
+        </is>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.9213262782590513</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0.03216768850094733</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>1.0, 0.8857142857142857, 0.9411764705882353, 0.8529411764705882, 0.9411764705882353, 0.9117647058823529, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.9206482593037215</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0.04326328084764177</v>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>1.0, 0.9476190476190477, 0.9752321981424148, 0.9303405572755419, 0.9597523219814241, 0.958204334365325, 0.936532507739938</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>0.9582401381605273</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0.958204334365325</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0.02203023747172731</v>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>0.9937106918238994, 0.9968652037617555, 0.9937304075235109, 0.9937304075235109, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="AR22" t="n">
+        <v>0.9959667311651696</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0.00219678391174473</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 0.9975669099756691, 0.9951690821256038, 0.9951456310679612, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="AV22" t="n">
+        <v>0.9968835198892984</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0.9975669099756691</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0.001695616708174987</v>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>0.9903381642512077, 0.9951456310679612, 0.9903846153846154, 0.9951456310679612, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0.9944788865747076</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0.9951456310679612</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0.00307601708217473</v>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 0.9951456310679612, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BD22" t="n">
+        <v>0.9993065187239945</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0.001698675272387779</v>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>0.9985970213684437, 0.9992297817715019, 0.9988615860469112, 0.999033422115302, 0.9986467909614228, 1.0, 0.999033422115302</t>
+        </is>
+      </c>
+      <c r="BH22" t="n">
+        <v>0.9990574320541262</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>0.999033422115302</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>0.0004372399597870666</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_no_fragmentation_Stk</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x32006cb10&gt;, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sign_sedimentation_Re', 'sedimentation_Stk', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.9845454545454545</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.9875</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.9937106918238994</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.9999419347346418</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0.5675578117370605, 0.5764837265014648, 0.5830841064453125, 0.5477619171142578, 0.5587778091430664, 0.5518531799316406, 0.5581760406494141</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0.5633849416460309</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.5587778091430664</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.01196701924054548</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0.005454301834106445, 0.005280017852783203, 0.004628896713256836, 0.004690885543823242, 0.004688262939453125, 0.00461888313293457, 0.005111217498779297</t>
+        </is>
+      </c>
+      <c r="T23" t="n">
+        <v>0.004924637930733817</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.004690885543823242</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.0003236207775700173</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.8301886792452831, 0.9245283018867925, 0.8867924528301887, 0.9433962264150944, 0.9433962264150944, 0.9245283018867925</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>0.9059598682240192</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.9245283018867925</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.03759296384429638</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>0.7692307692307692, 0.7096774193548386, 0.8461538461538461, 0.7999999999999999, 0.88, 0.888888888888889, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.8215848258244571</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.06040375981742707</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>0.9090909090909091, 0.6470588235294118, 0.9166666666666666, 0.75, 1.0, 0.9230769230769231, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="AF23" t="n">
+        <v>0.8575765970723953</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.1112338106493786</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>0.6666666666666666, 0.7857142857142857, 0.7857142857142857, 0.8571428571428571, 0.7857142857142857, 0.8571428571428571, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.7993197278911565</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0.06345155818427765</v>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>0.976068376068376, 0.9084249084249084, 0.9945054945054945, 0.9157509157509158, 0.9890109890109889, 0.9413919413919414, 0.9871794871794872</t>
+        </is>
+      </c>
+      <c r="AN23" t="n">
+        <v>0.958904587476016</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0.976068376068376</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.03377449532269193</v>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>0.9937106918238994, 1.0, 0.9937304075235109, 1.0, 0.9937304075235109, 0.9968652037617555, 0.9937304075235109</t>
+        </is>
+      </c>
+      <c r="AR23" t="n">
+        <v>0.9959667311651696</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0.9937304075235109</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0.002762889579380034</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 0.9882352941176471, 1.0, 0.9882352941176471, 0.9941520467836257, 0.9882352941176471</t>
+        </is>
+      </c>
+      <c r="AV23" t="n">
+        <v>0.992421881033115</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0.9882352941176471</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0.005198236195245808</v>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 0.9882352941176471, 1.0, 0.9882352941176471, 0.9883720930232558, 0.9882352941176471</t>
+        </is>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0.9915961733530622</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0.9882352941176471</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0.00531556170907939</v>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 0.9882352941176471, 1.0, 0.9882352941176471, 1.0, 0.9882352941176471</t>
+        </is>
+      </c>
+      <c r="BD23" t="n">
+        <v>0.9932573029211685</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0.9882352941176471</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0.005839526916084106</v>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>0.999949124949125, 1.0, 0.9999497234791351, 1.0, 0.9999497234791352, 1.0, 0.9998994469582704</t>
+        </is>
+      </c>
+      <c r="BH23" t="n">
+        <v>0.9999640026950951</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>0.9999497234791352</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>3.522174730037765e-05</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>XGBClassifier_splashing_Stk</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>{'estimator': XGBClassifier(base_score=None, booster=None, callbacks=None,
+              colsample_bylevel=None, colsample_bynode=None,
+              colsample_bytree=None, device=None, early_stopping_rounds=None,
+              enable_categorical=False, eval_metric=None, feature_types=None,
+              gamma=None, grow_policy=None, importance_type=None,
+              interaction_constraints=None, learning_rate=None, max_bin=None,
+              max_cat_threshold=None, max_cat_to_onehot=None,
+              max_delta_step=None, max_depth=None, max_leaves=None,
+              min_child_weight=None, missing=nan, monotone_constraints=None,
+              multi_strategy=None, n_estimators=None, n_jobs=None,
+              num_parallel_tree=None, random_state=None, ...), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'sedimentation_Stk', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.8933333333333333</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.8846153846153846</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.9199999999999999</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9332561728395062</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.9999751984126984</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0.0450739860534668, 0.03595590591430664, 0.03643202781677246, 0.03467202186584473, 0.031442880630493164, 0.0366971492767334, 0.037554025650024414</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0.03683257102966309</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.03643202781677246</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.003837883890394383</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>0.006886959075927734, 0.0059320926666259766, 0.006489276885986328, 0.005816936492919922, 0.005574941635131836, 0.005979061126708984, 0.005656003952026367</t>
+        </is>
+      </c>
+      <c r="T24" t="n">
+        <v>0.006047895976475307</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.005932092666625977</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.0004387645131705288</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.8490566037735849, 0.9056603773584906, 0.8301886792452831, 0.9433962264150944, 0.8301886792452831, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>0.8815014475391834</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.05130014228769739</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8857142857142857, 0.9253731343283583, 0.8695652173913043, 0.9565217391304348, 0.8524590163934426, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.9063155080509312</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.04221928175201459</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.8857142857142857, 0.9393939393939394, 0.8571428571428571, 0.9428571428571428, 0.9629629629629629, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="AF24" t="n">
+        <v>0.9166242964562292</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.9393939393939394</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0.0375721138836347</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>1.0, 0.8857142857142857, 0.9117647058823529, 0.8823529411764706, 0.9705882352941176, 0.7647058823529411, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.8996398559423768</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0.06995061177413654</v>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>0.9879699248120302, 0.9301587301587302, 0.955108359133127, 0.9117647058823528, 0.9473684210526316, 0.9388544891640866, 0.9287925696594428</t>
+        </is>
+      </c>
+      <c r="AN24" t="n">
+        <v>0.9428595999803431</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0.9388544891640866</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0.02251167875492806</v>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="AR24" t="n">
+        <v>0.9977594515655674</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0.001417051170840857</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="AV24" t="n">
+        <v>0.9982688114216364</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0.001094907038779773</v>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0.9965459942243395</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0.002184519446236978</v>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BD24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="inlineStr">
+        <is>
+          <t>0.9999784157133607, 1.0, 0.9999785204914512, 0.9999785204914511, 0.9999785204914512, 1.0, 0.9999785204914511</t>
+        </is>
+      </c>
+      <c r="BH24" t="n">
+        <v>0.999984642525595</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>0.9999785204914512</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>9.712984233463661e-06</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>XGBClassifier_no_fragmentation_Stk</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>{'estimator': XGBClassifier(base_score=None, booster=None, callbacks=None,
+              colsample_bylevel=None, colsample_bynode=None,
+              colsample_bytree=None, device=None, early_stopping_rounds=None,
+              enable_categorical=False, eval_metric=None, feature_types=None,
+              gamma=None, grow_policy=None, importance_type=None,
+              interaction_constraints=None, learning_rate=None, max_bin=None,
+              max_cat_threshold=None, max_cat_to_onehot=None,
+              max_delta_step=None, max_depth=None, max_leaves=None,
+              min_child_weight=None, missing=nan, monotone_constraints=None,
+              multi_strategy=None, n_estimators=None, n_jobs=None,
+              num_parallel_tree=None, random_state=None, ...), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sign_sedimentation_Re', 'sedimentation_Stk', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.8717948717948718</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.9999999999999999</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0.04730534553527832, 0.03271007537841797, 0.028319120407104492, 0.027498960494995117, 0.028037071228027344, 0.029113054275512695, 0.04513692855834961</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0.03401722226824079</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.0291130542755127</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.007898461807384205</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>0.005719661712646484, 0.005619049072265625, 0.0052111148834228516, 0.004999876022338867, 0.005113124847412109, 0.004996061325073242, 0.004838228225708008</t>
+        </is>
+      </c>
+      <c r="T25" t="n">
+        <v>0.005213873726981027</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.005113124847412109</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.0003081032520498362</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.7924528301886793, 0.9433962264150944, 0.8301886792452831, 0.9245283018867925, 0.9245283018867925, 0.9245283018867925</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>0.8897873614854747</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.9245283018867925</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.05280899595913958</v>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>0.7692307692307692, 0.5925925925925927, 0.88, 0.7096774193548386, 0.8461538461538461, 0.8461538461538461, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.7858501900898213</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.09610031075657319</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>0.9090909090909091, 0.6153846153846154, 1.0, 0.6470588235294118, 0.9166666666666666, 0.9166666666666666, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="AF25" t="n">
+        <v>0.8374300769258752</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.136305918473907</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>0.6666666666666666, 0.5714285714285714, 0.7857142857142857, 0.7857142857142857, 0.7857142857142857, 0.7857142857142857, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.748299319727891</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0.08895712129674845</v>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>0.9641025641025641, 0.8901098901098901, 0.978021978021978, 0.9120879120879122, 0.9743589743589743, 0.9413919413919415, 0.989010989010989</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>0.949869178440607</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0.9641025641025641</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0.03422083953113136</v>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="AR25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="AV25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BD25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BH25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>LogisticRegression_splashing_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>{'estimator': LogisticRegression(fit_intercept=False), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.8269230769230769</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8858024691358024</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.8013468013468014</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.8674033149171271</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.8177083333333334</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.8418230563002681</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.9038442460317461</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0.013457775115966797, 0.003464221954345703, 0.0033440589904785156, 0.0033609867095947266, 0.0071980953216552734, 0.0033440589904785156, 0.0034418106079101562</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0.005373001098632812</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.003441810607910156</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.003552642646690151</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>0.005399227142333984, 0.006783008575439453, 0.0054471492767333984, 0.005080223083496094, 0.0052509307861328125, 0.004643917083740234, 0.004721879959106445</t>
+        </is>
+      </c>
+      <c r="T26" t="n">
+        <v>0.005332333700997489</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.005250930786132812</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.0006588813407340738</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.7924528301886793, 0.8490566037735849, 0.7924528301886793, 0.8113207547169812, 0.7169811320754716, 0.7169811320754716</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>0.8007387441349706</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.7924528301886793</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.06791424517985484</v>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8358208955223881, 0.8823529411764706, 0.8358208955223881, 0.8484848484848485, 0.7692307692307693, 0.782608695652174</t>
+        </is>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.8424537412065973</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.8358208955223881</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.05443237726411872</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.875, 0.8823529411764706, 0.8484848484848485, 0.875, 0.8064516129032258, 0.7714285714285715</t>
+        </is>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.8573678738357513</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0.05156326200329429</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8, 0.8823529411764706, 0.8235294117647058, 0.8235294117647058, 0.7352941176470589, 0.7941176470588235</t>
+        </is>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0.8288115246098439</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0.06176934313175476</v>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>0.9503759398496241, 0.8365079365079365, 0.913312693498452, 0.84984520123839, 0.9380804953560372, 0.8343653250773995, 0.8591331269349846</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>0.8830886740661177</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0.8591331269349846</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0.0458068841803581</v>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>0.8018867924528302, 0.8025078369905956, 0.7962382445141066, 0.8087774294670846, 0.8087774294670846, 0.8244514106583072, 0.8213166144200627</t>
+        </is>
+      </c>
+      <c r="AR26" t="n">
+        <v>0.8091365368528675</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0.8087774294670846</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0.00960670871567345</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>0.845965770171149, 0.8444444444444444, 0.8395061728395062, 0.851581508515815, 0.85012285012285, 0.8606965174129354, 0.8585607940446649</t>
+        </is>
+      </c>
+      <c r="AV26" t="n">
+        <v>0.8501254367930523</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0.85012285012285</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0.007044434646001391</v>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>0.8480392156862745, 0.855, 0.8542713567839196, 0.8536585365853658, 0.8606965174129353, 0.8826530612244898, 0.8781725888324873</t>
+        </is>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0.8617844680750675</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0.0123212411989612</v>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>0.8439024390243902, 0.8341463414634146, 0.8252427184466019, 0.8495145631067961, 0.8398058252427184, 0.8398058252427184, 0.8398058252427184</t>
+        </is>
+      </c>
+      <c r="BD26" t="n">
+        <v>0.8388890768241941</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0.8398058252427184</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0.007063716928812917</v>
+      </c>
+      <c r="BG26" t="inlineStr">
+        <is>
+          <t>0.8894668681200086, 0.9051775780915704, 0.8973064696279749, 0.9051250107397543, 0.89219434659335, 0.9097431050777558, 0.9041369533465075</t>
+        </is>
+      </c>
+      <c r="BH26" t="n">
+        <v>0.9004500473709889</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0.9041369533465075</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>0.006998243955679154</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>LogisticRegression_no_fragmentation_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>{'estimator': LogisticRegression(fit_intercept=False), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.7555555555555556</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.9290909090909091</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.8451178451178452</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.6633663366336634</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.8481012658227848</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.7444444444444445</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.9313087910811753</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0.004318952560424805, 0.0029261112213134766, 0.0027930736541748047, 0.0027098655700683594, 0.0028879642486572266, 0.0027778148651123047, 0.0028731822967529297</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0.003040994916643415</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.00287318229675293</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.000526216793938707</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>0.004152059555053711, 0.004306793212890625, 0.004371166229248047, 0.0038979053497314453, 0.0039348602294921875, 0.0041961669921875, 0.003973722457885742</t>
+        </is>
+      </c>
+      <c r="T27" t="n">
+        <v>0.004118953432355609</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.004152059555053711</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.00017312160274854</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>0.8703703703703703, 0.7169811320754716, 0.8867924528301887, 0.8301886792452831, 0.8679245283018868, 0.8867924528301887, 0.8867924528301887</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>0.8494060097833683</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.8703703703703703</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.05717308600454714</v>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>0.7586206896551724, 0.5714285714285714, 0.8125000000000001, 0.742857142857143, 0.7741935483870968, 0.7857142857142857, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.7526919499724249</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.7741935483870968</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.07850025297489785</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>0.7857142857142857, 0.47619047619047616, 0.7222222222222222, 0.6190476190476191, 0.7058823529411765, 0.7857142857142857, 0.7</t>
+        </is>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.684967320261438</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0.1002029565407049</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.7142857142857143, 0.9285714285714286, 0.9285714285714286, 0.8571428571428571, 0.7857142857142857, 1.0</t>
+        </is>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0.8496598639455781</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0.1007537881990401</v>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>0.9401709401709402, 0.8772893772893773, 0.9688644688644689, 0.9175824175824177, 0.891941391941392, 0.9432234432234433, 0.9890109890109889</t>
+        </is>
+      </c>
+      <c r="AN27" t="n">
+        <v>0.932583289726147</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0.9401709401709402</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0.03704322048085008</v>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>0.8427672955974843, 0.8526645768025078, 0.8338557993730408, 0.8463949843260188, 0.8432601880877743, 0.8401253918495298, 0.8432601880877743</t>
+        </is>
+      </c>
+      <c r="AR27" t="n">
+        <v>0.8431897748748759</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0.8432601880877743</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0.005301579090494343</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>0.7448979591836734, 0.7614213197969542, 0.736318407960199, 0.751269035532995, 0.7368421052631577, 0.7384615384615385, 0.7395833333333333</t>
+        </is>
+      </c>
+      <c r="AV27" t="n">
+        <v>0.7441133856474071</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0.7395833333333333</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0.008598018140371306</v>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>0.6517857142857143, 0.6696428571428571, 0.6379310344827587, 0.6607142857142857, 0.6666666666666666, 0.6545454545454545, 0.6635514018691588</t>
+        </is>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0.6578339163866994</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0.6607142857142857</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0.01001409125050462</v>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>0.8690476190476191, 0.8823529411764706, 0.8705882352941177, 0.8705882352941177, 0.8235294117647058, 0.8470588235294118, 0.8352941176470589</t>
+        </is>
+      </c>
+      <c r="BD27" t="n">
+        <v>0.856922769107643</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0.8690476190476191</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0.02016860314842748</v>
+      </c>
+      <c r="BG27" t="inlineStr">
+        <is>
+          <t>0.9308099308099308, 0.9422825540472599, 0.9276520864756159, 0.9362996480643538, 0.9334841628959275, 0.9351935646053293, 0.9222222222222223</t>
+        </is>
+      </c>
+      <c r="BH27" t="n">
+        <v>0.93256345273152</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>0.9334841628959275</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>0.005979998658646051</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>KNeighborsClassifier_splashing_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>{'estimator': KNeighborsClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.8979591836734694</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.8753858024691358</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.9023569023569024</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.9179487179487179</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.9322916666666666</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.9250645994832041</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.9650545634920635</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0.00451207160949707, 0.006139039993286133, 0.0027091503143310547, 0.0027008056640625, 0.002794981002807617, 0.0026471614837646484, 0.0025568008422851562</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0.003437144415719168</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.002709150314331055</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.00127275460780346</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>0.00745081901550293, 0.008826017379760742, 0.0059812068939208984, 0.005836963653564453, 0.006107807159423828, 0.0061337947845458984, 0.006054878234863281</t>
+        </is>
+      </c>
+      <c r="T28" t="n">
+        <v>0.006627355303083148</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.006107807159423828</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.001027875506084579</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.7547169811320755, 0.8490566037735849, 0.7924528301886793, 0.8867924528301887, 0.7735849056603774, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>0.8277927523210543</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.05020739045150253</v>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>0.9189189189189189, 0.8, 0.8823529411764706, 0.8253968253968255, 0.9142857142857143, 0.806451612903226, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.861394136265375</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.04639718261514306</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>0.8717948717948718, 0.8666666666666667, 0.8823529411764706, 0.896551724137931, 0.8888888888888888, 0.8928571428571429, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="AF28" t="n">
+        <v>0.8830664538140631</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0.01006145855735717</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>0.9714285714285714, 0.7428571428571429, 0.8823529411764706, 0.7647058823529411, 0.9411764705882353, 0.7352941176470589, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0.8457382953181273</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0.0901874676551734</v>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>0.9105263157894736, 0.8523809523809524, 0.9458204334365324, 0.9256965944272446, 0.958204334365325, 0.890092879256966, 0.8722910216718267</t>
+        </is>
+      </c>
+      <c r="AN28" t="n">
+        <v>0.9078589330469029</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0.9105263157894736</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0.03577618394883013</v>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>0.9088050314465409, 0.8840125391849529, 0.896551724137931, 0.9090909090909091, 0.8840125391849529, 0.8840125391849529, 0.9059561128526645</t>
+        </is>
+      </c>
+      <c r="AR28" t="n">
+        <v>0.896063056440415</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0.896551724137931</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0.01112165925061054</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>0.9294403892944039, 0.9090909090909092, 0.9212410501193318, 0.9301204819277109, 0.9099756690997567, 0.9099756690997567, 0.9271844660194175</t>
+        </is>
+      </c>
+      <c r="AV28" t="n">
+        <v>0.919575519235898</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0.9212410501193318</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0.008971568256650582</v>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>0.9271844660194175, 0.9158415841584159, 0.9061032863849765, 0.9234449760765551, 0.9121951219512195, 0.9121951219512195, 0.9271844660194175</t>
+        </is>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0.917735574651603</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0.9158415841584159</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0.007666727028896789</v>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>0.9317073170731708, 0.9024390243902439, 0.9368932038834952, 0.9368932038834952, 0.9077669902912622, 0.9077669902912622, 0.9271844660194175</t>
+        </is>
+      </c>
+      <c r="BD28" t="n">
+        <v>0.921521599404621</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0.9271844660194175</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0.0138919944270699</v>
+      </c>
+      <c r="BG28" t="inlineStr">
+        <is>
+          <t>0.9636088927260954, 0.962173727000428, 0.964923962539737, 0.9693917003178967, 0.9582008763639488, 0.9661053355099235, 0.9687687945699802</t>
+        </is>
+      </c>
+      <c r="BH28" t="n">
+        <v>0.9647390412897157</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>0.964923962539737</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>0.003593501616458011</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>KNeighborsClassifier_no_fragmentation_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>{'estimator': KNeighborsClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.8292682926829269</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.810126582278481</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.8258064516129032</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.9639995354778772</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0.002920866012573242, 0.002074718475341797, 0.0021729469299316406, 0.002079010009765625, 0.0021131038665771484, 0.002335071563720703, 0.0023391246795654297</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>0.002290691648210798</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.002172946929931641</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.0002773058732180589</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>0.0064411163330078125, 0.005961179733276367, 0.005251884460449219, 0.005357980728149414, 0.005299806594848633, 0.00522613525390625, 0.005182027816772461</t>
+        </is>
+      </c>
+      <c r="T29" t="n">
+        <v>0.005531447274344308</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.005299806594848633</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.0004455142427837516</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.7547169811320755, 0.9433962264150944, 0.8113207547169812, 0.8113207547169812, 0.8490566037735849, 0.9245283018867925</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>0.8600379355096336</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.06698471018043896</v>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>0.8749999999999999, 0.5517241379310344, 0.888888888888889, 0.6428571428571429, 0.5833333333333334, 0.7142857142857143, 0.8750000000000001</t>
+        </is>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.7330127453280163</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.1354180579884486</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>0.8235294117647058, 0.5333333333333333, 0.9230769230769231, 0.6428571428571429, 0.7, 0.7142857142857143, 0.7777777777777778</t>
+        </is>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.7306943290136567</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.1169397797367399</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>0.9333333333333333, 0.5714285714285714, 0.8571428571428571, 0.6428571428571429, 0.5, 0.7142857142857143, 1.0</t>
+        </is>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.745578231292517</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0.1750904647078131</v>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>0.970940170940171, 0.7866300366300367, 0.9322344322344321, 0.8974358974358976, 0.8873626373626374, 0.8965201465201464, 0.967032967032967</t>
+        </is>
+      </c>
+      <c r="AN29" t="n">
+        <v>0.9054508983080414</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0.8974358974358976</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0.05780278617645025</v>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>0.8930817610062893, 0.9122257053291536, 0.8996865203761756, 0.9028213166144201, 0.8934169278996865, 0.9028213166144201, 0.9153605015673981</t>
+        </is>
+      </c>
+      <c r="AR29" t="n">
+        <v>0.902773435629649</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0.9028213166144201</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0.007917305243749024</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>0.8045977011494253, 0.8390804597701149, 0.8181818181818181, 0.8187134502923977, 0.8023255813953488, 0.8208092485549133, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="AV29" t="n">
+        <v>0.820830503214559</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0.8187134502923977</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0.01415783587470498</v>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>0.7777777777777778, 0.8202247191011236, 0.7912087912087912, 0.813953488372093, 0.7931034482758621, 0.8068181818181818, 0.8372093023255814</t>
+        </is>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0.8057565298399157</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0.8068181818181818</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0.01859904133833272</v>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>0.8333333333333334, 0.8588235294117647, 0.8470588235294118, 0.8235294117647058, 0.8117647058823529, 0.8352941176470589, 0.8470588235294118</t>
+        </is>
+      </c>
+      <c r="BD29" t="n">
+        <v>0.8366946778711483</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0.8352941176470589</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0.01469987872650075</v>
+      </c>
+      <c r="BG29" t="inlineStr">
+        <is>
+          <t>0.9665750915750917, 0.9727752639517344, 0.962242332830568, 0.9635746606334843, 0.9669683257918552, 0.9673956762192055, 0.9699849170437406</t>
+        </is>
+      </c>
+      <c r="BH29" t="n">
+        <v>0.9670737525779544</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>0.9669683257918552</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>0.00331515533222134</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SVC_splashing_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>{'estimator': SVC(probability=True), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.8431372549019608</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.8686868686868686</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9274691358024691</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.8922558922558923</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.9210526315789473</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.9114583333333334</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.9162303664921465</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.9509672619047618</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0.009139060974121094, 0.007838964462280273, 0.007873058319091797, 0.00767827033996582, 0.007742166519165039, 0.007651090621948242, 0.007400989532470703</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>0.007903371538434709</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.007742166519165039</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.0005243617198518821</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>0.005811929702758789, 0.0057179927825927734, 0.005391836166381836, 0.005655765533447266, 0.005440711975097656, 0.005650043487548828, 0.005573749542236328</t>
+        </is>
+      </c>
+      <c r="T30" t="n">
+        <v>0.005606004170009068</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.005650043487548828</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.0001381470405330805</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.7358490566037735, 0.9245283018867925, 0.7358490566037735, 0.8867924528301887, 0.8490566037735849, 0.8301886792452831</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>0.838524508335829</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.07145049096409614</v>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>0.9315068493150684, 0.7941176470588236, 0.9428571428571428, 0.787878787878788, 0.9117647058823528, 0.8787878787878787, 0.8695652173913043</t>
+        </is>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.8737826041673371</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0.8787878787878787</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.05771213117467276</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8181818181818182, 0.9166666666666666, 0.8125, 0.9117647058823529, 0.90625, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.8738918414255654</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0.0412287995289299</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>0.9714285714285714, 0.7714285714285715, 0.9705882352941176, 0.7647058823529411, 0.9117647058823529, 0.8529411764705882, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.8750300120048019</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0.07857635781408312</v>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>0.9849624060150376, 0.8571428571428572, 0.9442724458204335, 0.9071207430340558, 0.9597523219814241, 0.9133126934984521, 0.8560371517027864</t>
+        </is>
+      </c>
+      <c r="AN30" t="n">
+        <v>0.9175143741707208</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0.9133126934984521</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0.04566825448295116</v>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>0.8584905660377359, 0.8934169278996865, 0.8746081504702194, 0.8840125391849529, 0.8808777429467085, 0.8746081504702194, 0.890282131661442</t>
+        </is>
+      </c>
+      <c r="AR30" t="n">
+        <v>0.8794708869529949</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0.8808777429467085</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0.01083280201797767</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>0.8915662650602411, 0.9154228855721392, 0.9033816425120774, 0.9104116222760291, 0.905940594059406, 0.9033816425120774, 0.914004914004914</t>
+        </is>
+      </c>
+      <c r="AV30" t="n">
+        <v>0.9063013665709835</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0.905940594059406</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0.007499941946569862</v>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>0.8809523809523809, 0.934010152284264, 0.8990384615384616, 0.9082125603864735, 0.9242424242424242, 0.8990384615384616, 0.9253731343283582</t>
+        </is>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0.9101239393244034</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0.9082125603864735</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0.01733217304401899</v>
+      </c>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>0.9024390243902439, 0.8975609756097561, 0.9077669902912622, 0.912621359223301, 0.8883495145631068, 0.9077669902912622, 0.9029126213592233</t>
+        </is>
+      </c>
+      <c r="BD30" t="n">
+        <v>0.9027739251040222</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0.9029126213592233</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0.007389212365561095</v>
+      </c>
+      <c r="BG30" t="inlineStr">
+        <is>
+          <t>0.9411396503345565, 0.9603765511339324, 0.9497164704871552, 0.9514348311710629, 0.947267806512587, 0.9502104991837786, 0.9571698599536043</t>
+        </is>
+      </c>
+      <c r="BH30" t="n">
+        <v>0.9510450955395253</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>0.9502104991837786</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>0.005850375436174139</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SVC_no_fragmentation_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>{'estimator': SVC(probability=True), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.6842105263157895</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9600000000000001</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.8720538720538721</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.8059701492537313</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.6835443037974683</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.7397260273972602</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.9543026361630472</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0.007559061050415039, 0.0065441131591796875, 0.006853818893432617, 0.006147861480712891, 0.006257057189941406, 0.0061380863189697266, 0.006921291351318359</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>0.006631612777709961</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.006544113159179688</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.0004809189546825349</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>0.00507807731628418, 0.004826784133911133, 0.004841327667236328, 0.004404783248901367, 0.004908084869384766, 0.004684925079345703, 0.004890918731689453</t>
+        </is>
+      </c>
+      <c r="T31" t="n">
+        <v>0.004804985863821847</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.004841327667236328</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.0001960194670902867</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>0.8518518518518519, 0.7358490566037735, 0.9056603773584906, 0.8490566037735849, 0.8301886792452831, 0.8490566037735849, 0.9245283018867925</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
+        <v>0.849455924927623</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.05616125879043537</v>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>0.6666666666666667, 0.5333333333333333, 0.8148148148148148, 0.6923076923076924, 0.6086956521739131, 0.6923076923076924, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.6950383869638529</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.6923076923076924</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.1035427531027226</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.5, 0.8461538461538461, 0.75, 0.7777777777777778, 0.75, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.7671376242804814</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.1202562711166219</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>0.5333333333333333, 0.5714285714285714, 0.7857142857142857, 0.6428571428571429, 0.5, 0.6428571428571429, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0.6476190476190476</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0.1216983797214332</v>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>0.9572649572649573, 0.8553113553113554, 0.9816849816849818, 0.9120879120879121, 0.9304029304029304, 0.9120879120879122, 0.9798534798534799</t>
+        </is>
+      </c>
+      <c r="AN31" t="n">
+        <v>0.9326705040990756</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0.9304029304029304</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0.04152521664175509</v>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>0.8742138364779874, 0.890282131661442, 0.877742946708464, 0.8746081504702194, 0.877742946708464, 0.8652037617554859, 0.8526645768025078</t>
+        </is>
+      </c>
+      <c r="AR31" t="n">
+        <v>0.8732083357977958</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.8746081504702194</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0.01083466427330128</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>0.7368421052631577, 0.787878787878788, 0.7664670658682634, 0.7468354430379747, 0.751592356687898, 0.7261146496815285, 0.6758620689655171</t>
+        </is>
+      </c>
+      <c r="AV31" t="n">
+        <v>0.7416560681975897</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0.7468354430379747</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0.03266986692966924</v>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>0.8235294117647058, 0.8125, 0.7804878048780488, 0.8082191780821918, 0.8194444444444444, 0.7916666666666666, 0.8166666666666667</t>
+        </is>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0.8075020246432463</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0.01458722479508863</v>
+      </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>0.6666666666666666, 0.7647058823529411, 0.7529411764705882, 0.6941176470588235, 0.6941176470588235, 0.6705882352941176, 0.5764705882352941</t>
+        </is>
+      </c>
+      <c r="BD31" t="n">
+        <v>0.688515406162465</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0.6941176470588235</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0.0577818939081381</v>
+      </c>
+      <c r="BG31" t="inlineStr">
+        <is>
+          <t>0.953958078958079, 0.960633484162896, 0.9481146304675717, 0.9543991955756662, 0.9564605329311212, 0.9564605329311212, 0.948868778280543</t>
+        </is>
+      </c>
+      <c r="BH31" t="n">
+        <v>0.9541278904724283</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>0.9543991955756662</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>0.004090497529779754</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_splashing_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x31c795610&gt;, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.9019607843137256</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.9993799603174603</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0.6300218105316162, 0.6198470592498779, 0.5708799362182617, 0.5742392539978027, 0.5723519325256348, 0.6038317680358887, 0.5797450542449951</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>0.5929881164005825</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.5797450542449951</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.02284107936313209</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>0.005659818649291992, 0.0055158138275146484, 0.005817890167236328, 0.005957841873168945, 0.005384922027587891, 0.005441904067993164, 0.005399942398071289</t>
+        </is>
+      </c>
+      <c r="T32" t="n">
+        <v>0.00559687614440918</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.005515813827514648</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.0002061206672660462</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.8679245283018868, 0.9056603773584906, 0.8301886792452831, 0.9433962264150944, 0.9056603773584906, 0.8679245283018868</t>
+        </is>
+      </c>
+      <c r="X32" t="n">
+        <v>0.8976739542777279</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0.04277025964339304</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8985507246376812, 0.9275362318840579, 0.8656716417910447, 0.9565217391304348, 0.9253731343283583, 0.9014084507042254</t>
+        </is>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.9210405920997179</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0.9253731343283583</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.03358650045032965</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.9117647058823529, 0.9142857142857143, 0.8787878787878788, 0.9428571428571428, 0.9393939393939394, 0.8648648648648649</t>
+        </is>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.9139857417168341</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0.02965844145929741</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>1.0, 0.8857142857142857, 0.9411764705882353, 0.8529411764705882, 0.9705882352941176, 0.9117647058823529, 0.9411764705882353</t>
+        </is>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.9290516206482593</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0.04632609353460133</v>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>0.9984962406015038, 0.9380952380952381, 0.976780185758514, 0.9473684210526316, 0.955108359133127, 0.9489164086687306, 0.9427244582043344</t>
+        </is>
+      </c>
+      <c r="AN32" t="n">
+        <v>0.9582127587877256</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0.9489164086687306</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0.02009182288819399</v>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="AR32" t="n">
+        <v>0.9973116235315324</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0.001097530367727006</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 0.9975669099756691, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="AV32" t="n">
+        <v>0.9979212271324464</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0.0008486710488706931</v>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 0.9951456310679612, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0.9958525129483339</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0.001693235431574141</v>
+      </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BD32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="inlineStr">
+        <is>
+          <t>0.9993308871141808, 0.9998716302952503, 0.9994630122862789, 0.9995059713033766, 0.9992911762178881, 1.0, 0.9995489303204742</t>
+        </is>
+      </c>
+      <c r="BH32" t="n">
+        <v>0.999573086791064</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>0.9995059713033766</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>0.0002469013067630454</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_no_fragmentation_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x31c709410&gt;, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.9268292682926829</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.9881818181818182</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.9873417721518988</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.9936305732484078</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.9999419347346418</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0.6124680042266846, 0.5860397815704346, 0.5696671009063721, 0.5573601722717285, 0.5754611492156982, 0.5673670768737793, 0.5653929710388184</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>0.5762508937290737</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.5696671009063721</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.01692482321722631</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>0.005569934844970703, 0.005295991897583008, 0.005210161209106445, 0.0047948360443115234, 0.005314826965332031, 0.00512385368347168, 0.004667043685913086</t>
+        </is>
+      </c>
+      <c r="T33" t="n">
+        <v>0.005139521190098354</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.005210161209106445</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.0002897657763899741</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.8490566037735849, 0.9433962264150944, 0.8867924528301887, 0.9433962264150944, 0.9245283018867925, 0.9622641509433962</t>
+        </is>
+      </c>
+      <c r="X33" t="n">
+        <v>0.9166916242387941</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0.9245283018867925</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.03609351621237702</v>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>0.8148148148148148, 0.75, 0.888888888888889, 0.7999999999999999, 0.88, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.8456311413454271</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.05636770130116441</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>0.9166666666666666, 0.6666666666666666, 0.9230769230769231, 0.75, 1.0, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.8631606488749346</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0.1075093771898189</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.8571428571428571, 0.8571428571428571, 0.8571428571428571, 0.7857142857142857, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.8394557823129251</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0.05774704878831079</v>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>0.982905982905983, 0.9175824175824175, 0.9926739926739927, 0.9267399267399268, 0.989010989010989, 0.9175824175824175, 0.9816849816849816</t>
+        </is>
+      </c>
+      <c r="AN33" t="n">
+        <v>0.9583115297401011</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0.9816849816849816</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0.03292616916475692</v>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>0.9937106918238994, 1.0, 0.9968652037617555, 0.9937304075235109, 0.9937304075235109, 0.9968652037617555, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="AR33" t="n">
+        <v>0.9959667311651696</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0.00219678391174473</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 0.9940828402366864, 0.988095238095238, 0.9882352941176471, 0.9941520467836257, 0.9940828402366864</t>
+        </is>
+      </c>
+      <c r="AV33" t="n">
+        <v>0.9923919282235888</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0.9940828402366864</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0.004155888070493598</v>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 1.0, 1.0, 0.9882352941176471, 0.9883720930232558, 1.0</t>
+        </is>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0.9949575178908773</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0.005823026954887154</v>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 0.9882352941176471, 0.9764705882352941, 0.9882352941176471, 1.0, 0.9882352941176471</t>
+        </is>
+      </c>
+      <c r="BD33" t="n">
+        <v>0.9898959583833534</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0.9882352941176471</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0.007520827163479012</v>
+      </c>
+      <c r="BG33" t="inlineStr">
+        <is>
+          <t>0.9998982498982498, 0.9999999999999999, 0.9999497234791352, 1.0, 0.9999497234791352, 0.9999999999999999, 0.9999497234791352</t>
+        </is>
+      </c>
+      <c r="BH33" t="n">
+        <v>0.9999639171908079</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>0.9999497234791352</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>3.550147888793166e-05</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>XGBClassifier_splashing_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>{'estimator': XGBClassifier(base_score=None, booster=None, callbacks=None,
+              colsample_bylevel=None, colsample_bynode=None,
+              colsample_bytree=None, device=None, early_stopping_rounds=None,
+              enable_categorical=False, eval_metric=None, feature_types=None,
+              gamma=None, grow_policy=None, importance_type=None,
+              interaction_constraints=None, learning_rate=None, max_bin=None,
+              max_cat_threshold=None, max_cat_to_onehot=None,
+              max_delta_step=None, max_depth=None, max_leaves=None,
+              min_child_weight=None, missing=nan, monotone_constraints=None,
+              multi_strategy=None, n_estimators=None, n_jobs=None,
+              num_parallel_tree=None, random_state=None, ...), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.910891089108911</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.9402006172839507</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.9999751984126984</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0.0447840690612793, 0.03411102294921875, 0.03708696365356445, 0.057431936264038086, 0.03099799156188965, 0.03522491455078125, 0.03696894645690918</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>0.03951512064252581</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.03696894645690918</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.008292032981517006</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>0.006973981857299805, 0.005768299102783203, 0.0055272579193115234, 0.006621122360229492, 0.0056688785552978516, 0.005767107009887695, 0.006066083908081055</t>
+        </is>
+      </c>
+      <c r="T34" t="n">
+        <v>0.006056104387555804</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.005768299102783203</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.0005011155766490603</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.8301886792452831, 0.8867924528301887, 0.8679245283018868, 0.9245283018867925, 0.8679245283018868, 0.8679245283018868</t>
+        </is>
+      </c>
+      <c r="X34" t="n">
+        <v>0.8868922831186984</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.04052839228310491</v>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8695652173913043, 0.9117647058823528, 0.8985507246376812, 0.9411764705882353, 0.888888888888889, 0.8955223880597014</t>
+        </is>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.9110986596671981</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.8985507246376812</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.03220377059286659</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.8823529411764706, 0.9117647058823529, 0.8857142857142857, 0.9411764705882353, 0.9655172413793104, 0.9090909090909091</t>
+        </is>
+      </c>
+      <c r="AF34" t="n">
+        <v>0.9202232142539301</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0.02921043131675378</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>1.0, 0.8571428571428571, 0.9117647058823529, 0.9117647058823529, 0.9411764705882353, 0.8235294117647058, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0.9039615846338533</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0.05326264238050186</v>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>0.9894736842105264, 0.9380952380952381, 0.9736842105263158, 0.9179566563467493, 0.9504643962848297, 0.9357585139318886, 0.9380804953560372</t>
+        </is>
+      </c>
+      <c r="AN34" t="n">
+        <v>0.9490733135359408</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0.9380952380952381</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0.02276184698623345</v>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="AR34" t="n">
+        <v>0.9977594515655674</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0.001417051170840857</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="AV34" t="n">
+        <v>0.9982688114216364</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0.001094907038779773</v>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0.9965459942243395</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0.002184519446236978</v>
+      </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BD34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG34" t="inlineStr">
+        <is>
+          <t>0.9999784157133607, 1.0, 0.9999785204914511, 0.9999785204914512, 0.9999785204914511, 1.0, 0.9999785204914512</t>
+        </is>
+      </c>
+      <c r="BH34" t="n">
+        <v>0.999984642525595</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>0.9999785204914512</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>9.712984233463659e-06</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>XGBClassifier_no_fragmentation_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>{'estimator': XGBClassifier(base_score=None, booster=None, callbacks=None,
+              colsample_bylevel=None, colsample_bynode=None,
+              colsample_bytree=None, device=None, early_stopping_rounds=None,
+              enable_categorical=False, eval_metric=None, feature_types=None,
+              gamma=None, grow_policy=None, importance_type=None,
+              interaction_constraints=None, learning_rate=None, max_bin=None,
+              max_cat_threshold=None, max_cat_to_onehot=None,
+              max_delta_step=None, max_depth=None, max_leaves=None,
+              min_child_weight=None, missing=nan, monotone_constraints=None,
+              multi_strategy=None, n_estimators=None, n_jobs=None,
+              num_parallel_tree=None, random_state=None, ...), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.8717948717948718</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.9872727272727273</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0.04535508155822754, 0.030457735061645508, 0.03690505027770996, 0.03257584571838379, 0.031723976135253906, 0.0294339656829834, 0.031539201736450195</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>0.0339986937386649</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.03172397613525391</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.005127482266990151</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>0.005602121353149414, 0.00534510612487793, 0.0051538944244384766, 0.005134105682373047, 0.005222797393798828, 0.004813194274902344, 0.004709959030151367</t>
+        </is>
+      </c>
+      <c r="T35" t="n">
+        <v>0.00514016832624163</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.005153894424438477</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.0002814363397437765</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.8490566037735849, 0.9245283018867925, 0.8867924528301887, 0.9245283018867925, 0.9056603773584906, 0.9433962264150944</t>
+        </is>
+      </c>
+      <c r="X35" t="n">
+        <v>0.9032644504342617</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0.0291230806376597</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>0.7499999999999999, 0.7333333333333334, 0.8461538461538461, 0.7999999999999999, 0.8461538461538461, 0.8148148148148148, 0.896551724137931</t>
+        </is>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.8124296520848245</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.05300274910577236</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>1.0, 0.6875, 0.9166666666666666, 0.75, 0.9166666666666666, 0.8461538461538461, 0.8666666666666667</t>
+        </is>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.8548076923076923</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.09850736899831899</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>0.6, 0.7857142857142857, 0.7857142857142857, 0.8571428571428571, 0.7857142857142857, 0.7857142857142857, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.789795918367347</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0.09249199341734415</v>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>0.9760683760683759, 0.9084249084249083, 0.978021978021978, 0.9157509157509157, 0.9853479853479853, 0.9285714285714286, 0.9871794871794871</t>
+        </is>
+      </c>
+      <c r="AN35" t="n">
+        <v>0.9541950113378684</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0.9760683760683759</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0.03236857087222359</v>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="AR35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="AV35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BD35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG35" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BH35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/metrics_modelling3.xlsx
+++ b/results/metrics_modelling3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ35"/>
+  <dimension ref="A1:BJ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6073,211 +6073,211 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LogisticRegression_splashing_Stk_diam</t>
+          <t>Logit_splashing_Stk_sign_diam</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{'estimator': LogisticRegression(fit_intercept=False), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': StatsModelsEstimator(model_class=&lt;class 'statsmodels.discrete.discrete_model.Logit'&gt;), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8269230769230769</v>
+        <v>0.8113207547169812</v>
       </c>
       <c r="G26" t="n">
         <v>0.8958333333333334</v>
       </c>
       <c r="H26" t="n">
-        <v>0.86</v>
+        <v>0.8514851485148515</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8858024691358024</v>
+        <v>0.878858024691358</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8013468013468014</v>
+        <v>0.8282828282828283</v>
       </c>
       <c r="K26" t="n">
-        <v>0.8674033149171271</v>
+        <v>0.873015873015873</v>
       </c>
       <c r="L26" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.859375</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8418230563002681</v>
+        <v>0.8661417322834646</v>
       </c>
       <c r="N26" t="n">
-        <v>0.9038442460317461</v>
+        <v>0.9011160714285714</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>0.013457775115966797, 0.003464221954345703, 0.0033440589904785156, 0.0033609867095947266, 0.0071980953216552734, 0.0033440589904785156, 0.0034418106079101562</t>
+          <t>0.004579782485961914, 0.0030908584594726562, 0.002978086471557617, 0.0031540393829345703, 0.008394956588745117, 0.002995014190673828, 0.008997201919555664</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0.005373001098632812</v>
+        <v>0.004884277071271624</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.003441810607910156</v>
+        <v>0.00315403938293457</v>
       </c>
       <c r="R26" t="n">
-        <v>0.003552642646690151</v>
+        <v>0.002471167683628091</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>0.005399227142333984, 0.006783008575439453, 0.0054471492767333984, 0.005080223083496094, 0.0052509307861328125, 0.004643917083740234, 0.004721879959106445</t>
+          <t>0.005811214447021484, 0.004441976547241211, 0.004347801208496094, 0.0045778751373291016, 0.004431247711181641, 0.004362821578979492, 0.004458904266357422</t>
         </is>
       </c>
       <c r="T26" t="n">
-        <v>0.005332333700997489</v>
+        <v>0.004633120128086635</v>
       </c>
       <c r="U26" t="n">
-        <v>0.005250930786132812</v>
+        <v>0.004441976547241211</v>
       </c>
       <c r="V26" t="n">
-        <v>0.0006588813407340738</v>
+        <v>0.0004859550144552821</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>0.9259259259259259, 0.7924528301886793, 0.8490566037735849, 0.7924528301886793, 0.8113207547169812, 0.7169811320754716, 0.7169811320754716</t>
+          <t>0.9074074074074074, 0.7735849056603774, 0.8301886792452831, 0.8113207547169812, 0.8490566037735849, 0.7169811320754716, 0.7358490566037735</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>0.8007387441349706</v>
+        <v>0.8034840770689827</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.7924528301886793</v>
+        <v>0.8113207547169812</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.06791424517985484</v>
+        <v>0.0616472441854517</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>0.9428571428571428, 0.8358208955223881, 0.8823529411764706, 0.8358208955223881, 0.8484848484848485, 0.7692307692307693, 0.782608695652174</t>
+          <t>0.9295774647887323, 0.823529411764706, 0.8695652173913043, 0.8529411764705882, 0.8823529411764706, 0.7761194029850745, 0.8055555555555555</t>
         </is>
       </c>
       <c r="AB26" t="n">
-        <v>0.8424537412065973</v>
+        <v>0.8485201671617758</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.8358208955223881</v>
+        <v>0.8529411764705882</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.05443237726411872</v>
+        <v>0.04764413907554068</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>0.9428571428571428, 0.875, 0.8823529411764706, 0.8484848484848485, 0.875, 0.8064516129032258, 0.7714285714285715</t>
+          <t>0.9166666666666666, 0.8484848484848485, 0.8571428571428571, 0.8529411764705882, 0.8823529411764706, 0.7878787878787878, 0.7631578947368421</t>
         </is>
       </c>
       <c r="AF26" t="n">
-        <v>0.8573678738357513</v>
+        <v>0.8440893103652946</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.875</v>
+        <v>0.8529411764705882</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.05156326200329429</v>
+        <v>0.04885717718405965</v>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>0.9428571428571428, 0.8, 0.8823529411764706, 0.8235294117647058, 0.8235294117647058, 0.7352941176470589, 0.7941176470588235</t>
+          <t>0.9428571428571428, 0.8, 0.8823529411764706, 0.8529411764705882, 0.8823529411764706, 0.7647058823529411, 0.8529411764705882</t>
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>0.8288115246098439</v>
+        <v>0.8540216086434574</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.8529411764705882</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.06176934313175476</v>
+        <v>0.05397757308868834</v>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>0.9503759398496241, 0.8365079365079365, 0.913312693498452, 0.84984520123839, 0.9380804953560372, 0.8343653250773995, 0.8591331269349846</t>
+          <t>0.9488721804511279, 0.8301587301587301, 0.9086687306501549, 0.8544891640866873, 0.9365325077399381, 0.8359133126934986, 0.8575851393188855</t>
         </is>
       </c>
       <c r="AN26" t="n">
-        <v>0.8830886740661177</v>
+        <v>0.8817456807284316</v>
       </c>
       <c r="AO26" t="n">
-        <v>0.8591331269349846</v>
+        <v>0.8575851393188855</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.0458068841803581</v>
+        <v>0.04523096740305244</v>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>0.8018867924528302, 0.8025078369905956, 0.7962382445141066, 0.8087774294670846, 0.8087774294670846, 0.8244514106583072, 0.8213166144200627</t>
+          <t>0.8081761006289309, 0.8119122257053292, 0.8025078369905956, 0.8307210031347962, 0.8056426332288401, 0.8181818181818182, 0.8150470219435737</t>
         </is>
       </c>
       <c r="AR26" t="n">
-        <v>0.8091365368528675</v>
+        <v>0.8131698056876976</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.8087774294670846</v>
+        <v>0.8119122257053292</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.00960670871567345</v>
+        <v>0.008730433153130501</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>0.845965770171149, 0.8444444444444444, 0.8395061728395062, 0.851581508515815, 0.85012285012285, 0.8606965174129354, 0.8585607940446649</t>
+          <t>0.8530120481927711, 0.8514851485148514, 0.8467153284671532, 0.8701923076923077, 0.8495145631067961, 0.8578431372549019, 0.8557457212713936</t>
         </is>
       </c>
       <c r="AV26" t="n">
-        <v>0.8501254367930523</v>
+        <v>0.8549297506428821</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.85012285012285</v>
+        <v>0.8530120481927711</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.007044434646001391</v>
+        <v>0.007115808673493368</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>0.8480392156862745, 0.855, 0.8542713567839196, 0.8536585365853658, 0.8606965174129353, 0.8826530612244898, 0.8781725888324873</t>
+          <t>0.8428571428571429, 0.864321608040201, 0.848780487804878, 0.861904761904762, 0.8495145631067961, 0.8663366336633663, 0.8620689655172413</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>0.8617844680750675</v>
+        <v>0.8565405946991982</v>
       </c>
       <c r="BA26" t="n">
-        <v>0.855</v>
+        <v>0.861904761904762</v>
       </c>
       <c r="BB26" t="n">
-        <v>0.0123212411989612</v>
+        <v>0.008557911585811406</v>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>0.8439024390243902, 0.8341463414634146, 0.8252427184466019, 0.8495145631067961, 0.8398058252427184, 0.8398058252427184, 0.8398058252427184</t>
+          <t>0.8634146341463415, 0.8390243902439024, 0.8446601941747572, 0.8786407766990292, 0.8495145631067961, 0.8495145631067961, 0.8495145631067961</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>0.8388890768241941</v>
+        <v>0.853469097797774</v>
       </c>
       <c r="BE26" t="n">
-        <v>0.8398058252427184</v>
+        <v>0.8495145631067961</v>
       </c>
       <c r="BF26" t="n">
-        <v>0.007063716928812917</v>
+        <v>0.01233860668906159</v>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>0.8894668681200086, 0.9051775780915704, 0.8973064696279749, 0.9051250107397543, 0.89219434659335, 0.9097431050777558, 0.9041369533465075</t>
+          <t>0.8882149794949277, 0.9058194266153188, 0.895631067961165, 0.9035784861242375, 0.8913351662513961, 0.9070796460176991, 0.9022897156113068</t>
         </is>
       </c>
       <c r="BH26" t="n">
-        <v>0.9004500473709889</v>
+        <v>0.8991354982965787</v>
       </c>
       <c r="BI26" t="n">
-        <v>0.9041369533465075</v>
+        <v>0.9022897156113068</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0.006998243955679154</v>
+        <v>0.006864583551809107</v>
       </c>
     </row>
     <row r="27">
@@ -6293,211 +6293,211 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LogisticRegression_no_fragmentation_Stk_diam</t>
+          <t>Logit_no_fragmentation_Stk_sign_diam</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>{'estimator': LogisticRegression(fit_intercept=False), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': StatsModelsEstimator(model_class=&lt;class 'statsmodels.discrete.discrete_model.Logit'&gt;), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.88</v>
       </c>
       <c r="F27" t="n">
-        <v>0.68</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="G27" t="n">
         <v>0.85</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7555555555555556</v>
+        <v>0.7906976744186046</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9290909090909091</v>
+        <v>0.95</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8451178451178452</v>
+        <v>0.8585858585858586</v>
       </c>
       <c r="K27" t="n">
-        <v>0.6633663366336634</v>
+        <v>0.7402597402597403</v>
       </c>
       <c r="L27" t="n">
-        <v>0.8481012658227848</v>
+        <v>0.7215189873417721</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="N27" t="n">
-        <v>0.9313087910811753</v>
+        <v>0.9300894205086517</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.004318952560424805, 0.0029261112213134766, 0.0027930736541748047, 0.0027098655700683594, 0.0028879642486572266, 0.0027778148651123047, 0.0028731822967529297</t>
+          <t>0.0077283382415771484, 0.0025179386138916016, 0.0025391578674316406, 0.0024182796478271484, 0.0023670196533203125, 0.006473064422607422, 0.002410888671875</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0.003040994916643415</v>
+        <v>0.003779241016932896</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.00287318229675293</v>
+        <v>0.002517938613891602</v>
       </c>
       <c r="R27" t="n">
-        <v>0.000526216793938707</v>
+        <v>0.002128034524710368</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0.004152059555053711, 0.004306793212890625, 0.004371166229248047, 0.0038979053497314453, 0.0039348602294921875, 0.0041961669921875, 0.003973722457885742</t>
+          <t>0.007433891296386719, 0.0037529468536376953, 0.0038330554962158203, 0.003862619400024414, 0.0069179534912109375, 0.00519108772277832, 0.003664255142211914</t>
         </is>
       </c>
       <c r="T27" t="n">
-        <v>0.004118953432355609</v>
+        <v>0.004950829914637974</v>
       </c>
       <c r="U27" t="n">
-        <v>0.004152059555053711</v>
+        <v>0.003862619400024414</v>
       </c>
       <c r="V27" t="n">
-        <v>0.00017312160274854</v>
+        <v>0.001493639517271375</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>0.8703703703703703, 0.7169811320754716, 0.8867924528301887, 0.8301886792452831, 0.8679245283018868, 0.8867924528301887, 0.8867924528301887</t>
+          <t>0.8888888888888888, 0.7358490566037735, 0.9056603773584906, 0.8301886792452831, 0.8301886792452831, 0.8679245283018868, 0.9622641509433962</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>0.8494060097833683</v>
+        <v>0.8601377657981431</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.8703703703703703</v>
+        <v>0.8679245283018868</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.05717308600454714</v>
+        <v>0.06615020382139397</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>0.7586206896551724, 0.5714285714285714, 0.8125000000000001, 0.742857142857143, 0.7741935483870968, 0.7857142857142857, 0.8235294117647058</t>
+          <t>0.7692307692307692, 0.5625000000000001, 0.8275862068965518, 0.689655172413793, 0.689655172413793, 0.7200000000000001, 0.9333333333333333</t>
         </is>
       </c>
       <c r="AB27" t="n">
-        <v>0.7526919499724249</v>
+        <v>0.7417086648983201</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.7741935483870968</v>
+        <v>0.7200000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.07850025297489785</v>
+        <v>0.1087976994671121</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>0.7857142857142857, 0.47619047619047616, 0.7222222222222222, 0.6190476190476191, 0.7058823529411765, 0.7857142857142857, 0.7</t>
+          <t>0.9090909090909091, 0.5, 0.8, 0.6666666666666666, 0.6666666666666666, 0.8181818181818182, 0.875</t>
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>0.684967320261438</v>
+        <v>0.7479437229437229</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.8</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.1002029565407049</v>
+        <v>0.133332542725491</v>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>0.7333333333333333, 0.7142857142857143, 0.9285714285714286, 0.9285714285714286, 0.8571428571428571, 0.7857142857142857, 1.0</t>
+          <t>0.6666666666666666, 0.6428571428571429, 0.8571428571428571, 0.7142857142857143, 0.7142857142857143, 0.6428571428571429, 1.0</t>
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0.8496598639455781</v>
+        <v>0.7482993197278912</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.1007537881990401</v>
+        <v>0.1232963874856589</v>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>0.9401709401709402, 0.8772893772893773, 0.9688644688644689, 0.9175824175824177, 0.891941391941392, 0.9432234432234433, 0.9890109890109889</t>
+          <t>0.9333333333333333, 0.8827838827838828, 0.9542124542124542, 0.913919413919414, 0.8974358974358975, 0.924908424908425, 0.9945054945054945</t>
         </is>
       </c>
       <c r="AN27" t="n">
-        <v>0.932583289726147</v>
+        <v>0.9287284144427003</v>
       </c>
       <c r="AO27" t="n">
-        <v>0.9401709401709402</v>
+        <v>0.924908424908425</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.03704322048085008</v>
+        <v>0.03447832911321202</v>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>0.8427672955974843, 0.8526645768025078, 0.8338557993730408, 0.8463949843260188, 0.8432601880877743, 0.8401253918495298, 0.8432601880877743</t>
+          <t>0.8679245283018868, 0.8934169278996865, 0.8620689655172413, 0.8652037617554859, 0.8683385579937304, 0.877742946708464, 0.8495297805642633</t>
         </is>
       </c>
       <c r="AR27" t="n">
-        <v>0.8431897748748759</v>
+        <v>0.8691750669629654</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.8432601880877743</v>
+        <v>0.8679245283018868</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.005301579090494343</v>
+        <v>0.01262392965591266</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>0.7448979591836734, 0.7614213197969542, 0.736318407960199, 0.751269035532995, 0.7368421052631577, 0.7384615384615385, 0.7395833333333333</t>
+          <t>0.75, 0.8000000000000002, 0.7380952380952379, 0.7485380116959064, 0.7499999999999999, 0.7692307692307693, 0.7142857142857143</t>
         </is>
       </c>
       <c r="AV27" t="n">
-        <v>0.7441133856474071</v>
+        <v>0.7528785333296611</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.7395833333333333</v>
+        <v>0.7499999999999999</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.008598018140371306</v>
+        <v>0.02458568624275207</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>0.6517857142857143, 0.6696428571428571, 0.6379310344827587, 0.6607142857142857, 0.6666666666666666, 0.6545454545454545, 0.6635514018691588</t>
+          <t>0.75, 0.8, 0.7469879518072289, 0.7441860465116279, 0.7590361445783133, 0.7738095238095238, 0.7228915662650602</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>0.6578339163866994</v>
+        <v>0.7567016047102506</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.6607142857142857</v>
+        <v>0.75</v>
       </c>
       <c r="BB27" t="n">
-        <v>0.01001409125050462</v>
+        <v>0.02271533925431839</v>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>0.8690476190476191, 0.8823529411764706, 0.8705882352941177, 0.8705882352941177, 0.8235294117647058, 0.8470588235294118, 0.8352941176470589</t>
+          <t>0.75, 0.8, 0.7294117647058823, 0.7529411764705882, 0.7411764705882353, 0.7647058823529411, 0.7058823529411765</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>0.856922769107643</v>
+        <v>0.7491596638655462</v>
       </c>
       <c r="BE27" t="n">
-        <v>0.8690476190476191</v>
+        <v>0.75</v>
       </c>
       <c r="BF27" t="n">
-        <v>0.02016860314842748</v>
+        <v>0.02717159027600797</v>
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>0.9308099308099308, 0.9422825540472599, 0.9276520864756159, 0.9362996480643538, 0.9334841628959275, 0.9351935646053293, 0.9222222222222223</t>
+          <t>0.932997557997558, 0.9409753645047764, 0.9276520864756158, 0.9374057315233786, 0.9338863750628457, 0.9370035193564605, 0.9206636500754148</t>
         </is>
       </c>
       <c r="BH27" t="n">
-        <v>0.93256345273152</v>
+        <v>0.9329406121422928</v>
       </c>
       <c r="BI27" t="n">
-        <v>0.9334841628959275</v>
+        <v>0.9338863750628457</v>
       </c>
       <c r="BJ27" t="n">
-        <v>0.005979998658646051</v>
+        <v>0.00633123507806117</v>
       </c>
     </row>
     <row r="28">
@@ -6513,211 +6513,211 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>KNeighborsClassifier_splashing_Stk_diam</t>
+          <t>LogisticRegression_splashing_Stk_sign_diam</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>{'estimator': KNeighborsClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': LogisticRegression(fit_intercept=False), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="F28" t="n">
-        <v>0.88</v>
+        <v>0.8269230769230769</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8979591836734694</v>
+        <v>0.86</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8753858024691358</v>
+        <v>0.8858024691358024</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9023569023569024</v>
+        <v>0.8013468013468014</v>
       </c>
       <c r="K28" t="n">
-        <v>0.9179487179487179</v>
+        <v>0.8674033149171271</v>
       </c>
       <c r="L28" t="n">
-        <v>0.9322916666666666</v>
+        <v>0.8177083333333334</v>
       </c>
       <c r="M28" t="n">
-        <v>0.9250645994832041</v>
+        <v>0.8418230563002681</v>
       </c>
       <c r="N28" t="n">
-        <v>0.9650545634920635</v>
+        <v>0.9038442460317461</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.00451207160949707, 0.006139039993286133, 0.0027091503143310547, 0.0027008056640625, 0.002794981002807617, 0.0026471614837646484, 0.0025568008422851562</t>
+          <t>0.014836311340332031, 0.0035021305084228516, 0.0033359527587890625, 0.0036993026733398438, 0.004848957061767578, 0.005038022994995117, 0.0032808780670166016</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0.003437144415719168</v>
+        <v>0.005505936486380441</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.002709150314331055</v>
+        <v>0.003699302673339844</v>
       </c>
       <c r="R28" t="n">
-        <v>0.00127275460780346</v>
+        <v>0.003866436868272365</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>0.00745081901550293, 0.008826017379760742, 0.0059812068939208984, 0.005836963653564453, 0.006107807159423828, 0.0061337947845458984, 0.006054878234863281</t>
+          <t>0.005201816558837891, 0.005276918411254883, 0.00475001335144043, 0.004732847213745117, 0.0047419071197509766, 0.0047647953033447266, 0.0049571990966796875</t>
         </is>
       </c>
       <c r="T28" t="n">
-        <v>0.006627355303083148</v>
+        <v>0.004917928150721959</v>
       </c>
       <c r="U28" t="n">
-        <v>0.006107807159423828</v>
+        <v>0.004764795303344727</v>
       </c>
       <c r="V28" t="n">
-        <v>0.001027875506084579</v>
+        <v>0.0002164295490640372</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>0.8888888888888888, 0.7547169811320755, 0.8490566037735849, 0.7924528301886793, 0.8867924528301887, 0.7735849056603774, 0.8490566037735849</t>
+          <t>0.9259259259259259, 0.7924528301886793, 0.8490566037735849, 0.7924528301886793, 0.8113207547169812, 0.7169811320754716, 0.7169811320754716</t>
         </is>
       </c>
       <c r="X28" t="n">
-        <v>0.8277927523210543</v>
+        <v>0.8007387441349706</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.8490566037735849</v>
+        <v>0.7924528301886793</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.05020739045150253</v>
+        <v>0.06791424517985484</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>0.9189189189189189, 0.8, 0.8823529411764706, 0.8253968253968255, 0.9142857142857143, 0.806451612903226, 0.8823529411764706</t>
+          <t>0.9428571428571428, 0.8358208955223881, 0.8823529411764706, 0.8358208955223881, 0.8484848484848485, 0.7692307692307693, 0.782608695652174</t>
         </is>
       </c>
       <c r="AB28" t="n">
-        <v>0.861394136265375</v>
+        <v>0.8424537412065973</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.8358208955223881</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.04639718261514306</v>
+        <v>0.05443237726411872</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>0.8717948717948718, 0.8666666666666667, 0.8823529411764706, 0.896551724137931, 0.8888888888888888, 0.8928571428571429, 0.8823529411764706</t>
+          <t>0.9428571428571428, 0.875, 0.8823529411764706, 0.8484848484848485, 0.875, 0.8064516129032258, 0.7714285714285715</t>
         </is>
       </c>
       <c r="AF28" t="n">
-        <v>0.8830664538140631</v>
+        <v>0.8573678738357513</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.875</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.01006145855735717</v>
+        <v>0.05156326200329429</v>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>0.9714285714285714, 0.7428571428571429, 0.8823529411764706, 0.7647058823529411, 0.9411764705882353, 0.7352941176470589, 0.8823529411764706</t>
+          <t>0.9428571428571428, 0.8, 0.8823529411764706, 0.8235294117647058, 0.8235294117647058, 0.7352941176470589, 0.7941176470588235</t>
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0.8457382953181273</v>
+        <v>0.8288115246098439</v>
       </c>
       <c r="AK28" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.0901874676551734</v>
+        <v>0.06176934313175476</v>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>0.9105263157894736, 0.8523809523809524, 0.9458204334365324, 0.9256965944272446, 0.958204334365325, 0.890092879256966, 0.8722910216718267</t>
+          <t>0.9503759398496241, 0.8365079365079365, 0.913312693498452, 0.84984520123839, 0.9380804953560372, 0.8343653250773995, 0.8591331269349846</t>
         </is>
       </c>
       <c r="AN28" t="n">
-        <v>0.9078589330469029</v>
+        <v>0.8830886740661177</v>
       </c>
       <c r="AO28" t="n">
-        <v>0.9105263157894736</v>
+        <v>0.8591331269349846</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.03577618394883013</v>
+        <v>0.0458068841803581</v>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>0.9088050314465409, 0.8840125391849529, 0.896551724137931, 0.9090909090909091, 0.8840125391849529, 0.8840125391849529, 0.9059561128526645</t>
+          <t>0.8018867924528302, 0.8025078369905956, 0.7962382445141066, 0.8087774294670846, 0.8087774294670846, 0.8244514106583072, 0.8213166144200627</t>
         </is>
       </c>
       <c r="AR28" t="n">
-        <v>0.896063056440415</v>
+        <v>0.8091365368528675</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.896551724137931</v>
+        <v>0.8087774294670846</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.01112165925061054</v>
+        <v>0.00960670871567345</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>0.9294403892944039, 0.9090909090909092, 0.9212410501193318, 0.9301204819277109, 0.9099756690997567, 0.9099756690997567, 0.9271844660194175</t>
+          <t>0.845965770171149, 0.8444444444444444, 0.8395061728395062, 0.851581508515815, 0.85012285012285, 0.8606965174129354, 0.8585607940446649</t>
         </is>
       </c>
       <c r="AV28" t="n">
-        <v>0.919575519235898</v>
+        <v>0.8501254367930523</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.9212410501193318</v>
+        <v>0.85012285012285</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.008971568256650582</v>
+        <v>0.007044434646001391</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>0.9271844660194175, 0.9158415841584159, 0.9061032863849765, 0.9234449760765551, 0.9121951219512195, 0.9121951219512195, 0.9271844660194175</t>
+          <t>0.8480392156862745, 0.855, 0.8542713567839196, 0.8536585365853658, 0.8606965174129353, 0.8826530612244898, 0.8781725888324873</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>0.917735574651603</v>
+        <v>0.8617844680750675</v>
       </c>
       <c r="BA28" t="n">
-        <v>0.9158415841584159</v>
+        <v>0.855</v>
       </c>
       <c r="BB28" t="n">
-        <v>0.007666727028896789</v>
+        <v>0.0123212411989612</v>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>0.9317073170731708, 0.9024390243902439, 0.9368932038834952, 0.9368932038834952, 0.9077669902912622, 0.9077669902912622, 0.9271844660194175</t>
+          <t>0.8439024390243902, 0.8341463414634146, 0.8252427184466019, 0.8495145631067961, 0.8398058252427184, 0.8398058252427184, 0.8398058252427184</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>0.921521599404621</v>
+        <v>0.8388890768241941</v>
       </c>
       <c r="BE28" t="n">
-        <v>0.9271844660194175</v>
+        <v>0.8398058252427184</v>
       </c>
       <c r="BF28" t="n">
-        <v>0.0138919944270699</v>
+        <v>0.007063716928812917</v>
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>0.9636088927260954, 0.962173727000428, 0.964923962539737, 0.9693917003178967, 0.9582008763639488, 0.9661053355099235, 0.9687687945699802</t>
+          <t>0.8894668681200086, 0.9051775780915704, 0.8973064696279749, 0.9051250107397543, 0.89219434659335, 0.9097431050777558, 0.9041369533465075</t>
         </is>
       </c>
       <c r="BH28" t="n">
-        <v>0.9647390412897157</v>
+        <v>0.9004500473709889</v>
       </c>
       <c r="BI28" t="n">
-        <v>0.964923962539737</v>
+        <v>0.9041369533465075</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0.003593501616458011</v>
+        <v>0.006998243955679154</v>
       </c>
     </row>
     <row r="29">
@@ -6733,211 +6733,211 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>KNeighborsClassifier_no_fragmentation_Stk_diam</t>
+          <t>LogisticRegression_no_fragmentation_Stk_sign_diam</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>{'estimator': KNeighborsClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': LogisticRegression(fit_intercept=False), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.68</v>
       </c>
       <c r="G29" t="n">
         <v>0.85</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8292682926829269</v>
+        <v>0.7555555555555556</v>
       </c>
       <c r="I29" t="n">
-        <v>0.97</v>
+        <v>0.9290909090909091</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.8451178451178452</v>
       </c>
       <c r="K29" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.6633663366336634</v>
       </c>
       <c r="L29" t="n">
-        <v>0.810126582278481</v>
+        <v>0.8481012658227848</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8258064516129032</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="N29" t="n">
-        <v>0.9639995354778772</v>
+        <v>0.9313087910811753</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>0.002920866012573242, 0.002074718475341797, 0.0021729469299316406, 0.002079010009765625, 0.0021131038665771484, 0.002335071563720703, 0.0023391246795654297</t>
+          <t>0.004235029220581055, 0.0029549598693847656, 0.0027039051055908203, 0.002979755401611328, 0.0031669139862060547, 0.002604961395263672, 0.0028200149536132812</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0.002290691648210798</v>
+        <v>0.003066505704607282</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.002172946929931641</v>
+        <v>0.002954959869384766</v>
       </c>
       <c r="R29" t="n">
-        <v>0.0002773058732180589</v>
+        <v>0.0005071991934765527</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>0.0064411163330078125, 0.005961179733276367, 0.005251884460449219, 0.005357980728149414, 0.005299806594848633, 0.00522613525390625, 0.005182027816772461</t>
+          <t>0.004194021224975586, 0.00437617301940918, 0.0039288997650146484, 0.003869295120239258, 0.0041081905364990234, 0.0038688182830810547, 0.003837108612060547</t>
         </is>
       </c>
       <c r="T29" t="n">
-        <v>0.005531447274344308</v>
+        <v>0.004026072365897042</v>
       </c>
       <c r="U29" t="n">
-        <v>0.005299806594848633</v>
+        <v>0.003928899765014648</v>
       </c>
       <c r="V29" t="n">
-        <v>0.0004455142427837516</v>
+        <v>0.000189728545462418</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>0.9259259259259259, 0.7547169811320755, 0.9433962264150944, 0.8113207547169812, 0.8113207547169812, 0.8490566037735849, 0.9245283018867925</t>
+          <t>0.8703703703703703, 0.7169811320754716, 0.8867924528301887, 0.8301886792452831, 0.8679245283018868, 0.8867924528301887, 0.8867924528301887</t>
         </is>
       </c>
       <c r="X29" t="n">
-        <v>0.8600379355096336</v>
+        <v>0.8494060097833683</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.8490566037735849</v>
+        <v>0.8703703703703703</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.06698471018043896</v>
+        <v>0.05717308600454714</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>0.8749999999999999, 0.5517241379310344, 0.888888888888889, 0.6428571428571429, 0.5833333333333334, 0.7142857142857143, 0.8750000000000001</t>
+          <t>0.7586206896551724, 0.5714285714285714, 0.8125000000000001, 0.742857142857143, 0.7741935483870968, 0.7857142857142857, 0.8235294117647058</t>
         </is>
       </c>
       <c r="AB29" t="n">
-        <v>0.7330127453280163</v>
+        <v>0.7526919499724249</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.1354180579884486</v>
+        <v>0.07850025297489785</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>0.8235294117647058, 0.5333333333333333, 0.9230769230769231, 0.6428571428571429, 0.7, 0.7142857142857143, 0.7777777777777778</t>
+          <t>0.7857142857142857, 0.47619047619047616, 0.7222222222222222, 0.6190476190476191, 0.7058823529411765, 0.7857142857142857, 0.7</t>
         </is>
       </c>
       <c r="AF29" t="n">
-        <v>0.7306943290136567</v>
+        <v>0.684967320261438</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.1169397797367399</v>
+        <v>0.1002029565407049</v>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>0.9333333333333333, 0.5714285714285714, 0.8571428571428571, 0.6428571428571429, 0.5, 0.7142857142857143, 1.0</t>
+          <t>0.7333333333333333, 0.7142857142857143, 0.9285714285714286, 0.9285714285714286, 0.8571428571428571, 0.7857142857142857, 1.0</t>
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0.745578231292517</v>
+        <v>0.8496598639455781</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.1750904647078131</v>
+        <v>0.1007537881990401</v>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>0.970940170940171, 0.7866300366300367, 0.9322344322344321, 0.8974358974358976, 0.8873626373626374, 0.8965201465201464, 0.967032967032967</t>
+          <t>0.9401709401709402, 0.8772893772893773, 0.9688644688644689, 0.9175824175824177, 0.891941391941392, 0.9432234432234433, 0.9890109890109889</t>
         </is>
       </c>
       <c r="AN29" t="n">
-        <v>0.9054508983080414</v>
+        <v>0.932583289726147</v>
       </c>
       <c r="AO29" t="n">
-        <v>0.8974358974358976</v>
+        <v>0.9401709401709402</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.05780278617645025</v>
+        <v>0.03704322048085008</v>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>0.8930817610062893, 0.9122257053291536, 0.8996865203761756, 0.9028213166144201, 0.8934169278996865, 0.9028213166144201, 0.9153605015673981</t>
+          <t>0.8427672955974843, 0.8526645768025078, 0.8338557993730408, 0.8463949843260188, 0.8432601880877743, 0.8401253918495298, 0.8432601880877743</t>
         </is>
       </c>
       <c r="AR29" t="n">
-        <v>0.902773435629649</v>
+        <v>0.8431897748748759</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.9028213166144201</v>
+        <v>0.8432601880877743</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.007917305243749024</v>
+        <v>0.005301579090494343</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>0.8045977011494253, 0.8390804597701149, 0.8181818181818181, 0.8187134502923977, 0.8023255813953488, 0.8208092485549133, 0.8421052631578947</t>
+          <t>0.7448979591836734, 0.7614213197969542, 0.736318407960199, 0.751269035532995, 0.7368421052631577, 0.7384615384615385, 0.7395833333333333</t>
         </is>
       </c>
       <c r="AV29" t="n">
-        <v>0.820830503214559</v>
+        <v>0.7441133856474071</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.8187134502923977</v>
+        <v>0.7395833333333333</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.01415783587470498</v>
+        <v>0.008598018140371306</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>0.7777777777777778, 0.8202247191011236, 0.7912087912087912, 0.813953488372093, 0.7931034482758621, 0.8068181818181818, 0.8372093023255814</t>
+          <t>0.6517857142857143, 0.6696428571428571, 0.6379310344827587, 0.6607142857142857, 0.6666666666666666, 0.6545454545454545, 0.6635514018691588</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>0.8057565298399157</v>
+        <v>0.6578339163866994</v>
       </c>
       <c r="BA29" t="n">
-        <v>0.8068181818181818</v>
+        <v>0.6607142857142857</v>
       </c>
       <c r="BB29" t="n">
-        <v>0.01859904133833272</v>
+        <v>0.01001409125050462</v>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>0.8333333333333334, 0.8588235294117647, 0.8470588235294118, 0.8235294117647058, 0.8117647058823529, 0.8352941176470589, 0.8470588235294118</t>
+          <t>0.8690476190476191, 0.8823529411764706, 0.8705882352941177, 0.8705882352941177, 0.8235294117647058, 0.8470588235294118, 0.8352941176470589</t>
         </is>
       </c>
       <c r="BD29" t="n">
-        <v>0.8366946778711483</v>
+        <v>0.856922769107643</v>
       </c>
       <c r="BE29" t="n">
-        <v>0.8352941176470589</v>
+        <v>0.8690476190476191</v>
       </c>
       <c r="BF29" t="n">
-        <v>0.01469987872650075</v>
+        <v>0.02016860314842748</v>
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>0.9665750915750917, 0.9727752639517344, 0.962242332830568, 0.9635746606334843, 0.9669683257918552, 0.9673956762192055, 0.9699849170437406</t>
+          <t>0.9308099308099308, 0.9422825540472599, 0.9276520864756159, 0.9362996480643538, 0.9334841628959275, 0.9351935646053293, 0.9222222222222223</t>
         </is>
       </c>
       <c r="BH29" t="n">
-        <v>0.9670737525779544</v>
+        <v>0.93256345273152</v>
       </c>
       <c r="BI29" t="n">
-        <v>0.9669683257918552</v>
+        <v>0.9334841628959275</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0.00331515533222134</v>
+        <v>0.005979998658646051</v>
       </c>
     </row>
     <row r="30">
@@ -6953,211 +6953,211 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SVC_splashing_Stk_diam</t>
+          <t>KNeighborsClassifier_splashing_Stk_sign_diam</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{'estimator': SVC(probability=True), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': KNeighborsClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8431372549019608</v>
+        <v>0.88</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8686868686868686</v>
+        <v>0.8979591836734694</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9274691358024691</v>
+        <v>0.8753858024691358</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8922558922558923</v>
+        <v>0.9023569023569024</v>
       </c>
       <c r="K30" t="n">
-        <v>0.9210526315789473</v>
+        <v>0.9179487179487179</v>
       </c>
       <c r="L30" t="n">
-        <v>0.9114583333333334</v>
+        <v>0.9322916666666666</v>
       </c>
       <c r="M30" t="n">
-        <v>0.9162303664921465</v>
+        <v>0.9250645994832041</v>
       </c>
       <c r="N30" t="n">
-        <v>0.9509672619047618</v>
+        <v>0.9650545634920635</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.009139060974121094, 0.007838964462280273, 0.007873058319091797, 0.00767827033996582, 0.007742166519165039, 0.007651090621948242, 0.007400989532470703</t>
+          <t>0.0036296844482421875, 0.002763032913208008, 0.0028879642486572266, 0.002808809280395508, 0.0025708675384521484, 0.002637147903442383, 0.0028848648071289062</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.007903371538434709</v>
+        <v>0.002883195877075195</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.007742166519165039</v>
+        <v>0.002808809280395508</v>
       </c>
       <c r="R30" t="n">
-        <v>0.0005243617198518821</v>
+        <v>0.0003241101685857505</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>0.005811929702758789, 0.0057179927825927734, 0.005391836166381836, 0.005655765533447266, 0.005440711975097656, 0.005650043487548828, 0.005573749542236328</t>
+          <t>0.007605075836181641, 0.006088972091674805, 0.005764007568359375, 0.005780935287475586, 0.006255149841308594, 0.0055637359619140625, 0.005830049514770508</t>
         </is>
       </c>
       <c r="T30" t="n">
-        <v>0.005606004170009068</v>
+        <v>0.006126846585954938</v>
       </c>
       <c r="U30" t="n">
-        <v>0.005650043487548828</v>
+        <v>0.005830049514770508</v>
       </c>
       <c r="V30" t="n">
-        <v>0.0001381470405330805</v>
+        <v>0.0006391452746055095</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>0.9074074074074074, 0.7358490566037735, 0.9245283018867925, 0.7358490566037735, 0.8867924528301887, 0.8490566037735849, 0.8301886792452831</t>
+          <t>0.8888888888888888, 0.7547169811320755, 0.8490566037735849, 0.7924528301886793, 0.8867924528301887, 0.7735849056603774, 0.8490566037735849</t>
         </is>
       </c>
       <c r="X30" t="n">
-        <v>0.838524508335829</v>
+        <v>0.8277927523210543</v>
       </c>
       <c r="Y30" t="n">
         <v>0.8490566037735849</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.07145049096409614</v>
+        <v>0.05020739045150253</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>0.9315068493150684, 0.7941176470588236, 0.9428571428571428, 0.787878787878788, 0.9117647058823528, 0.8787878787878787, 0.8695652173913043</t>
+          <t>0.9189189189189189, 0.8, 0.8823529411764706, 0.8253968253968255, 0.9142857142857143, 0.806451612903226, 0.8823529411764706</t>
         </is>
       </c>
       <c r="AB30" t="n">
-        <v>0.8737826041673371</v>
+        <v>0.861394136265375</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.8787878787878787</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.05771213117467276</v>
+        <v>0.04639718261514306</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>0.8947368421052632, 0.8181818181818182, 0.9166666666666666, 0.8125, 0.9117647058823529, 0.90625, 0.8571428571428571</t>
+          <t>0.8717948717948718, 0.8666666666666667, 0.8823529411764706, 0.896551724137931, 0.8888888888888888, 0.8928571428571429, 0.8823529411764706</t>
         </is>
       </c>
       <c r="AF30" t="n">
-        <v>0.8738918414255654</v>
+        <v>0.8830664538140631</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.0412287995289299</v>
+        <v>0.01006145855735717</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>0.9714285714285714, 0.7714285714285715, 0.9705882352941176, 0.7647058823529411, 0.9117647058823529, 0.8529411764705882, 0.8823529411764706</t>
+          <t>0.9714285714285714, 0.7428571428571429, 0.8823529411764706, 0.7647058823529411, 0.9411764705882353, 0.7352941176470589, 0.8823529411764706</t>
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0.8750300120048019</v>
+        <v>0.8457382953181273</v>
       </c>
       <c r="AK30" t="n">
         <v>0.8823529411764706</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.07857635781408312</v>
+        <v>0.0901874676551734</v>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>0.9849624060150376, 0.8571428571428572, 0.9442724458204335, 0.9071207430340558, 0.9597523219814241, 0.9133126934984521, 0.8560371517027864</t>
+          <t>0.9105263157894736, 0.8523809523809524, 0.9458204334365324, 0.9256965944272446, 0.958204334365325, 0.890092879256966, 0.8722910216718267</t>
         </is>
       </c>
       <c r="AN30" t="n">
-        <v>0.9175143741707208</v>
+        <v>0.9078589330469029</v>
       </c>
       <c r="AO30" t="n">
-        <v>0.9133126934984521</v>
+        <v>0.9105263157894736</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.04566825448295116</v>
+        <v>0.03577618394883013</v>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>0.8584905660377359, 0.8934169278996865, 0.8746081504702194, 0.8840125391849529, 0.8808777429467085, 0.8746081504702194, 0.890282131661442</t>
+          <t>0.9088050314465409, 0.8840125391849529, 0.896551724137931, 0.9090909090909091, 0.8840125391849529, 0.8840125391849529, 0.9059561128526645</t>
         </is>
       </c>
       <c r="AR30" t="n">
-        <v>0.8794708869529949</v>
+        <v>0.896063056440415</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.8808777429467085</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.01083280201797767</v>
+        <v>0.01112165925061054</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>0.8915662650602411, 0.9154228855721392, 0.9033816425120774, 0.9104116222760291, 0.905940594059406, 0.9033816425120774, 0.914004914004914</t>
+          <t>0.9294403892944039, 0.9090909090909092, 0.9212410501193318, 0.9301204819277109, 0.9099756690997567, 0.9099756690997567, 0.9271844660194175</t>
         </is>
       </c>
       <c r="AV30" t="n">
-        <v>0.9063013665709835</v>
+        <v>0.919575519235898</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.905940594059406</v>
+        <v>0.9212410501193318</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.007499941946569862</v>
+        <v>0.008971568256650582</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>0.8809523809523809, 0.934010152284264, 0.8990384615384616, 0.9082125603864735, 0.9242424242424242, 0.8990384615384616, 0.9253731343283582</t>
+          <t>0.9271844660194175, 0.9158415841584159, 0.9061032863849765, 0.9234449760765551, 0.9121951219512195, 0.9121951219512195, 0.9271844660194175</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>0.9101239393244034</v>
+        <v>0.917735574651603</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.9082125603864735</v>
+        <v>0.9158415841584159</v>
       </c>
       <c r="BB30" t="n">
-        <v>0.01733217304401899</v>
+        <v>0.007666727028896789</v>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>0.9024390243902439, 0.8975609756097561, 0.9077669902912622, 0.912621359223301, 0.8883495145631068, 0.9077669902912622, 0.9029126213592233</t>
+          <t>0.9317073170731708, 0.9024390243902439, 0.9368932038834952, 0.9368932038834952, 0.9077669902912622, 0.9077669902912622, 0.9271844660194175</t>
         </is>
       </c>
       <c r="BD30" t="n">
-        <v>0.9027739251040222</v>
+        <v>0.921521599404621</v>
       </c>
       <c r="BE30" t="n">
-        <v>0.9029126213592233</v>
+        <v>0.9271844660194175</v>
       </c>
       <c r="BF30" t="n">
-        <v>0.007389212365561095</v>
+        <v>0.0138919944270699</v>
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>0.9411396503345565, 0.9603765511339324, 0.9497164704871552, 0.9514348311710629, 0.947267806512587, 0.9502104991837786, 0.9571698599536043</t>
+          <t>0.9636088927260954, 0.962173727000428, 0.964923962539737, 0.9693917003178967, 0.9582008763639488, 0.9661053355099235, 0.9687687945699802</t>
         </is>
       </c>
       <c r="BH30" t="n">
-        <v>0.9510450955395253</v>
+        <v>0.9647390412897157</v>
       </c>
       <c r="BI30" t="n">
-        <v>0.9502104991837786</v>
+        <v>0.964923962539737</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0.005850375436174139</v>
+        <v>0.003593501616458011</v>
       </c>
     </row>
     <row r="31">
@@ -7173,211 +7173,211 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SVC_no_fragmentation_Stk_diam</t>
+          <t>KNeighborsClassifier_no_fragmentation_Stk_sign_diam</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{'estimator': SVC(probability=True), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': KNeighborsClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.84</v>
+        <v>0.9066666666666666</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="G31" t="n">
-        <v>0.65</v>
+        <v>0.85</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.8292682926829269</v>
       </c>
       <c r="I31" t="n">
-        <v>0.9600000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8720538720538721</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="K31" t="n">
-        <v>0.8059701492537313</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="L31" t="n">
-        <v>0.6835443037974683</v>
+        <v>0.810126582278481</v>
       </c>
       <c r="M31" t="n">
-        <v>0.7397260273972602</v>
+        <v>0.8258064516129032</v>
       </c>
       <c r="N31" t="n">
-        <v>0.9543026361630472</v>
+        <v>0.9639995354778772</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.007559061050415039, 0.0065441131591796875, 0.006853818893432617, 0.006147861480712891, 0.006257057189941406, 0.0061380863189697266, 0.006921291351318359</t>
+          <t>0.0029959678649902344, 0.0020170211791992188, 0.001981973648071289, 0.0019562244415283203, 0.001981019973754883, 0.0019292831420898438, 0.0019729137420654297</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0.006631612777709961</v>
+        <v>0.002119200570242746</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.006544113159179688</v>
+        <v>0.001981019973754883</v>
       </c>
       <c r="R31" t="n">
-        <v>0.0004809189546825349</v>
+        <v>0.0003587908874962409</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>0.00507807731628418, 0.004826784133911133, 0.004841327667236328, 0.004404783248901367, 0.004908084869384766, 0.004684925079345703, 0.004890918731689453</t>
+          <t>0.006351947784423828, 0.005641937255859375, 0.005509853363037109, 0.005350828170776367, 0.005233049392700195, 0.00521397590637207, 0.0053560733795166016</t>
         </is>
       </c>
       <c r="T31" t="n">
-        <v>0.004804985863821847</v>
+        <v>0.005522523607526507</v>
       </c>
       <c r="U31" t="n">
-        <v>0.004841327667236328</v>
+        <v>0.005356073379516602</v>
       </c>
       <c r="V31" t="n">
-        <v>0.0001960194670902867</v>
+        <v>0.0003661667508639343</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>0.8518518518518519, 0.7358490566037735, 0.9056603773584906, 0.8490566037735849, 0.8301886792452831, 0.8490566037735849, 0.9245283018867925</t>
+          <t>0.9259259259259259, 0.7547169811320755, 0.9433962264150944, 0.8113207547169812, 0.8113207547169812, 0.8490566037735849, 0.9245283018867925</t>
         </is>
       </c>
       <c r="X31" t="n">
-        <v>0.849455924927623</v>
+        <v>0.8600379355096336</v>
       </c>
       <c r="Y31" t="n">
         <v>0.8490566037735849</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.05616125879043537</v>
+        <v>0.06698471018043896</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>0.6666666666666667, 0.5333333333333333, 0.8148148148148148, 0.6923076923076924, 0.6086956521739131, 0.6923076923076924, 0.8571428571428571</t>
+          <t>0.8749999999999999, 0.5517241379310344, 0.888888888888889, 0.6428571428571429, 0.5833333333333334, 0.7142857142857143, 0.8750000000000001</t>
         </is>
       </c>
       <c r="AB31" t="n">
-        <v>0.6950383869638529</v>
+        <v>0.7330127453280163</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.6923076923076924</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.1035427531027226</v>
+        <v>0.1354180579884486</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>0.8888888888888888, 0.5, 0.8461538461538461, 0.75, 0.7777777777777778, 0.75, 0.8571428571428571</t>
+          <t>0.8235294117647058, 0.5333333333333333, 0.9230769230769231, 0.6428571428571429, 0.7, 0.7142857142857143, 0.7777777777777778</t>
         </is>
       </c>
       <c r="AF31" t="n">
-        <v>0.7671376242804814</v>
+        <v>0.7306943290136567</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.1202562711166219</v>
+        <v>0.1169397797367399</v>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>0.5333333333333333, 0.5714285714285714, 0.7857142857142857, 0.6428571428571429, 0.5, 0.6428571428571429, 0.8571428571428571</t>
+          <t>0.9333333333333333, 0.5714285714285714, 0.8571428571428571, 0.6428571428571429, 0.5, 0.7142857142857143, 1.0</t>
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0.6476190476190476</v>
+        <v>0.745578231292517</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AL31" t="n">
-        <v>0.1216983797214332</v>
+        <v>0.1750904647078131</v>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>0.9572649572649573, 0.8553113553113554, 0.9816849816849818, 0.9120879120879121, 0.9304029304029304, 0.9120879120879122, 0.9798534798534799</t>
+          <t>0.970940170940171, 0.7866300366300367, 0.9322344322344321, 0.8974358974358976, 0.8873626373626374, 0.8965201465201464, 0.967032967032967</t>
         </is>
       </c>
       <c r="AN31" t="n">
-        <v>0.9326705040990756</v>
+        <v>0.9054508983080414</v>
       </c>
       <c r="AO31" t="n">
-        <v>0.9304029304029304</v>
+        <v>0.8974358974358976</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.04152521664175509</v>
+        <v>0.05780278617645025</v>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>0.8742138364779874, 0.890282131661442, 0.877742946708464, 0.8746081504702194, 0.877742946708464, 0.8652037617554859, 0.8526645768025078</t>
+          <t>0.8930817610062893, 0.9122257053291536, 0.8996865203761756, 0.9028213166144201, 0.8934169278996865, 0.9028213166144201, 0.9153605015673981</t>
         </is>
       </c>
       <c r="AR31" t="n">
-        <v>0.8732083357977958</v>
+        <v>0.902773435629649</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.8746081504702194</v>
+        <v>0.9028213166144201</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.01083466427330128</v>
+        <v>0.007917305243749024</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>0.7368421052631577, 0.787878787878788, 0.7664670658682634, 0.7468354430379747, 0.751592356687898, 0.7261146496815285, 0.6758620689655171</t>
+          <t>0.8045977011494253, 0.8390804597701149, 0.8181818181818181, 0.8187134502923977, 0.8023255813953488, 0.8208092485549133, 0.8421052631578947</t>
         </is>
       </c>
       <c r="AV31" t="n">
-        <v>0.7416560681975897</v>
+        <v>0.820830503214559</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.7468354430379747</v>
+        <v>0.8187134502923977</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.03266986692966924</v>
+        <v>0.01415783587470498</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>0.8235294117647058, 0.8125, 0.7804878048780488, 0.8082191780821918, 0.8194444444444444, 0.7916666666666666, 0.8166666666666667</t>
+          <t>0.7777777777777778, 0.8202247191011236, 0.7912087912087912, 0.813953488372093, 0.7931034482758621, 0.8068181818181818, 0.8372093023255814</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>0.8075020246432463</v>
+        <v>0.8057565298399157</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.8125</v>
+        <v>0.8068181818181818</v>
       </c>
       <c r="BB31" t="n">
-        <v>0.01458722479508863</v>
+        <v>0.01859904133833272</v>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>0.6666666666666666, 0.7647058823529411, 0.7529411764705882, 0.6941176470588235, 0.6941176470588235, 0.6705882352941176, 0.5764705882352941</t>
+          <t>0.8333333333333334, 0.8588235294117647, 0.8470588235294118, 0.8235294117647058, 0.8117647058823529, 0.8352941176470589, 0.8470588235294118</t>
         </is>
       </c>
       <c r="BD31" t="n">
-        <v>0.688515406162465</v>
+        <v>0.8366946778711483</v>
       </c>
       <c r="BE31" t="n">
-        <v>0.6941176470588235</v>
+        <v>0.8352941176470589</v>
       </c>
       <c r="BF31" t="n">
-        <v>0.0577818939081381</v>
+        <v>0.01469987872650075</v>
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>0.953958078958079, 0.960633484162896, 0.9481146304675717, 0.9543991955756662, 0.9564605329311212, 0.9564605329311212, 0.948868778280543</t>
+          <t>0.9665750915750917, 0.9727752639517344, 0.962242332830568, 0.9635746606334843, 0.9669683257918552, 0.9673956762192055, 0.9699849170437406</t>
         </is>
       </c>
       <c r="BH31" t="n">
-        <v>0.9541278904724283</v>
+        <v>0.9670737525779544</v>
       </c>
       <c r="BI31" t="n">
-        <v>0.9543991955756662</v>
+        <v>0.9669683257918552</v>
       </c>
       <c r="BJ31" t="n">
-        <v>0.004090497529779754</v>
+        <v>0.00331515533222134</v>
       </c>
     </row>
     <row r="32">
@@ -7393,211 +7393,211 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CatBoostClassifier_splashing_Stk_diam</t>
+          <t>SVC_splashing_Stk_sign_diam</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x31c795610&gt;, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': SVC(probability=True), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8518518518518519</v>
+        <v>0.8431372549019608</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9019607843137256</v>
+        <v>0.8686868686868686</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.9274691358024691</v>
       </c>
       <c r="J32" t="n">
-        <v>0.9966329966329966</v>
+        <v>0.8922558922558923</v>
       </c>
       <c r="K32" t="n">
-        <v>0.9948186528497409</v>
+        <v>0.9210526315789473</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0.9114583333333334</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9974025974025974</v>
+        <v>0.9162303664921465</v>
       </c>
       <c r="N32" t="n">
-        <v>0.9993799603174603</v>
+        <v>0.9509672619047618</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.6300218105316162, 0.6198470592498779, 0.5708799362182617, 0.5742392539978027, 0.5723519325256348, 0.6038317680358887, 0.5797450542449951</t>
+          <t>0.008783817291259766, 0.007644176483154297, 0.007768869400024414, 0.007622241973876953, 0.007577180862426758, 0.007479190826416016, 0.007491111755371094</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0.5929881164005825</v>
+        <v>0.007766655513218471</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.5797450542449951</v>
+        <v>0.007622241973876953</v>
       </c>
       <c r="R32" t="n">
-        <v>0.02284107936313209</v>
+        <v>0.000425095000994442</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.005659818649291992, 0.0055158138275146484, 0.005817890167236328, 0.005957841873168945, 0.005384922027587891, 0.005441904067993164, 0.005399942398071289</t>
+          <t>0.005681276321411133, 0.005949974060058594, 0.005304098129272461, 0.005135774612426758, 0.0056650638580322266, 0.0052127838134765625, 0.005366086959838867</t>
         </is>
       </c>
       <c r="T32" t="n">
-        <v>0.00559687614440918</v>
+        <v>0.005473579679216657</v>
       </c>
       <c r="U32" t="n">
-        <v>0.005515813827514648</v>
+        <v>0.005366086959838867</v>
       </c>
       <c r="V32" t="n">
-        <v>0.0002061206672660462</v>
+        <v>0.000274944440943485</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.9629629629629629, 0.8679245283018868, 0.9056603773584906, 0.8301886792452831, 0.9433962264150944, 0.9056603773584906, 0.8679245283018868</t>
+          <t>0.9074074074074074, 0.7358490566037735, 0.9245283018867925, 0.7358490566037735, 0.8867924528301887, 0.8490566037735849, 0.8301886792452831</t>
         </is>
       </c>
       <c r="X32" t="n">
-        <v>0.8976739542777279</v>
+        <v>0.838524508335829</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.9056603773584906</v>
+        <v>0.8490566037735849</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.04277025964339304</v>
+        <v>0.07145049096409614</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.9722222222222222, 0.8985507246376812, 0.9275362318840579, 0.8656716417910447, 0.9565217391304348, 0.9253731343283583, 0.9014084507042254</t>
+          <t>0.9315068493150684, 0.7941176470588236, 0.9428571428571428, 0.787878787878788, 0.9117647058823528, 0.8787878787878787, 0.8695652173913043</t>
         </is>
       </c>
       <c r="AB32" t="n">
-        <v>0.9210405920997179</v>
+        <v>0.8737826041673371</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.9253731343283583</v>
+        <v>0.8787878787878787</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.03358650045032965</v>
+        <v>0.05771213117467276</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>0.9459459459459459, 0.9117647058823529, 0.9142857142857143, 0.8787878787878788, 0.9428571428571428, 0.9393939393939394, 0.8648648648648649</t>
+          <t>0.8947368421052632, 0.8181818181818182, 0.9166666666666666, 0.8125, 0.9117647058823529, 0.90625, 0.8571428571428571</t>
         </is>
       </c>
       <c r="AF32" t="n">
-        <v>0.9139857417168341</v>
+        <v>0.8738918414255654</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.9142857142857143</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.02965844145929741</v>
+        <v>0.0412287995289299</v>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>1.0, 0.8857142857142857, 0.9411764705882353, 0.8529411764705882, 0.9705882352941176, 0.9117647058823529, 0.9411764705882353</t>
+          <t>0.9714285714285714, 0.7714285714285715, 0.9705882352941176, 0.7647058823529411, 0.9117647058823529, 0.8529411764705882, 0.8823529411764706</t>
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0.9290516206482593</v>
+        <v>0.8750300120048019</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.04632609353460133</v>
+        <v>0.07857635781408312</v>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>0.9984962406015038, 0.9380952380952381, 0.976780185758514, 0.9473684210526316, 0.955108359133127, 0.9489164086687306, 0.9427244582043344</t>
+          <t>0.9849624060150376, 0.8571428571428572, 0.9442724458204335, 0.9071207430340558, 0.9597523219814241, 0.9133126934984521, 0.8560371517027864</t>
         </is>
       </c>
       <c r="AN32" t="n">
-        <v>0.9582127587877256</v>
+        <v>0.9175143741707208</v>
       </c>
       <c r="AO32" t="n">
-        <v>0.9489164086687306</v>
+        <v>0.9133126934984521</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.02009182288819399</v>
+        <v>0.04566825448295116</v>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>0.9968553459119497, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+          <t>0.8584905660377359, 0.8934169278996865, 0.8746081504702194, 0.8840125391849529, 0.8808777429467085, 0.8746081504702194, 0.890282131661442</t>
         </is>
       </c>
       <c r="AR32" t="n">
-        <v>0.9973116235315324</v>
+        <v>0.8794708869529949</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.9968652037617555</v>
+        <v>0.8808777429467085</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.001097530367727006</v>
+        <v>0.01083280201797767</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>0.9975669099756691, 0.9975669099756691, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+          <t>0.8915662650602411, 0.9154228855721392, 0.9033816425120774, 0.9104116222760291, 0.905940594059406, 0.9033816425120774, 0.914004914004914</t>
         </is>
       </c>
       <c r="AV32" t="n">
-        <v>0.9979212271324464</v>
+        <v>0.9063013665709835</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.9975786924939467</v>
+        <v>0.905940594059406</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.0008486710488706931</v>
+        <v>0.007499941946569862</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>0.9951456310679612, 0.9951456310679612, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+          <t>0.8809523809523809, 0.934010152284264, 0.8990384615384616, 0.9082125603864735, 0.9242424242424242, 0.8990384615384616, 0.9253731343283582</t>
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>0.9958525129483339</v>
+        <v>0.9101239393244034</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.9951690821256038</v>
+        <v>0.9082125603864735</v>
       </c>
       <c r="BB32" t="n">
-        <v>0.001693235431574141</v>
+        <v>0.01733217304401899</v>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+          <t>0.9024390243902439, 0.8975609756097561, 0.9077669902912622, 0.912621359223301, 0.8883495145631068, 0.9077669902912622, 0.9029126213592233</t>
         </is>
       </c>
       <c r="BD32" t="n">
-        <v>1</v>
+        <v>0.9027739251040222</v>
       </c>
       <c r="BE32" t="n">
-        <v>1</v>
+        <v>0.9029126213592233</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>0.007389212365561095</v>
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>0.9993308871141808, 0.9998716302952503, 0.9994630122862789, 0.9995059713033766, 0.9992911762178881, 1.0, 0.9995489303204742</t>
+          <t>0.9411396503345565, 0.9603765511339324, 0.9497594295042531, 0.9514348311710629, 0.947267806512587, 0.9502104991837786, 0.9572342984792508</t>
         </is>
       </c>
       <c r="BH32" t="n">
-        <v>0.999573086791064</v>
+        <v>0.9510604380456317</v>
       </c>
       <c r="BI32" t="n">
-        <v>0.9995059713033766</v>
+        <v>0.9502104991837786</v>
       </c>
       <c r="BJ32" t="n">
-        <v>0.0002469013067630454</v>
+        <v>0.005858666205929211</v>
       </c>
     </row>
     <row r="33">
@@ -7613,211 +7613,211 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CatBoostClassifier_no_fragmentation_Stk_diam</t>
+          <t>SVC_no_fragmentation_Stk_sign_diam</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x31c709410&gt;, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': SVC(probability=True), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.96</v>
+        <v>0.84</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="G33" t="n">
-        <v>0.95</v>
+        <v>0.65</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9268292682926829</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9881818181818182</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>0.9966329966329966</v>
+        <v>0.8720538720538721</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>0.8059701492537313</v>
       </c>
       <c r="L33" t="n">
-        <v>0.9873417721518988</v>
+        <v>0.6835443037974683</v>
       </c>
       <c r="M33" t="n">
-        <v>0.9936305732484078</v>
+        <v>0.7397260273972602</v>
       </c>
       <c r="N33" t="n">
-        <v>0.9999419347346418</v>
+        <v>0.9543026361630472</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.6124680042266846, 0.5860397815704346, 0.5696671009063721, 0.5573601722717285, 0.5754611492156982, 0.5673670768737793, 0.5653929710388184</t>
+          <t>0.007184743881225586, 0.006306171417236328, 0.006584882736206055, 0.006494998931884766, 0.006639242172241211, 0.006242036819458008, 0.006880044937133789</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0.5762508937290737</v>
+        <v>0.006618874413626534</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.5696671009063721</v>
+        <v>0.006584882736206055</v>
       </c>
       <c r="R33" t="n">
-        <v>0.01692482321722631</v>
+        <v>0.0003035794665890919</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>0.005569934844970703, 0.005295991897583008, 0.005210161209106445, 0.0047948360443115234, 0.005314826965332031, 0.00512385368347168, 0.004667043685913086</t>
+          <t>0.0052242279052734375, 0.00495600700378418, 0.004622936248779297, 0.00446629524230957, 0.005150794982910156, 0.004815101623535156, 0.00541377067565918</t>
         </is>
       </c>
       <c r="T33" t="n">
-        <v>0.005139521190098354</v>
+        <v>0.004949876240321568</v>
       </c>
       <c r="U33" t="n">
-        <v>0.005210161209106445</v>
+        <v>0.00495600700378418</v>
       </c>
       <c r="V33" t="n">
-        <v>0.0002897657763899741</v>
+        <v>0.0003139102118260986</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>0.9074074074074074, 0.8490566037735849, 0.9433962264150944, 0.8867924528301887, 0.9433962264150944, 0.9245283018867925, 0.9622641509433962</t>
+          <t>0.8518518518518519, 0.7358490566037735, 0.9056603773584906, 0.8490566037735849, 0.8301886792452831, 0.8490566037735849, 0.9245283018867925</t>
         </is>
       </c>
       <c r="X33" t="n">
-        <v>0.9166916242387941</v>
+        <v>0.849455924927623</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.9245283018867925</v>
+        <v>0.8490566037735849</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.03609351621237702</v>
+        <v>0.05616125879043537</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>0.8148148148148148, 0.75, 0.888888888888889, 0.7999999999999999, 0.88, 0.8571428571428571, 0.9285714285714286</t>
+          <t>0.6666666666666667, 0.5333333333333333, 0.8148148148148148, 0.6923076923076924, 0.6086956521739131, 0.6923076923076924, 0.8571428571428571</t>
         </is>
       </c>
       <c r="AB33" t="n">
-        <v>0.8456311413454271</v>
+        <v>0.6950383869638529</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.6923076923076924</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.05636770130116441</v>
+        <v>0.1035427531027226</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>0.9166666666666666, 0.6666666666666666, 0.9230769230769231, 0.75, 1.0, 0.8571428571428571, 0.9285714285714286</t>
+          <t>0.8888888888888888, 0.5, 0.8461538461538461, 0.75, 0.7777777777777778, 0.75, 0.8571428571428571</t>
         </is>
       </c>
       <c r="AF33" t="n">
-        <v>0.8631606488749346</v>
+        <v>0.7671376242804814</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.1075093771898189</v>
+        <v>0.1202562711166219</v>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>0.7333333333333333, 0.8571428571428571, 0.8571428571428571, 0.8571428571428571, 0.7857142857142857, 0.8571428571428571, 0.9285714285714286</t>
+          <t>0.5333333333333333, 0.5714285714285714, 0.7857142857142857, 0.6428571428571429, 0.5, 0.6428571428571429, 0.8571428571428571</t>
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0.8394557823129251</v>
+        <v>0.6476190476190476</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.05774704878831079</v>
+        <v>0.1216983797214332</v>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>0.982905982905983, 0.9175824175824175, 0.9926739926739927, 0.9267399267399268, 0.989010989010989, 0.9175824175824175, 0.9816849816849816</t>
+          <t>0.9572649572649573, 0.8553113553113554, 0.9816849816849818, 0.9120879120879121, 0.9304029304029304, 0.9120879120879122, 0.9798534798534799</t>
         </is>
       </c>
       <c r="AN33" t="n">
-        <v>0.9583115297401011</v>
+        <v>0.9326705040990756</v>
       </c>
       <c r="AO33" t="n">
-        <v>0.9816849816849816</v>
+        <v>0.9304029304029304</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.03292616916475692</v>
+        <v>0.04152521664175509</v>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>0.9937106918238994, 1.0, 0.9968652037617555, 0.9937304075235109, 0.9937304075235109, 0.9968652037617555, 0.9968652037617555</t>
+          <t>0.8742138364779874, 0.890282131661442, 0.877742946708464, 0.8746081504702194, 0.877742946708464, 0.8652037617554859, 0.8526645768025078</t>
         </is>
       </c>
       <c r="AR33" t="n">
-        <v>0.9959667311651696</v>
+        <v>0.8732083357977958</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.9968652037617555</v>
+        <v>0.8746081504702194</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.00219678391174473</v>
+        <v>0.01083466427330128</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>0.9880952380952381, 1.0, 0.9940828402366864, 0.988095238095238, 0.9882352941176471, 0.9941520467836257, 0.9940828402366864</t>
+          <t>0.7368421052631577, 0.787878787878788, 0.7664670658682634, 0.7468354430379747, 0.751592356687898, 0.7261146496815285, 0.6758620689655171</t>
         </is>
       </c>
       <c r="AV33" t="n">
-        <v>0.9923919282235888</v>
+        <v>0.7416560681975897</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.9940828402366864</v>
+        <v>0.7468354430379747</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.004155888070493598</v>
+        <v>0.03266986692966924</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>0.9880952380952381, 1.0, 1.0, 1.0, 0.9882352941176471, 0.9883720930232558, 1.0</t>
+          <t>0.8235294117647058, 0.8125, 0.7804878048780488, 0.8082191780821918, 0.8194444444444444, 0.7916666666666666, 0.8166666666666667</t>
         </is>
       </c>
       <c r="AZ33" t="n">
-        <v>0.9949575178908773</v>
+        <v>0.8075020246432463</v>
       </c>
       <c r="BA33" t="n">
-        <v>1</v>
+        <v>0.8125</v>
       </c>
       <c r="BB33" t="n">
-        <v>0.005823026954887154</v>
+        <v>0.01458722479508863</v>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>0.9880952380952381, 1.0, 0.9882352941176471, 0.9764705882352941, 0.9882352941176471, 1.0, 0.9882352941176471</t>
+          <t>0.6666666666666666, 0.7647058823529411, 0.7529411764705882, 0.6941176470588235, 0.6941176470588235, 0.6705882352941176, 0.5764705882352941</t>
         </is>
       </c>
       <c r="BD33" t="n">
-        <v>0.9898959583833534</v>
+        <v>0.688515406162465</v>
       </c>
       <c r="BE33" t="n">
-        <v>0.9882352941176471</v>
+        <v>0.6941176470588235</v>
       </c>
       <c r="BF33" t="n">
-        <v>0.007520827163479012</v>
+        <v>0.0577818939081381</v>
       </c>
       <c r="BG33" t="inlineStr">
         <is>
-          <t>0.9998982498982498, 0.9999999999999999, 0.9999497234791352, 1.0, 0.9999497234791352, 0.9999999999999999, 0.9999497234791352</t>
+          <t>0.9539326414326413, 0.960633484162896, 0.9481146304675716, 0.9544494720965309, 0.9564605329311212, 0.9564605329311212, 0.9487179487179487</t>
         </is>
       </c>
       <c r="BH33" t="n">
-        <v>0.9999639171908079</v>
+        <v>0.954109891819976</v>
       </c>
       <c r="BI33" t="n">
-        <v>0.9999497234791352</v>
+        <v>0.9544494720965309</v>
       </c>
       <c r="BJ33" t="n">
-        <v>3.550147888793166e-05</v>
+        <v>0.004119140442349333</v>
       </c>
     </row>
     <row r="34">
@@ -7833,10 +7833,450 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>XGBClassifier_splashing_Stk_diam</t>
+          <t>CatBoostClassifier_splashing_Stk_sign_diam</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
+        <is>
+          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x313c94ad0&gt;, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.9019607843137256</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.9993799603174603</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0.6523277759552002, 0.6203281879425049, 0.5884196758270264, 0.5701701641082764, 0.5647592544555664, 0.5600991249084473, 0.5552771091461182</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>0.5873401846204486</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.5701701641082764</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.03356780950881129</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>0.006026029586791992, 0.0058689117431640625, 0.006097316741943359, 0.005630970001220703, 0.005321979522705078, 0.007342100143432617, 0.005506992340087891</t>
+        </is>
+      </c>
+      <c r="T34" t="n">
+        <v>0.005970614297049386</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.005868911743164062</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.0006166119220999024</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.8679245283018868, 0.9056603773584906, 0.8301886792452831, 0.9433962264150944, 0.9056603773584906, 0.8679245283018868</t>
+        </is>
+      </c>
+      <c r="X34" t="n">
+        <v>0.8976739542777279</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.04277025964339304</v>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8985507246376812, 0.9275362318840579, 0.8656716417910447, 0.9565217391304348, 0.9253731343283583, 0.9014084507042254</t>
+        </is>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.9210405920997179</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.9253731343283583</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.03358650045032965</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.9117647058823529, 0.9142857142857143, 0.8787878787878788, 0.9428571428571428, 0.9393939393939394, 0.8648648648648649</t>
+        </is>
+      </c>
+      <c r="AF34" t="n">
+        <v>0.9139857417168341</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0.02965844145929741</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>1.0, 0.8857142857142857, 0.9411764705882353, 0.8529411764705882, 0.9705882352941176, 0.9117647058823529, 0.9411764705882353</t>
+        </is>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0.9290516206482593</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0.04632609353460133</v>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>0.9984962406015038, 0.9380952380952381, 0.976780185758514, 0.9473684210526316, 0.955108359133127, 0.9489164086687306, 0.9427244582043344</t>
+        </is>
+      </c>
+      <c r="AN34" t="n">
+        <v>0.9582127587877256</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0.9489164086687306</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0.02009182288819399</v>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="AR34" t="n">
+        <v>0.9973116235315324</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0.001097530367727006</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 0.9975669099756691, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="AV34" t="n">
+        <v>0.9979212271324464</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0.0008486710488706931</v>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 0.9951456310679612, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0.9958525129483339</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0.001693235431574141</v>
+      </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BD34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG34" t="inlineStr">
+        <is>
+          <t>0.9993308871141808, 0.9998716302952503, 0.9994630122862789, 0.9995059713033766, 0.9992911762178881, 1.0, 0.9995489303204742</t>
+        </is>
+      </c>
+      <c r="BH34" t="n">
+        <v>0.999573086791064</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>0.9995059713033766</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>0.0002469013067630454</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_no_fragmentation_Stk_sign_diam</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x313ec0210&gt;, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.9268292682926829</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.9881818181818182</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.9873417721518988</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.9936305732484078</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.9999419347346418</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0.5537810325622559, 0.5640349388122559, 0.5537948608398438, 0.5568521022796631, 0.5563790798187256, 0.5508599281311035, 0.574822187423706</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>0.5586463042667934</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.5563790798187256</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.007624125908208271</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>0.00483393669128418, 0.005019187927246094, 0.005173921585083008, 0.004854917526245117, 0.004739999771118164, 0.004809141159057617, 0.005529880523681641</t>
+        </is>
+      </c>
+      <c r="T35" t="n">
+        <v>0.004994426454816546</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.004854917526245117</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.0002574118367026693</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.8490566037735849, 0.9433962264150944, 0.8867924528301887, 0.9433962264150944, 0.9245283018867925, 0.9622641509433962</t>
+        </is>
+      </c>
+      <c r="X35" t="n">
+        <v>0.9166916242387941</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.9245283018867925</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0.03609351621237702</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>0.8148148148148148, 0.75, 0.888888888888889, 0.7999999999999999, 0.88, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.8456311413454271</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.05636770130116441</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>0.9166666666666666, 0.6666666666666666, 0.9230769230769231, 0.75, 1.0, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.8631606488749346</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.1075093771898189</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.8571428571428571, 0.8571428571428571, 0.8571428571428571, 0.7857142857142857, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.8394557823129251</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0.05774704878831079</v>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>0.982905982905983, 0.9175824175824175, 0.9926739926739927, 0.9267399267399268, 0.989010989010989, 0.9175824175824175, 0.9816849816849816</t>
+        </is>
+      </c>
+      <c r="AN35" t="n">
+        <v>0.9583115297401011</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0.9816849816849816</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0.03292616916475692</v>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>0.9937106918238994, 1.0, 0.9968652037617555, 0.9937304075235109, 0.9937304075235109, 0.9968652037617555, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="AR35" t="n">
+        <v>0.9959667311651696</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0.00219678391174473</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 0.9940828402366864, 0.988095238095238, 0.9882352941176471, 0.9941520467836257, 0.9940828402366864</t>
+        </is>
+      </c>
+      <c r="AV35" t="n">
+        <v>0.9923919282235888</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0.9940828402366864</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0.004155888070493598</v>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 1.0, 1.0, 0.9882352941176471, 0.9883720930232558, 1.0</t>
+        </is>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0.9949575178908773</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0.005823026954887154</v>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 0.9882352941176471, 0.9764705882352941, 0.9882352941176471, 1.0, 0.9882352941176471</t>
+        </is>
+      </c>
+      <c r="BD35" t="n">
+        <v>0.9898959583833534</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0.9882352941176471</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0.007520827163479012</v>
+      </c>
+      <c r="BG35" t="inlineStr">
+        <is>
+          <t>0.9998982498982498, 0.9999999999999999, 0.9999497234791352, 1.0, 0.9999497234791352, 0.9999999999999999, 0.9999497234791352</t>
+        </is>
+      </c>
+      <c r="BH35" t="n">
+        <v>0.9999639171908079</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>0.9999497234791352</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>3.550147888793166e-05</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>XGBClassifier_splashing_Stk_sign_diam</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>{'estimator': XGBClassifier(base_score=None, booster=None, callbacks=None,
               colsample_bylevel=None, colsample_bynode=None,
@@ -7851,222 +8291,222 @@
               num_parallel_tree=None, random_state=None, ...), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="E36" t="n">
         <v>0.88</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F36" t="n">
         <v>0.8679245283018868</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G36" t="n">
         <v>0.9583333333333334</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H36" t="n">
         <v>0.910891089108911</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I36" t="n">
         <v>0.9402006172839507</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J36" t="n">
         <v>0.9966329966329966</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K36" t="n">
         <v>0.9948186528497409</v>
       </c>
-      <c r="L34" t="n">
+      <c r="L36" t="n">
         <v>1</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M36" t="n">
         <v>0.9974025974025974</v>
       </c>
-      <c r="N34" t="n">
+      <c r="N36" t="n">
         <v>0.9999751984126984</v>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>0.0447840690612793, 0.03411102294921875, 0.03708696365356445, 0.057431936264038086, 0.03099799156188965, 0.03522491455078125, 0.03696894645690918</t>
-        </is>
-      </c>
-      <c r="P34" t="n">
-        <v>0.03951512064252581</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0.03696894645690918</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0.008292032981517006</v>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>0.006973981857299805, 0.005768299102783203, 0.0055272579193115234, 0.006621122360229492, 0.0056688785552978516, 0.005767107009887695, 0.006066083908081055</t>
-        </is>
-      </c>
-      <c r="T34" t="n">
-        <v>0.006056104387555804</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0.005768299102783203</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0.0005011155766490603</v>
-      </c>
-      <c r="W34" t="inlineStr">
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0.040802955627441406, 0.030202150344848633, 0.030688047409057617, 0.03177809715270996, 0.03363394737243652, 0.02948927879333496, 0.03243398666381836</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>0.0327183519090925</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.03177809715270996</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.003546515287605371</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>0.0064771175384521484, 0.005926847457885742, 0.005608081817626953, 0.007224082946777344, 0.006040096282958984, 0.005604743957519531, 0.005717039108276367</t>
+        </is>
+      </c>
+      <c r="T36" t="n">
+        <v>0.006085429872785296</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.005926847457885742</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.0005440306500429145</v>
+      </c>
+      <c r="W36" t="inlineStr">
         <is>
           <t>0.9629629629629629, 0.8301886792452831, 0.8867924528301887, 0.8679245283018868, 0.9245283018867925, 0.8679245283018868, 0.8679245283018868</t>
         </is>
       </c>
-      <c r="X34" t="n">
+      <c r="X36" t="n">
         <v>0.8868922831186984</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="Y36" t="n">
         <v>0.8679245283018868</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="Z36" t="n">
         <v>0.04052839228310491</v>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>0.9722222222222222, 0.8695652173913043, 0.9117647058823528, 0.8985507246376812, 0.9411764705882353, 0.888888888888889, 0.8955223880597014</t>
         </is>
       </c>
-      <c r="AB34" t="n">
+      <c r="AB36" t="n">
         <v>0.9110986596671981</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AC36" t="n">
         <v>0.8985507246376812</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AD36" t="n">
         <v>0.03220377059286659</v>
       </c>
-      <c r="AE34" t="inlineStr">
+      <c r="AE36" t="inlineStr">
         <is>
           <t>0.9459459459459459, 0.8823529411764706, 0.9117647058823529, 0.8857142857142857, 0.9411764705882353, 0.9655172413793104, 0.9090909090909091</t>
         </is>
       </c>
-      <c r="AF34" t="n">
+      <c r="AF36" t="n">
         <v>0.9202232142539301</v>
       </c>
-      <c r="AG34" t="n">
+      <c r="AG36" t="n">
         <v>0.9117647058823529</v>
       </c>
-      <c r="AH34" t="n">
+      <c r="AH36" t="n">
         <v>0.02921043131675378</v>
       </c>
-      <c r="AI34" t="inlineStr">
+      <c r="AI36" t="inlineStr">
         <is>
           <t>1.0, 0.8571428571428571, 0.9117647058823529, 0.9117647058823529, 0.9411764705882353, 0.8235294117647058, 0.8823529411764706</t>
         </is>
       </c>
-      <c r="AJ34" t="n">
+      <c r="AJ36" t="n">
         <v>0.9039615846338533</v>
       </c>
-      <c r="AK34" t="n">
+      <c r="AK36" t="n">
         <v>0.9117647058823529</v>
       </c>
-      <c r="AL34" t="n">
+      <c r="AL36" t="n">
         <v>0.05326264238050186</v>
       </c>
-      <c r="AM34" t="inlineStr">
+      <c r="AM36" t="inlineStr">
         <is>
           <t>0.9894736842105264, 0.9380952380952381, 0.9736842105263158, 0.9179566563467493, 0.9504643962848297, 0.9357585139318886, 0.9380804953560372</t>
         </is>
       </c>
-      <c r="AN34" t="n">
+      <c r="AN36" t="n">
         <v>0.9490733135359408</v>
       </c>
-      <c r="AO34" t="n">
+      <c r="AO36" t="n">
         <v>0.9380952380952381</v>
       </c>
-      <c r="AP34" t="n">
+      <c r="AP36" t="n">
         <v>0.02276184698623345</v>
       </c>
-      <c r="AQ34" t="inlineStr">
+      <c r="AQ36" t="inlineStr">
         <is>
           <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
         </is>
       </c>
-      <c r="AR34" t="n">
+      <c r="AR36" t="n">
         <v>0.9977594515655674</v>
       </c>
-      <c r="AS34" t="n">
+      <c r="AS36" t="n">
         <v>0.9968652037617555</v>
       </c>
-      <c r="AT34" t="n">
+      <c r="AT36" t="n">
         <v>0.001417051170840857</v>
       </c>
-      <c r="AU34" t="inlineStr">
+      <c r="AU36" t="inlineStr">
         <is>
           <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
         </is>
       </c>
-      <c r="AV34" t="n">
+      <c r="AV36" t="n">
         <v>0.9982688114216364</v>
       </c>
-      <c r="AW34" t="n">
+      <c r="AW36" t="n">
         <v>0.9975786924939467</v>
       </c>
-      <c r="AX34" t="n">
+      <c r="AX36" t="n">
         <v>0.001094907038779773</v>
       </c>
-      <c r="AY34" t="inlineStr">
+      <c r="AY36" t="inlineStr">
         <is>
           <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
         </is>
       </c>
-      <c r="AZ34" t="n">
+      <c r="AZ36" t="n">
         <v>0.9965459942243395</v>
       </c>
-      <c r="BA34" t="n">
+      <c r="BA36" t="n">
         <v>0.9951690821256038</v>
       </c>
-      <c r="BB34" t="n">
+      <c r="BB36" t="n">
         <v>0.002184519446236978</v>
       </c>
-      <c r="BC34" t="inlineStr">
+      <c r="BC36" t="inlineStr">
         <is>
           <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
         </is>
       </c>
-      <c r="BD34" t="n">
+      <c r="BD36" t="n">
         <v>1</v>
       </c>
-      <c r="BE34" t="n">
+      <c r="BE36" t="n">
         <v>1</v>
       </c>
-      <c r="BF34" t="n">
+      <c r="BF36" t="n">
         <v>0</v>
       </c>
-      <c r="BG34" t="inlineStr">
+      <c r="BG36" t="inlineStr">
         <is>
           <t>0.9999784157133607, 1.0, 0.9999785204914511, 0.9999785204914512, 0.9999785204914511, 1.0, 0.9999785204914512</t>
         </is>
       </c>
-      <c r="BH34" t="n">
+      <c r="BH36" t="n">
         <v>0.999984642525595</v>
       </c>
-      <c r="BI34" t="n">
+      <c r="BI36" t="n">
         <v>0.9999785204914512</v>
       </c>
-      <c r="BJ34" t="n">
+      <c r="BJ36" t="n">
         <v>9.712984233463659e-06</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>df_dimless</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>no_fragmentation</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>XGBClassifier_no_fragmentation_Stk_diam</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>XGBClassifier_no_fragmentation_Stk_sign_diam</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>{'estimator': XGBClassifier(base_score=None, booster=None, callbacks=None,
               colsample_bylevel=None, colsample_bynode=None,
@@ -8081,203 +8521,2863 @@
               num_parallel_tree=None, random_state=None, ...), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
-      <c r="E35" t="n">
+      <c r="E37" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F37" t="n">
         <v>0.8947368421052632</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G37" t="n">
         <v>0.85</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H37" t="n">
         <v>0.8717948717948718</v>
       </c>
-      <c r="I35" t="n">
+      <c r="I37" t="n">
         <v>0.9872727272727273</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J37" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K37" t="n">
         <v>1</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L37" t="n">
         <v>1</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M37" t="n">
         <v>1</v>
       </c>
-      <c r="N35" t="n">
+      <c r="N37" t="n">
         <v>1</v>
       </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>0.04535508155822754, 0.030457735061645508, 0.03690505027770996, 0.03257584571838379, 0.031723976135253906, 0.0294339656829834, 0.031539201736450195</t>
-        </is>
-      </c>
-      <c r="P35" t="n">
-        <v>0.0339986937386649</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0.03172397613525391</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0.005127482266990151</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>0.005602121353149414, 0.00534510612487793, 0.0051538944244384766, 0.005134105682373047, 0.005222797393798828, 0.004813194274902344, 0.004709959030151367</t>
-        </is>
-      </c>
-      <c r="T35" t="n">
-        <v>0.00514016832624163</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0.005153894424438477</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0.0002814363397437765</v>
-      </c>
-      <c r="W35" t="inlineStr">
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0.04026985168457031, 0.031887054443359375, 0.04086709022521973, 0.03770804405212402, 0.04977989196777344, 0.05083012580871582, 0.038622140884399414</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>0.04142345700945173</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.04026985168457031</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.006239853612459083</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>0.005672931671142578, 0.004897117614746094, 0.005450010299682617, 0.005733966827392578, 0.005303859710693359, 0.005242824554443359, 0.005798816680908203</t>
+        </is>
+      </c>
+      <c r="T37" t="n">
+        <v>0.005442789622715541</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.005450010299682617</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.0002979938687250144</v>
+      </c>
+      <c r="W37" t="inlineStr">
         <is>
           <t>0.8888888888888888, 0.8490566037735849, 0.9245283018867925, 0.8867924528301887, 0.9245283018867925, 0.9056603773584906, 0.9433962264150944</t>
         </is>
       </c>
-      <c r="X35" t="n">
+      <c r="X37" t="n">
         <v>0.9032644504342617</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="Y37" t="n">
         <v>0.9056603773584906</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="Z37" t="n">
         <v>0.0291230806376597</v>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>0.7499999999999999, 0.7333333333333334, 0.8461538461538461, 0.7999999999999999, 0.8461538461538461, 0.8148148148148148, 0.896551724137931</t>
         </is>
       </c>
-      <c r="AB35" t="n">
+      <c r="AB37" t="n">
         <v>0.8124296520848245</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AC37" t="n">
         <v>0.8148148148148148</v>
       </c>
-      <c r="AD35" t="n">
+      <c r="AD37" t="n">
         <v>0.05300274910577236</v>
       </c>
-      <c r="AE35" t="inlineStr">
+      <c r="AE37" t="inlineStr">
         <is>
           <t>1.0, 0.6875, 0.9166666666666666, 0.75, 0.9166666666666666, 0.8461538461538461, 0.8666666666666667</t>
         </is>
       </c>
-      <c r="AF35" t="n">
+      <c r="AF37" t="n">
         <v>0.8548076923076923</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AG37" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="AH35" t="n">
+      <c r="AH37" t="n">
         <v>0.09850736899831899</v>
       </c>
-      <c r="AI35" t="inlineStr">
+      <c r="AI37" t="inlineStr">
         <is>
           <t>0.6, 0.7857142857142857, 0.7857142857142857, 0.8571428571428571, 0.7857142857142857, 0.7857142857142857, 0.9285714285714286</t>
         </is>
       </c>
-      <c r="AJ35" t="n">
+      <c r="AJ37" t="n">
         <v>0.789795918367347</v>
       </c>
-      <c r="AK35" t="n">
+      <c r="AK37" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="AL35" t="n">
+      <c r="AL37" t="n">
         <v>0.09249199341734415</v>
       </c>
-      <c r="AM35" t="inlineStr">
+      <c r="AM37" t="inlineStr">
         <is>
           <t>0.9760683760683759, 0.9084249084249083, 0.978021978021978, 0.9157509157509157, 0.9853479853479853, 0.9285714285714286, 0.9871794871794871</t>
         </is>
       </c>
-      <c r="AN35" t="n">
+      <c r="AN37" t="n">
         <v>0.9541950113378684</v>
       </c>
-      <c r="AO35" t="n">
+      <c r="AO37" t="n">
         <v>0.9760683760683759</v>
       </c>
-      <c r="AP35" t="n">
+      <c r="AP37" t="n">
         <v>0.03236857087222359</v>
       </c>
-      <c r="AQ35" t="inlineStr">
+      <c r="AQ37" t="inlineStr">
         <is>
           <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
         </is>
       </c>
-      <c r="AR35" t="n">
+      <c r="AR37" t="n">
         <v>1</v>
       </c>
-      <c r="AS35" t="n">
+      <c r="AS37" t="n">
         <v>1</v>
       </c>
-      <c r="AT35" t="n">
+      <c r="AT37" t="n">
         <v>0</v>
       </c>
-      <c r="AU35" t="inlineStr">
+      <c r="AU37" t="inlineStr">
         <is>
           <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
         </is>
       </c>
-      <c r="AV35" t="n">
+      <c r="AV37" t="n">
         <v>1</v>
       </c>
-      <c r="AW35" t="n">
+      <c r="AW37" t="n">
         <v>1</v>
       </c>
-      <c r="AX35" t="n">
+      <c r="AX37" t="n">
         <v>0</v>
       </c>
-      <c r="AY35" t="inlineStr">
+      <c r="AY37" t="inlineStr">
         <is>
           <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
         </is>
       </c>
-      <c r="AZ35" t="n">
+      <c r="AZ37" t="n">
         <v>1</v>
       </c>
-      <c r="BA35" t="n">
+      <c r="BA37" t="n">
         <v>1</v>
       </c>
-      <c r="BB35" t="n">
+      <c r="BB37" t="n">
         <v>0</v>
       </c>
-      <c r="BC35" t="inlineStr">
+      <c r="BC37" t="inlineStr">
         <is>
           <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
         </is>
       </c>
-      <c r="BD35" t="n">
+      <c r="BD37" t="n">
         <v>1</v>
       </c>
-      <c r="BE35" t="n">
+      <c r="BE37" t="n">
         <v>1</v>
       </c>
-      <c r="BF35" t="n">
+      <c r="BF37" t="n">
         <v>0</v>
       </c>
-      <c r="BG35" t="inlineStr">
+      <c r="BG37" t="inlineStr">
         <is>
           <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
         </is>
       </c>
-      <c r="BH35" t="n">
+      <c r="BH37" t="n">
         <v>1</v>
       </c>
-      <c r="BI35" t="n">
+      <c r="BI37" t="n">
         <v>1</v>
       </c>
-      <c r="BJ35" t="n">
+      <c r="BJ37" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Logit_splashing_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>{'estimator': StatsModelsEstimator(model_class=&lt;class 'statsmodels.discrete.discrete_model.Logit'&gt;), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.8742283950617283</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.8451178451178452</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.9010989010989011</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.8770053475935828</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.9131696428571429</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0.0048160552978515625, 0.003237009048461914, 0.003264188766479492, 0.0032880306243896484, 0.0031218528747558594, 0.008654117584228516, 0.003083944320678711</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>0.004209314073835101</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.003264188766479492</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.001899655765919592</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>0.008605003356933594, 0.0076029300689697266, 0.004608631134033203, 0.0048449039459228516, 0.004541158676147461, 0.0052700042724609375, 0.012530088424682617</t>
+        </is>
+      </c>
+      <c r="T38" t="n">
+        <v>0.006857531411307198</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.005270004272460938</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.002745937967926399</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.7735849056603774, 0.8490566037735849, 0.8301886792452831, 0.8490566037735849, 0.7358490566037735, 0.7358490566037735</t>
+        </is>
+      </c>
+      <c r="X38" t="n">
+        <v>0.8142158330837576</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0.8301886792452831</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.06447104647695899</v>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.823529411764706, 0.8787878787878787, 0.8656716417910447, 0.8823529411764706, 0.78125, 0.7999999999999999</t>
+        </is>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.8534927166253203</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0.8656716417910447</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.05152719830957708</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8484848484848485, 0.90625, 0.8787878787878788, 0.8823529411764706, 0.8333333333333334, 0.7777777777777778</t>
+        </is>
+      </c>
+      <c r="AF38" t="n">
+        <v>0.8671205603453502</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0.04943436338982635</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8, 0.8529411764705882, 0.8529411764705882, 0.8823529411764706, 0.7352941176470589, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0.8414165666266508</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0.8529411764705882</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0.06039023928818352</v>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>0.9548872180451128, 0.8523809523809525, 0.93343653250774, 0.8637770897832817, 0.9334365325077401, 0.8436532507739938, 0.8699690402476781</t>
+        </is>
+      </c>
+      <c r="AN38" t="n">
+        <v>0.893077230892357</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0.8699690402476781</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0.04237523637504653</v>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>0.8113207547169812, 0.8244514106583072, 0.8150470219435737, 0.8181818181818182, 0.8244514106583072, 0.8338557993730408, 0.8401253918495298</t>
+        </is>
+      </c>
+      <c r="AR38" t="n">
+        <v>0.823919086768794</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0.8244514106583072</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0.009504112454133573</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>0.8507462686567164, 0.8600000000000001, 0.8535980148883374, 0.8578431372549019, 0.8627450980392157, 0.8678304239401496, 0.8746928746928747</t>
+        </is>
+      </c>
+      <c r="AV38" t="n">
+        <v>0.8610651167817424</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0.8600000000000001</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0.007635063539837203</v>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>0.868020304568528, 0.882051282051282, 0.8730964467005076, 0.8663366336633663, 0.8712871287128713, 0.8923076923076924, 0.8855721393034826</t>
+        </is>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0.8769530896153901</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0.8730964467005076</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>0.009067398435164287</v>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>0.8341463414634146, 0.8390243902439024, 0.8349514563106796, 0.8495145631067961, 0.8543689320388349, 0.8446601941747572, 0.8640776699029126</t>
+        </is>
+      </c>
+      <c r="BD38" t="n">
+        <v>0.8458205067487568</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0.8446601941747572</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>0.01015593810188877</v>
+      </c>
+      <c r="BG38" t="inlineStr">
+        <is>
+          <t>0.8959421541118067, 0.9114676936243047, 0.9020749205258184, 0.910537846894063, 0.9004854368932038, 0.9135664575994501, 0.907788469799811</t>
+        </is>
+      </c>
+      <c r="BH38" t="n">
+        <v>0.9059804256354939</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>0.907788469799811</v>
+      </c>
+      <c r="BJ38" t="n">
+        <v>0.006069971402500744</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Logit_no_fragmentation_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>{'estimator': StatsModelsEstimator(model_class=&lt;class 'statsmodels.discrete.discrete_model.Logit'&gt;), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.8292682926829269</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.9518181818181819</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.8619528619528619</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.7375</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.7468354430379747</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.7421383647798743</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.9374637092091511</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0.008121728897094727, 0.006970882415771484, 0.006665945053100586, 0.002713918685913086, 0.007676124572753906, 0.002629995346069336, 0.008806228637695312</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>0.006226403372628348</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.006970882415771484</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.002341202197361861</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>0.005633115768432617, 0.007889747619628906, 0.009768962860107422, 0.006706953048706055, 0.008363962173461914, 0.010586977005004883, 0.012262821197509766</t>
+        </is>
+      </c>
+      <c r="T39" t="n">
+        <v>0.00874464852469308</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.008363962173461914</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.002122348754311415</v>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>0.8518518518518519, 0.7358490566037735, 0.8867924528301887, 0.8490566037735849, 0.8490566037735849, 0.8679245283018868, 0.9433962264150944</t>
+        </is>
+      </c>
+      <c r="X39" t="n">
+        <v>0.854846760507138</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.05765542722960909</v>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>0.6923076923076923, 0.5625000000000001, 0.7857142857142857, 0.7333333333333334, 0.7333333333333334, 0.7200000000000001, 0.9032258064516129</t>
+        </is>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.7329163501628939</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0.7333333333333334</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.09460512538739281</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>0.8181818181818182, 0.5, 0.7857142857142857, 0.6875, 0.6875, 0.8181818181818182, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.7315153334060897</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0.109479499037221</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>0.6, 0.6428571428571429, 0.7857142857142857, 0.7857142857142857, 0.7857142857142857, 0.6428571428571429, 1.0</t>
+        </is>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0.7489795918367347</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0.1263659231054099</v>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>0.941880341880342, 0.8937728937728937, 0.9597069597069597, 0.9322344322344323, 0.8974358974358974, 0.9285714285714286, 0.9963369963369964</t>
+        </is>
+      </c>
+      <c r="AN39" t="n">
+        <v>0.9357055642769928</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0.9322344322344323</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0.03289860248950959</v>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>0.8805031446540881, 0.890282131661442, 0.8652037617554859, 0.8683385579937304, 0.877742946708464, 0.8871473354231975, 0.8557993730407524</t>
+        </is>
+      </c>
+      <c r="AR39" t="n">
+        <v>0.8750024644624513</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0.877742946708464</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0.01151343805044437</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>0.7764705882352941, 0.7928994082840236, 0.7455621301775148, 0.7586206896551726, 0.7664670658682634, 0.7804878048780488, 0.7294117647058823</t>
+        </is>
+      </c>
+      <c r="AV39" t="n">
+        <v>0.7642742074005999</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0.7664670658682634</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0.02011870916778079</v>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>0.7674418604651163, 0.7976190476190477, 0.75, 0.7415730337078652, 0.7804878048780488, 0.810126582278481, 0.7294117647058823</t>
+        </is>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0.7680942990934917</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0.7674418604651163</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0.02756697794469797</v>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>0.7857142857142857, 0.788235294117647, 0.7411764705882353, 0.7764705882352941, 0.7529411764705882, 0.7529411764705882, 0.7294117647058823</t>
+        </is>
+      </c>
+      <c r="BD39" t="n">
+        <v>0.7609843937575029</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>0.7529411764705882</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>0.02108680277938419</v>
+      </c>
+      <c r="BG39" t="inlineStr">
+        <is>
+          <t>0.9395604395604396, 0.9486676721970839, 0.9361488185017597, 0.9430869783810961, 0.9412770236299648, 0.9462041226747109, 0.9297637003519357</t>
+        </is>
+      </c>
+      <c r="BH39" t="n">
+        <v>0.9406726793281416</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>0.9412770236299648</v>
+      </c>
+      <c r="BJ39" t="n">
+        <v>0.005872685742408556</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>LogisticRegression_splashing_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>{'estimator': LogisticRegression(fit_intercept=False), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.8796296296296297</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.835016835016835</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.8950276243093923</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.8686327077747988</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.9140625</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0.011718034744262695, 0.0037431716918945312, 0.0035619735717773438, 0.0034360885620117188, 0.004189014434814453, 0.003453969955444336, 0.003676891326904297</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>0.004825592041015625</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.003676891326904297</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.002823648685873421</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>0.011250019073486328, 0.005260944366455078, 0.004951000213623047, 0.004943132400512695, 0.005147218704223633, 0.0047149658203125, 0.0048980712890625</t>
+        </is>
+      </c>
+      <c r="T40" t="n">
+        <v>0.005880764552525112</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.004951000213623047</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.002198036435352096</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.7924528301886793, 0.8490566037735849, 0.8113207547169812, 0.8490566037735849, 0.7358490566037735, 0.7169811320754716</t>
+        </is>
+      </c>
+      <c r="X40" t="n">
+        <v>0.8115204152940001</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0.8113207547169812</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0.06647662856511974</v>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8358208955223881, 0.8787878787878787, 0.8484848484848485, 0.8823529411764706, 0.7741935483870968, 0.782608695652174</t>
+        </is>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.849300850124</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.05475403542775047</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.875, 0.90625, 0.875, 0.8823529411764706, 0.8571428571428571, 0.7714285714285715</t>
+        </is>
+      </c>
+      <c r="AF40" t="n">
+        <v>0.8728616446578632</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0.04876932657644783</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8, 0.8529411764705882, 0.8235294117647058, 0.8823529411764706, 0.7058823529411765, 0.7941176470588235</t>
+        </is>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0.8288115246098441</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0.06931148892748354</v>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>0.956390977443609, 0.853968253968254, 0.9380804953560371, 0.8715170278637772, 0.934984520123839, 0.8498452012383901, 0.871517027863777</t>
+        </is>
+      </c>
+      <c r="AN40" t="n">
+        <v>0.8966147862653834</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0.8715170278637772</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0.04145694891377123</v>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>0.8144654088050315, 0.8244514106583072, 0.8150470219435737, 0.8244514106583072, 0.8181818181818182, 0.8401253918495298, 0.8432601880877743</t>
+        </is>
+      </c>
+      <c r="AR40" t="n">
+        <v>0.8257118071691918</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0.8244514106583072</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0.01079546299645075</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>0.8528678304239401, 0.8600000000000001, 0.8528678304239402, 0.8606965174129354, 0.8550000000000001, 0.8708860759493672, 0.8762376237623762</t>
+        </is>
+      </c>
+      <c r="AV40" t="n">
+        <v>0.8612222682817944</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0.8600000000000001</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0.008442497252294352</v>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>0.8724489795918368, 0.882051282051282, 0.8769230769230769, 0.8826530612244898, 0.8814432989690721, 0.91005291005291, 0.8939393939393939</t>
+        </is>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0.8856445718217231</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0.882051282051282</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>0.01167580365754328</v>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>0.8341463414634146, 0.8390243902439024, 0.8300970873786407, 0.8398058252427184, 0.8300970873786407, 0.8349514563106796, 0.8592233009708737</t>
+        </is>
+      </c>
+      <c r="BD40" t="n">
+        <v>0.8381922127126957</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>0.8349514563106796</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>0.009285446544649863</v>
+      </c>
+      <c r="BG40" t="inlineStr">
+        <is>
+          <t>0.8971077055903303, 0.9126658108686351, 0.9032777730045537, 0.9113970272360168, 0.9010439041154739, 0.9164447117449953, 0.9092061173640348</t>
+        </is>
+      </c>
+      <c r="BH40" t="n">
+        <v>0.9073061499891486</v>
+      </c>
+      <c r="BI40" t="n">
+        <v>0.9092061173640348</v>
+      </c>
+      <c r="BJ40" t="n">
+        <v>0.006459060535969795</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>LogisticRegression_no_fragmentation_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>{'estimator': LogisticRegression(fit_intercept=False), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.6296296296296297</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.723404255319149</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.9463636363636363</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.8585858585858586</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.6796116504854369</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.8860759493670886</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.938102427128092</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0.004247188568115234, 0.0031168460845947266, 0.0028901100158691406, 0.0030291080474853516, 0.002825021743774414, 0.0029990673065185547, 0.002905130386352539</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>0.003144638878958566</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.002999067306518555</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.0004590722142820697</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>0.004426002502441406, 0.004179954528808594, 0.004321098327636719, 0.0042569637298583984, 0.004033088684082031, 0.003998994827270508, 0.0041468143463134766</t>
+        </is>
+      </c>
+      <c r="T41" t="n">
+        <v>0.004194702420915876</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0.004179954528808594</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.0001415643991239777</v>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.6981132075471698, 0.8867924528301887, 0.8301886792452831, 0.8679245283018868, 0.8867924528301887, 0.8867924528301887</t>
+        </is>
+      </c>
+      <c r="X41" t="n">
+        <v>0.8493560946391135</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0.06475654627967456</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>0.8125, 0.5555555555555556, 0.8125000000000001, 0.742857142857143, 0.7878787878787878, 0.7857142857142857, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.7600764548243539</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.08707821193812958</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>0.7647058823529411, 0.45454545454545453, 0.7222222222222222, 0.6190476190476191, 0.6842105263157895, 0.7857142857142857, 0.7</t>
+        </is>
+      </c>
+      <c r="AF41" t="n">
+        <v>0.6757779985997588</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0.1034899643372142</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>0.8666666666666667, 0.7142857142857143, 0.9285714285714286, 0.9285714285714286, 0.9285714285714286, 0.7857142857142857, 1.0</t>
+        </is>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0.8789115646258504</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0.09102437378872236</v>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>0.9452991452991454, 0.8992673992673992, 0.9743589743589743, 0.9285714285714286, 0.8772893772893773, 0.945054945054945, 0.9908424908424909</t>
+        </is>
+      </c>
+      <c r="AN41" t="n">
+        <v>0.9372405372405372</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0.945054945054945</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0.03681654940284883</v>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>0.8490566037735849, 0.8683385579937304, 0.8401253918495298, 0.8526645768025078, 0.8620689655172413, 0.8495297805642633, 0.8495297805642633</t>
+        </is>
+      </c>
+      <c r="AR41" t="n">
+        <v>0.8530448081521601</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0.8495297805642633</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0.008643797990457379</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>0.7551020408163266, 0.7857142857142858, 0.7437185929648242, 0.7589743589743589, 0.7708333333333334, 0.7599999999999999, 0.7525773195876289</t>
+        </is>
+      </c>
+      <c r="AV41" t="n">
+        <v>0.760988561627251</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0.7589743589743589</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0.01263197284387405</v>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>0.6607142857142857, 0.6936936936936937, 0.6491228070175439, 0.6727272727272727, 0.6915887850467289, 0.6608695652173913, 0.6697247706422018</t>
+        </is>
+      </c>
+      <c r="AZ41" t="n">
+        <v>0.6712058828655884</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0.6697247706422018</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>0.0152608180360979</v>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>0.8809523809523809, 0.9058823529411765, 0.8705882352941177, 0.8705882352941177, 0.8705882352941177, 0.8941176470588236, 0.8588235294117647</t>
+        </is>
+      </c>
+      <c r="BD41" t="n">
+        <v>0.8787915166066427</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>0.8705882352941177</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>0.01499559463001682</v>
+      </c>
+      <c r="BG41" t="inlineStr">
+        <is>
+          <t>0.9391534391534391, 0.949270990447461, 0.9355957767722474, 0.9432378079436904, 0.9416792357968828, 0.9440925087983911, 0.9301659125188536</t>
+        </is>
+      </c>
+      <c r="BH41" t="n">
+        <v>0.9404565244901379</v>
+      </c>
+      <c r="BI41" t="n">
+        <v>0.9416792357968828</v>
+      </c>
+      <c r="BJ41" t="n">
+        <v>0.005749128469435981</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>KNeighborsClassifier_splashing_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>{'estimator': KNeighborsClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.8627450980392157</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.888888888888889</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.8807870370370371</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.8922558922558923</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.969469246031746</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0.003793954849243164, 0.0029909610748291016, 0.0027277469635009766, 0.0031108856201171875, 0.0028829574584960938, 0.0027370452880859375, 0.003046751022338867</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>0.003041471753801618</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.002990961074829102</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.0003359110834777238</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>0.008078813552856445, 0.006407260894775391, 0.005907297134399414, 0.005999088287353516, 0.006329059600830078, 0.0063440799713134766, 0.006106138229370117</t>
+        </is>
+      </c>
+      <c r="T42" t="n">
+        <v>0.00645310538155692</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.006329059600830078</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0.0006862659876028768</v>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.8301886792452831, 0.8113207547169812, 0.8301886792452831, 0.8867924528301887, 0.8679245283018868, 0.8113207547169812</t>
+        </is>
+      </c>
+      <c r="X42" t="n">
+        <v>0.8466606768493562</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0.8301886792452831</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0.03136514516103273</v>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>0.9189189189189189, 0.8695652173913043, 0.8529411764705882, 0.8615384615384616, 0.9117647058823528, 0.8923076923076922, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.880597004236025</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.02500572843510363</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>0.8717948717948718, 0.8823529411764706, 0.8529411764705882, 0.9032258064516129, 0.9117647058823529, 0.9354838709677419, 0.8333333333333334</t>
+        </is>
+      </c>
+      <c r="AF42" t="n">
+        <v>0.8844138151538531</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0.03267445569076566</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>0.9714285714285714, 0.8571428571428571, 0.8529411764705882, 0.8235294117647058, 0.9117647058823529, 0.8529411764705882, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0.8788715486194477</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0.04557652733062977</v>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>0.9233082706766917, 0.876984126984127, 0.9264705882352942, 0.9404024767801857, 0.8862229102167183, 0.9256965944272446, 0.9148606811145511</t>
+        </is>
+      </c>
+      <c r="AN42" t="n">
+        <v>0.913420806919259</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0.9233082706766917</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0.02143493365917203</v>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>0.8867924528301887, 0.9059561128526645, 0.8840125391849529, 0.896551724137931, 0.8871473354231975, 0.890282131661442, 0.890282131661442</t>
+        </is>
+      </c>
+      <c r="AR42" t="n">
+        <v>0.8915749182502598</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0.890282131661442</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0.006913702663926735</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>0.9113300492610837, 0.9271844660194175, 0.9116945107398567, 0.9200968523002421, 0.9121951219512194, 0.9144254278728607, 0.9152542372881356</t>
+        </is>
+      </c>
+      <c r="AV42" t="n">
+        <v>0.9160258093475452</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0.9144254278728607</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0.005341615995420642</v>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>0.9203980099502488, 0.9227053140096618, 0.8967136150234741, 0.9178743961352657, 0.9166666666666666, 0.9211822660098522, 0.9130434782608695</t>
+        </is>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0.9155119637222912</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0.9178743961352657</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>0.008230221522813365</v>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>0.9024390243902439, 0.9317073170731708, 0.9271844660194175, 0.9223300970873787, 0.9077669902912622, 0.9077669902912622, 0.9174757281553398</t>
+        </is>
+      </c>
+      <c r="BD42" t="n">
+        <v>0.9166672304725821</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>0.9174757281553398</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>0.01021489510604613</v>
+      </c>
+      <c r="BG42" t="inlineStr">
+        <is>
+          <t>0.9671918843082237, 0.9732563115104835, 0.9687902740785291, 0.969219864249506, 0.967157831428817, 0.9677377781596358, 0.9640218231806856</t>
+        </is>
+      </c>
+      <c r="BH42" t="n">
+        <v>0.9681965381308402</v>
+      </c>
+      <c r="BI42" t="n">
+        <v>0.9677377781596358</v>
+      </c>
+      <c r="BJ42" t="n">
+        <v>0.002583684299501075</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>KNeighborsClassifier_no_fragmentation_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>{'estimator': KNeighborsClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.7692307692307692</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.9477272727272728</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.9124579124579124</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.8354430379746836</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.8354430379746836</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.8354430379746836</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.9684995935431425</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0.0032041072845458984, 0.0021648406982421875, 0.0022459030151367188, 0.0022649765014648438, 0.002054929733276367, 0.002274751663208008, 0.002343893051147461</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>0.002364771706717355</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.002264976501464844</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.0003531667036938368</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>0.006680965423583984, 0.005949258804321289, 0.005681037902832031, 0.006164073944091797, 0.0054247379302978516, 0.0060100555419921875, 0.005404949188232422</t>
+        </is>
+      </c>
+      <c r="T43" t="n">
+        <v>0.005902154105050223</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0.005949258804321289</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.0004162832059434329</v>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>0.8703703703703703, 0.7169811320754716, 0.9056603773584906, 0.8113207547169812, 0.8490566037735849, 0.8867924528301887, 0.9245283018867925</t>
+        </is>
+      </c>
+      <c r="X43" t="n">
+        <v>0.8521014275731258</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0.8703703703703703</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0.06500688228973209</v>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>0.7586206896551724, 0.5161290322580646, 0.8275862068965518, 0.6428571428571429, 0.6666666666666666, 0.7692307692307692, 0.8750000000000001</t>
+        </is>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.7222986439377668</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0.7586206896551724</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0.1132865319292221</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>0.7857142857142857, 0.47058823529411764, 0.8, 0.6428571428571429, 0.8, 0.8333333333333334, 0.7777777777777778</t>
+        </is>
+      </c>
+      <c r="AF43" t="n">
+        <v>0.7300386821395224</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0.1199719647039606</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.5714285714285714, 0.8571428571428571, 0.6428571428571429, 0.5714285714285714, 0.7142857142857143, 1.0</t>
+        </is>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0.7272108843537415</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0.1449889529367376</v>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>0.9487179487179488, 0.8168498168498168, 0.9322344322344323, 0.9258241758241759, 0.9331501831501832, 0.8836996336996337, 0.978937728937729</t>
+        </is>
+      </c>
+      <c r="AN43" t="n">
+        <v>0.9170591313448458</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0.9322344322344323</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0.04862692091284145</v>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>0.9025157232704403, 0.9184952978056427, 0.9090909090909091, 0.9059561128526645, 0.896551724137931, 0.9059561128526645, 0.9122257053291536</t>
+        </is>
+      </c>
+      <c r="AR43" t="n">
+        <v>0.9072559407627724</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0.9059561128526645</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>0.006489748354856868</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>0.8208092485549132, 0.8539325842696629, 0.8379888268156425, 0.8295454545454546, 0.8023952095808382, 0.8275862068965517, 0.8390804597701149</t>
+        </is>
+      </c>
+      <c r="AV43" t="n">
+        <v>0.8301911414904539</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>0.8295454545454546</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>0.01498244841136084</v>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>0.797752808988764, 0.8172043010752689, 0.7978723404255319, 0.8021978021978022, 0.8170731707317073, 0.8089887640449438, 0.8202247191011236</t>
+        </is>
+      </c>
+      <c r="AZ43" t="n">
+        <v>0.8087591295093061</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>0.8089887640449438</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>0.008901596686457524</v>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>0.8452380952380952, 0.8941176470588236, 0.8823529411764706, 0.8588235294117647, 0.788235294117647, 0.8470588235294118, 0.8588235294117647</t>
+        </is>
+      </c>
+      <c r="BD43" t="n">
+        <v>0.8535214085634253</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>0.8588235294117647</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>0.031414718679916</v>
+      </c>
+      <c r="BG43" t="inlineStr">
+        <is>
+          <t>0.9700091575091574, 0.9787078934137757, 0.9681749622926094, 0.9672699849170436, 0.9679235796882856, 0.9707893413775767, 0.9695827048768224</t>
+        </is>
+      </c>
+      <c r="BH43" t="n">
+        <v>0.9703510891536101</v>
+      </c>
+      <c r="BI43" t="n">
+        <v>0.9695827048768224</v>
+      </c>
+      <c r="BJ43" t="n">
+        <v>0.003602719364528168</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SVC_splashing_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>{'estimator': SVC(probability=True), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.9112654320987654</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.8855218855218855</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.9388888888888889</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.8802083333333334</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.9086021505376345</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.9446676587301588</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0.009501934051513672, 0.007731914520263672, 0.00802469253540039, 0.00768589973449707, 0.00768589973449707, 0.007425069808959961, 0.0075740814208984375</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>0.007947070258004325</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.00768589973449707</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.0006566085865918883</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>0.006008148193359375, 0.005760908126831055, 0.006105184555053711, 0.0058710575103759766, 0.00563502311706543, 0.005822896957397461, 0.005860090255737305</t>
+        </is>
+      </c>
+      <c r="T44" t="n">
+        <v>0.005866186959402902</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0.005860090255737305</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0.0001432919664786477</v>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.7547169811320755, 0.8679245283018868, 0.8301886792452831, 0.8679245283018868, 0.8113207547169812, 0.7924528301886793</t>
+        </is>
+      </c>
+      <c r="X44" t="n">
+        <v>0.8331336727563142</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0.8301886792452831</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0.04814558246414295</v>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>0.9315068493150684, 0.8115942028985507, 0.9014084507042254, 0.8615384615384616, 0.8955223880597014, 0.8484848484848485, 0.8405797101449276</t>
+        </is>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.8700907015922548</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0.8615384615384616</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.03823276074855284</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8235294117647058, 0.8648648648648649, 0.9032258064516129, 0.9090909090909091, 0.875, 0.8285714285714286</t>
+        </is>
+      </c>
+      <c r="AF44" t="n">
+        <v>0.8712884661212549</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0.03198114499209478</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>0.9714285714285714, 0.8, 0.9411764705882353, 0.8235294117647058, 0.8823529411764706, 0.8235294117647058, 0.8529411764705882</t>
+        </is>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0.8707082833133253</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0.8529411764705882</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0.05977692240854524</v>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>0.9654135338345864, 0.8650793650793651, 0.9349845201238389, 0.9303405572755419, 0.9287925696594428, 0.9102167182662538, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="AN44" t="n">
+        <v>0.9167400293450714</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0.9287925696594428</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0.03145531802324551</v>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>0.8710691823899371, 0.8808777429467085, 0.8683385579937304, 0.8808777429467085, 0.877742946708464, 0.8746081504702194, 0.8840125391849529</t>
+        </is>
+      </c>
+      <c r="AR44" t="n">
+        <v>0.8767895518058173</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0.877742946708464</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0.005283499335282098</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>0.8997555012224939, 0.9054726368159205, 0.8975609756097561, 0.9073170731707318, 0.9037037037037038, 0.9024390243902438, 0.9086419753086421</t>
+        </is>
+      </c>
+      <c r="AV44" t="n">
+        <v>0.9035558414602132</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>0.9037037037037038</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>0.003690525940804103</v>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>0.9019607843137255, 0.9238578680203046, 0.9019607843137255, 0.9117647058823529, 0.9195979899497487, 0.9068627450980392, 0.9246231155778895</t>
+        </is>
+      </c>
+      <c r="AZ44" t="n">
+        <v>0.9129468561651122</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>0.009098070677856621</v>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>0.8975609756097561, 0.8878048780487805, 0.8932038834951457, 0.9029126213592233, 0.8883495145631068, 0.8980582524271845, 0.8932038834951457</t>
+        </is>
+      </c>
+      <c r="BD44" t="n">
+        <v>0.8944420012854776</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>0.8932038834951457</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>0.005053886032916946</v>
+      </c>
+      <c r="BG44" t="inlineStr">
+        <is>
+          <t>0.9373839844593135, 0.9583654257595208, 0.9418979293753759, 0.9498238680298994, 0.9390626342469284, 0.9469026548672567, 0.9534109459575566</t>
+        </is>
+      </c>
+      <c r="BH44" t="n">
+        <v>0.9466924918136931</v>
+      </c>
+      <c r="BI44" t="n">
+        <v>0.9469026548672567</v>
+      </c>
+      <c r="BJ44" t="n">
+        <v>0.007162357584063435</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SVC_no_fragmentation_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>{'estimator': SVC(probability=True), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.9545454545454545</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.8956228956228957</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.8076923076923077</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.7974683544303798</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.802547770700637</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.9561607246545117</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0.0073587894439697266, 0.00621485710144043, 0.006346940994262695, 0.006153106689453125, 0.00634002685546875, 0.006042003631591797, 0.006780147552490234</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>0.006462267466953823</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.00634002685546875</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.0004253496600402123</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>0.005382061004638672, 0.00481104850769043, 0.004828929901123047, 0.004662036895751953, 0.005089998245239258, 0.004976987838745117, 0.004726886749267578</t>
+        </is>
+      </c>
+      <c r="T45" t="n">
+        <v>0.004925421306065151</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0.004828929901123047</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0.0002297338635988773</v>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>0.8703703703703703, 0.7735849056603774, 0.9245283018867925, 0.8490566037735849, 0.8301886792452831, 0.8301886792452831, 0.9245283018867925</t>
+        </is>
+      </c>
+      <c r="X45" t="n">
+        <v>0.8574922631526405</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0.05036450422769549</v>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>0.7407407407407408, 0.6000000000000001, 0.8571428571428571, 0.6923076923076924, 0.6086956521739131, 0.6666666666666666, 0.8666666666666666</t>
+        </is>
+      </c>
+      <c r="AB45" t="n">
+        <v>0.7188886108140766</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0.6923076923076924</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.1008115445459597</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>0.8333333333333334, 0.5625, 0.8571428571428571, 0.75, 0.7777777777777778, 0.6923076923076923, 0.8125</t>
+        </is>
+      </c>
+      <c r="AF45" t="n">
+        <v>0.7550802372230944</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0.09366039101426438</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>0.6666666666666666, 0.6428571428571429, 0.8571428571428571, 0.6428571428571429, 0.5, 0.6428571428571429, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0.6972789115646257</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>0.1351158099730694</v>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>0.9658119658119658, 0.8736263736263736, 0.9688644688644689, 0.9194139194139194, 0.9432234432234432, 0.9029304029304029, 0.989010989010989</t>
+        </is>
+      </c>
+      <c r="AN45" t="n">
+        <v>0.9375545089830805</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0.9432234432234432</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>0.03793494394833614</v>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>0.8805031446540881, 0.8996865203761756, 0.8746081504702194, 0.877742946708464, 0.877742946708464, 0.8871473354231975, 0.8652037617554859</t>
+        </is>
+      </c>
+      <c r="AR45" t="n">
+        <v>0.8803764008708707</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>0.877742946708464</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>0.009972062303319113</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>0.7625, 0.813953488372093, 0.761904761904762, 0.7719298245614037, 0.7547169811320755, 0.7857142857142857, 0.732919254658385</t>
+        </is>
+      </c>
+      <c r="AV45" t="n">
+        <v>0.7690912280490007</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>0.7625</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>0.02362542907799888</v>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>0.8026315789473685, 0.8045977011494253, 0.7710843373493976, 0.7674418604651163, 0.8108108108108109, 0.7951807228915663, 0.7763157894736842</t>
+        </is>
+      </c>
+      <c r="AZ45" t="n">
+        <v>0.7897232572981956</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>0.7951807228915663</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>0.01641416142363613</v>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>0.7261904761904762, 0.8235294117647058, 0.7529411764705882, 0.7764705882352941, 0.7058823529411765, 0.7764705882352941, 0.6941176470588235</t>
+        </is>
+      </c>
+      <c r="BD45" t="n">
+        <v>0.7508003201280512</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>0.7529411764705882</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>0.04217010279243825</v>
+      </c>
+      <c r="BG45" t="inlineStr">
+        <is>
+          <t>0.9537545787545788, 0.9613876319758673, 0.9489190548014077, 0.9517848164906988, 0.9519859225741579, 0.9608848667672197, 0.9497486173956762</t>
+        </is>
+      </c>
+      <c r="BH45" t="n">
+        <v>0.9540664983942296</v>
+      </c>
+      <c r="BI45" t="n">
+        <v>0.9519859225741579</v>
+      </c>
+      <c r="BJ45" t="n">
+        <v>0.004703518105213435</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_splashing_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x30ab3ebd0&gt;, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.910891089108911</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.9552469135802468</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.9995287698412699</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0.621589183807373, 0.5981440544128418, 0.5600321292877197, 0.5747199058532715, 0.5665068626403809, 0.5702159404754639, 0.5689918994903564</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>0.5800285679953439</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.5702159404754639</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.02029928681288866</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>0.005820751190185547, 0.006584882736206055, 0.0058841705322265625, 0.006227016448974609, 0.006042003631591797, 0.0054781436920166016, 0.005802154541015625</t>
+        </is>
+      </c>
+      <c r="T46" t="n">
+        <v>0.005977017538888114</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0.005884170532226562</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0.0003270462324023239</v>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.8679245283018868, 0.9056603773584906, 0.8301886792452831, 0.9245283018867925, 0.9245283018867925, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="X46" t="n">
+        <v>0.8949785364879704</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0.04394937038790471</v>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8985507246376812, 0.9275362318840579, 0.8656716417910447, 0.9411764705882353, 0.9411764705882353, 0.8857142857142858</t>
+        </is>
+      </c>
+      <c r="AB46" t="n">
+        <v>0.9188640067751089</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0.9275362318840579</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.03434896516858366</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.9117647058823529, 0.9142857142857143, 0.8787878787878788, 0.9411764705882353, 0.9411764705882353, 0.8611111111111112</t>
+        </is>
+      </c>
+      <c r="AF46" t="n">
+        <v>0.9134640424556392</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0.03056108645419631</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>1.0, 0.8857142857142857, 0.9411764705882353, 0.8529411764705882, 0.9411764705882353, 0.9411764705882353, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0.9248499399759904</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0.04362321037141777</v>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>0.9984962406015038, 0.9507936507936509, 0.9829721362229102, 0.955108359133127, 0.9535603715170279, 0.9458204334365325, 0.9442724458204335</t>
+        </is>
+      </c>
+      <c r="AN46" t="n">
+        <v>0.9615748053607408</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0.9535603715170279</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>0.01923868646800988</v>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 0.9968652037617555, 0.9968652037617555, 0.9937304075235109, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="AR46" t="n">
+        <v>0.9968637954974975</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>0.001675622622249898</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 0.9975669099756691, 0.9975786924939467, 0.9951456310679612, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="AV46" t="n">
+        <v>0.9975736469287341</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>0.001297393947929273</v>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 0.9951456310679612, 0.9951690821256038, 0.9951456310679612, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="AZ46" t="n">
+        <v>0.9958491627972421</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>0.001694606963530478</v>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 0.9951456310679612, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BD46" t="n">
+        <v>0.9993065187239945</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>0.001698675272387779</v>
+      </c>
+      <c r="BG46" t="inlineStr">
+        <is>
+          <t>0.9992877185409023, 0.9999572100984168, 0.9993770942520835, 0.9995918893375719, 0.9993341352349858, 1.0, 0.9995489303204742</t>
+        </is>
+      </c>
+      <c r="BH46" t="n">
+        <v>0.9995852825406335</v>
+      </c>
+      <c r="BI46" t="n">
+        <v>0.9995489303204742</v>
+      </c>
+      <c r="BJ46" t="n">
+        <v>0.0002690319894887233</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_no_fragmentation_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x30ab27e10&gt;, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.9863636363636363</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.9875</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.9937106918238994</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.9998838694692834</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.5513520240783691, 0.5501439571380615, 0.5662021636962891, 0.5486657619476318, 0.5495359897613525, 0.5538780689239502, 0.5715949535369873</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>0.555910417011806</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.5513520240783691</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.00847858251258366</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>0.005712270736694336, 0.005410194396972656, 0.00564885139465332, 0.005407094955444336, 0.005228996276855469, 0.004937887191772461, 0.005530118942260742</t>
+        </is>
+      </c>
+      <c r="T47" t="n">
+        <v>0.005410773413521903</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0.005410194396972656</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0.0002445121348606561</v>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.8301886792452831, 0.9245283018867925, 0.8867924528301887, 0.9433962264150944, 0.9433962264150944, 0.9433962264150944</t>
+        </is>
+      </c>
+      <c r="X47" t="n">
+        <v>0.9113007886592792</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0.9245283018867925</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0.03865656424883146</v>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>0.8148148148148148, 0.7096774193548386, 0.8461538461538461, 0.7999999999999999, 0.88, 0.888888888888889, 0.896551724137931</t>
+        </is>
+      </c>
+      <c r="AB47" t="n">
+        <v>0.833726670478617</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.06114254623195546</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>0.9166666666666666, 0.6470588235294118, 0.9166666666666666, 0.75, 1.0, 0.9230769230769231, 0.8666666666666667</t>
+        </is>
+      </c>
+      <c r="AF47" t="n">
+        <v>0.8600193923723337</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0.1117965670925468</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.7857142857142857, 0.7857142857142857, 0.8571428571428571, 0.7857142857142857, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0.819047619047619</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>0.06044859834428046</v>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>0.9794871794871796, 0.9047619047619048, 0.9908424908424909, 0.9267399267399268, 0.989010989010989, 0.9157509157509157, 0.9926739926739926</t>
+        </is>
+      </c>
+      <c r="AN47" t="n">
+        <v>0.9570381998953428</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>0.9794871794871796</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>0.03643838628042798</v>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>0.9937106918238994, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9937304075235109, 0.9968652037617555, 0.9937304075235109</t>
+        </is>
+      </c>
+      <c r="AR47" t="n">
+        <v>0.9959667311651696</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>0.00219678391174473</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 0.9940828402366864, 0.9940828402366864, 0.9882352941176471, 0.9941520467836257, 0.9882352941176471</t>
+        </is>
+      </c>
+      <c r="AV47" t="n">
+        <v>0.99241193622679</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>0.9940828402366864</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>0.004135440870806592</v>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 1.0, 1.0, 0.9882352941176471, 0.9883720930232558, 0.9882352941176471</t>
+        </is>
+      </c>
+      <c r="AZ47" t="n">
+        <v>0.9932768456219697</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>0.9883720930232558</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>0.005822892655344211</v>
+      </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 0.9882352941176471, 0.9882352941176471, 0.9882352941176471, 1.0, 0.9882352941176471</t>
+        </is>
+      </c>
+      <c r="BD47" t="n">
+        <v>0.991576630652261</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>0.9882352941176471</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>0.005327616940100686</v>
+      </c>
+      <c r="BG47" t="inlineStr">
+        <is>
+          <t>0.999949124949125, 1.0, 0.9999497234791352, 1.0, 0.9998994469582705, 1.0, 0.9998994469582705</t>
+        </is>
+      </c>
+      <c r="BH47" t="n">
+        <v>0.9999568203349716</v>
+      </c>
+      <c r="BI47" t="n">
+        <v>0.9999497234791352</v>
+      </c>
+      <c r="BJ47" t="n">
+        <v>4.189518119265814e-05</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>XGBClassifier_splashing_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>{'estimator': XGBClassifier(base_score=None, booster=None, callbacks=None,
+              colsample_bylevel=None, colsample_bynode=None,
+              colsample_bytree=None, device=None, early_stopping_rounds=None,
+              enable_categorical=False, eval_metric=None, feature_types=None,
+              gamma=None, grow_policy=None, importance_type=None,
+              interaction_constraints=None, learning_rate=None, max_bin=None,
+              max_cat_threshold=None, max_cat_to_onehot=None,
+              max_delta_step=None, max_depth=None, max_leaves=None,
+              min_child_weight=None, missing=nan, monotone_constraints=None,
+              multi_strategy=None, n_estimators=None, n_jobs=None,
+              num_parallel_tree=None, random_state=None, ...), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.910891089108911</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.9409722222222222</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.9999751984126984</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.04561781883239746, 0.04239511489868164, 0.03745007514953613, 0.05150890350341797, 0.03781414031982422, 0.0435488224029541, 0.04444599151611328</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>0.04325440951756069</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.0435488224029541</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.004460207150859975</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>0.007827997207641602, 0.006701946258544922, 0.00662994384765625, 0.006490230560302734, 0.006531953811645508, 0.006342172622680664, 0.005711078643798828</t>
+        </is>
+      </c>
+      <c r="T48" t="n">
+        <v>0.006605046136038644</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0.006531953811645508</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0.0005846151748731591</v>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.8490566037735849, 0.8867924528301887, 0.8490566037735849, 0.9245283018867925, 0.8301886792452831, 0.8867924528301887</t>
+        </is>
+      </c>
+      <c r="X48" t="n">
+        <v>0.881551362683438</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0.03892747661948757</v>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>0.958904109589041, 0.8823529411764706, 0.9117647058823528, 0.8857142857142858, 0.9411764705882353, 0.8524590163934426, 0.9142857142857143</t>
+        </is>
+      </c>
+      <c r="AB48" t="n">
+        <v>0.9066653205185061</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0.9117647058823528</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.03374768933991756</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>0.9210526315789473, 0.9090909090909091, 0.9117647058823529, 0.8611111111111112, 0.9411764705882353, 0.9629629629629629, 0.8888888888888888</t>
+        </is>
+      </c>
+      <c r="AF48" t="n">
+        <v>0.9137210971576296</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0.030803584167263</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>1.0, 0.8571428571428571, 0.9117647058823529, 0.9117647058823529, 0.9411764705882353, 0.7647058823529411, 0.9411764705882353</t>
+        </is>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0.9039615846338535</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>0.06938422418810822</v>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>0.9804511278195489, 0.9412698412698413, 0.9705882352941176, 0.9380804953560371, 0.9458204334365325, 0.9311145510835914, 0.9427244582043344</t>
+        </is>
+      </c>
+      <c r="AN48" t="n">
+        <v>0.9500070203520004</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0.9427244582043344</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>0.01688828419465269</v>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="AR48" t="n">
+        <v>0.9977594515655674</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>0.001417051170840857</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="AV48" t="n">
+        <v>0.9982688114216364</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>0.001094907038779773</v>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="AZ48" t="n">
+        <v>0.9965459942243395</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>0.002184519446236978</v>
+      </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BD48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG48" t="inlineStr">
+        <is>
+          <t>0.9999784157133607, 0.9999999999999999, 0.9999785204914511, 0.9999785204914512, 0.9999785204914512, 1.0, 0.9999785204914512</t>
+        </is>
+      </c>
+      <c r="BH48" t="n">
+        <v>0.999984642525595</v>
+      </c>
+      <c r="BI48" t="n">
+        <v>0.9999785204914512</v>
+      </c>
+      <c r="BJ48" t="n">
+        <v>9.712984233428587e-06</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>XGBClassifier_no_fragmentation_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>{'estimator': XGBClassifier(base_score=None, booster=None, callbacks=None,
+              colsample_bylevel=None, colsample_bynode=None,
+              colsample_bytree=None, device=None, early_stopping_rounds=None,
+              enable_categorical=False, eval_metric=None, feature_types=None,
+              gamma=None, grow_policy=None, importance_type=None,
+              interaction_constraints=None, learning_rate=None, max_bin=None,
+              max_cat_threshold=None, max_cat_to_onehot=None,
+              max_delta_step=None, max_depth=None, max_leaves=None,
+              min_child_weight=None, missing=nan, monotone_constraints=None,
+              multi_strategy=None, n_estimators=None, n_jobs=None,
+              num_parallel_tree=None, random_state=None, ...), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.9189189189189189</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.9918181818181818</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.040087223052978516, 0.034047842025756836, 0.03880500793457031, 0.03655886650085449, 0.02805185317993164, 0.029697179794311523, 0.032996177673339844</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>0.03432059288024902</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.03404784202575684</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.004155467747294397</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>0.005447864532470703, 0.0055103302001953125, 0.005059719085693359, 0.005346059799194336, 0.004913330078125, 0.005151033401489258, 0.0051310062408447266</t>
+        </is>
+      </c>
+      <c r="T49" t="n">
+        <v>0.005222763334001813</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0.005151033401489258</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0.0002015880468839288</v>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.8490566037735849, 0.9245283018867925, 0.8679245283018868, 0.9245283018867925, 0.9056603773584906, 0.9433962264150944</t>
+        </is>
+      </c>
+      <c r="X49" t="n">
+        <v>0.9005690326445043</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0.03131362832610417</v>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>0.7692307692307692, 0.7142857142857143, 0.8461538461538461, 0.7586206896551724, 0.8461538461538461, 0.8148148148148148, 0.896551724137931</t>
+        </is>
+      </c>
+      <c r="AB49" t="n">
+        <v>0.8065444863474419</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.05795095063066099</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>0.9090909090909091, 0.7142857142857143, 0.9166666666666666, 0.7333333333333333, 0.9166666666666666, 0.8461538461538461, 0.8666666666666667</t>
+        </is>
+      </c>
+      <c r="AF49" t="n">
+        <v>0.8432662575519717</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0.07962884487224849</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>0.6666666666666666, 0.7142857142857143, 0.7857142857142857, 0.7857142857142857, 0.7857142857142857, 0.7857142857142857, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0.7789115646258503</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>0.07498437988111771</v>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>0.9794871794871796, 0.9139194139194139, 0.9835164835164836, 0.9230769230769231, 0.9908424908424909, 0.9358974358974359, 0.9926739926739928</t>
+        </is>
+      </c>
+      <c r="AN49" t="n">
+        <v>0.9599162742019886</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0.9794871794871796</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>0.03166621171178035</v>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="AR49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="AV49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="AZ49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BD49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG49" t="inlineStr">
+        <is>
+          <t>0.9999999999999999, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BH49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ49" t="n">
+        <v>4.196248604251576e-17</v>
       </c>
     </row>
   </sheetData>

--- a/results/metrics_modelling3.xlsx
+++ b/results/metrics_modelling3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK51"/>
+  <dimension ref="A1:BK53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11971,6 +11971,448 @@
         <v>0.004629350087943543</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DecisionStump_splashing_greater_or_equal_kl</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>{'estimator': DecisionStumpEstimator(less_sign=False), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'inclination', 'Re', 'We'), 'log_features': (), 'minmax_features': (), 'passthrough_features': ('K', 'relative_roughness'), 'std_features': (), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>0.7733333333333333</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.8780487804878049</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.8089887640449439</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.7824074074074074</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.7744107744107744</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.8930817610062893</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.7395833333333334</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.8091168091168093</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.7888392857142857</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.0009999275207519531, 0.0009720325469970703, 0.001028299331665039, 0.001001119613647461, 0.0009963512420654297, 0.0009982585906982422, 0.0010044574737548828</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>0.001000063759940011</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.0009999275207519531</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1.521501112110338e-05</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>0.00299835205078125, 0.003001689910888672, 0.004131317138671875, 0.00299835205078125, 0.0030028820037841797, 0.004002094268798828, 0.0029954910278320312</t>
+        </is>
+      </c>
+      <c r="U52" t="n">
+        <v>0.003304311207362584</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0.003001689910888672</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0.000483421014286239</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.7169811320754716, 0.7735849056603774, 0.7924528301886793, 0.7547169811320755, 0.7735849056603774, 0.7169811320754716</t>
+        </is>
+      </c>
+      <c r="Y52" t="n">
+        <v>0.773884396525906</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0.7735849056603774</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0.05400311129267731</v>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>0.9117647058823529, 0.7619047619047619, 0.8000000000000002, 0.8358208955223881, 0.7719298245614036, 0.8000000000000002, 0.7692307692307693</t>
+        </is>
+      </c>
+      <c r="AC52" t="n">
+        <v>0.8072358510145251</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.8000000000000002</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0.04868838338201792</v>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>0.9393939393939394, 0.8571428571428571, 0.9230769230769231, 0.8484848484848485, 0.9565217391304348, 0.9230769230769231, 0.8064516129032258</t>
+        </is>
+      </c>
+      <c r="AG52" t="n">
+        <v>0.8934498347441646</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0.05175932188844546</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>0.8857142857142857, 0.6857142857142857, 0.7058823529411765, 0.8235294117647058, 0.6470588235294118, 0.7058823529411765, 0.7352941176470589</t>
+        </is>
+      </c>
+      <c r="AK52" t="n">
+        <v>0.7412965186074428</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>0.07758241980271595</v>
+      </c>
+      <c r="AN52" t="inlineStr">
+        <is>
+          <t>0.8902255639097744, 0.7317460317460317, 0.8003095975232198, 0.780185758513932, 0.7972136222910217, 0.8003095975232198, 0.7097523219814242</t>
+        </is>
+      </c>
+      <c r="AO52" t="n">
+        <v>0.7871060704983749</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>0.7972136222910217</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>0.05369315704565144</v>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>0.7547169811320755, 0.7836990595611285, 0.774294670846395, 0.7711598746081505, 0.7774294670846394, 0.774294670846395, 0.7836990595611285</t>
+        </is>
+      </c>
+      <c r="AS52" t="n">
+        <v>0.7741848262342733</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>0.774294670846395</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>0.009100552752323209</v>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>0.7903225806451611, 0.8169761273209549, 0.8105263157894737, 0.804289544235925, 0.814621409921671, 0.8105263157894737, 0.8160000000000001</t>
+        </is>
+      </c>
+      <c r="AW52" t="n">
+        <v>0.8090374705289513</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>0.8105263157894737</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>0.008618109631169334</v>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>0.8802395209580839, 0.8953488372093024, 0.8850574712643678, 0.8982035928143712, 0.8813559322033898, 0.8850574712643678, 0.9053254437869822</t>
+        </is>
+      </c>
+      <c r="BA52" t="n">
+        <v>0.8900840385001236</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>0.8850574712643678</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>0.008860609656082421</v>
+      </c>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>0.7170731707317073, 0.751219512195122, 0.7475728155339806, 0.7281553398058253, 0.7572815533980582, 0.7475728155339806, 0.7427184466019418</t>
+        </is>
+      </c>
+      <c r="BE52" t="n">
+        <v>0.7416562362572309</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>0.7475728155339806</v>
+      </c>
+      <c r="BG52" t="n">
+        <v>0.01305673449402361</v>
+      </c>
+      <c r="BH52" t="inlineStr">
+        <is>
+          <t>0.7700410101446147, 0.7966623876765083, 0.7852908325457513, 0.7888564309648596, 0.7857204227167283, 0.7852908325457513, 0.8005627631239797</t>
+        </is>
+      </c>
+      <c r="BI52" t="n">
+        <v>0.7874892399597417</v>
+      </c>
+      <c r="BJ52" t="n">
+        <v>0.7857204227167283</v>
+      </c>
+      <c r="BK52" t="n">
+        <v>0.009056712480178981</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>DecisionStump_no_fragmentation_less_kl</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>{'estimator': DecisionStumpEstimator(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'inclination', 'Re', 'We'), 'log_features': (), 'minmax_features': (), 'passthrough_features': ('K', 'relative_roughness'), 'std_features': (), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.7863636363636364</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.5073529411764706</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.8734177215189873</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.641860465116279</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.7830391359888513</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>0.0009992122650146484, 0.0, 0.001001119613647461, 0.0009984970092773438, 0.0010001659393310547, 0.0010004043579101562, 0.001001596450805664</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>0.0008572850908551897</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.001000165939331055</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0.0003499865417194363</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>0.0030050277709960938, 0.003998279571533203, 0.0040051937103271484, 0.003999471664428711, 0.004006385803222656, 0.002999544143676758, 0.0030057430267333984</t>
+        </is>
+      </c>
+      <c r="U53" t="n">
+        <v>0.003574235098702567</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0.003998279571533203</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0.0004943349529150095</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>0.7592592592592593, 0.6792452830188679, 0.6792452830188679, 0.6792452830188679, 0.7735849056603774, 0.8113207547169812, 0.7924528301886793</t>
+        </is>
+      </c>
+      <c r="Y53" t="n">
+        <v>0.7391933712688429</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0.7592592592592593</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0.05399162204934726</v>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>0.6486486486486486, 0.5853658536585367, 0.6046511627906977, 0.6046511627906977, 0.6470588235294117, 0.7058823529411764, 0.717948717948718</t>
+        </is>
+      </c>
+      <c r="AC53" t="n">
+        <v>0.6448866746154124</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.6470588235294117</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0.04759640829931121</v>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>0.5454545454545454, 0.4444444444444444, 0.4482758620689655, 0.4482758620689655, 0.55, 0.6, 0.56</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
+        <v>0.5137786734338459</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0.06008844131041598</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>0.8, 0.8571428571428571, 0.9285714285714286, 0.9285714285714286, 0.7857142857142857, 0.8571428571428571, 1.0</t>
+        </is>
+      </c>
+      <c r="AK53" t="n">
+        <v>0.8795918367346938</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>0.07116569703739875</v>
+      </c>
+      <c r="AN53" t="inlineStr">
+        <is>
+          <t>0.7717948717948718, 0.7362637362637363, 0.7591575091575091, 0.7591575091575091, 0.7774725274725274, 0.8260073260073261, 0.858974358974359</t>
+        </is>
+      </c>
+      <c r="AO53" t="n">
+        <v>0.7841182626896911</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>0.7717948717948718</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>0.03980361553852785</v>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>0.7358490566037735, 0.7492163009404389, 0.7492163009404389, 0.7492163009404389, 0.7335423197492164, 0.7272727272727273, 0.7304075235109718</t>
+        </is>
+      </c>
+      <c r="AS53" t="n">
+        <v>0.7392457899940009</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>0.7358490566037735</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>0.008974327046072948</v>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>0.6410256410256411, 0.6521739130434783, 0.6491228070175439, 0.6491228070175439, 0.6413502109704642, 0.6329113924050632, 0.6293103448275862</t>
+        </is>
+      </c>
+      <c r="AW53" t="n">
+        <v>0.6421453023296173</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>0.6413502109704642</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>0.008016333455327197</v>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>0.5, 0.5172413793103449, 0.5174825174825175, 0.5174825174825175, 0.5, 0.4934210526315789, 0.4965986394557823</t>
+        </is>
+      </c>
+      <c r="BA53" t="n">
+        <v>0.506032300908963</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>0.0100617608357479</v>
+      </c>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>0.8928571428571429, 0.8823529411764706, 0.8705882352941177, 0.8705882352941177, 0.8941176470588236, 0.8823529411764706, 0.8588235294117647</t>
+        </is>
+      </c>
+      <c r="BE53" t="n">
+        <v>0.8788115246098439</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="BG53" t="n">
+        <v>0.01190081008855812</v>
+      </c>
+      <c r="BH53" t="inlineStr">
+        <is>
+          <t>0.7861721611721613, 0.7916038210155857, 0.7878582202111614, 0.7878582202111614, 0.7846656611362495, 0.7766465560583209, 0.7712921065862243</t>
+        </is>
+      </c>
+      <c r="BI53" t="n">
+        <v>0.7837281066272662</v>
+      </c>
+      <c r="BJ53" t="n">
+        <v>0.7861721611721613</v>
+      </c>
+      <c r="BK53" t="n">
+        <v>0.006631067788558371</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/metrics_modelling3.xlsx
+++ b/results/metrics_modelling3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ53"/>
+  <dimension ref="A1:BJ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12260,6 +12260,1326 @@
         <v>0.006631067788558371</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier_splashing_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>{'estimator': AdaBoostClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.8815586419753086</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.9593908629441624</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.984375</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.9717223650385605</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.9953621031746032</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0.04229545593261719, 0.04643964767456055, 0.04575991630554199, 0.04851102828979492, 0.04134535789489746, 0.04512667655944824, 0.040598392486572266</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>0.04429663930620466</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.04512667655944824</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.002714393570599508</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>0.01538991928100586, 0.015076637268066406, 0.010388374328613281, 0.01736736297607422, 0.013797998428344727, 0.012734413146972656, 0.014501333236694336</t>
+        </is>
+      </c>
+      <c r="T54" t="n">
+        <v>0.01417943409511021</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0.01450133323669434</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0.002040394583262948</v>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.8113207547169812, 0.9056603773584906, 0.7924528301886793, 0.9245283018867925, 0.8113207547169812, 0.8301886792452831</t>
+        </is>
+      </c>
+      <c r="X54" t="n">
+        <v>0.852051512428871</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0.8301886792452831</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0.04903608490660909</v>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>0.9210526315789475, 0.8571428571428571, 0.9315068493150686, 0.8405797101449276, 0.9411764705882353, 0.84375, 0.8656716417910447</t>
+        </is>
+      </c>
+      <c r="AB54" t="n">
+        <v>0.8858400229372974</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0.8656716417910447</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.04042252933524638</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>0.8536585365853658, 0.8571428571428571, 0.8717948717948718, 0.8285714285714286, 0.9411764705882353, 0.9, 0.8787878787878788</t>
+        </is>
+      </c>
+      <c r="AF54" t="n">
+        <v>0.8758760062100911</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0.8717948717948718</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0.03370782503572691</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>1.0, 0.8571428571428571, 1.0, 0.8529411764705882, 0.9411764705882353, 0.7941176470588235, 0.8529411764705882</t>
+        </is>
+      </c>
+      <c r="AJ54" t="n">
+        <v>0.8997599039615846</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>0.07480638944209077</v>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>0.9353383458646617, 0.8714285714285714, 0.9226006191950464, 0.9009287925696594, 0.9411764705882353, 0.836687306501548, 0.8978328173374613</t>
+        </is>
+      </c>
+      <c r="AN54" t="n">
+        <v>0.9008561319264548</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>0.9009287925696594</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>0.03439339782656949</v>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>0.9276729559748428, 0.9247648902821317, 0.9278996865203761, 0.9247648902821317, 0.9153605015673981, 0.9498432601880877, 0.9310344827586207</t>
+        </is>
+      </c>
+      <c r="AR54" t="n">
+        <v>0.9287629525105128</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>0.9276729559748428</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>0.009732619941746736</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>0.9440389294403893, 0.9411764705882352, 0.943765281173594, 0.9423076923076923, 0.9346246973365618, 0.9611650485436893, 0.9473684210526316</t>
+        </is>
+      </c>
+      <c r="AV54" t="n">
+        <v>0.9449209343489706</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>0.943765281173594</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>0.007548296340363749</v>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>0.941747572815534, 0.9458128078817734, 0.9507389162561576, 0.9333333333333333, 0.9323671497584541, 0.9611650485436893, 0.9339622641509434</t>
+        </is>
+      </c>
+      <c r="AZ54" t="n">
+        <v>0.9427324418199835</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>0.941747572815534</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>0.009906864732307152</v>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>0.9463414634146341, 0.9365853658536586, 0.9368932038834952, 0.9514563106796117, 0.9368932038834952, 0.9611650485436893, 0.9611650485436893</t>
+        </is>
+      </c>
+      <c r="BD54" t="n">
+        <v>0.9472142349717533</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>0.9463414634146341</v>
+      </c>
+      <c r="BF54" t="n">
+        <v>0.0102401699157158</v>
+      </c>
+      <c r="BG54" t="inlineStr">
+        <is>
+          <t>0.9849341679257501, 0.9855370132648695, 0.9842984792507947, 0.9883366268579775, 0.9821934874130079, 0.9935991064524444, 0.9862960735458373</t>
+        </is>
+      </c>
+      <c r="BH54" t="n">
+        <v>0.986456422101526</v>
+      </c>
+      <c r="BI54" t="n">
+        <v>0.9855370132648695</v>
+      </c>
+      <c r="BJ54" t="n">
+        <v>0.00339265427510108</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier_no_fragmentation_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>{'estimator': AdaBoostClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.761904761904762</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.8945454545454545</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.9764309764309764</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.9493670886075949</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.9554140127388535</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.9983451399372896</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0.04655003547668457, 0.043056488037109375, 0.04389595985412598, 0.0430448055267334, 0.042558908462524414, 0.04320216178894043, 0.043022871017456055</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>0.04361874716622489</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.04305648803710938</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.001251668155833141</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>0.011513233184814453, 0.012504100799560547, 0.012018680572509766, 0.010513067245483398, 0.012743234634399414, 0.012613534927368164, 0.010503053665161133</t>
+        </is>
+      </c>
+      <c r="T55" t="n">
+        <v>0.01177270071847098</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0.01201868057250977</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0.0008872424329106799</v>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>0.8518518518518519, 0.7924528301886793, 0.9245283018867925, 0.8113207547169812, 0.9056603773584906, 0.8679245283018868, 0.9056603773584906</t>
+        </is>
+      </c>
+      <c r="X55" t="n">
+        <v>0.8656284316661675</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0.04655774709538191</v>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.5925925925925927, 0.8461538461538461, 0.6875000000000001, 0.8148148148148148, 0.7407407407407408, 0.8275862068965518</t>
+        </is>
+      </c>
+      <c r="AB55" t="n">
+        <v>0.7489602192188399</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0.7407407407407408</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.08324269801375989</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.6153846153846154, 0.9166666666666666, 0.6111111111111112, 0.8461538461538461, 0.7692307692307693, 0.8</t>
+        </is>
+      </c>
+      <c r="AF55" t="n">
+        <v>0.755982905982906</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>0.1051066120353698</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.5714285714285714, 0.7857142857142857, 0.7857142857142857, 0.7857142857142857, 0.7142857142857143, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="AJ55" t="n">
+        <v>0.7476190476190475</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>0.08341589690323446</v>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>0.876923076923077, 0.8699633699633699, 0.9725274725274725, 0.8965201465201466, 0.946886446886447, 0.9120879120879121, 0.9413919413919414</t>
+        </is>
+      </c>
+      <c r="AN55" t="n">
+        <v>0.9166143380429095</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>0.9120879120879121</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>0.03552178990496289</v>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>0.9842767295597484, 0.9843260188087775, 0.9686520376175548, 0.9749216300940439, 0.9749216300940439, 0.9811912225705329, 0.9749216300940439</t>
+        </is>
+      </c>
+      <c r="AR55" t="n">
+        <v>0.9776015569769635</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>0.9749216300940439</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>0.005402406025743921</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>0.970059880239521, 0.9710982658959537, 0.941860465116279, 0.9523809523809523, 0.9534883720930232, 0.9651162790697674, 0.9534883720930232</t>
+        </is>
+      </c>
+      <c r="AV55" t="n">
+        <v>0.9582132266983601</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>0.9534883720930232</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>0.01000068786525098</v>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>0.9759036144578314, 0.9545454545454546, 0.9310344827586207, 0.963855421686747, 0.9425287356321839, 0.9540229885057471, 0.9425287356321839</t>
+        </is>
+      </c>
+      <c r="AZ55" t="n">
+        <v>0.9520599190312525</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>0.9540229885057471</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>0.01384321962691562</v>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>0.9642857142857143, 0.9882352941176471, 0.9529411764705882, 0.9411764705882353, 0.9647058823529412, 0.9764705882352941, 0.9647058823529412</t>
+        </is>
+      </c>
+      <c r="BD55" t="n">
+        <v>0.9646458583433375</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>0.9647058823529412</v>
+      </c>
+      <c r="BF55" t="n">
+        <v>0.01406228169870084</v>
+      </c>
+      <c r="BG55" t="inlineStr">
+        <is>
+          <t>0.9983465608465608, 0.998340874811463, 0.9959276018099548, 0.998265460030166, 0.9964303670186023, 0.9974358974358974, 0.9966817496229261</t>
+        </is>
+      </c>
+      <c r="BH55" t="n">
+        <v>0.9973469302250815</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>0.9974358974358974</v>
+      </c>
+      <c r="BJ55" t="n">
+        <v>0.000936242175825913</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier_splashing_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>{'estimator': RandomForestClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.9019607843137256</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.9540895061728395</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.9999751984126984</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0.08300065994262695, 0.08986687660217285, 0.08384990692138672, 0.0838019847869873, 0.08411645889282227, 0.08526420593261719, 0.08512067794799805</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>0.08500296728951591</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.08411645889282227</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.002114803410730603</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>0.01667308807373047, 0.014289140701293945, 0.012070417404174805, 0.012803792953491211, 0.011937856674194336, 0.012521743774414062, 0.01160287857055664</t>
+        </is>
+      </c>
+      <c r="T56" t="n">
+        <v>0.0131284168788365</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0.01252174377441406</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0.00165828957663176</v>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.9056603773584906, 0.9056603773584906, 0.8490566037735849, 0.9245283018867925, 0.8490566037735849, 0.8113207547169812</t>
+        </is>
+      </c>
+      <c r="X56" t="n">
+        <v>0.8842467804731956</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0.04465478103184949</v>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>0.958904109589041, 0.9275362318840579, 0.9295774647887325, 0.8787878787878787, 0.9411764705882353, 0.8709677419354839, 0.861111111111111</t>
+        </is>
+      </c>
+      <c r="AB56" t="n">
+        <v>0.9097230012406486</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0.9275362318840579</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.03574049493633244</v>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>0.9210526315789473, 0.9411764705882353, 0.8918918918918919, 0.90625, 0.9411764705882353, 0.9642857142857143, 0.8157894736842105</t>
+        </is>
+      </c>
+      <c r="AF56" t="n">
+        <v>0.9116603789453193</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0.9210526315789473</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0.04505763835239565</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>1.0, 0.9142857142857143, 0.9705882352941176, 0.8529411764705882, 0.9411764705882353, 0.7941176470588235, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="AJ56" t="n">
+        <v>0.912124849939976</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>0.06482637499291748</v>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>0.9962406015037594, 0.9531746031746031, 0.9876160990712075, 0.9210526315789473, 0.9396284829721362, 0.93343653250774, 0.9303405572755418</t>
+        </is>
+      </c>
+      <c r="AN56" t="n">
+        <v>0.9516413582977049</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>0.9396284829721362</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>0.02712601410933079</v>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="AR56" t="n">
+        <v>0.9977594515655674</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>0.001417051170840857</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="AV56" t="n">
+        <v>0.9982688114216364</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>0.001094907038779773</v>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="AZ56" t="n">
+        <v>0.9965459942243395</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>0.002184519446236978</v>
+      </c>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BD56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG56" t="inlineStr">
+        <is>
+          <t>0.9999784157133607, 0.9999999999999999, 0.9999785204914512, 0.9999785204914511, 0.9999785204914512, 1.0, 0.9999785204914512</t>
+        </is>
+      </c>
+      <c r="BH56" t="n">
+        <v>0.999984642525595</v>
+      </c>
+      <c r="BI56" t="n">
+        <v>0.9999785204914512</v>
+      </c>
+      <c r="BJ56" t="n">
+        <v>9.712984233428587e-06</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier_no_fragmentation_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>{'estimator': RandomForestClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0.9466666666666667</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.9836363636363636</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0.07860326766967773, 0.07773756980895996, 0.07647180557250977, 0.08232712745666504, 0.08237171173095703, 0.0821986198425293, 0.07474780082702637</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>0.07920827184404645</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0.07860326766967773</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0.002893091210809317</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>0.009609460830688477, 0.012346744537353516, 0.01396632194519043, 0.009385347366333008, 0.011641263961791992, 0.011887550354003906, 0.013554096221923828</t>
+        </is>
+      </c>
+      <c r="T57" t="n">
+        <v>0.01177011217389788</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0.01188755035400391</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0.001635514437545498</v>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>0.8333333333333334, 0.7924528301886793, 0.9056603773584906, 0.8113207547169812, 0.9433962264150944, 0.9433962264150944, 0.9433962264150944</t>
+        </is>
+      </c>
+      <c r="X57" t="n">
+        <v>0.8818508535489668</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0.06239373065756213</v>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>0.6666666666666665, 0.6206896551724138, 0.8148148148148148, 0.6428571428571429, 0.88, 0.888888888888889, 0.896551724137931</t>
+        </is>
+      </c>
+      <c r="AB57" t="n">
+        <v>0.7729241275054084</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.1154711366108976</v>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>0.75, 0.6, 0.8461538461538461, 0.6428571428571429, 1.0, 0.9230769230769231, 0.8666666666666667</t>
+        </is>
+      </c>
+      <c r="AF57" t="n">
+        <v>0.8041077969649398</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>0.1356457100227356</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>0.6, 0.6428571428571429, 0.7857142857142857, 0.6428571428571429, 0.7857142857142857, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="AJ57" t="n">
+        <v>0.7489795918367347</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>0.1142492653247217</v>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>0.9521367521367521, 0.8589743589743589, 0.9752747252747253, 0.9175824175824177, 0.9908424908424909, 0.9093406593406593, 0.9871794871794871</t>
+        </is>
+      </c>
+      <c r="AN57" t="n">
+        <v>0.941618698761556</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>0.9521367521367521</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>0.04502670042190914</v>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="AR57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="AV57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="AZ57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BD57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG57" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BH57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>LGBMClassifier_splashing_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>{'estimator': LGBMClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.9517746913580247</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.9999751984126984</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>0.13146328926086426, 0.01901865005493164, 0.020598173141479492, 0.01701521873474121, 0.0210115909576416, 0.022017240524291992, 0.018513917922973633</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>0.03566258294241769</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0.02059817314147949</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.03914146525364429</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>0.011510848999023438, 0.010015487670898438, 0.011011838912963867, 0.009507179260253906, 0.008506298065185547, 0.010508298873901367, 0.01151418685913086</t>
+        </is>
+      </c>
+      <c r="T58" t="n">
+        <v>0.01036773409162249</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0.01050829887390137</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0.00102715079973434</v>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.8490566037735849, 0.9433962264150944, 0.8490566037735849, 0.9056603773584906, 0.8679245283018868, 0.8867924528301887</t>
+        </is>
+      </c>
+      <c r="X58" t="n">
+        <v>0.8949785364879705</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0.04157065551294201</v>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.888888888888889, 0.9565217391304348, 0.8823529411764706, 0.9253731343283583, 0.8923076923076922, 0.9142857142857143</t>
+        </is>
+      </c>
+      <c r="AB58" t="n">
+        <v>0.9188503331913973</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.03221653434902594</v>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.8648648648648649, 0.9428571428571428, 0.8823529411764706, 0.9393939393939394, 0.9354838709677419, 0.8888888888888888</t>
+        </is>
+      </c>
+      <c r="AF58" t="n">
+        <v>0.9142553705849993</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>0.9354838709677419</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>0.03163541475077126</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>1.0, 0.9142857142857143, 0.9705882352941176, 0.8823529411764706, 0.9117647058823529, 0.8529411764705882, 0.9411764705882353</t>
+        </is>
+      </c>
+      <c r="AJ58" t="n">
+        <v>0.9247298919567827</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>0.04669914237959417</v>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>0.9954887218045113, 0.9523809523809523, 0.9845201238390093, 0.9458204334365325, 0.9427244582043344, 0.9202786377708978, 0.9256965944272446</t>
+        </is>
+      </c>
+      <c r="AN58" t="n">
+        <v>0.9524157031233546</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>0.9458204334365325</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>0.02610445918315244</v>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="AR58" t="n">
+        <v>0.9977594515655674</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>0.001417051170840857</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="AV58" t="n">
+        <v>0.9982688114216364</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>0.001094907038779773</v>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="AZ58" t="n">
+        <v>0.9965459942243395</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>0.002184519446236978</v>
+      </c>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BD58" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE58" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG58" t="inlineStr">
+        <is>
+          <t>0.9999784157133607, 1.0, 0.9999785204914512, 0.9999785204914512, 0.9999785204914511, 1.0, 0.9999785204914511</t>
+        </is>
+      </c>
+      <c r="BH58" t="n">
+        <v>0.999984642525595</v>
+      </c>
+      <c r="BI58" t="n">
+        <v>0.9999785204914512</v>
+      </c>
+      <c r="BJ58" t="n">
+        <v>9.712984233463661e-06</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>LGBMClassifier_no_fragmentation_Stk_diam</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>{'estimator': LGBMClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.8780487804878048</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.9854545454545455</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1</v>
+      </c>
+      <c r="N59" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0.019602537155151367, 0.014482259750366211, 0.02073359489440918, 0.01558375358581543, 0.014885902404785156, 0.013393163681030273, 0.015613317489624023</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>0.01632778985159738</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0.01558375358581543</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.002543793573807909</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>0.009006738662719727, 0.006963491439819336, 0.007121086120605469, 0.00627446174621582, 0.012955904006958008, 0.0137939453125, 0.010265588760375977</t>
+        </is>
+      </c>
+      <c r="T59" t="n">
+        <v>0.009483030864170619</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0.009006738662719727</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0.002769885506555768</v>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>0.8518518518518519, 0.9056603773584906, 0.9433962264150944, 0.8867924528301887, 0.9245283018867925, 0.9245283018867925, 0.9433962264150944</t>
+        </is>
+      </c>
+      <c r="X59" t="n">
+        <v>0.9114505340920437</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0.9245283018867925</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0.03065163791537664</v>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>0.6666666666666667, 0.8275862068965518, 0.88, 0.7999999999999999, 0.8461538461538461, 0.8571428571428571, 0.896551724137931</t>
+        </is>
+      </c>
+      <c r="AB59" t="n">
+        <v>0.8248716144282646</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.07103954153456497</v>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.8, 1.0, 0.75, 0.9166666666666666, 0.8571428571428571, 0.8666666666666667</t>
+        </is>
+      </c>
+      <c r="AF59" t="n">
+        <v>0.8684807256235827</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>0.07454129035294924</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>0.5333333333333333, 0.8571428571428571, 0.7857142857142857, 0.8571428571428571, 0.7857142857142857, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="AJ59" t="n">
+        <v>0.8006802721088435</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>0.1182265172078387</v>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>0.958974358974359, 0.9322344322344323, 0.990842490842491, 0.9377289377289377, 0.9816849816849818, 0.9139194139194139, 0.9816849816849818</t>
+        </is>
+      </c>
+      <c r="AN59" t="n">
+        <v>0.9567242281527996</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>0.958974358974359</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>0.02727641748426234</v>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="AR59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="AV59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="AZ59" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BD59" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE59" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG59" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BH59" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI59" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ59" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/metrics_modelling3.xlsx
+++ b/results/metrics_modelling3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ59"/>
+  <dimension ref="A1:DH60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -739,6 +739,256 @@
           <t>cv_train_roc_auc_std</t>
         </is>
       </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>holdout_test_f1_macro</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>holdout_test_accuracy_balanced</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>holdout_test_precision_class_0</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>holdout_test_recall_class_0</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>holdout_test_f1_class_0</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>holdout_train_f1_macro</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>holdout_train_accuracy_balanced</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>holdout_train_precision_class_0</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>holdout_train_recall_class_0</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>holdout_train_f1_class_0</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_accuracy_balanced</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_accuracy_balanced_mean</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_accuracy_balanced_median</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_accuracy_balanced_std</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_f1_class_0</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_f1_class_0_mean</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_f1_class_0_median</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_f1_class_0_std</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_f1_macro</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_f1_macro_mean</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_f1_macro_median</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_f1_macro_std</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_precision_class_0</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_precision_class_0_mean</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_precision_class_0_median</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_precision_class_0_std</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_recall_class_0</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_recall_class_0_mean</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_recall_class_0_median</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>cv_test_recall_class_0_std</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_accuracy_balanced</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_accuracy_balanced_mean</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_accuracy_balanced_median</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_accuracy_balanced_std</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_f1_class_0</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_f1_class_0_mean</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_f1_class_0_median</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_f1_class_0_std</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_f1_macro</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_f1_macro_mean</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_f1_macro_median</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_f1_macro_std</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_precision_class_0</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_precision_class_0_mean</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_precision_class_0_median</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_precision_class_0_std</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_recall_class_0</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_recall_class_0_mean</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_recall_class_0_median</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>cv_train_recall_class_0_std</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -959,6 +1209,56 @@
       <c r="BJ2" t="n">
         <v>0.006878900544216725</v>
       </c>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
+      <c r="CD2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr"/>
+      <c r="CF2" t="inlineStr"/>
+      <c r="CG2" t="inlineStr"/>
+      <c r="CH2" t="inlineStr"/>
+      <c r="CI2" t="inlineStr"/>
+      <c r="CJ2" t="inlineStr"/>
+      <c r="CK2" t="inlineStr"/>
+      <c r="CL2" t="inlineStr"/>
+      <c r="CM2" t="inlineStr"/>
+      <c r="CN2" t="inlineStr"/>
+      <c r="CO2" t="inlineStr"/>
+      <c r="CP2" t="inlineStr"/>
+      <c r="CQ2" t="inlineStr"/>
+      <c r="CR2" t="inlineStr"/>
+      <c r="CS2" t="inlineStr"/>
+      <c r="CT2" t="inlineStr"/>
+      <c r="CU2" t="inlineStr"/>
+      <c r="CV2" t="inlineStr"/>
+      <c r="CW2" t="inlineStr"/>
+      <c r="CX2" t="inlineStr"/>
+      <c r="CY2" t="inlineStr"/>
+      <c r="CZ2" t="inlineStr"/>
+      <c r="DA2" t="inlineStr"/>
+      <c r="DB2" t="inlineStr"/>
+      <c r="DC2" t="inlineStr"/>
+      <c r="DD2" t="inlineStr"/>
+      <c r="DE2" t="inlineStr"/>
+      <c r="DF2" t="inlineStr"/>
+      <c r="DG2" t="inlineStr"/>
+      <c r="DH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1179,6 +1479,56 @@
       <c r="BJ3" t="n">
         <v>0.005635428789683134</v>
       </c>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+      <c r="BO3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="inlineStr"/>
+      <c r="BX3" t="inlineStr"/>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="inlineStr"/>
+      <c r="CA3" t="inlineStr"/>
+      <c r="CB3" t="inlineStr"/>
+      <c r="CC3" t="inlineStr"/>
+      <c r="CD3" t="inlineStr"/>
+      <c r="CE3" t="inlineStr"/>
+      <c r="CF3" t="inlineStr"/>
+      <c r="CG3" t="inlineStr"/>
+      <c r="CH3" t="inlineStr"/>
+      <c r="CI3" t="inlineStr"/>
+      <c r="CJ3" t="inlineStr"/>
+      <c r="CK3" t="inlineStr"/>
+      <c r="CL3" t="inlineStr"/>
+      <c r="CM3" t="inlineStr"/>
+      <c r="CN3" t="inlineStr"/>
+      <c r="CO3" t="inlineStr"/>
+      <c r="CP3" t="inlineStr"/>
+      <c r="CQ3" t="inlineStr"/>
+      <c r="CR3" t="inlineStr"/>
+      <c r="CS3" t="inlineStr"/>
+      <c r="CT3" t="inlineStr"/>
+      <c r="CU3" t="inlineStr"/>
+      <c r="CV3" t="inlineStr"/>
+      <c r="CW3" t="inlineStr"/>
+      <c r="CX3" t="inlineStr"/>
+      <c r="CY3" t="inlineStr"/>
+      <c r="CZ3" t="inlineStr"/>
+      <c r="DA3" t="inlineStr"/>
+      <c r="DB3" t="inlineStr"/>
+      <c r="DC3" t="inlineStr"/>
+      <c r="DD3" t="inlineStr"/>
+      <c r="DE3" t="inlineStr"/>
+      <c r="DF3" t="inlineStr"/>
+      <c r="DG3" t="inlineStr"/>
+      <c r="DH3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1399,6 +1749,56 @@
       <c r="BJ4" t="n">
         <v>0.007603060102699606</v>
       </c>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr"/>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
+      <c r="BZ4" t="inlineStr"/>
+      <c r="CA4" t="inlineStr"/>
+      <c r="CB4" t="inlineStr"/>
+      <c r="CC4" t="inlineStr"/>
+      <c r="CD4" t="inlineStr"/>
+      <c r="CE4" t="inlineStr"/>
+      <c r="CF4" t="inlineStr"/>
+      <c r="CG4" t="inlineStr"/>
+      <c r="CH4" t="inlineStr"/>
+      <c r="CI4" t="inlineStr"/>
+      <c r="CJ4" t="inlineStr"/>
+      <c r="CK4" t="inlineStr"/>
+      <c r="CL4" t="inlineStr"/>
+      <c r="CM4" t="inlineStr"/>
+      <c r="CN4" t="inlineStr"/>
+      <c r="CO4" t="inlineStr"/>
+      <c r="CP4" t="inlineStr"/>
+      <c r="CQ4" t="inlineStr"/>
+      <c r="CR4" t="inlineStr"/>
+      <c r="CS4" t="inlineStr"/>
+      <c r="CT4" t="inlineStr"/>
+      <c r="CU4" t="inlineStr"/>
+      <c r="CV4" t="inlineStr"/>
+      <c r="CW4" t="inlineStr"/>
+      <c r="CX4" t="inlineStr"/>
+      <c r="CY4" t="inlineStr"/>
+      <c r="CZ4" t="inlineStr"/>
+      <c r="DA4" t="inlineStr"/>
+      <c r="DB4" t="inlineStr"/>
+      <c r="DC4" t="inlineStr"/>
+      <c r="DD4" t="inlineStr"/>
+      <c r="DE4" t="inlineStr"/>
+      <c r="DF4" t="inlineStr"/>
+      <c r="DG4" t="inlineStr"/>
+      <c r="DH4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1619,6 +2019,56 @@
       <c r="BJ5" t="n">
         <v>0.005604009792409489</v>
       </c>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="inlineStr"/>
+      <c r="BS5" t="inlineStr"/>
+      <c r="BT5" t="inlineStr"/>
+      <c r="BU5" t="inlineStr"/>
+      <c r="BV5" t="inlineStr"/>
+      <c r="BW5" t="inlineStr"/>
+      <c r="BX5" t="inlineStr"/>
+      <c r="BY5" t="inlineStr"/>
+      <c r="BZ5" t="inlineStr"/>
+      <c r="CA5" t="inlineStr"/>
+      <c r="CB5" t="inlineStr"/>
+      <c r="CC5" t="inlineStr"/>
+      <c r="CD5" t="inlineStr"/>
+      <c r="CE5" t="inlineStr"/>
+      <c r="CF5" t="inlineStr"/>
+      <c r="CG5" t="inlineStr"/>
+      <c r="CH5" t="inlineStr"/>
+      <c r="CI5" t="inlineStr"/>
+      <c r="CJ5" t="inlineStr"/>
+      <c r="CK5" t="inlineStr"/>
+      <c r="CL5" t="inlineStr"/>
+      <c r="CM5" t="inlineStr"/>
+      <c r="CN5" t="inlineStr"/>
+      <c r="CO5" t="inlineStr"/>
+      <c r="CP5" t="inlineStr"/>
+      <c r="CQ5" t="inlineStr"/>
+      <c r="CR5" t="inlineStr"/>
+      <c r="CS5" t="inlineStr"/>
+      <c r="CT5" t="inlineStr"/>
+      <c r="CU5" t="inlineStr"/>
+      <c r="CV5" t="inlineStr"/>
+      <c r="CW5" t="inlineStr"/>
+      <c r="CX5" t="inlineStr"/>
+      <c r="CY5" t="inlineStr"/>
+      <c r="CZ5" t="inlineStr"/>
+      <c r="DA5" t="inlineStr"/>
+      <c r="DB5" t="inlineStr"/>
+      <c r="DC5" t="inlineStr"/>
+      <c r="DD5" t="inlineStr"/>
+      <c r="DE5" t="inlineStr"/>
+      <c r="DF5" t="inlineStr"/>
+      <c r="DG5" t="inlineStr"/>
+      <c r="DH5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1839,6 +2289,56 @@
       <c r="BJ6" t="n">
         <v>0.002061603425119283</v>
       </c>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="inlineStr"/>
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr"/>
+      <c r="BZ6" t="inlineStr"/>
+      <c r="CA6" t="inlineStr"/>
+      <c r="CB6" t="inlineStr"/>
+      <c r="CC6" t="inlineStr"/>
+      <c r="CD6" t="inlineStr"/>
+      <c r="CE6" t="inlineStr"/>
+      <c r="CF6" t="inlineStr"/>
+      <c r="CG6" t="inlineStr"/>
+      <c r="CH6" t="inlineStr"/>
+      <c r="CI6" t="inlineStr"/>
+      <c r="CJ6" t="inlineStr"/>
+      <c r="CK6" t="inlineStr"/>
+      <c r="CL6" t="inlineStr"/>
+      <c r="CM6" t="inlineStr"/>
+      <c r="CN6" t="inlineStr"/>
+      <c r="CO6" t="inlineStr"/>
+      <c r="CP6" t="inlineStr"/>
+      <c r="CQ6" t="inlineStr"/>
+      <c r="CR6" t="inlineStr"/>
+      <c r="CS6" t="inlineStr"/>
+      <c r="CT6" t="inlineStr"/>
+      <c r="CU6" t="inlineStr"/>
+      <c r="CV6" t="inlineStr"/>
+      <c r="CW6" t="inlineStr"/>
+      <c r="CX6" t="inlineStr"/>
+      <c r="CY6" t="inlineStr"/>
+      <c r="CZ6" t="inlineStr"/>
+      <c r="DA6" t="inlineStr"/>
+      <c r="DB6" t="inlineStr"/>
+      <c r="DC6" t="inlineStr"/>
+      <c r="DD6" t="inlineStr"/>
+      <c r="DE6" t="inlineStr"/>
+      <c r="DF6" t="inlineStr"/>
+      <c r="DG6" t="inlineStr"/>
+      <c r="DH6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2059,6 +2559,56 @@
       <c r="BJ7" t="n">
         <v>0.002556083322909469</v>
       </c>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
+      <c r="BO7" t="inlineStr"/>
+      <c r="BP7" t="inlineStr"/>
+      <c r="BQ7" t="inlineStr"/>
+      <c r="BR7" t="inlineStr"/>
+      <c r="BS7" t="inlineStr"/>
+      <c r="BT7" t="inlineStr"/>
+      <c r="BU7" t="inlineStr"/>
+      <c r="BV7" t="inlineStr"/>
+      <c r="BW7" t="inlineStr"/>
+      <c r="BX7" t="inlineStr"/>
+      <c r="BY7" t="inlineStr"/>
+      <c r="BZ7" t="inlineStr"/>
+      <c r="CA7" t="inlineStr"/>
+      <c r="CB7" t="inlineStr"/>
+      <c r="CC7" t="inlineStr"/>
+      <c r="CD7" t="inlineStr"/>
+      <c r="CE7" t="inlineStr"/>
+      <c r="CF7" t="inlineStr"/>
+      <c r="CG7" t="inlineStr"/>
+      <c r="CH7" t="inlineStr"/>
+      <c r="CI7" t="inlineStr"/>
+      <c r="CJ7" t="inlineStr"/>
+      <c r="CK7" t="inlineStr"/>
+      <c r="CL7" t="inlineStr"/>
+      <c r="CM7" t="inlineStr"/>
+      <c r="CN7" t="inlineStr"/>
+      <c r="CO7" t="inlineStr"/>
+      <c r="CP7" t="inlineStr"/>
+      <c r="CQ7" t="inlineStr"/>
+      <c r="CR7" t="inlineStr"/>
+      <c r="CS7" t="inlineStr"/>
+      <c r="CT7" t="inlineStr"/>
+      <c r="CU7" t="inlineStr"/>
+      <c r="CV7" t="inlineStr"/>
+      <c r="CW7" t="inlineStr"/>
+      <c r="CX7" t="inlineStr"/>
+      <c r="CY7" t="inlineStr"/>
+      <c r="CZ7" t="inlineStr"/>
+      <c r="DA7" t="inlineStr"/>
+      <c r="DB7" t="inlineStr"/>
+      <c r="DC7" t="inlineStr"/>
+      <c r="DD7" t="inlineStr"/>
+      <c r="DE7" t="inlineStr"/>
+      <c r="DF7" t="inlineStr"/>
+      <c r="DG7" t="inlineStr"/>
+      <c r="DH7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2279,6 +2829,56 @@
       <c r="BJ8" t="n">
         <v>0.005460178801644405</v>
       </c>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+      <c r="BO8" t="inlineStr"/>
+      <c r="BP8" t="inlineStr"/>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr"/>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="inlineStr"/>
+      <c r="CA8" t="inlineStr"/>
+      <c r="CB8" t="inlineStr"/>
+      <c r="CC8" t="inlineStr"/>
+      <c r="CD8" t="inlineStr"/>
+      <c r="CE8" t="inlineStr"/>
+      <c r="CF8" t="inlineStr"/>
+      <c r="CG8" t="inlineStr"/>
+      <c r="CH8" t="inlineStr"/>
+      <c r="CI8" t="inlineStr"/>
+      <c r="CJ8" t="inlineStr"/>
+      <c r="CK8" t="inlineStr"/>
+      <c r="CL8" t="inlineStr"/>
+      <c r="CM8" t="inlineStr"/>
+      <c r="CN8" t="inlineStr"/>
+      <c r="CO8" t="inlineStr"/>
+      <c r="CP8" t="inlineStr"/>
+      <c r="CQ8" t="inlineStr"/>
+      <c r="CR8" t="inlineStr"/>
+      <c r="CS8" t="inlineStr"/>
+      <c r="CT8" t="inlineStr"/>
+      <c r="CU8" t="inlineStr"/>
+      <c r="CV8" t="inlineStr"/>
+      <c r="CW8" t="inlineStr"/>
+      <c r="CX8" t="inlineStr"/>
+      <c r="CY8" t="inlineStr"/>
+      <c r="CZ8" t="inlineStr"/>
+      <c r="DA8" t="inlineStr"/>
+      <c r="DB8" t="inlineStr"/>
+      <c r="DC8" t="inlineStr"/>
+      <c r="DD8" t="inlineStr"/>
+      <c r="DE8" t="inlineStr"/>
+      <c r="DF8" t="inlineStr"/>
+      <c r="DG8" t="inlineStr"/>
+      <c r="DH8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2499,6 +3099,56 @@
       <c r="BJ9" t="n">
         <v>0.002988427262158605</v>
       </c>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr"/>
+      <c r="BR9" t="inlineStr"/>
+      <c r="BS9" t="inlineStr"/>
+      <c r="BT9" t="inlineStr"/>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="inlineStr"/>
+      <c r="BW9" t="inlineStr"/>
+      <c r="BX9" t="inlineStr"/>
+      <c r="BY9" t="inlineStr"/>
+      <c r="BZ9" t="inlineStr"/>
+      <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="inlineStr"/>
+      <c r="CC9" t="inlineStr"/>
+      <c r="CD9" t="inlineStr"/>
+      <c r="CE9" t="inlineStr"/>
+      <c r="CF9" t="inlineStr"/>
+      <c r="CG9" t="inlineStr"/>
+      <c r="CH9" t="inlineStr"/>
+      <c r="CI9" t="inlineStr"/>
+      <c r="CJ9" t="inlineStr"/>
+      <c r="CK9" t="inlineStr"/>
+      <c r="CL9" t="inlineStr"/>
+      <c r="CM9" t="inlineStr"/>
+      <c r="CN9" t="inlineStr"/>
+      <c r="CO9" t="inlineStr"/>
+      <c r="CP9" t="inlineStr"/>
+      <c r="CQ9" t="inlineStr"/>
+      <c r="CR9" t="inlineStr"/>
+      <c r="CS9" t="inlineStr"/>
+      <c r="CT9" t="inlineStr"/>
+      <c r="CU9" t="inlineStr"/>
+      <c r="CV9" t="inlineStr"/>
+      <c r="CW9" t="inlineStr"/>
+      <c r="CX9" t="inlineStr"/>
+      <c r="CY9" t="inlineStr"/>
+      <c r="CZ9" t="inlineStr"/>
+      <c r="DA9" t="inlineStr"/>
+      <c r="DB9" t="inlineStr"/>
+      <c r="DC9" t="inlineStr"/>
+      <c r="DD9" t="inlineStr"/>
+      <c r="DE9" t="inlineStr"/>
+      <c r="DF9" t="inlineStr"/>
+      <c r="DG9" t="inlineStr"/>
+      <c r="DH9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2719,6 +3369,56 @@
       <c r="BJ10" t="n">
         <v>0.0005871770933261723</v>
       </c>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr"/>
+      <c r="BQ10" t="inlineStr"/>
+      <c r="BR10" t="inlineStr"/>
+      <c r="BS10" t="inlineStr"/>
+      <c r="BT10" t="inlineStr"/>
+      <c r="BU10" t="inlineStr"/>
+      <c r="BV10" t="inlineStr"/>
+      <c r="BW10" t="inlineStr"/>
+      <c r="BX10" t="inlineStr"/>
+      <c r="BY10" t="inlineStr"/>
+      <c r="BZ10" t="inlineStr"/>
+      <c r="CA10" t="inlineStr"/>
+      <c r="CB10" t="inlineStr"/>
+      <c r="CC10" t="inlineStr"/>
+      <c r="CD10" t="inlineStr"/>
+      <c r="CE10" t="inlineStr"/>
+      <c r="CF10" t="inlineStr"/>
+      <c r="CG10" t="inlineStr"/>
+      <c r="CH10" t="inlineStr"/>
+      <c r="CI10" t="inlineStr"/>
+      <c r="CJ10" t="inlineStr"/>
+      <c r="CK10" t="inlineStr"/>
+      <c r="CL10" t="inlineStr"/>
+      <c r="CM10" t="inlineStr"/>
+      <c r="CN10" t="inlineStr"/>
+      <c r="CO10" t="inlineStr"/>
+      <c r="CP10" t="inlineStr"/>
+      <c r="CQ10" t="inlineStr"/>
+      <c r="CR10" t="inlineStr"/>
+      <c r="CS10" t="inlineStr"/>
+      <c r="CT10" t="inlineStr"/>
+      <c r="CU10" t="inlineStr"/>
+      <c r="CV10" t="inlineStr"/>
+      <c r="CW10" t="inlineStr"/>
+      <c r="CX10" t="inlineStr"/>
+      <c r="CY10" t="inlineStr"/>
+      <c r="CZ10" t="inlineStr"/>
+      <c r="DA10" t="inlineStr"/>
+      <c r="DB10" t="inlineStr"/>
+      <c r="DC10" t="inlineStr"/>
+      <c r="DD10" t="inlineStr"/>
+      <c r="DE10" t="inlineStr"/>
+      <c r="DF10" t="inlineStr"/>
+      <c r="DG10" t="inlineStr"/>
+      <c r="DH10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2939,6 +3639,56 @@
       <c r="BJ11" t="n">
         <v>5.274484965747932e-05</v>
       </c>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+      <c r="BO11" t="inlineStr"/>
+      <c r="BP11" t="inlineStr"/>
+      <c r="BQ11" t="inlineStr"/>
+      <c r="BR11" t="inlineStr"/>
+      <c r="BS11" t="inlineStr"/>
+      <c r="BT11" t="inlineStr"/>
+      <c r="BU11" t="inlineStr"/>
+      <c r="BV11" t="inlineStr"/>
+      <c r="BW11" t="inlineStr"/>
+      <c r="BX11" t="inlineStr"/>
+      <c r="BY11" t="inlineStr"/>
+      <c r="BZ11" t="inlineStr"/>
+      <c r="CA11" t="inlineStr"/>
+      <c r="CB11" t="inlineStr"/>
+      <c r="CC11" t="inlineStr"/>
+      <c r="CD11" t="inlineStr"/>
+      <c r="CE11" t="inlineStr"/>
+      <c r="CF11" t="inlineStr"/>
+      <c r="CG11" t="inlineStr"/>
+      <c r="CH11" t="inlineStr"/>
+      <c r="CI11" t="inlineStr"/>
+      <c r="CJ11" t="inlineStr"/>
+      <c r="CK11" t="inlineStr"/>
+      <c r="CL11" t="inlineStr"/>
+      <c r="CM11" t="inlineStr"/>
+      <c r="CN11" t="inlineStr"/>
+      <c r="CO11" t="inlineStr"/>
+      <c r="CP11" t="inlineStr"/>
+      <c r="CQ11" t="inlineStr"/>
+      <c r="CR11" t="inlineStr"/>
+      <c r="CS11" t="inlineStr"/>
+      <c r="CT11" t="inlineStr"/>
+      <c r="CU11" t="inlineStr"/>
+      <c r="CV11" t="inlineStr"/>
+      <c r="CW11" t="inlineStr"/>
+      <c r="CX11" t="inlineStr"/>
+      <c r="CY11" t="inlineStr"/>
+      <c r="CZ11" t="inlineStr"/>
+      <c r="DA11" t="inlineStr"/>
+      <c r="DB11" t="inlineStr"/>
+      <c r="DC11" t="inlineStr"/>
+      <c r="DD11" t="inlineStr"/>
+      <c r="DE11" t="inlineStr"/>
+      <c r="DF11" t="inlineStr"/>
+      <c r="DG11" t="inlineStr"/>
+      <c r="DH11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3169,6 +3919,56 @@
       <c r="BJ12" t="n">
         <v>1.988619454760789e-05</v>
       </c>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+      <c r="BO12" t="inlineStr"/>
+      <c r="BP12" t="inlineStr"/>
+      <c r="BQ12" t="inlineStr"/>
+      <c r="BR12" t="inlineStr"/>
+      <c r="BS12" t="inlineStr"/>
+      <c r="BT12" t="inlineStr"/>
+      <c r="BU12" t="inlineStr"/>
+      <c r="BV12" t="inlineStr"/>
+      <c r="BW12" t="inlineStr"/>
+      <c r="BX12" t="inlineStr"/>
+      <c r="BY12" t="inlineStr"/>
+      <c r="BZ12" t="inlineStr"/>
+      <c r="CA12" t="inlineStr"/>
+      <c r="CB12" t="inlineStr"/>
+      <c r="CC12" t="inlineStr"/>
+      <c r="CD12" t="inlineStr"/>
+      <c r="CE12" t="inlineStr"/>
+      <c r="CF12" t="inlineStr"/>
+      <c r="CG12" t="inlineStr"/>
+      <c r="CH12" t="inlineStr"/>
+      <c r="CI12" t="inlineStr"/>
+      <c r="CJ12" t="inlineStr"/>
+      <c r="CK12" t="inlineStr"/>
+      <c r="CL12" t="inlineStr"/>
+      <c r="CM12" t="inlineStr"/>
+      <c r="CN12" t="inlineStr"/>
+      <c r="CO12" t="inlineStr"/>
+      <c r="CP12" t="inlineStr"/>
+      <c r="CQ12" t="inlineStr"/>
+      <c r="CR12" t="inlineStr"/>
+      <c r="CS12" t="inlineStr"/>
+      <c r="CT12" t="inlineStr"/>
+      <c r="CU12" t="inlineStr"/>
+      <c r="CV12" t="inlineStr"/>
+      <c r="CW12" t="inlineStr"/>
+      <c r="CX12" t="inlineStr"/>
+      <c r="CY12" t="inlineStr"/>
+      <c r="CZ12" t="inlineStr"/>
+      <c r="DA12" t="inlineStr"/>
+      <c r="DB12" t="inlineStr"/>
+      <c r="DC12" t="inlineStr"/>
+      <c r="DD12" t="inlineStr"/>
+      <c r="DE12" t="inlineStr"/>
+      <c r="DF12" t="inlineStr"/>
+      <c r="DG12" t="inlineStr"/>
+      <c r="DH12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3399,6 +4199,56 @@
       <c r="BJ13" t="n">
         <v>4.196248604251576e-17</v>
       </c>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+      <c r="BO13" t="inlineStr"/>
+      <c r="BP13" t="inlineStr"/>
+      <c r="BQ13" t="inlineStr"/>
+      <c r="BR13" t="inlineStr"/>
+      <c r="BS13" t="inlineStr"/>
+      <c r="BT13" t="inlineStr"/>
+      <c r="BU13" t="inlineStr"/>
+      <c r="BV13" t="inlineStr"/>
+      <c r="BW13" t="inlineStr"/>
+      <c r="BX13" t="inlineStr"/>
+      <c r="BY13" t="inlineStr"/>
+      <c r="BZ13" t="inlineStr"/>
+      <c r="CA13" t="inlineStr"/>
+      <c r="CB13" t="inlineStr"/>
+      <c r="CC13" t="inlineStr"/>
+      <c r="CD13" t="inlineStr"/>
+      <c r="CE13" t="inlineStr"/>
+      <c r="CF13" t="inlineStr"/>
+      <c r="CG13" t="inlineStr"/>
+      <c r="CH13" t="inlineStr"/>
+      <c r="CI13" t="inlineStr"/>
+      <c r="CJ13" t="inlineStr"/>
+      <c r="CK13" t="inlineStr"/>
+      <c r="CL13" t="inlineStr"/>
+      <c r="CM13" t="inlineStr"/>
+      <c r="CN13" t="inlineStr"/>
+      <c r="CO13" t="inlineStr"/>
+      <c r="CP13" t="inlineStr"/>
+      <c r="CQ13" t="inlineStr"/>
+      <c r="CR13" t="inlineStr"/>
+      <c r="CS13" t="inlineStr"/>
+      <c r="CT13" t="inlineStr"/>
+      <c r="CU13" t="inlineStr"/>
+      <c r="CV13" t="inlineStr"/>
+      <c r="CW13" t="inlineStr"/>
+      <c r="CX13" t="inlineStr"/>
+      <c r="CY13" t="inlineStr"/>
+      <c r="CZ13" t="inlineStr"/>
+      <c r="DA13" t="inlineStr"/>
+      <c r="DB13" t="inlineStr"/>
+      <c r="DC13" t="inlineStr"/>
+      <c r="DD13" t="inlineStr"/>
+      <c r="DE13" t="inlineStr"/>
+      <c r="DF13" t="inlineStr"/>
+      <c r="DG13" t="inlineStr"/>
+      <c r="DH13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3619,6 +4469,56 @@
       <c r="BJ14" t="n">
         <v>0.007205630596929708</v>
       </c>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
+      <c r="BO14" t="inlineStr"/>
+      <c r="BP14" t="inlineStr"/>
+      <c r="BQ14" t="inlineStr"/>
+      <c r="BR14" t="inlineStr"/>
+      <c r="BS14" t="inlineStr"/>
+      <c r="BT14" t="inlineStr"/>
+      <c r="BU14" t="inlineStr"/>
+      <c r="BV14" t="inlineStr"/>
+      <c r="BW14" t="inlineStr"/>
+      <c r="BX14" t="inlineStr"/>
+      <c r="BY14" t="inlineStr"/>
+      <c r="BZ14" t="inlineStr"/>
+      <c r="CA14" t="inlineStr"/>
+      <c r="CB14" t="inlineStr"/>
+      <c r="CC14" t="inlineStr"/>
+      <c r="CD14" t="inlineStr"/>
+      <c r="CE14" t="inlineStr"/>
+      <c r="CF14" t="inlineStr"/>
+      <c r="CG14" t="inlineStr"/>
+      <c r="CH14" t="inlineStr"/>
+      <c r="CI14" t="inlineStr"/>
+      <c r="CJ14" t="inlineStr"/>
+      <c r="CK14" t="inlineStr"/>
+      <c r="CL14" t="inlineStr"/>
+      <c r="CM14" t="inlineStr"/>
+      <c r="CN14" t="inlineStr"/>
+      <c r="CO14" t="inlineStr"/>
+      <c r="CP14" t="inlineStr"/>
+      <c r="CQ14" t="inlineStr"/>
+      <c r="CR14" t="inlineStr"/>
+      <c r="CS14" t="inlineStr"/>
+      <c r="CT14" t="inlineStr"/>
+      <c r="CU14" t="inlineStr"/>
+      <c r="CV14" t="inlineStr"/>
+      <c r="CW14" t="inlineStr"/>
+      <c r="CX14" t="inlineStr"/>
+      <c r="CY14" t="inlineStr"/>
+      <c r="CZ14" t="inlineStr"/>
+      <c r="DA14" t="inlineStr"/>
+      <c r="DB14" t="inlineStr"/>
+      <c r="DC14" t="inlineStr"/>
+      <c r="DD14" t="inlineStr"/>
+      <c r="DE14" t="inlineStr"/>
+      <c r="DF14" t="inlineStr"/>
+      <c r="DG14" t="inlineStr"/>
+      <c r="DH14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3839,6 +4739,56 @@
       <c r="BJ15" t="n">
         <v>0.006311578643324333</v>
       </c>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="inlineStr"/>
+      <c r="BO15" t="inlineStr"/>
+      <c r="BP15" t="inlineStr"/>
+      <c r="BQ15" t="inlineStr"/>
+      <c r="BR15" t="inlineStr"/>
+      <c r="BS15" t="inlineStr"/>
+      <c r="BT15" t="inlineStr"/>
+      <c r="BU15" t="inlineStr"/>
+      <c r="BV15" t="inlineStr"/>
+      <c r="BW15" t="inlineStr"/>
+      <c r="BX15" t="inlineStr"/>
+      <c r="BY15" t="inlineStr"/>
+      <c r="BZ15" t="inlineStr"/>
+      <c r="CA15" t="inlineStr"/>
+      <c r="CB15" t="inlineStr"/>
+      <c r="CC15" t="inlineStr"/>
+      <c r="CD15" t="inlineStr"/>
+      <c r="CE15" t="inlineStr"/>
+      <c r="CF15" t="inlineStr"/>
+      <c r="CG15" t="inlineStr"/>
+      <c r="CH15" t="inlineStr"/>
+      <c r="CI15" t="inlineStr"/>
+      <c r="CJ15" t="inlineStr"/>
+      <c r="CK15" t="inlineStr"/>
+      <c r="CL15" t="inlineStr"/>
+      <c r="CM15" t="inlineStr"/>
+      <c r="CN15" t="inlineStr"/>
+      <c r="CO15" t="inlineStr"/>
+      <c r="CP15" t="inlineStr"/>
+      <c r="CQ15" t="inlineStr"/>
+      <c r="CR15" t="inlineStr"/>
+      <c r="CS15" t="inlineStr"/>
+      <c r="CT15" t="inlineStr"/>
+      <c r="CU15" t="inlineStr"/>
+      <c r="CV15" t="inlineStr"/>
+      <c r="CW15" t="inlineStr"/>
+      <c r="CX15" t="inlineStr"/>
+      <c r="CY15" t="inlineStr"/>
+      <c r="CZ15" t="inlineStr"/>
+      <c r="DA15" t="inlineStr"/>
+      <c r="DB15" t="inlineStr"/>
+      <c r="DC15" t="inlineStr"/>
+      <c r="DD15" t="inlineStr"/>
+      <c r="DE15" t="inlineStr"/>
+      <c r="DF15" t="inlineStr"/>
+      <c r="DG15" t="inlineStr"/>
+      <c r="DH15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4059,6 +5009,56 @@
       <c r="BJ16" t="n">
         <v>0.007001423478172876</v>
       </c>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="inlineStr"/>
+      <c r="BO16" t="inlineStr"/>
+      <c r="BP16" t="inlineStr"/>
+      <c r="BQ16" t="inlineStr"/>
+      <c r="BR16" t="inlineStr"/>
+      <c r="BS16" t="inlineStr"/>
+      <c r="BT16" t="inlineStr"/>
+      <c r="BU16" t="inlineStr"/>
+      <c r="BV16" t="inlineStr"/>
+      <c r="BW16" t="inlineStr"/>
+      <c r="BX16" t="inlineStr"/>
+      <c r="BY16" t="inlineStr"/>
+      <c r="BZ16" t="inlineStr"/>
+      <c r="CA16" t="inlineStr"/>
+      <c r="CB16" t="inlineStr"/>
+      <c r="CC16" t="inlineStr"/>
+      <c r="CD16" t="inlineStr"/>
+      <c r="CE16" t="inlineStr"/>
+      <c r="CF16" t="inlineStr"/>
+      <c r="CG16" t="inlineStr"/>
+      <c r="CH16" t="inlineStr"/>
+      <c r="CI16" t="inlineStr"/>
+      <c r="CJ16" t="inlineStr"/>
+      <c r="CK16" t="inlineStr"/>
+      <c r="CL16" t="inlineStr"/>
+      <c r="CM16" t="inlineStr"/>
+      <c r="CN16" t="inlineStr"/>
+      <c r="CO16" t="inlineStr"/>
+      <c r="CP16" t="inlineStr"/>
+      <c r="CQ16" t="inlineStr"/>
+      <c r="CR16" t="inlineStr"/>
+      <c r="CS16" t="inlineStr"/>
+      <c r="CT16" t="inlineStr"/>
+      <c r="CU16" t="inlineStr"/>
+      <c r="CV16" t="inlineStr"/>
+      <c r="CW16" t="inlineStr"/>
+      <c r="CX16" t="inlineStr"/>
+      <c r="CY16" t="inlineStr"/>
+      <c r="CZ16" t="inlineStr"/>
+      <c r="DA16" t="inlineStr"/>
+      <c r="DB16" t="inlineStr"/>
+      <c r="DC16" t="inlineStr"/>
+      <c r="DD16" t="inlineStr"/>
+      <c r="DE16" t="inlineStr"/>
+      <c r="DF16" t="inlineStr"/>
+      <c r="DG16" t="inlineStr"/>
+      <c r="DH16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4279,6 +5279,56 @@
       <c r="BJ17" t="n">
         <v>0.005684785794350271</v>
       </c>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="inlineStr"/>
+      <c r="BM17" t="inlineStr"/>
+      <c r="BN17" t="inlineStr"/>
+      <c r="BO17" t="inlineStr"/>
+      <c r="BP17" t="inlineStr"/>
+      <c r="BQ17" t="inlineStr"/>
+      <c r="BR17" t="inlineStr"/>
+      <c r="BS17" t="inlineStr"/>
+      <c r="BT17" t="inlineStr"/>
+      <c r="BU17" t="inlineStr"/>
+      <c r="BV17" t="inlineStr"/>
+      <c r="BW17" t="inlineStr"/>
+      <c r="BX17" t="inlineStr"/>
+      <c r="BY17" t="inlineStr"/>
+      <c r="BZ17" t="inlineStr"/>
+      <c r="CA17" t="inlineStr"/>
+      <c r="CB17" t="inlineStr"/>
+      <c r="CC17" t="inlineStr"/>
+      <c r="CD17" t="inlineStr"/>
+      <c r="CE17" t="inlineStr"/>
+      <c r="CF17" t="inlineStr"/>
+      <c r="CG17" t="inlineStr"/>
+      <c r="CH17" t="inlineStr"/>
+      <c r="CI17" t="inlineStr"/>
+      <c r="CJ17" t="inlineStr"/>
+      <c r="CK17" t="inlineStr"/>
+      <c r="CL17" t="inlineStr"/>
+      <c r="CM17" t="inlineStr"/>
+      <c r="CN17" t="inlineStr"/>
+      <c r="CO17" t="inlineStr"/>
+      <c r="CP17" t="inlineStr"/>
+      <c r="CQ17" t="inlineStr"/>
+      <c r="CR17" t="inlineStr"/>
+      <c r="CS17" t="inlineStr"/>
+      <c r="CT17" t="inlineStr"/>
+      <c r="CU17" t="inlineStr"/>
+      <c r="CV17" t="inlineStr"/>
+      <c r="CW17" t="inlineStr"/>
+      <c r="CX17" t="inlineStr"/>
+      <c r="CY17" t="inlineStr"/>
+      <c r="CZ17" t="inlineStr"/>
+      <c r="DA17" t="inlineStr"/>
+      <c r="DB17" t="inlineStr"/>
+      <c r="DC17" t="inlineStr"/>
+      <c r="DD17" t="inlineStr"/>
+      <c r="DE17" t="inlineStr"/>
+      <c r="DF17" t="inlineStr"/>
+      <c r="DG17" t="inlineStr"/>
+      <c r="DH17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4499,6 +5549,56 @@
       <c r="BJ18" t="n">
         <v>0.002800999199045301</v>
       </c>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
+      <c r="BO18" t="inlineStr"/>
+      <c r="BP18" t="inlineStr"/>
+      <c r="BQ18" t="inlineStr"/>
+      <c r="BR18" t="inlineStr"/>
+      <c r="BS18" t="inlineStr"/>
+      <c r="BT18" t="inlineStr"/>
+      <c r="BU18" t="inlineStr"/>
+      <c r="BV18" t="inlineStr"/>
+      <c r="BW18" t="inlineStr"/>
+      <c r="BX18" t="inlineStr"/>
+      <c r="BY18" t="inlineStr"/>
+      <c r="BZ18" t="inlineStr"/>
+      <c r="CA18" t="inlineStr"/>
+      <c r="CB18" t="inlineStr"/>
+      <c r="CC18" t="inlineStr"/>
+      <c r="CD18" t="inlineStr"/>
+      <c r="CE18" t="inlineStr"/>
+      <c r="CF18" t="inlineStr"/>
+      <c r="CG18" t="inlineStr"/>
+      <c r="CH18" t="inlineStr"/>
+      <c r="CI18" t="inlineStr"/>
+      <c r="CJ18" t="inlineStr"/>
+      <c r="CK18" t="inlineStr"/>
+      <c r="CL18" t="inlineStr"/>
+      <c r="CM18" t="inlineStr"/>
+      <c r="CN18" t="inlineStr"/>
+      <c r="CO18" t="inlineStr"/>
+      <c r="CP18" t="inlineStr"/>
+      <c r="CQ18" t="inlineStr"/>
+      <c r="CR18" t="inlineStr"/>
+      <c r="CS18" t="inlineStr"/>
+      <c r="CT18" t="inlineStr"/>
+      <c r="CU18" t="inlineStr"/>
+      <c r="CV18" t="inlineStr"/>
+      <c r="CW18" t="inlineStr"/>
+      <c r="CX18" t="inlineStr"/>
+      <c r="CY18" t="inlineStr"/>
+      <c r="CZ18" t="inlineStr"/>
+      <c r="DA18" t="inlineStr"/>
+      <c r="DB18" t="inlineStr"/>
+      <c r="DC18" t="inlineStr"/>
+      <c r="DD18" t="inlineStr"/>
+      <c r="DE18" t="inlineStr"/>
+      <c r="DF18" t="inlineStr"/>
+      <c r="DG18" t="inlineStr"/>
+      <c r="DH18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4719,6 +5819,56 @@
       <c r="BJ19" t="n">
         <v>0.004564434495284856</v>
       </c>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="inlineStr"/>
+      <c r="BO19" t="inlineStr"/>
+      <c r="BP19" t="inlineStr"/>
+      <c r="BQ19" t="inlineStr"/>
+      <c r="BR19" t="inlineStr"/>
+      <c r="BS19" t="inlineStr"/>
+      <c r="BT19" t="inlineStr"/>
+      <c r="BU19" t="inlineStr"/>
+      <c r="BV19" t="inlineStr"/>
+      <c r="BW19" t="inlineStr"/>
+      <c r="BX19" t="inlineStr"/>
+      <c r="BY19" t="inlineStr"/>
+      <c r="BZ19" t="inlineStr"/>
+      <c r="CA19" t="inlineStr"/>
+      <c r="CB19" t="inlineStr"/>
+      <c r="CC19" t="inlineStr"/>
+      <c r="CD19" t="inlineStr"/>
+      <c r="CE19" t="inlineStr"/>
+      <c r="CF19" t="inlineStr"/>
+      <c r="CG19" t="inlineStr"/>
+      <c r="CH19" t="inlineStr"/>
+      <c r="CI19" t="inlineStr"/>
+      <c r="CJ19" t="inlineStr"/>
+      <c r="CK19" t="inlineStr"/>
+      <c r="CL19" t="inlineStr"/>
+      <c r="CM19" t="inlineStr"/>
+      <c r="CN19" t="inlineStr"/>
+      <c r="CO19" t="inlineStr"/>
+      <c r="CP19" t="inlineStr"/>
+      <c r="CQ19" t="inlineStr"/>
+      <c r="CR19" t="inlineStr"/>
+      <c r="CS19" t="inlineStr"/>
+      <c r="CT19" t="inlineStr"/>
+      <c r="CU19" t="inlineStr"/>
+      <c r="CV19" t="inlineStr"/>
+      <c r="CW19" t="inlineStr"/>
+      <c r="CX19" t="inlineStr"/>
+      <c r="CY19" t="inlineStr"/>
+      <c r="CZ19" t="inlineStr"/>
+      <c r="DA19" t="inlineStr"/>
+      <c r="DB19" t="inlineStr"/>
+      <c r="DC19" t="inlineStr"/>
+      <c r="DD19" t="inlineStr"/>
+      <c r="DE19" t="inlineStr"/>
+      <c r="DF19" t="inlineStr"/>
+      <c r="DG19" t="inlineStr"/>
+      <c r="DH19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4939,6 +6089,56 @@
       <c r="BJ20" t="n">
         <v>0.005477492640031644</v>
       </c>
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="inlineStr"/>
+      <c r="BM20" t="inlineStr"/>
+      <c r="BN20" t="inlineStr"/>
+      <c r="BO20" t="inlineStr"/>
+      <c r="BP20" t="inlineStr"/>
+      <c r="BQ20" t="inlineStr"/>
+      <c r="BR20" t="inlineStr"/>
+      <c r="BS20" t="inlineStr"/>
+      <c r="BT20" t="inlineStr"/>
+      <c r="BU20" t="inlineStr"/>
+      <c r="BV20" t="inlineStr"/>
+      <c r="BW20" t="inlineStr"/>
+      <c r="BX20" t="inlineStr"/>
+      <c r="BY20" t="inlineStr"/>
+      <c r="BZ20" t="inlineStr"/>
+      <c r="CA20" t="inlineStr"/>
+      <c r="CB20" t="inlineStr"/>
+      <c r="CC20" t="inlineStr"/>
+      <c r="CD20" t="inlineStr"/>
+      <c r="CE20" t="inlineStr"/>
+      <c r="CF20" t="inlineStr"/>
+      <c r="CG20" t="inlineStr"/>
+      <c r="CH20" t="inlineStr"/>
+      <c r="CI20" t="inlineStr"/>
+      <c r="CJ20" t="inlineStr"/>
+      <c r="CK20" t="inlineStr"/>
+      <c r="CL20" t="inlineStr"/>
+      <c r="CM20" t="inlineStr"/>
+      <c r="CN20" t="inlineStr"/>
+      <c r="CO20" t="inlineStr"/>
+      <c r="CP20" t="inlineStr"/>
+      <c r="CQ20" t="inlineStr"/>
+      <c r="CR20" t="inlineStr"/>
+      <c r="CS20" t="inlineStr"/>
+      <c r="CT20" t="inlineStr"/>
+      <c r="CU20" t="inlineStr"/>
+      <c r="CV20" t="inlineStr"/>
+      <c r="CW20" t="inlineStr"/>
+      <c r="CX20" t="inlineStr"/>
+      <c r="CY20" t="inlineStr"/>
+      <c r="CZ20" t="inlineStr"/>
+      <c r="DA20" t="inlineStr"/>
+      <c r="DB20" t="inlineStr"/>
+      <c r="DC20" t="inlineStr"/>
+      <c r="DD20" t="inlineStr"/>
+      <c r="DE20" t="inlineStr"/>
+      <c r="DF20" t="inlineStr"/>
+      <c r="DG20" t="inlineStr"/>
+      <c r="DH20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5159,6 +6359,56 @@
       <c r="BJ21" t="n">
         <v>0.003730130754326795</v>
       </c>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="inlineStr"/>
+      <c r="BM21" t="inlineStr"/>
+      <c r="BN21" t="inlineStr"/>
+      <c r="BO21" t="inlineStr"/>
+      <c r="BP21" t="inlineStr"/>
+      <c r="BQ21" t="inlineStr"/>
+      <c r="BR21" t="inlineStr"/>
+      <c r="BS21" t="inlineStr"/>
+      <c r="BT21" t="inlineStr"/>
+      <c r="BU21" t="inlineStr"/>
+      <c r="BV21" t="inlineStr"/>
+      <c r="BW21" t="inlineStr"/>
+      <c r="BX21" t="inlineStr"/>
+      <c r="BY21" t="inlineStr"/>
+      <c r="BZ21" t="inlineStr"/>
+      <c r="CA21" t="inlineStr"/>
+      <c r="CB21" t="inlineStr"/>
+      <c r="CC21" t="inlineStr"/>
+      <c r="CD21" t="inlineStr"/>
+      <c r="CE21" t="inlineStr"/>
+      <c r="CF21" t="inlineStr"/>
+      <c r="CG21" t="inlineStr"/>
+      <c r="CH21" t="inlineStr"/>
+      <c r="CI21" t="inlineStr"/>
+      <c r="CJ21" t="inlineStr"/>
+      <c r="CK21" t="inlineStr"/>
+      <c r="CL21" t="inlineStr"/>
+      <c r="CM21" t="inlineStr"/>
+      <c r="CN21" t="inlineStr"/>
+      <c r="CO21" t="inlineStr"/>
+      <c r="CP21" t="inlineStr"/>
+      <c r="CQ21" t="inlineStr"/>
+      <c r="CR21" t="inlineStr"/>
+      <c r="CS21" t="inlineStr"/>
+      <c r="CT21" t="inlineStr"/>
+      <c r="CU21" t="inlineStr"/>
+      <c r="CV21" t="inlineStr"/>
+      <c r="CW21" t="inlineStr"/>
+      <c r="CX21" t="inlineStr"/>
+      <c r="CY21" t="inlineStr"/>
+      <c r="CZ21" t="inlineStr"/>
+      <c r="DA21" t="inlineStr"/>
+      <c r="DB21" t="inlineStr"/>
+      <c r="DC21" t="inlineStr"/>
+      <c r="DD21" t="inlineStr"/>
+      <c r="DE21" t="inlineStr"/>
+      <c r="DF21" t="inlineStr"/>
+      <c r="DG21" t="inlineStr"/>
+      <c r="DH21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5379,6 +6629,56 @@
       <c r="BJ22" t="n">
         <v>0.0004372399597870666</v>
       </c>
+      <c r="BK22" t="inlineStr"/>
+      <c r="BL22" t="inlineStr"/>
+      <c r="BM22" t="inlineStr"/>
+      <c r="BN22" t="inlineStr"/>
+      <c r="BO22" t="inlineStr"/>
+      <c r="BP22" t="inlineStr"/>
+      <c r="BQ22" t="inlineStr"/>
+      <c r="BR22" t="inlineStr"/>
+      <c r="BS22" t="inlineStr"/>
+      <c r="BT22" t="inlineStr"/>
+      <c r="BU22" t="inlineStr"/>
+      <c r="BV22" t="inlineStr"/>
+      <c r="BW22" t="inlineStr"/>
+      <c r="BX22" t="inlineStr"/>
+      <c r="BY22" t="inlineStr"/>
+      <c r="BZ22" t="inlineStr"/>
+      <c r="CA22" t="inlineStr"/>
+      <c r="CB22" t="inlineStr"/>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="inlineStr"/>
+      <c r="CM22" t="inlineStr"/>
+      <c r="CN22" t="inlineStr"/>
+      <c r="CO22" t="inlineStr"/>
+      <c r="CP22" t="inlineStr"/>
+      <c r="CQ22" t="inlineStr"/>
+      <c r="CR22" t="inlineStr"/>
+      <c r="CS22" t="inlineStr"/>
+      <c r="CT22" t="inlineStr"/>
+      <c r="CU22" t="inlineStr"/>
+      <c r="CV22" t="inlineStr"/>
+      <c r="CW22" t="inlineStr"/>
+      <c r="CX22" t="inlineStr"/>
+      <c r="CY22" t="inlineStr"/>
+      <c r="CZ22" t="inlineStr"/>
+      <c r="DA22" t="inlineStr"/>
+      <c r="DB22" t="inlineStr"/>
+      <c r="DC22" t="inlineStr"/>
+      <c r="DD22" t="inlineStr"/>
+      <c r="DE22" t="inlineStr"/>
+      <c r="DF22" t="inlineStr"/>
+      <c r="DG22" t="inlineStr"/>
+      <c r="DH22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5599,6 +6899,56 @@
       <c r="BJ23" t="n">
         <v>3.522174730037765e-05</v>
       </c>
+      <c r="BK23" t="inlineStr"/>
+      <c r="BL23" t="inlineStr"/>
+      <c r="BM23" t="inlineStr"/>
+      <c r="BN23" t="inlineStr"/>
+      <c r="BO23" t="inlineStr"/>
+      <c r="BP23" t="inlineStr"/>
+      <c r="BQ23" t="inlineStr"/>
+      <c r="BR23" t="inlineStr"/>
+      <c r="BS23" t="inlineStr"/>
+      <c r="BT23" t="inlineStr"/>
+      <c r="BU23" t="inlineStr"/>
+      <c r="BV23" t="inlineStr"/>
+      <c r="BW23" t="inlineStr"/>
+      <c r="BX23" t="inlineStr"/>
+      <c r="BY23" t="inlineStr"/>
+      <c r="BZ23" t="inlineStr"/>
+      <c r="CA23" t="inlineStr"/>
+      <c r="CB23" t="inlineStr"/>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="inlineStr"/>
+      <c r="CM23" t="inlineStr"/>
+      <c r="CN23" t="inlineStr"/>
+      <c r="CO23" t="inlineStr"/>
+      <c r="CP23" t="inlineStr"/>
+      <c r="CQ23" t="inlineStr"/>
+      <c r="CR23" t="inlineStr"/>
+      <c r="CS23" t="inlineStr"/>
+      <c r="CT23" t="inlineStr"/>
+      <c r="CU23" t="inlineStr"/>
+      <c r="CV23" t="inlineStr"/>
+      <c r="CW23" t="inlineStr"/>
+      <c r="CX23" t="inlineStr"/>
+      <c r="CY23" t="inlineStr"/>
+      <c r="CZ23" t="inlineStr"/>
+      <c r="DA23" t="inlineStr"/>
+      <c r="DB23" t="inlineStr"/>
+      <c r="DC23" t="inlineStr"/>
+      <c r="DD23" t="inlineStr"/>
+      <c r="DE23" t="inlineStr"/>
+      <c r="DF23" t="inlineStr"/>
+      <c r="DG23" t="inlineStr"/>
+      <c r="DH23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5829,6 +7179,56 @@
       <c r="BJ24" t="n">
         <v>9.712984233463661e-06</v>
       </c>
+      <c r="BK24" t="inlineStr"/>
+      <c r="BL24" t="inlineStr"/>
+      <c r="BM24" t="inlineStr"/>
+      <c r="BN24" t="inlineStr"/>
+      <c r="BO24" t="inlineStr"/>
+      <c r="BP24" t="inlineStr"/>
+      <c r="BQ24" t="inlineStr"/>
+      <c r="BR24" t="inlineStr"/>
+      <c r="BS24" t="inlineStr"/>
+      <c r="BT24" t="inlineStr"/>
+      <c r="BU24" t="inlineStr"/>
+      <c r="BV24" t="inlineStr"/>
+      <c r="BW24" t="inlineStr"/>
+      <c r="BX24" t="inlineStr"/>
+      <c r="BY24" t="inlineStr"/>
+      <c r="BZ24" t="inlineStr"/>
+      <c r="CA24" t="inlineStr"/>
+      <c r="CB24" t="inlineStr"/>
+      <c r="CC24" t="inlineStr"/>
+      <c r="CD24" t="inlineStr"/>
+      <c r="CE24" t="inlineStr"/>
+      <c r="CF24" t="inlineStr"/>
+      <c r="CG24" t="inlineStr"/>
+      <c r="CH24" t="inlineStr"/>
+      <c r="CI24" t="inlineStr"/>
+      <c r="CJ24" t="inlineStr"/>
+      <c r="CK24" t="inlineStr"/>
+      <c r="CL24" t="inlineStr"/>
+      <c r="CM24" t="inlineStr"/>
+      <c r="CN24" t="inlineStr"/>
+      <c r="CO24" t="inlineStr"/>
+      <c r="CP24" t="inlineStr"/>
+      <c r="CQ24" t="inlineStr"/>
+      <c r="CR24" t="inlineStr"/>
+      <c r="CS24" t="inlineStr"/>
+      <c r="CT24" t="inlineStr"/>
+      <c r="CU24" t="inlineStr"/>
+      <c r="CV24" t="inlineStr"/>
+      <c r="CW24" t="inlineStr"/>
+      <c r="CX24" t="inlineStr"/>
+      <c r="CY24" t="inlineStr"/>
+      <c r="CZ24" t="inlineStr"/>
+      <c r="DA24" t="inlineStr"/>
+      <c r="DB24" t="inlineStr"/>
+      <c r="DC24" t="inlineStr"/>
+      <c r="DD24" t="inlineStr"/>
+      <c r="DE24" t="inlineStr"/>
+      <c r="DF24" t="inlineStr"/>
+      <c r="DG24" t="inlineStr"/>
+      <c r="DH24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6059,6 +7459,56 @@
       <c r="BJ25" t="n">
         <v>0</v>
       </c>
+      <c r="BK25" t="inlineStr"/>
+      <c r="BL25" t="inlineStr"/>
+      <c r="BM25" t="inlineStr"/>
+      <c r="BN25" t="inlineStr"/>
+      <c r="BO25" t="inlineStr"/>
+      <c r="BP25" t="inlineStr"/>
+      <c r="BQ25" t="inlineStr"/>
+      <c r="BR25" t="inlineStr"/>
+      <c r="BS25" t="inlineStr"/>
+      <c r="BT25" t="inlineStr"/>
+      <c r="BU25" t="inlineStr"/>
+      <c r="BV25" t="inlineStr"/>
+      <c r="BW25" t="inlineStr"/>
+      <c r="BX25" t="inlineStr"/>
+      <c r="BY25" t="inlineStr"/>
+      <c r="BZ25" t="inlineStr"/>
+      <c r="CA25" t="inlineStr"/>
+      <c r="CB25" t="inlineStr"/>
+      <c r="CC25" t="inlineStr"/>
+      <c r="CD25" t="inlineStr"/>
+      <c r="CE25" t="inlineStr"/>
+      <c r="CF25" t="inlineStr"/>
+      <c r="CG25" t="inlineStr"/>
+      <c r="CH25" t="inlineStr"/>
+      <c r="CI25" t="inlineStr"/>
+      <c r="CJ25" t="inlineStr"/>
+      <c r="CK25" t="inlineStr"/>
+      <c r="CL25" t="inlineStr"/>
+      <c r="CM25" t="inlineStr"/>
+      <c r="CN25" t="inlineStr"/>
+      <c r="CO25" t="inlineStr"/>
+      <c r="CP25" t="inlineStr"/>
+      <c r="CQ25" t="inlineStr"/>
+      <c r="CR25" t="inlineStr"/>
+      <c r="CS25" t="inlineStr"/>
+      <c r="CT25" t="inlineStr"/>
+      <c r="CU25" t="inlineStr"/>
+      <c r="CV25" t="inlineStr"/>
+      <c r="CW25" t="inlineStr"/>
+      <c r="CX25" t="inlineStr"/>
+      <c r="CY25" t="inlineStr"/>
+      <c r="CZ25" t="inlineStr"/>
+      <c r="DA25" t="inlineStr"/>
+      <c r="DB25" t="inlineStr"/>
+      <c r="DC25" t="inlineStr"/>
+      <c r="DD25" t="inlineStr"/>
+      <c r="DE25" t="inlineStr"/>
+      <c r="DF25" t="inlineStr"/>
+      <c r="DG25" t="inlineStr"/>
+      <c r="DH25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6279,6 +7729,56 @@
       <c r="BJ26" t="n">
         <v>0.006864583551809107</v>
       </c>
+      <c r="BK26" t="inlineStr"/>
+      <c r="BL26" t="inlineStr"/>
+      <c r="BM26" t="inlineStr"/>
+      <c r="BN26" t="inlineStr"/>
+      <c r="BO26" t="inlineStr"/>
+      <c r="BP26" t="inlineStr"/>
+      <c r="BQ26" t="inlineStr"/>
+      <c r="BR26" t="inlineStr"/>
+      <c r="BS26" t="inlineStr"/>
+      <c r="BT26" t="inlineStr"/>
+      <c r="BU26" t="inlineStr"/>
+      <c r="BV26" t="inlineStr"/>
+      <c r="BW26" t="inlineStr"/>
+      <c r="BX26" t="inlineStr"/>
+      <c r="BY26" t="inlineStr"/>
+      <c r="BZ26" t="inlineStr"/>
+      <c r="CA26" t="inlineStr"/>
+      <c r="CB26" t="inlineStr"/>
+      <c r="CC26" t="inlineStr"/>
+      <c r="CD26" t="inlineStr"/>
+      <c r="CE26" t="inlineStr"/>
+      <c r="CF26" t="inlineStr"/>
+      <c r="CG26" t="inlineStr"/>
+      <c r="CH26" t="inlineStr"/>
+      <c r="CI26" t="inlineStr"/>
+      <c r="CJ26" t="inlineStr"/>
+      <c r="CK26" t="inlineStr"/>
+      <c r="CL26" t="inlineStr"/>
+      <c r="CM26" t="inlineStr"/>
+      <c r="CN26" t="inlineStr"/>
+      <c r="CO26" t="inlineStr"/>
+      <c r="CP26" t="inlineStr"/>
+      <c r="CQ26" t="inlineStr"/>
+      <c r="CR26" t="inlineStr"/>
+      <c r="CS26" t="inlineStr"/>
+      <c r="CT26" t="inlineStr"/>
+      <c r="CU26" t="inlineStr"/>
+      <c r="CV26" t="inlineStr"/>
+      <c r="CW26" t="inlineStr"/>
+      <c r="CX26" t="inlineStr"/>
+      <c r="CY26" t="inlineStr"/>
+      <c r="CZ26" t="inlineStr"/>
+      <c r="DA26" t="inlineStr"/>
+      <c r="DB26" t="inlineStr"/>
+      <c r="DC26" t="inlineStr"/>
+      <c r="DD26" t="inlineStr"/>
+      <c r="DE26" t="inlineStr"/>
+      <c r="DF26" t="inlineStr"/>
+      <c r="DG26" t="inlineStr"/>
+      <c r="DH26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6499,6 +7999,56 @@
       <c r="BJ27" t="n">
         <v>0.00633123507806117</v>
       </c>
+      <c r="BK27" t="inlineStr"/>
+      <c r="BL27" t="inlineStr"/>
+      <c r="BM27" t="inlineStr"/>
+      <c r="BN27" t="inlineStr"/>
+      <c r="BO27" t="inlineStr"/>
+      <c r="BP27" t="inlineStr"/>
+      <c r="BQ27" t="inlineStr"/>
+      <c r="BR27" t="inlineStr"/>
+      <c r="BS27" t="inlineStr"/>
+      <c r="BT27" t="inlineStr"/>
+      <c r="BU27" t="inlineStr"/>
+      <c r="BV27" t="inlineStr"/>
+      <c r="BW27" t="inlineStr"/>
+      <c r="BX27" t="inlineStr"/>
+      <c r="BY27" t="inlineStr"/>
+      <c r="BZ27" t="inlineStr"/>
+      <c r="CA27" t="inlineStr"/>
+      <c r="CB27" t="inlineStr"/>
+      <c r="CC27" t="inlineStr"/>
+      <c r="CD27" t="inlineStr"/>
+      <c r="CE27" t="inlineStr"/>
+      <c r="CF27" t="inlineStr"/>
+      <c r="CG27" t="inlineStr"/>
+      <c r="CH27" t="inlineStr"/>
+      <c r="CI27" t="inlineStr"/>
+      <c r="CJ27" t="inlineStr"/>
+      <c r="CK27" t="inlineStr"/>
+      <c r="CL27" t="inlineStr"/>
+      <c r="CM27" t="inlineStr"/>
+      <c r="CN27" t="inlineStr"/>
+      <c r="CO27" t="inlineStr"/>
+      <c r="CP27" t="inlineStr"/>
+      <c r="CQ27" t="inlineStr"/>
+      <c r="CR27" t="inlineStr"/>
+      <c r="CS27" t="inlineStr"/>
+      <c r="CT27" t="inlineStr"/>
+      <c r="CU27" t="inlineStr"/>
+      <c r="CV27" t="inlineStr"/>
+      <c r="CW27" t="inlineStr"/>
+      <c r="CX27" t="inlineStr"/>
+      <c r="CY27" t="inlineStr"/>
+      <c r="CZ27" t="inlineStr"/>
+      <c r="DA27" t="inlineStr"/>
+      <c r="DB27" t="inlineStr"/>
+      <c r="DC27" t="inlineStr"/>
+      <c r="DD27" t="inlineStr"/>
+      <c r="DE27" t="inlineStr"/>
+      <c r="DF27" t="inlineStr"/>
+      <c r="DG27" t="inlineStr"/>
+      <c r="DH27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6719,6 +8269,56 @@
       <c r="BJ28" t="n">
         <v>0.006998243955679154</v>
       </c>
+      <c r="BK28" t="inlineStr"/>
+      <c r="BL28" t="inlineStr"/>
+      <c r="BM28" t="inlineStr"/>
+      <c r="BN28" t="inlineStr"/>
+      <c r="BO28" t="inlineStr"/>
+      <c r="BP28" t="inlineStr"/>
+      <c r="BQ28" t="inlineStr"/>
+      <c r="BR28" t="inlineStr"/>
+      <c r="BS28" t="inlineStr"/>
+      <c r="BT28" t="inlineStr"/>
+      <c r="BU28" t="inlineStr"/>
+      <c r="BV28" t="inlineStr"/>
+      <c r="BW28" t="inlineStr"/>
+      <c r="BX28" t="inlineStr"/>
+      <c r="BY28" t="inlineStr"/>
+      <c r="BZ28" t="inlineStr"/>
+      <c r="CA28" t="inlineStr"/>
+      <c r="CB28" t="inlineStr"/>
+      <c r="CC28" t="inlineStr"/>
+      <c r="CD28" t="inlineStr"/>
+      <c r="CE28" t="inlineStr"/>
+      <c r="CF28" t="inlineStr"/>
+      <c r="CG28" t="inlineStr"/>
+      <c r="CH28" t="inlineStr"/>
+      <c r="CI28" t="inlineStr"/>
+      <c r="CJ28" t="inlineStr"/>
+      <c r="CK28" t="inlineStr"/>
+      <c r="CL28" t="inlineStr"/>
+      <c r="CM28" t="inlineStr"/>
+      <c r="CN28" t="inlineStr"/>
+      <c r="CO28" t="inlineStr"/>
+      <c r="CP28" t="inlineStr"/>
+      <c r="CQ28" t="inlineStr"/>
+      <c r="CR28" t="inlineStr"/>
+      <c r="CS28" t="inlineStr"/>
+      <c r="CT28" t="inlineStr"/>
+      <c r="CU28" t="inlineStr"/>
+      <c r="CV28" t="inlineStr"/>
+      <c r="CW28" t="inlineStr"/>
+      <c r="CX28" t="inlineStr"/>
+      <c r="CY28" t="inlineStr"/>
+      <c r="CZ28" t="inlineStr"/>
+      <c r="DA28" t="inlineStr"/>
+      <c r="DB28" t="inlineStr"/>
+      <c r="DC28" t="inlineStr"/>
+      <c r="DD28" t="inlineStr"/>
+      <c r="DE28" t="inlineStr"/>
+      <c r="DF28" t="inlineStr"/>
+      <c r="DG28" t="inlineStr"/>
+      <c r="DH28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6939,6 +8539,56 @@
       <c r="BJ29" t="n">
         <v>0.005979998658646051</v>
       </c>
+      <c r="BK29" t="inlineStr"/>
+      <c r="BL29" t="inlineStr"/>
+      <c r="BM29" t="inlineStr"/>
+      <c r="BN29" t="inlineStr"/>
+      <c r="BO29" t="inlineStr"/>
+      <c r="BP29" t="inlineStr"/>
+      <c r="BQ29" t="inlineStr"/>
+      <c r="BR29" t="inlineStr"/>
+      <c r="BS29" t="inlineStr"/>
+      <c r="BT29" t="inlineStr"/>
+      <c r="BU29" t="inlineStr"/>
+      <c r="BV29" t="inlineStr"/>
+      <c r="BW29" t="inlineStr"/>
+      <c r="BX29" t="inlineStr"/>
+      <c r="BY29" t="inlineStr"/>
+      <c r="BZ29" t="inlineStr"/>
+      <c r="CA29" t="inlineStr"/>
+      <c r="CB29" t="inlineStr"/>
+      <c r="CC29" t="inlineStr"/>
+      <c r="CD29" t="inlineStr"/>
+      <c r="CE29" t="inlineStr"/>
+      <c r="CF29" t="inlineStr"/>
+      <c r="CG29" t="inlineStr"/>
+      <c r="CH29" t="inlineStr"/>
+      <c r="CI29" t="inlineStr"/>
+      <c r="CJ29" t="inlineStr"/>
+      <c r="CK29" t="inlineStr"/>
+      <c r="CL29" t="inlineStr"/>
+      <c r="CM29" t="inlineStr"/>
+      <c r="CN29" t="inlineStr"/>
+      <c r="CO29" t="inlineStr"/>
+      <c r="CP29" t="inlineStr"/>
+      <c r="CQ29" t="inlineStr"/>
+      <c r="CR29" t="inlineStr"/>
+      <c r="CS29" t="inlineStr"/>
+      <c r="CT29" t="inlineStr"/>
+      <c r="CU29" t="inlineStr"/>
+      <c r="CV29" t="inlineStr"/>
+      <c r="CW29" t="inlineStr"/>
+      <c r="CX29" t="inlineStr"/>
+      <c r="CY29" t="inlineStr"/>
+      <c r="CZ29" t="inlineStr"/>
+      <c r="DA29" t="inlineStr"/>
+      <c r="DB29" t="inlineStr"/>
+      <c r="DC29" t="inlineStr"/>
+      <c r="DD29" t="inlineStr"/>
+      <c r="DE29" t="inlineStr"/>
+      <c r="DF29" t="inlineStr"/>
+      <c r="DG29" t="inlineStr"/>
+      <c r="DH29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7159,6 +8809,56 @@
       <c r="BJ30" t="n">
         <v>0.003593501616458011</v>
       </c>
+      <c r="BK30" t="inlineStr"/>
+      <c r="BL30" t="inlineStr"/>
+      <c r="BM30" t="inlineStr"/>
+      <c r="BN30" t="inlineStr"/>
+      <c r="BO30" t="inlineStr"/>
+      <c r="BP30" t="inlineStr"/>
+      <c r="BQ30" t="inlineStr"/>
+      <c r="BR30" t="inlineStr"/>
+      <c r="BS30" t="inlineStr"/>
+      <c r="BT30" t="inlineStr"/>
+      <c r="BU30" t="inlineStr"/>
+      <c r="BV30" t="inlineStr"/>
+      <c r="BW30" t="inlineStr"/>
+      <c r="BX30" t="inlineStr"/>
+      <c r="BY30" t="inlineStr"/>
+      <c r="BZ30" t="inlineStr"/>
+      <c r="CA30" t="inlineStr"/>
+      <c r="CB30" t="inlineStr"/>
+      <c r="CC30" t="inlineStr"/>
+      <c r="CD30" t="inlineStr"/>
+      <c r="CE30" t="inlineStr"/>
+      <c r="CF30" t="inlineStr"/>
+      <c r="CG30" t="inlineStr"/>
+      <c r="CH30" t="inlineStr"/>
+      <c r="CI30" t="inlineStr"/>
+      <c r="CJ30" t="inlineStr"/>
+      <c r="CK30" t="inlineStr"/>
+      <c r="CL30" t="inlineStr"/>
+      <c r="CM30" t="inlineStr"/>
+      <c r="CN30" t="inlineStr"/>
+      <c r="CO30" t="inlineStr"/>
+      <c r="CP30" t="inlineStr"/>
+      <c r="CQ30" t="inlineStr"/>
+      <c r="CR30" t="inlineStr"/>
+      <c r="CS30" t="inlineStr"/>
+      <c r="CT30" t="inlineStr"/>
+      <c r="CU30" t="inlineStr"/>
+      <c r="CV30" t="inlineStr"/>
+      <c r="CW30" t="inlineStr"/>
+      <c r="CX30" t="inlineStr"/>
+      <c r="CY30" t="inlineStr"/>
+      <c r="CZ30" t="inlineStr"/>
+      <c r="DA30" t="inlineStr"/>
+      <c r="DB30" t="inlineStr"/>
+      <c r="DC30" t="inlineStr"/>
+      <c r="DD30" t="inlineStr"/>
+      <c r="DE30" t="inlineStr"/>
+      <c r="DF30" t="inlineStr"/>
+      <c r="DG30" t="inlineStr"/>
+      <c r="DH30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7379,6 +9079,56 @@
       <c r="BJ31" t="n">
         <v>0.00331515533222134</v>
       </c>
+      <c r="BK31" t="inlineStr"/>
+      <c r="BL31" t="inlineStr"/>
+      <c r="BM31" t="inlineStr"/>
+      <c r="BN31" t="inlineStr"/>
+      <c r="BO31" t="inlineStr"/>
+      <c r="BP31" t="inlineStr"/>
+      <c r="BQ31" t="inlineStr"/>
+      <c r="BR31" t="inlineStr"/>
+      <c r="BS31" t="inlineStr"/>
+      <c r="BT31" t="inlineStr"/>
+      <c r="BU31" t="inlineStr"/>
+      <c r="BV31" t="inlineStr"/>
+      <c r="BW31" t="inlineStr"/>
+      <c r="BX31" t="inlineStr"/>
+      <c r="BY31" t="inlineStr"/>
+      <c r="BZ31" t="inlineStr"/>
+      <c r="CA31" t="inlineStr"/>
+      <c r="CB31" t="inlineStr"/>
+      <c r="CC31" t="inlineStr"/>
+      <c r="CD31" t="inlineStr"/>
+      <c r="CE31" t="inlineStr"/>
+      <c r="CF31" t="inlineStr"/>
+      <c r="CG31" t="inlineStr"/>
+      <c r="CH31" t="inlineStr"/>
+      <c r="CI31" t="inlineStr"/>
+      <c r="CJ31" t="inlineStr"/>
+      <c r="CK31" t="inlineStr"/>
+      <c r="CL31" t="inlineStr"/>
+      <c r="CM31" t="inlineStr"/>
+      <c r="CN31" t="inlineStr"/>
+      <c r="CO31" t="inlineStr"/>
+      <c r="CP31" t="inlineStr"/>
+      <c r="CQ31" t="inlineStr"/>
+      <c r="CR31" t="inlineStr"/>
+      <c r="CS31" t="inlineStr"/>
+      <c r="CT31" t="inlineStr"/>
+      <c r="CU31" t="inlineStr"/>
+      <c r="CV31" t="inlineStr"/>
+      <c r="CW31" t="inlineStr"/>
+      <c r="CX31" t="inlineStr"/>
+      <c r="CY31" t="inlineStr"/>
+      <c r="CZ31" t="inlineStr"/>
+      <c r="DA31" t="inlineStr"/>
+      <c r="DB31" t="inlineStr"/>
+      <c r="DC31" t="inlineStr"/>
+      <c r="DD31" t="inlineStr"/>
+      <c r="DE31" t="inlineStr"/>
+      <c r="DF31" t="inlineStr"/>
+      <c r="DG31" t="inlineStr"/>
+      <c r="DH31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7599,6 +9349,56 @@
       <c r="BJ32" t="n">
         <v>0.005858666205929211</v>
       </c>
+      <c r="BK32" t="inlineStr"/>
+      <c r="BL32" t="inlineStr"/>
+      <c r="BM32" t="inlineStr"/>
+      <c r="BN32" t="inlineStr"/>
+      <c r="BO32" t="inlineStr"/>
+      <c r="BP32" t="inlineStr"/>
+      <c r="BQ32" t="inlineStr"/>
+      <c r="BR32" t="inlineStr"/>
+      <c r="BS32" t="inlineStr"/>
+      <c r="BT32" t="inlineStr"/>
+      <c r="BU32" t="inlineStr"/>
+      <c r="BV32" t="inlineStr"/>
+      <c r="BW32" t="inlineStr"/>
+      <c r="BX32" t="inlineStr"/>
+      <c r="BY32" t="inlineStr"/>
+      <c r="BZ32" t="inlineStr"/>
+      <c r="CA32" t="inlineStr"/>
+      <c r="CB32" t="inlineStr"/>
+      <c r="CC32" t="inlineStr"/>
+      <c r="CD32" t="inlineStr"/>
+      <c r="CE32" t="inlineStr"/>
+      <c r="CF32" t="inlineStr"/>
+      <c r="CG32" t="inlineStr"/>
+      <c r="CH32" t="inlineStr"/>
+      <c r="CI32" t="inlineStr"/>
+      <c r="CJ32" t="inlineStr"/>
+      <c r="CK32" t="inlineStr"/>
+      <c r="CL32" t="inlineStr"/>
+      <c r="CM32" t="inlineStr"/>
+      <c r="CN32" t="inlineStr"/>
+      <c r="CO32" t="inlineStr"/>
+      <c r="CP32" t="inlineStr"/>
+      <c r="CQ32" t="inlineStr"/>
+      <c r="CR32" t="inlineStr"/>
+      <c r="CS32" t="inlineStr"/>
+      <c r="CT32" t="inlineStr"/>
+      <c r="CU32" t="inlineStr"/>
+      <c r="CV32" t="inlineStr"/>
+      <c r="CW32" t="inlineStr"/>
+      <c r="CX32" t="inlineStr"/>
+      <c r="CY32" t="inlineStr"/>
+      <c r="CZ32" t="inlineStr"/>
+      <c r="DA32" t="inlineStr"/>
+      <c r="DB32" t="inlineStr"/>
+      <c r="DC32" t="inlineStr"/>
+      <c r="DD32" t="inlineStr"/>
+      <c r="DE32" t="inlineStr"/>
+      <c r="DF32" t="inlineStr"/>
+      <c r="DG32" t="inlineStr"/>
+      <c r="DH32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7819,6 +9619,56 @@
       <c r="BJ33" t="n">
         <v>0.004119140442349333</v>
       </c>
+      <c r="BK33" t="inlineStr"/>
+      <c r="BL33" t="inlineStr"/>
+      <c r="BM33" t="inlineStr"/>
+      <c r="BN33" t="inlineStr"/>
+      <c r="BO33" t="inlineStr"/>
+      <c r="BP33" t="inlineStr"/>
+      <c r="BQ33" t="inlineStr"/>
+      <c r="BR33" t="inlineStr"/>
+      <c r="BS33" t="inlineStr"/>
+      <c r="BT33" t="inlineStr"/>
+      <c r="BU33" t="inlineStr"/>
+      <c r="BV33" t="inlineStr"/>
+      <c r="BW33" t="inlineStr"/>
+      <c r="BX33" t="inlineStr"/>
+      <c r="BY33" t="inlineStr"/>
+      <c r="BZ33" t="inlineStr"/>
+      <c r="CA33" t="inlineStr"/>
+      <c r="CB33" t="inlineStr"/>
+      <c r="CC33" t="inlineStr"/>
+      <c r="CD33" t="inlineStr"/>
+      <c r="CE33" t="inlineStr"/>
+      <c r="CF33" t="inlineStr"/>
+      <c r="CG33" t="inlineStr"/>
+      <c r="CH33" t="inlineStr"/>
+      <c r="CI33" t="inlineStr"/>
+      <c r="CJ33" t="inlineStr"/>
+      <c r="CK33" t="inlineStr"/>
+      <c r="CL33" t="inlineStr"/>
+      <c r="CM33" t="inlineStr"/>
+      <c r="CN33" t="inlineStr"/>
+      <c r="CO33" t="inlineStr"/>
+      <c r="CP33" t="inlineStr"/>
+      <c r="CQ33" t="inlineStr"/>
+      <c r="CR33" t="inlineStr"/>
+      <c r="CS33" t="inlineStr"/>
+      <c r="CT33" t="inlineStr"/>
+      <c r="CU33" t="inlineStr"/>
+      <c r="CV33" t="inlineStr"/>
+      <c r="CW33" t="inlineStr"/>
+      <c r="CX33" t="inlineStr"/>
+      <c r="CY33" t="inlineStr"/>
+      <c r="CZ33" t="inlineStr"/>
+      <c r="DA33" t="inlineStr"/>
+      <c r="DB33" t="inlineStr"/>
+      <c r="DC33" t="inlineStr"/>
+      <c r="DD33" t="inlineStr"/>
+      <c r="DE33" t="inlineStr"/>
+      <c r="DF33" t="inlineStr"/>
+      <c r="DG33" t="inlineStr"/>
+      <c r="DH33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8039,6 +9889,56 @@
       <c r="BJ34" t="n">
         <v>0.0002469013067630454</v>
       </c>
+      <c r="BK34" t="inlineStr"/>
+      <c r="BL34" t="inlineStr"/>
+      <c r="BM34" t="inlineStr"/>
+      <c r="BN34" t="inlineStr"/>
+      <c r="BO34" t="inlineStr"/>
+      <c r="BP34" t="inlineStr"/>
+      <c r="BQ34" t="inlineStr"/>
+      <c r="BR34" t="inlineStr"/>
+      <c r="BS34" t="inlineStr"/>
+      <c r="BT34" t="inlineStr"/>
+      <c r="BU34" t="inlineStr"/>
+      <c r="BV34" t="inlineStr"/>
+      <c r="BW34" t="inlineStr"/>
+      <c r="BX34" t="inlineStr"/>
+      <c r="BY34" t="inlineStr"/>
+      <c r="BZ34" t="inlineStr"/>
+      <c r="CA34" t="inlineStr"/>
+      <c r="CB34" t="inlineStr"/>
+      <c r="CC34" t="inlineStr"/>
+      <c r="CD34" t="inlineStr"/>
+      <c r="CE34" t="inlineStr"/>
+      <c r="CF34" t="inlineStr"/>
+      <c r="CG34" t="inlineStr"/>
+      <c r="CH34" t="inlineStr"/>
+      <c r="CI34" t="inlineStr"/>
+      <c r="CJ34" t="inlineStr"/>
+      <c r="CK34" t="inlineStr"/>
+      <c r="CL34" t="inlineStr"/>
+      <c r="CM34" t="inlineStr"/>
+      <c r="CN34" t="inlineStr"/>
+      <c r="CO34" t="inlineStr"/>
+      <c r="CP34" t="inlineStr"/>
+      <c r="CQ34" t="inlineStr"/>
+      <c r="CR34" t="inlineStr"/>
+      <c r="CS34" t="inlineStr"/>
+      <c r="CT34" t="inlineStr"/>
+      <c r="CU34" t="inlineStr"/>
+      <c r="CV34" t="inlineStr"/>
+      <c r="CW34" t="inlineStr"/>
+      <c r="CX34" t="inlineStr"/>
+      <c r="CY34" t="inlineStr"/>
+      <c r="CZ34" t="inlineStr"/>
+      <c r="DA34" t="inlineStr"/>
+      <c r="DB34" t="inlineStr"/>
+      <c r="DC34" t="inlineStr"/>
+      <c r="DD34" t="inlineStr"/>
+      <c r="DE34" t="inlineStr"/>
+      <c r="DF34" t="inlineStr"/>
+      <c r="DG34" t="inlineStr"/>
+      <c r="DH34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -8259,6 +10159,56 @@
       <c r="BJ35" t="n">
         <v>3.550147888793166e-05</v>
       </c>
+      <c r="BK35" t="inlineStr"/>
+      <c r="BL35" t="inlineStr"/>
+      <c r="BM35" t="inlineStr"/>
+      <c r="BN35" t="inlineStr"/>
+      <c r="BO35" t="inlineStr"/>
+      <c r="BP35" t="inlineStr"/>
+      <c r="BQ35" t="inlineStr"/>
+      <c r="BR35" t="inlineStr"/>
+      <c r="BS35" t="inlineStr"/>
+      <c r="BT35" t="inlineStr"/>
+      <c r="BU35" t="inlineStr"/>
+      <c r="BV35" t="inlineStr"/>
+      <c r="BW35" t="inlineStr"/>
+      <c r="BX35" t="inlineStr"/>
+      <c r="BY35" t="inlineStr"/>
+      <c r="BZ35" t="inlineStr"/>
+      <c r="CA35" t="inlineStr"/>
+      <c r="CB35" t="inlineStr"/>
+      <c r="CC35" t="inlineStr"/>
+      <c r="CD35" t="inlineStr"/>
+      <c r="CE35" t="inlineStr"/>
+      <c r="CF35" t="inlineStr"/>
+      <c r="CG35" t="inlineStr"/>
+      <c r="CH35" t="inlineStr"/>
+      <c r="CI35" t="inlineStr"/>
+      <c r="CJ35" t="inlineStr"/>
+      <c r="CK35" t="inlineStr"/>
+      <c r="CL35" t="inlineStr"/>
+      <c r="CM35" t="inlineStr"/>
+      <c r="CN35" t="inlineStr"/>
+      <c r="CO35" t="inlineStr"/>
+      <c r="CP35" t="inlineStr"/>
+      <c r="CQ35" t="inlineStr"/>
+      <c r="CR35" t="inlineStr"/>
+      <c r="CS35" t="inlineStr"/>
+      <c r="CT35" t="inlineStr"/>
+      <c r="CU35" t="inlineStr"/>
+      <c r="CV35" t="inlineStr"/>
+      <c r="CW35" t="inlineStr"/>
+      <c r="CX35" t="inlineStr"/>
+      <c r="CY35" t="inlineStr"/>
+      <c r="CZ35" t="inlineStr"/>
+      <c r="DA35" t="inlineStr"/>
+      <c r="DB35" t="inlineStr"/>
+      <c r="DC35" t="inlineStr"/>
+      <c r="DD35" t="inlineStr"/>
+      <c r="DE35" t="inlineStr"/>
+      <c r="DF35" t="inlineStr"/>
+      <c r="DG35" t="inlineStr"/>
+      <c r="DH35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -8489,6 +10439,56 @@
       <c r="BJ36" t="n">
         <v>9.712984233463659e-06</v>
       </c>
+      <c r="BK36" t="inlineStr"/>
+      <c r="BL36" t="inlineStr"/>
+      <c r="BM36" t="inlineStr"/>
+      <c r="BN36" t="inlineStr"/>
+      <c r="BO36" t="inlineStr"/>
+      <c r="BP36" t="inlineStr"/>
+      <c r="BQ36" t="inlineStr"/>
+      <c r="BR36" t="inlineStr"/>
+      <c r="BS36" t="inlineStr"/>
+      <c r="BT36" t="inlineStr"/>
+      <c r="BU36" t="inlineStr"/>
+      <c r="BV36" t="inlineStr"/>
+      <c r="BW36" t="inlineStr"/>
+      <c r="BX36" t="inlineStr"/>
+      <c r="BY36" t="inlineStr"/>
+      <c r="BZ36" t="inlineStr"/>
+      <c r="CA36" t="inlineStr"/>
+      <c r="CB36" t="inlineStr"/>
+      <c r="CC36" t="inlineStr"/>
+      <c r="CD36" t="inlineStr"/>
+      <c r="CE36" t="inlineStr"/>
+      <c r="CF36" t="inlineStr"/>
+      <c r="CG36" t="inlineStr"/>
+      <c r="CH36" t="inlineStr"/>
+      <c r="CI36" t="inlineStr"/>
+      <c r="CJ36" t="inlineStr"/>
+      <c r="CK36" t="inlineStr"/>
+      <c r="CL36" t="inlineStr"/>
+      <c r="CM36" t="inlineStr"/>
+      <c r="CN36" t="inlineStr"/>
+      <c r="CO36" t="inlineStr"/>
+      <c r="CP36" t="inlineStr"/>
+      <c r="CQ36" t="inlineStr"/>
+      <c r="CR36" t="inlineStr"/>
+      <c r="CS36" t="inlineStr"/>
+      <c r="CT36" t="inlineStr"/>
+      <c r="CU36" t="inlineStr"/>
+      <c r="CV36" t="inlineStr"/>
+      <c r="CW36" t="inlineStr"/>
+      <c r="CX36" t="inlineStr"/>
+      <c r="CY36" t="inlineStr"/>
+      <c r="CZ36" t="inlineStr"/>
+      <c r="DA36" t="inlineStr"/>
+      <c r="DB36" t="inlineStr"/>
+      <c r="DC36" t="inlineStr"/>
+      <c r="DD36" t="inlineStr"/>
+      <c r="DE36" t="inlineStr"/>
+      <c r="DF36" t="inlineStr"/>
+      <c r="DG36" t="inlineStr"/>
+      <c r="DH36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -8719,6 +10719,56 @@
       <c r="BJ37" t="n">
         <v>0</v>
       </c>
+      <c r="BK37" t="inlineStr"/>
+      <c r="BL37" t="inlineStr"/>
+      <c r="BM37" t="inlineStr"/>
+      <c r="BN37" t="inlineStr"/>
+      <c r="BO37" t="inlineStr"/>
+      <c r="BP37" t="inlineStr"/>
+      <c r="BQ37" t="inlineStr"/>
+      <c r="BR37" t="inlineStr"/>
+      <c r="BS37" t="inlineStr"/>
+      <c r="BT37" t="inlineStr"/>
+      <c r="BU37" t="inlineStr"/>
+      <c r="BV37" t="inlineStr"/>
+      <c r="BW37" t="inlineStr"/>
+      <c r="BX37" t="inlineStr"/>
+      <c r="BY37" t="inlineStr"/>
+      <c r="BZ37" t="inlineStr"/>
+      <c r="CA37" t="inlineStr"/>
+      <c r="CB37" t="inlineStr"/>
+      <c r="CC37" t="inlineStr"/>
+      <c r="CD37" t="inlineStr"/>
+      <c r="CE37" t="inlineStr"/>
+      <c r="CF37" t="inlineStr"/>
+      <c r="CG37" t="inlineStr"/>
+      <c r="CH37" t="inlineStr"/>
+      <c r="CI37" t="inlineStr"/>
+      <c r="CJ37" t="inlineStr"/>
+      <c r="CK37" t="inlineStr"/>
+      <c r="CL37" t="inlineStr"/>
+      <c r="CM37" t="inlineStr"/>
+      <c r="CN37" t="inlineStr"/>
+      <c r="CO37" t="inlineStr"/>
+      <c r="CP37" t="inlineStr"/>
+      <c r="CQ37" t="inlineStr"/>
+      <c r="CR37" t="inlineStr"/>
+      <c r="CS37" t="inlineStr"/>
+      <c r="CT37" t="inlineStr"/>
+      <c r="CU37" t="inlineStr"/>
+      <c r="CV37" t="inlineStr"/>
+      <c r="CW37" t="inlineStr"/>
+      <c r="CX37" t="inlineStr"/>
+      <c r="CY37" t="inlineStr"/>
+      <c r="CZ37" t="inlineStr"/>
+      <c r="DA37" t="inlineStr"/>
+      <c r="DB37" t="inlineStr"/>
+      <c r="DC37" t="inlineStr"/>
+      <c r="DD37" t="inlineStr"/>
+      <c r="DE37" t="inlineStr"/>
+      <c r="DF37" t="inlineStr"/>
+      <c r="DG37" t="inlineStr"/>
+      <c r="DH37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -8939,6 +10989,56 @@
       <c r="BJ38" t="n">
         <v>0.006069971402500744</v>
       </c>
+      <c r="BK38" t="inlineStr"/>
+      <c r="BL38" t="inlineStr"/>
+      <c r="BM38" t="inlineStr"/>
+      <c r="BN38" t="inlineStr"/>
+      <c r="BO38" t="inlineStr"/>
+      <c r="BP38" t="inlineStr"/>
+      <c r="BQ38" t="inlineStr"/>
+      <c r="BR38" t="inlineStr"/>
+      <c r="BS38" t="inlineStr"/>
+      <c r="BT38" t="inlineStr"/>
+      <c r="BU38" t="inlineStr"/>
+      <c r="BV38" t="inlineStr"/>
+      <c r="BW38" t="inlineStr"/>
+      <c r="BX38" t="inlineStr"/>
+      <c r="BY38" t="inlineStr"/>
+      <c r="BZ38" t="inlineStr"/>
+      <c r="CA38" t="inlineStr"/>
+      <c r="CB38" t="inlineStr"/>
+      <c r="CC38" t="inlineStr"/>
+      <c r="CD38" t="inlineStr"/>
+      <c r="CE38" t="inlineStr"/>
+      <c r="CF38" t="inlineStr"/>
+      <c r="CG38" t="inlineStr"/>
+      <c r="CH38" t="inlineStr"/>
+      <c r="CI38" t="inlineStr"/>
+      <c r="CJ38" t="inlineStr"/>
+      <c r="CK38" t="inlineStr"/>
+      <c r="CL38" t="inlineStr"/>
+      <c r="CM38" t="inlineStr"/>
+      <c r="CN38" t="inlineStr"/>
+      <c r="CO38" t="inlineStr"/>
+      <c r="CP38" t="inlineStr"/>
+      <c r="CQ38" t="inlineStr"/>
+      <c r="CR38" t="inlineStr"/>
+      <c r="CS38" t="inlineStr"/>
+      <c r="CT38" t="inlineStr"/>
+      <c r="CU38" t="inlineStr"/>
+      <c r="CV38" t="inlineStr"/>
+      <c r="CW38" t="inlineStr"/>
+      <c r="CX38" t="inlineStr"/>
+      <c r="CY38" t="inlineStr"/>
+      <c r="CZ38" t="inlineStr"/>
+      <c r="DA38" t="inlineStr"/>
+      <c r="DB38" t="inlineStr"/>
+      <c r="DC38" t="inlineStr"/>
+      <c r="DD38" t="inlineStr"/>
+      <c r="DE38" t="inlineStr"/>
+      <c r="DF38" t="inlineStr"/>
+      <c r="DG38" t="inlineStr"/>
+      <c r="DH38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -9159,6 +11259,56 @@
       <c r="BJ39" t="n">
         <v>0.005872685742408556</v>
       </c>
+      <c r="BK39" t="inlineStr"/>
+      <c r="BL39" t="inlineStr"/>
+      <c r="BM39" t="inlineStr"/>
+      <c r="BN39" t="inlineStr"/>
+      <c r="BO39" t="inlineStr"/>
+      <c r="BP39" t="inlineStr"/>
+      <c r="BQ39" t="inlineStr"/>
+      <c r="BR39" t="inlineStr"/>
+      <c r="BS39" t="inlineStr"/>
+      <c r="BT39" t="inlineStr"/>
+      <c r="BU39" t="inlineStr"/>
+      <c r="BV39" t="inlineStr"/>
+      <c r="BW39" t="inlineStr"/>
+      <c r="BX39" t="inlineStr"/>
+      <c r="BY39" t="inlineStr"/>
+      <c r="BZ39" t="inlineStr"/>
+      <c r="CA39" t="inlineStr"/>
+      <c r="CB39" t="inlineStr"/>
+      <c r="CC39" t="inlineStr"/>
+      <c r="CD39" t="inlineStr"/>
+      <c r="CE39" t="inlineStr"/>
+      <c r="CF39" t="inlineStr"/>
+      <c r="CG39" t="inlineStr"/>
+      <c r="CH39" t="inlineStr"/>
+      <c r="CI39" t="inlineStr"/>
+      <c r="CJ39" t="inlineStr"/>
+      <c r="CK39" t="inlineStr"/>
+      <c r="CL39" t="inlineStr"/>
+      <c r="CM39" t="inlineStr"/>
+      <c r="CN39" t="inlineStr"/>
+      <c r="CO39" t="inlineStr"/>
+      <c r="CP39" t="inlineStr"/>
+      <c r="CQ39" t="inlineStr"/>
+      <c r="CR39" t="inlineStr"/>
+      <c r="CS39" t="inlineStr"/>
+      <c r="CT39" t="inlineStr"/>
+      <c r="CU39" t="inlineStr"/>
+      <c r="CV39" t="inlineStr"/>
+      <c r="CW39" t="inlineStr"/>
+      <c r="CX39" t="inlineStr"/>
+      <c r="CY39" t="inlineStr"/>
+      <c r="CZ39" t="inlineStr"/>
+      <c r="DA39" t="inlineStr"/>
+      <c r="DB39" t="inlineStr"/>
+      <c r="DC39" t="inlineStr"/>
+      <c r="DD39" t="inlineStr"/>
+      <c r="DE39" t="inlineStr"/>
+      <c r="DF39" t="inlineStr"/>
+      <c r="DG39" t="inlineStr"/>
+      <c r="DH39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -9379,6 +11529,56 @@
       <c r="BJ40" t="n">
         <v>0.006459060535969795</v>
       </c>
+      <c r="BK40" t="inlineStr"/>
+      <c r="BL40" t="inlineStr"/>
+      <c r="BM40" t="inlineStr"/>
+      <c r="BN40" t="inlineStr"/>
+      <c r="BO40" t="inlineStr"/>
+      <c r="BP40" t="inlineStr"/>
+      <c r="BQ40" t="inlineStr"/>
+      <c r="BR40" t="inlineStr"/>
+      <c r="BS40" t="inlineStr"/>
+      <c r="BT40" t="inlineStr"/>
+      <c r="BU40" t="inlineStr"/>
+      <c r="BV40" t="inlineStr"/>
+      <c r="BW40" t="inlineStr"/>
+      <c r="BX40" t="inlineStr"/>
+      <c r="BY40" t="inlineStr"/>
+      <c r="BZ40" t="inlineStr"/>
+      <c r="CA40" t="inlineStr"/>
+      <c r="CB40" t="inlineStr"/>
+      <c r="CC40" t="inlineStr"/>
+      <c r="CD40" t="inlineStr"/>
+      <c r="CE40" t="inlineStr"/>
+      <c r="CF40" t="inlineStr"/>
+      <c r="CG40" t="inlineStr"/>
+      <c r="CH40" t="inlineStr"/>
+      <c r="CI40" t="inlineStr"/>
+      <c r="CJ40" t="inlineStr"/>
+      <c r="CK40" t="inlineStr"/>
+      <c r="CL40" t="inlineStr"/>
+      <c r="CM40" t="inlineStr"/>
+      <c r="CN40" t="inlineStr"/>
+      <c r="CO40" t="inlineStr"/>
+      <c r="CP40" t="inlineStr"/>
+      <c r="CQ40" t="inlineStr"/>
+      <c r="CR40" t="inlineStr"/>
+      <c r="CS40" t="inlineStr"/>
+      <c r="CT40" t="inlineStr"/>
+      <c r="CU40" t="inlineStr"/>
+      <c r="CV40" t="inlineStr"/>
+      <c r="CW40" t="inlineStr"/>
+      <c r="CX40" t="inlineStr"/>
+      <c r="CY40" t="inlineStr"/>
+      <c r="CZ40" t="inlineStr"/>
+      <c r="DA40" t="inlineStr"/>
+      <c r="DB40" t="inlineStr"/>
+      <c r="DC40" t="inlineStr"/>
+      <c r="DD40" t="inlineStr"/>
+      <c r="DE40" t="inlineStr"/>
+      <c r="DF40" t="inlineStr"/>
+      <c r="DG40" t="inlineStr"/>
+      <c r="DH40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -9599,6 +11799,56 @@
       <c r="BJ41" t="n">
         <v>0.005749128469435981</v>
       </c>
+      <c r="BK41" t="inlineStr"/>
+      <c r="BL41" t="inlineStr"/>
+      <c r="BM41" t="inlineStr"/>
+      <c r="BN41" t="inlineStr"/>
+      <c r="BO41" t="inlineStr"/>
+      <c r="BP41" t="inlineStr"/>
+      <c r="BQ41" t="inlineStr"/>
+      <c r="BR41" t="inlineStr"/>
+      <c r="BS41" t="inlineStr"/>
+      <c r="BT41" t="inlineStr"/>
+      <c r="BU41" t="inlineStr"/>
+      <c r="BV41" t="inlineStr"/>
+      <c r="BW41" t="inlineStr"/>
+      <c r="BX41" t="inlineStr"/>
+      <c r="BY41" t="inlineStr"/>
+      <c r="BZ41" t="inlineStr"/>
+      <c r="CA41" t="inlineStr"/>
+      <c r="CB41" t="inlineStr"/>
+      <c r="CC41" t="inlineStr"/>
+      <c r="CD41" t="inlineStr"/>
+      <c r="CE41" t="inlineStr"/>
+      <c r="CF41" t="inlineStr"/>
+      <c r="CG41" t="inlineStr"/>
+      <c r="CH41" t="inlineStr"/>
+      <c r="CI41" t="inlineStr"/>
+      <c r="CJ41" t="inlineStr"/>
+      <c r="CK41" t="inlineStr"/>
+      <c r="CL41" t="inlineStr"/>
+      <c r="CM41" t="inlineStr"/>
+      <c r="CN41" t="inlineStr"/>
+      <c r="CO41" t="inlineStr"/>
+      <c r="CP41" t="inlineStr"/>
+      <c r="CQ41" t="inlineStr"/>
+      <c r="CR41" t="inlineStr"/>
+      <c r="CS41" t="inlineStr"/>
+      <c r="CT41" t="inlineStr"/>
+      <c r="CU41" t="inlineStr"/>
+      <c r="CV41" t="inlineStr"/>
+      <c r="CW41" t="inlineStr"/>
+      <c r="CX41" t="inlineStr"/>
+      <c r="CY41" t="inlineStr"/>
+      <c r="CZ41" t="inlineStr"/>
+      <c r="DA41" t="inlineStr"/>
+      <c r="DB41" t="inlineStr"/>
+      <c r="DC41" t="inlineStr"/>
+      <c r="DD41" t="inlineStr"/>
+      <c r="DE41" t="inlineStr"/>
+      <c r="DF41" t="inlineStr"/>
+      <c r="DG41" t="inlineStr"/>
+      <c r="DH41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -9819,6 +12069,56 @@
       <c r="BJ42" t="n">
         <v>0.002583684299501075</v>
       </c>
+      <c r="BK42" t="inlineStr"/>
+      <c r="BL42" t="inlineStr"/>
+      <c r="BM42" t="inlineStr"/>
+      <c r="BN42" t="inlineStr"/>
+      <c r="BO42" t="inlineStr"/>
+      <c r="BP42" t="inlineStr"/>
+      <c r="BQ42" t="inlineStr"/>
+      <c r="BR42" t="inlineStr"/>
+      <c r="BS42" t="inlineStr"/>
+      <c r="BT42" t="inlineStr"/>
+      <c r="BU42" t="inlineStr"/>
+      <c r="BV42" t="inlineStr"/>
+      <c r="BW42" t="inlineStr"/>
+      <c r="BX42" t="inlineStr"/>
+      <c r="BY42" t="inlineStr"/>
+      <c r="BZ42" t="inlineStr"/>
+      <c r="CA42" t="inlineStr"/>
+      <c r="CB42" t="inlineStr"/>
+      <c r="CC42" t="inlineStr"/>
+      <c r="CD42" t="inlineStr"/>
+      <c r="CE42" t="inlineStr"/>
+      <c r="CF42" t="inlineStr"/>
+      <c r="CG42" t="inlineStr"/>
+      <c r="CH42" t="inlineStr"/>
+      <c r="CI42" t="inlineStr"/>
+      <c r="CJ42" t="inlineStr"/>
+      <c r="CK42" t="inlineStr"/>
+      <c r="CL42" t="inlineStr"/>
+      <c r="CM42" t="inlineStr"/>
+      <c r="CN42" t="inlineStr"/>
+      <c r="CO42" t="inlineStr"/>
+      <c r="CP42" t="inlineStr"/>
+      <c r="CQ42" t="inlineStr"/>
+      <c r="CR42" t="inlineStr"/>
+      <c r="CS42" t="inlineStr"/>
+      <c r="CT42" t="inlineStr"/>
+      <c r="CU42" t="inlineStr"/>
+      <c r="CV42" t="inlineStr"/>
+      <c r="CW42" t="inlineStr"/>
+      <c r="CX42" t="inlineStr"/>
+      <c r="CY42" t="inlineStr"/>
+      <c r="CZ42" t="inlineStr"/>
+      <c r="DA42" t="inlineStr"/>
+      <c r="DB42" t="inlineStr"/>
+      <c r="DC42" t="inlineStr"/>
+      <c r="DD42" t="inlineStr"/>
+      <c r="DE42" t="inlineStr"/>
+      <c r="DF42" t="inlineStr"/>
+      <c r="DG42" t="inlineStr"/>
+      <c r="DH42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -10039,6 +12339,56 @@
       <c r="BJ43" t="n">
         <v>0.003602719364528168</v>
       </c>
+      <c r="BK43" t="inlineStr"/>
+      <c r="BL43" t="inlineStr"/>
+      <c r="BM43" t="inlineStr"/>
+      <c r="BN43" t="inlineStr"/>
+      <c r="BO43" t="inlineStr"/>
+      <c r="BP43" t="inlineStr"/>
+      <c r="BQ43" t="inlineStr"/>
+      <c r="BR43" t="inlineStr"/>
+      <c r="BS43" t="inlineStr"/>
+      <c r="BT43" t="inlineStr"/>
+      <c r="BU43" t="inlineStr"/>
+      <c r="BV43" t="inlineStr"/>
+      <c r="BW43" t="inlineStr"/>
+      <c r="BX43" t="inlineStr"/>
+      <c r="BY43" t="inlineStr"/>
+      <c r="BZ43" t="inlineStr"/>
+      <c r="CA43" t="inlineStr"/>
+      <c r="CB43" t="inlineStr"/>
+      <c r="CC43" t="inlineStr"/>
+      <c r="CD43" t="inlineStr"/>
+      <c r="CE43" t="inlineStr"/>
+      <c r="CF43" t="inlineStr"/>
+      <c r="CG43" t="inlineStr"/>
+      <c r="CH43" t="inlineStr"/>
+      <c r="CI43" t="inlineStr"/>
+      <c r="CJ43" t="inlineStr"/>
+      <c r="CK43" t="inlineStr"/>
+      <c r="CL43" t="inlineStr"/>
+      <c r="CM43" t="inlineStr"/>
+      <c r="CN43" t="inlineStr"/>
+      <c r="CO43" t="inlineStr"/>
+      <c r="CP43" t="inlineStr"/>
+      <c r="CQ43" t="inlineStr"/>
+      <c r="CR43" t="inlineStr"/>
+      <c r="CS43" t="inlineStr"/>
+      <c r="CT43" t="inlineStr"/>
+      <c r="CU43" t="inlineStr"/>
+      <c r="CV43" t="inlineStr"/>
+      <c r="CW43" t="inlineStr"/>
+      <c r="CX43" t="inlineStr"/>
+      <c r="CY43" t="inlineStr"/>
+      <c r="CZ43" t="inlineStr"/>
+      <c r="DA43" t="inlineStr"/>
+      <c r="DB43" t="inlineStr"/>
+      <c r="DC43" t="inlineStr"/>
+      <c r="DD43" t="inlineStr"/>
+      <c r="DE43" t="inlineStr"/>
+      <c r="DF43" t="inlineStr"/>
+      <c r="DG43" t="inlineStr"/>
+      <c r="DH43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -10259,6 +12609,56 @@
       <c r="BJ44" t="n">
         <v>0.007162357584063435</v>
       </c>
+      <c r="BK44" t="inlineStr"/>
+      <c r="BL44" t="inlineStr"/>
+      <c r="BM44" t="inlineStr"/>
+      <c r="BN44" t="inlineStr"/>
+      <c r="BO44" t="inlineStr"/>
+      <c r="BP44" t="inlineStr"/>
+      <c r="BQ44" t="inlineStr"/>
+      <c r="BR44" t="inlineStr"/>
+      <c r="BS44" t="inlineStr"/>
+      <c r="BT44" t="inlineStr"/>
+      <c r="BU44" t="inlineStr"/>
+      <c r="BV44" t="inlineStr"/>
+      <c r="BW44" t="inlineStr"/>
+      <c r="BX44" t="inlineStr"/>
+      <c r="BY44" t="inlineStr"/>
+      <c r="BZ44" t="inlineStr"/>
+      <c r="CA44" t="inlineStr"/>
+      <c r="CB44" t="inlineStr"/>
+      <c r="CC44" t="inlineStr"/>
+      <c r="CD44" t="inlineStr"/>
+      <c r="CE44" t="inlineStr"/>
+      <c r="CF44" t="inlineStr"/>
+      <c r="CG44" t="inlineStr"/>
+      <c r="CH44" t="inlineStr"/>
+      <c r="CI44" t="inlineStr"/>
+      <c r="CJ44" t="inlineStr"/>
+      <c r="CK44" t="inlineStr"/>
+      <c r="CL44" t="inlineStr"/>
+      <c r="CM44" t="inlineStr"/>
+      <c r="CN44" t="inlineStr"/>
+      <c r="CO44" t="inlineStr"/>
+      <c r="CP44" t="inlineStr"/>
+      <c r="CQ44" t="inlineStr"/>
+      <c r="CR44" t="inlineStr"/>
+      <c r="CS44" t="inlineStr"/>
+      <c r="CT44" t="inlineStr"/>
+      <c r="CU44" t="inlineStr"/>
+      <c r="CV44" t="inlineStr"/>
+      <c r="CW44" t="inlineStr"/>
+      <c r="CX44" t="inlineStr"/>
+      <c r="CY44" t="inlineStr"/>
+      <c r="CZ44" t="inlineStr"/>
+      <c r="DA44" t="inlineStr"/>
+      <c r="DB44" t="inlineStr"/>
+      <c r="DC44" t="inlineStr"/>
+      <c r="DD44" t="inlineStr"/>
+      <c r="DE44" t="inlineStr"/>
+      <c r="DF44" t="inlineStr"/>
+      <c r="DG44" t="inlineStr"/>
+      <c r="DH44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -10479,6 +12879,56 @@
       <c r="BJ45" t="n">
         <v>0.004703518105213435</v>
       </c>
+      <c r="BK45" t="inlineStr"/>
+      <c r="BL45" t="inlineStr"/>
+      <c r="BM45" t="inlineStr"/>
+      <c r="BN45" t="inlineStr"/>
+      <c r="BO45" t="inlineStr"/>
+      <c r="BP45" t="inlineStr"/>
+      <c r="BQ45" t="inlineStr"/>
+      <c r="BR45" t="inlineStr"/>
+      <c r="BS45" t="inlineStr"/>
+      <c r="BT45" t="inlineStr"/>
+      <c r="BU45" t="inlineStr"/>
+      <c r="BV45" t="inlineStr"/>
+      <c r="BW45" t="inlineStr"/>
+      <c r="BX45" t="inlineStr"/>
+      <c r="BY45" t="inlineStr"/>
+      <c r="BZ45" t="inlineStr"/>
+      <c r="CA45" t="inlineStr"/>
+      <c r="CB45" t="inlineStr"/>
+      <c r="CC45" t="inlineStr"/>
+      <c r="CD45" t="inlineStr"/>
+      <c r="CE45" t="inlineStr"/>
+      <c r="CF45" t="inlineStr"/>
+      <c r="CG45" t="inlineStr"/>
+      <c r="CH45" t="inlineStr"/>
+      <c r="CI45" t="inlineStr"/>
+      <c r="CJ45" t="inlineStr"/>
+      <c r="CK45" t="inlineStr"/>
+      <c r="CL45" t="inlineStr"/>
+      <c r="CM45" t="inlineStr"/>
+      <c r="CN45" t="inlineStr"/>
+      <c r="CO45" t="inlineStr"/>
+      <c r="CP45" t="inlineStr"/>
+      <c r="CQ45" t="inlineStr"/>
+      <c r="CR45" t="inlineStr"/>
+      <c r="CS45" t="inlineStr"/>
+      <c r="CT45" t="inlineStr"/>
+      <c r="CU45" t="inlineStr"/>
+      <c r="CV45" t="inlineStr"/>
+      <c r="CW45" t="inlineStr"/>
+      <c r="CX45" t="inlineStr"/>
+      <c r="CY45" t="inlineStr"/>
+      <c r="CZ45" t="inlineStr"/>
+      <c r="DA45" t="inlineStr"/>
+      <c r="DB45" t="inlineStr"/>
+      <c r="DC45" t="inlineStr"/>
+      <c r="DD45" t="inlineStr"/>
+      <c r="DE45" t="inlineStr"/>
+      <c r="DF45" t="inlineStr"/>
+      <c r="DG45" t="inlineStr"/>
+      <c r="DH45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -10699,6 +13149,56 @@
       <c r="BJ46" t="n">
         <v>0.0002690319894887233</v>
       </c>
+      <c r="BK46" t="inlineStr"/>
+      <c r="BL46" t="inlineStr"/>
+      <c r="BM46" t="inlineStr"/>
+      <c r="BN46" t="inlineStr"/>
+      <c r="BO46" t="inlineStr"/>
+      <c r="BP46" t="inlineStr"/>
+      <c r="BQ46" t="inlineStr"/>
+      <c r="BR46" t="inlineStr"/>
+      <c r="BS46" t="inlineStr"/>
+      <c r="BT46" t="inlineStr"/>
+      <c r="BU46" t="inlineStr"/>
+      <c r="BV46" t="inlineStr"/>
+      <c r="BW46" t="inlineStr"/>
+      <c r="BX46" t="inlineStr"/>
+      <c r="BY46" t="inlineStr"/>
+      <c r="BZ46" t="inlineStr"/>
+      <c r="CA46" t="inlineStr"/>
+      <c r="CB46" t="inlineStr"/>
+      <c r="CC46" t="inlineStr"/>
+      <c r="CD46" t="inlineStr"/>
+      <c r="CE46" t="inlineStr"/>
+      <c r="CF46" t="inlineStr"/>
+      <c r="CG46" t="inlineStr"/>
+      <c r="CH46" t="inlineStr"/>
+      <c r="CI46" t="inlineStr"/>
+      <c r="CJ46" t="inlineStr"/>
+      <c r="CK46" t="inlineStr"/>
+      <c r="CL46" t="inlineStr"/>
+      <c r="CM46" t="inlineStr"/>
+      <c r="CN46" t="inlineStr"/>
+      <c r="CO46" t="inlineStr"/>
+      <c r="CP46" t="inlineStr"/>
+      <c r="CQ46" t="inlineStr"/>
+      <c r="CR46" t="inlineStr"/>
+      <c r="CS46" t="inlineStr"/>
+      <c r="CT46" t="inlineStr"/>
+      <c r="CU46" t="inlineStr"/>
+      <c r="CV46" t="inlineStr"/>
+      <c r="CW46" t="inlineStr"/>
+      <c r="CX46" t="inlineStr"/>
+      <c r="CY46" t="inlineStr"/>
+      <c r="CZ46" t="inlineStr"/>
+      <c r="DA46" t="inlineStr"/>
+      <c r="DB46" t="inlineStr"/>
+      <c r="DC46" t="inlineStr"/>
+      <c r="DD46" t="inlineStr"/>
+      <c r="DE46" t="inlineStr"/>
+      <c r="DF46" t="inlineStr"/>
+      <c r="DG46" t="inlineStr"/>
+      <c r="DH46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -10919,6 +13419,56 @@
       <c r="BJ47" t="n">
         <v>4.189518119265814e-05</v>
       </c>
+      <c r="BK47" t="inlineStr"/>
+      <c r="BL47" t="inlineStr"/>
+      <c r="BM47" t="inlineStr"/>
+      <c r="BN47" t="inlineStr"/>
+      <c r="BO47" t="inlineStr"/>
+      <c r="BP47" t="inlineStr"/>
+      <c r="BQ47" t="inlineStr"/>
+      <c r="BR47" t="inlineStr"/>
+      <c r="BS47" t="inlineStr"/>
+      <c r="BT47" t="inlineStr"/>
+      <c r="BU47" t="inlineStr"/>
+      <c r="BV47" t="inlineStr"/>
+      <c r="BW47" t="inlineStr"/>
+      <c r="BX47" t="inlineStr"/>
+      <c r="BY47" t="inlineStr"/>
+      <c r="BZ47" t="inlineStr"/>
+      <c r="CA47" t="inlineStr"/>
+      <c r="CB47" t="inlineStr"/>
+      <c r="CC47" t="inlineStr"/>
+      <c r="CD47" t="inlineStr"/>
+      <c r="CE47" t="inlineStr"/>
+      <c r="CF47" t="inlineStr"/>
+      <c r="CG47" t="inlineStr"/>
+      <c r="CH47" t="inlineStr"/>
+      <c r="CI47" t="inlineStr"/>
+      <c r="CJ47" t="inlineStr"/>
+      <c r="CK47" t="inlineStr"/>
+      <c r="CL47" t="inlineStr"/>
+      <c r="CM47" t="inlineStr"/>
+      <c r="CN47" t="inlineStr"/>
+      <c r="CO47" t="inlineStr"/>
+      <c r="CP47" t="inlineStr"/>
+      <c r="CQ47" t="inlineStr"/>
+      <c r="CR47" t="inlineStr"/>
+      <c r="CS47" t="inlineStr"/>
+      <c r="CT47" t="inlineStr"/>
+      <c r="CU47" t="inlineStr"/>
+      <c r="CV47" t="inlineStr"/>
+      <c r="CW47" t="inlineStr"/>
+      <c r="CX47" t="inlineStr"/>
+      <c r="CY47" t="inlineStr"/>
+      <c r="CZ47" t="inlineStr"/>
+      <c r="DA47" t="inlineStr"/>
+      <c r="DB47" t="inlineStr"/>
+      <c r="DC47" t="inlineStr"/>
+      <c r="DD47" t="inlineStr"/>
+      <c r="DE47" t="inlineStr"/>
+      <c r="DF47" t="inlineStr"/>
+      <c r="DG47" t="inlineStr"/>
+      <c r="DH47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -11149,6 +13699,56 @@
       <c r="BJ48" t="n">
         <v>9.712984233428587e-06</v>
       </c>
+      <c r="BK48" t="inlineStr"/>
+      <c r="BL48" t="inlineStr"/>
+      <c r="BM48" t="inlineStr"/>
+      <c r="BN48" t="inlineStr"/>
+      <c r="BO48" t="inlineStr"/>
+      <c r="BP48" t="inlineStr"/>
+      <c r="BQ48" t="inlineStr"/>
+      <c r="BR48" t="inlineStr"/>
+      <c r="BS48" t="inlineStr"/>
+      <c r="BT48" t="inlineStr"/>
+      <c r="BU48" t="inlineStr"/>
+      <c r="BV48" t="inlineStr"/>
+      <c r="BW48" t="inlineStr"/>
+      <c r="BX48" t="inlineStr"/>
+      <c r="BY48" t="inlineStr"/>
+      <c r="BZ48" t="inlineStr"/>
+      <c r="CA48" t="inlineStr"/>
+      <c r="CB48" t="inlineStr"/>
+      <c r="CC48" t="inlineStr"/>
+      <c r="CD48" t="inlineStr"/>
+      <c r="CE48" t="inlineStr"/>
+      <c r="CF48" t="inlineStr"/>
+      <c r="CG48" t="inlineStr"/>
+      <c r="CH48" t="inlineStr"/>
+      <c r="CI48" t="inlineStr"/>
+      <c r="CJ48" t="inlineStr"/>
+      <c r="CK48" t="inlineStr"/>
+      <c r="CL48" t="inlineStr"/>
+      <c r="CM48" t="inlineStr"/>
+      <c r="CN48" t="inlineStr"/>
+      <c r="CO48" t="inlineStr"/>
+      <c r="CP48" t="inlineStr"/>
+      <c r="CQ48" t="inlineStr"/>
+      <c r="CR48" t="inlineStr"/>
+      <c r="CS48" t="inlineStr"/>
+      <c r="CT48" t="inlineStr"/>
+      <c r="CU48" t="inlineStr"/>
+      <c r="CV48" t="inlineStr"/>
+      <c r="CW48" t="inlineStr"/>
+      <c r="CX48" t="inlineStr"/>
+      <c r="CY48" t="inlineStr"/>
+      <c r="CZ48" t="inlineStr"/>
+      <c r="DA48" t="inlineStr"/>
+      <c r="DB48" t="inlineStr"/>
+      <c r="DC48" t="inlineStr"/>
+      <c r="DD48" t="inlineStr"/>
+      <c r="DE48" t="inlineStr"/>
+      <c r="DF48" t="inlineStr"/>
+      <c r="DG48" t="inlineStr"/>
+      <c r="DH48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -11379,6 +13979,56 @@
       <c r="BJ49" t="n">
         <v>4.196248604251576e-17</v>
       </c>
+      <c r="BK49" t="inlineStr"/>
+      <c r="BL49" t="inlineStr"/>
+      <c r="BM49" t="inlineStr"/>
+      <c r="BN49" t="inlineStr"/>
+      <c r="BO49" t="inlineStr"/>
+      <c r="BP49" t="inlineStr"/>
+      <c r="BQ49" t="inlineStr"/>
+      <c r="BR49" t="inlineStr"/>
+      <c r="BS49" t="inlineStr"/>
+      <c r="BT49" t="inlineStr"/>
+      <c r="BU49" t="inlineStr"/>
+      <c r="BV49" t="inlineStr"/>
+      <c r="BW49" t="inlineStr"/>
+      <c r="BX49" t="inlineStr"/>
+      <c r="BY49" t="inlineStr"/>
+      <c r="BZ49" t="inlineStr"/>
+      <c r="CA49" t="inlineStr"/>
+      <c r="CB49" t="inlineStr"/>
+      <c r="CC49" t="inlineStr"/>
+      <c r="CD49" t="inlineStr"/>
+      <c r="CE49" t="inlineStr"/>
+      <c r="CF49" t="inlineStr"/>
+      <c r="CG49" t="inlineStr"/>
+      <c r="CH49" t="inlineStr"/>
+      <c r="CI49" t="inlineStr"/>
+      <c r="CJ49" t="inlineStr"/>
+      <c r="CK49" t="inlineStr"/>
+      <c r="CL49" t="inlineStr"/>
+      <c r="CM49" t="inlineStr"/>
+      <c r="CN49" t="inlineStr"/>
+      <c r="CO49" t="inlineStr"/>
+      <c r="CP49" t="inlineStr"/>
+      <c r="CQ49" t="inlineStr"/>
+      <c r="CR49" t="inlineStr"/>
+      <c r="CS49" t="inlineStr"/>
+      <c r="CT49" t="inlineStr"/>
+      <c r="CU49" t="inlineStr"/>
+      <c r="CV49" t="inlineStr"/>
+      <c r="CW49" t="inlineStr"/>
+      <c r="CX49" t="inlineStr"/>
+      <c r="CY49" t="inlineStr"/>
+      <c r="CZ49" t="inlineStr"/>
+      <c r="DA49" t="inlineStr"/>
+      <c r="DB49" t="inlineStr"/>
+      <c r="DC49" t="inlineStr"/>
+      <c r="DD49" t="inlineStr"/>
+      <c r="DE49" t="inlineStr"/>
+      <c r="DF49" t="inlineStr"/>
+      <c r="DG49" t="inlineStr"/>
+      <c r="DH49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -11599,6 +14249,56 @@
       <c r="BJ50" t="n">
         <v>0.01108411101526533</v>
       </c>
+      <c r="BK50" t="inlineStr"/>
+      <c r="BL50" t="inlineStr"/>
+      <c r="BM50" t="inlineStr"/>
+      <c r="BN50" t="inlineStr"/>
+      <c r="BO50" t="inlineStr"/>
+      <c r="BP50" t="inlineStr"/>
+      <c r="BQ50" t="inlineStr"/>
+      <c r="BR50" t="inlineStr"/>
+      <c r="BS50" t="inlineStr"/>
+      <c r="BT50" t="inlineStr"/>
+      <c r="BU50" t="inlineStr"/>
+      <c r="BV50" t="inlineStr"/>
+      <c r="BW50" t="inlineStr"/>
+      <c r="BX50" t="inlineStr"/>
+      <c r="BY50" t="inlineStr"/>
+      <c r="BZ50" t="inlineStr"/>
+      <c r="CA50" t="inlineStr"/>
+      <c r="CB50" t="inlineStr"/>
+      <c r="CC50" t="inlineStr"/>
+      <c r="CD50" t="inlineStr"/>
+      <c r="CE50" t="inlineStr"/>
+      <c r="CF50" t="inlineStr"/>
+      <c r="CG50" t="inlineStr"/>
+      <c r="CH50" t="inlineStr"/>
+      <c r="CI50" t="inlineStr"/>
+      <c r="CJ50" t="inlineStr"/>
+      <c r="CK50" t="inlineStr"/>
+      <c r="CL50" t="inlineStr"/>
+      <c r="CM50" t="inlineStr"/>
+      <c r="CN50" t="inlineStr"/>
+      <c r="CO50" t="inlineStr"/>
+      <c r="CP50" t="inlineStr"/>
+      <c r="CQ50" t="inlineStr"/>
+      <c r="CR50" t="inlineStr"/>
+      <c r="CS50" t="inlineStr"/>
+      <c r="CT50" t="inlineStr"/>
+      <c r="CU50" t="inlineStr"/>
+      <c r="CV50" t="inlineStr"/>
+      <c r="CW50" t="inlineStr"/>
+      <c r="CX50" t="inlineStr"/>
+      <c r="CY50" t="inlineStr"/>
+      <c r="CZ50" t="inlineStr"/>
+      <c r="DA50" t="inlineStr"/>
+      <c r="DB50" t="inlineStr"/>
+      <c r="DC50" t="inlineStr"/>
+      <c r="DD50" t="inlineStr"/>
+      <c r="DE50" t="inlineStr"/>
+      <c r="DF50" t="inlineStr"/>
+      <c r="DG50" t="inlineStr"/>
+      <c r="DH50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -11819,6 +14519,56 @@
       <c r="BJ51" t="n">
         <v>0.004629350087943543</v>
       </c>
+      <c r="BK51" t="inlineStr"/>
+      <c r="BL51" t="inlineStr"/>
+      <c r="BM51" t="inlineStr"/>
+      <c r="BN51" t="inlineStr"/>
+      <c r="BO51" t="inlineStr"/>
+      <c r="BP51" t="inlineStr"/>
+      <c r="BQ51" t="inlineStr"/>
+      <c r="BR51" t="inlineStr"/>
+      <c r="BS51" t="inlineStr"/>
+      <c r="BT51" t="inlineStr"/>
+      <c r="BU51" t="inlineStr"/>
+      <c r="BV51" t="inlineStr"/>
+      <c r="BW51" t="inlineStr"/>
+      <c r="BX51" t="inlineStr"/>
+      <c r="BY51" t="inlineStr"/>
+      <c r="BZ51" t="inlineStr"/>
+      <c r="CA51" t="inlineStr"/>
+      <c r="CB51" t="inlineStr"/>
+      <c r="CC51" t="inlineStr"/>
+      <c r="CD51" t="inlineStr"/>
+      <c r="CE51" t="inlineStr"/>
+      <c r="CF51" t="inlineStr"/>
+      <c r="CG51" t="inlineStr"/>
+      <c r="CH51" t="inlineStr"/>
+      <c r="CI51" t="inlineStr"/>
+      <c r="CJ51" t="inlineStr"/>
+      <c r="CK51" t="inlineStr"/>
+      <c r="CL51" t="inlineStr"/>
+      <c r="CM51" t="inlineStr"/>
+      <c r="CN51" t="inlineStr"/>
+      <c r="CO51" t="inlineStr"/>
+      <c r="CP51" t="inlineStr"/>
+      <c r="CQ51" t="inlineStr"/>
+      <c r="CR51" t="inlineStr"/>
+      <c r="CS51" t="inlineStr"/>
+      <c r="CT51" t="inlineStr"/>
+      <c r="CU51" t="inlineStr"/>
+      <c r="CV51" t="inlineStr"/>
+      <c r="CW51" t="inlineStr"/>
+      <c r="CX51" t="inlineStr"/>
+      <c r="CY51" t="inlineStr"/>
+      <c r="CZ51" t="inlineStr"/>
+      <c r="DA51" t="inlineStr"/>
+      <c r="DB51" t="inlineStr"/>
+      <c r="DC51" t="inlineStr"/>
+      <c r="DD51" t="inlineStr"/>
+      <c r="DE51" t="inlineStr"/>
+      <c r="DF51" t="inlineStr"/>
+      <c r="DG51" t="inlineStr"/>
+      <c r="DH51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -12039,6 +14789,56 @@
       <c r="BJ52" t="n">
         <v>0.009056712480178981</v>
       </c>
+      <c r="BK52" t="inlineStr"/>
+      <c r="BL52" t="inlineStr"/>
+      <c r="BM52" t="inlineStr"/>
+      <c r="BN52" t="inlineStr"/>
+      <c r="BO52" t="inlineStr"/>
+      <c r="BP52" t="inlineStr"/>
+      <c r="BQ52" t="inlineStr"/>
+      <c r="BR52" t="inlineStr"/>
+      <c r="BS52" t="inlineStr"/>
+      <c r="BT52" t="inlineStr"/>
+      <c r="BU52" t="inlineStr"/>
+      <c r="BV52" t="inlineStr"/>
+      <c r="BW52" t="inlineStr"/>
+      <c r="BX52" t="inlineStr"/>
+      <c r="BY52" t="inlineStr"/>
+      <c r="BZ52" t="inlineStr"/>
+      <c r="CA52" t="inlineStr"/>
+      <c r="CB52" t="inlineStr"/>
+      <c r="CC52" t="inlineStr"/>
+      <c r="CD52" t="inlineStr"/>
+      <c r="CE52" t="inlineStr"/>
+      <c r="CF52" t="inlineStr"/>
+      <c r="CG52" t="inlineStr"/>
+      <c r="CH52" t="inlineStr"/>
+      <c r="CI52" t="inlineStr"/>
+      <c r="CJ52" t="inlineStr"/>
+      <c r="CK52" t="inlineStr"/>
+      <c r="CL52" t="inlineStr"/>
+      <c r="CM52" t="inlineStr"/>
+      <c r="CN52" t="inlineStr"/>
+      <c r="CO52" t="inlineStr"/>
+      <c r="CP52" t="inlineStr"/>
+      <c r="CQ52" t="inlineStr"/>
+      <c r="CR52" t="inlineStr"/>
+      <c r="CS52" t="inlineStr"/>
+      <c r="CT52" t="inlineStr"/>
+      <c r="CU52" t="inlineStr"/>
+      <c r="CV52" t="inlineStr"/>
+      <c r="CW52" t="inlineStr"/>
+      <c r="CX52" t="inlineStr"/>
+      <c r="CY52" t="inlineStr"/>
+      <c r="CZ52" t="inlineStr"/>
+      <c r="DA52" t="inlineStr"/>
+      <c r="DB52" t="inlineStr"/>
+      <c r="DC52" t="inlineStr"/>
+      <c r="DD52" t="inlineStr"/>
+      <c r="DE52" t="inlineStr"/>
+      <c r="DF52" t="inlineStr"/>
+      <c r="DG52" t="inlineStr"/>
+      <c r="DH52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -12259,6 +15059,56 @@
       <c r="BJ53" t="n">
         <v>0.006631067788558371</v>
       </c>
+      <c r="BK53" t="inlineStr"/>
+      <c r="BL53" t="inlineStr"/>
+      <c r="BM53" t="inlineStr"/>
+      <c r="BN53" t="inlineStr"/>
+      <c r="BO53" t="inlineStr"/>
+      <c r="BP53" t="inlineStr"/>
+      <c r="BQ53" t="inlineStr"/>
+      <c r="BR53" t="inlineStr"/>
+      <c r="BS53" t="inlineStr"/>
+      <c r="BT53" t="inlineStr"/>
+      <c r="BU53" t="inlineStr"/>
+      <c r="BV53" t="inlineStr"/>
+      <c r="BW53" t="inlineStr"/>
+      <c r="BX53" t="inlineStr"/>
+      <c r="BY53" t="inlineStr"/>
+      <c r="BZ53" t="inlineStr"/>
+      <c r="CA53" t="inlineStr"/>
+      <c r="CB53" t="inlineStr"/>
+      <c r="CC53" t="inlineStr"/>
+      <c r="CD53" t="inlineStr"/>
+      <c r="CE53" t="inlineStr"/>
+      <c r="CF53" t="inlineStr"/>
+      <c r="CG53" t="inlineStr"/>
+      <c r="CH53" t="inlineStr"/>
+      <c r="CI53" t="inlineStr"/>
+      <c r="CJ53" t="inlineStr"/>
+      <c r="CK53" t="inlineStr"/>
+      <c r="CL53" t="inlineStr"/>
+      <c r="CM53" t="inlineStr"/>
+      <c r="CN53" t="inlineStr"/>
+      <c r="CO53" t="inlineStr"/>
+      <c r="CP53" t="inlineStr"/>
+      <c r="CQ53" t="inlineStr"/>
+      <c r="CR53" t="inlineStr"/>
+      <c r="CS53" t="inlineStr"/>
+      <c r="CT53" t="inlineStr"/>
+      <c r="CU53" t="inlineStr"/>
+      <c r="CV53" t="inlineStr"/>
+      <c r="CW53" t="inlineStr"/>
+      <c r="CX53" t="inlineStr"/>
+      <c r="CY53" t="inlineStr"/>
+      <c r="CZ53" t="inlineStr"/>
+      <c r="DA53" t="inlineStr"/>
+      <c r="DB53" t="inlineStr"/>
+      <c r="DC53" t="inlineStr"/>
+      <c r="DD53" t="inlineStr"/>
+      <c r="DE53" t="inlineStr"/>
+      <c r="DF53" t="inlineStr"/>
+      <c r="DG53" t="inlineStr"/>
+      <c r="DH53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -12479,6 +15329,56 @@
       <c r="BJ54" t="n">
         <v>0.00339265427510108</v>
       </c>
+      <c r="BK54" t="inlineStr"/>
+      <c r="BL54" t="inlineStr"/>
+      <c r="BM54" t="inlineStr"/>
+      <c r="BN54" t="inlineStr"/>
+      <c r="BO54" t="inlineStr"/>
+      <c r="BP54" t="inlineStr"/>
+      <c r="BQ54" t="inlineStr"/>
+      <c r="BR54" t="inlineStr"/>
+      <c r="BS54" t="inlineStr"/>
+      <c r="BT54" t="inlineStr"/>
+      <c r="BU54" t="inlineStr"/>
+      <c r="BV54" t="inlineStr"/>
+      <c r="BW54" t="inlineStr"/>
+      <c r="BX54" t="inlineStr"/>
+      <c r="BY54" t="inlineStr"/>
+      <c r="BZ54" t="inlineStr"/>
+      <c r="CA54" t="inlineStr"/>
+      <c r="CB54" t="inlineStr"/>
+      <c r="CC54" t="inlineStr"/>
+      <c r="CD54" t="inlineStr"/>
+      <c r="CE54" t="inlineStr"/>
+      <c r="CF54" t="inlineStr"/>
+      <c r="CG54" t="inlineStr"/>
+      <c r="CH54" t="inlineStr"/>
+      <c r="CI54" t="inlineStr"/>
+      <c r="CJ54" t="inlineStr"/>
+      <c r="CK54" t="inlineStr"/>
+      <c r="CL54" t="inlineStr"/>
+      <c r="CM54" t="inlineStr"/>
+      <c r="CN54" t="inlineStr"/>
+      <c r="CO54" t="inlineStr"/>
+      <c r="CP54" t="inlineStr"/>
+      <c r="CQ54" t="inlineStr"/>
+      <c r="CR54" t="inlineStr"/>
+      <c r="CS54" t="inlineStr"/>
+      <c r="CT54" t="inlineStr"/>
+      <c r="CU54" t="inlineStr"/>
+      <c r="CV54" t="inlineStr"/>
+      <c r="CW54" t="inlineStr"/>
+      <c r="CX54" t="inlineStr"/>
+      <c r="CY54" t="inlineStr"/>
+      <c r="CZ54" t="inlineStr"/>
+      <c r="DA54" t="inlineStr"/>
+      <c r="DB54" t="inlineStr"/>
+      <c r="DC54" t="inlineStr"/>
+      <c r="DD54" t="inlineStr"/>
+      <c r="DE54" t="inlineStr"/>
+      <c r="DF54" t="inlineStr"/>
+      <c r="DG54" t="inlineStr"/>
+      <c r="DH54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -12699,6 +15599,56 @@
       <c r="BJ55" t="n">
         <v>0.000936242175825913</v>
       </c>
+      <c r="BK55" t="inlineStr"/>
+      <c r="BL55" t="inlineStr"/>
+      <c r="BM55" t="inlineStr"/>
+      <c r="BN55" t="inlineStr"/>
+      <c r="BO55" t="inlineStr"/>
+      <c r="BP55" t="inlineStr"/>
+      <c r="BQ55" t="inlineStr"/>
+      <c r="BR55" t="inlineStr"/>
+      <c r="BS55" t="inlineStr"/>
+      <c r="BT55" t="inlineStr"/>
+      <c r="BU55" t="inlineStr"/>
+      <c r="BV55" t="inlineStr"/>
+      <c r="BW55" t="inlineStr"/>
+      <c r="BX55" t="inlineStr"/>
+      <c r="BY55" t="inlineStr"/>
+      <c r="BZ55" t="inlineStr"/>
+      <c r="CA55" t="inlineStr"/>
+      <c r="CB55" t="inlineStr"/>
+      <c r="CC55" t="inlineStr"/>
+      <c r="CD55" t="inlineStr"/>
+      <c r="CE55" t="inlineStr"/>
+      <c r="CF55" t="inlineStr"/>
+      <c r="CG55" t="inlineStr"/>
+      <c r="CH55" t="inlineStr"/>
+      <c r="CI55" t="inlineStr"/>
+      <c r="CJ55" t="inlineStr"/>
+      <c r="CK55" t="inlineStr"/>
+      <c r="CL55" t="inlineStr"/>
+      <c r="CM55" t="inlineStr"/>
+      <c r="CN55" t="inlineStr"/>
+      <c r="CO55" t="inlineStr"/>
+      <c r="CP55" t="inlineStr"/>
+      <c r="CQ55" t="inlineStr"/>
+      <c r="CR55" t="inlineStr"/>
+      <c r="CS55" t="inlineStr"/>
+      <c r="CT55" t="inlineStr"/>
+      <c r="CU55" t="inlineStr"/>
+      <c r="CV55" t="inlineStr"/>
+      <c r="CW55" t="inlineStr"/>
+      <c r="CX55" t="inlineStr"/>
+      <c r="CY55" t="inlineStr"/>
+      <c r="CZ55" t="inlineStr"/>
+      <c r="DA55" t="inlineStr"/>
+      <c r="DB55" t="inlineStr"/>
+      <c r="DC55" t="inlineStr"/>
+      <c r="DD55" t="inlineStr"/>
+      <c r="DE55" t="inlineStr"/>
+      <c r="DF55" t="inlineStr"/>
+      <c r="DG55" t="inlineStr"/>
+      <c r="DH55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -12919,6 +15869,56 @@
       <c r="BJ56" t="n">
         <v>9.712984233428587e-06</v>
       </c>
+      <c r="BK56" t="inlineStr"/>
+      <c r="BL56" t="inlineStr"/>
+      <c r="BM56" t="inlineStr"/>
+      <c r="BN56" t="inlineStr"/>
+      <c r="BO56" t="inlineStr"/>
+      <c r="BP56" t="inlineStr"/>
+      <c r="BQ56" t="inlineStr"/>
+      <c r="BR56" t="inlineStr"/>
+      <c r="BS56" t="inlineStr"/>
+      <c r="BT56" t="inlineStr"/>
+      <c r="BU56" t="inlineStr"/>
+      <c r="BV56" t="inlineStr"/>
+      <c r="BW56" t="inlineStr"/>
+      <c r="BX56" t="inlineStr"/>
+      <c r="BY56" t="inlineStr"/>
+      <c r="BZ56" t="inlineStr"/>
+      <c r="CA56" t="inlineStr"/>
+      <c r="CB56" t="inlineStr"/>
+      <c r="CC56" t="inlineStr"/>
+      <c r="CD56" t="inlineStr"/>
+      <c r="CE56" t="inlineStr"/>
+      <c r="CF56" t="inlineStr"/>
+      <c r="CG56" t="inlineStr"/>
+      <c r="CH56" t="inlineStr"/>
+      <c r="CI56" t="inlineStr"/>
+      <c r="CJ56" t="inlineStr"/>
+      <c r="CK56" t="inlineStr"/>
+      <c r="CL56" t="inlineStr"/>
+      <c r="CM56" t="inlineStr"/>
+      <c r="CN56" t="inlineStr"/>
+      <c r="CO56" t="inlineStr"/>
+      <c r="CP56" t="inlineStr"/>
+      <c r="CQ56" t="inlineStr"/>
+      <c r="CR56" t="inlineStr"/>
+      <c r="CS56" t="inlineStr"/>
+      <c r="CT56" t="inlineStr"/>
+      <c r="CU56" t="inlineStr"/>
+      <c r="CV56" t="inlineStr"/>
+      <c r="CW56" t="inlineStr"/>
+      <c r="CX56" t="inlineStr"/>
+      <c r="CY56" t="inlineStr"/>
+      <c r="CZ56" t="inlineStr"/>
+      <c r="DA56" t="inlineStr"/>
+      <c r="DB56" t="inlineStr"/>
+      <c r="DC56" t="inlineStr"/>
+      <c r="DD56" t="inlineStr"/>
+      <c r="DE56" t="inlineStr"/>
+      <c r="DF56" t="inlineStr"/>
+      <c r="DG56" t="inlineStr"/>
+      <c r="DH56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -13139,6 +16139,56 @@
       <c r="BJ57" t="n">
         <v>0</v>
       </c>
+      <c r="BK57" t="inlineStr"/>
+      <c r="BL57" t="inlineStr"/>
+      <c r="BM57" t="inlineStr"/>
+      <c r="BN57" t="inlineStr"/>
+      <c r="BO57" t="inlineStr"/>
+      <c r="BP57" t="inlineStr"/>
+      <c r="BQ57" t="inlineStr"/>
+      <c r="BR57" t="inlineStr"/>
+      <c r="BS57" t="inlineStr"/>
+      <c r="BT57" t="inlineStr"/>
+      <c r="BU57" t="inlineStr"/>
+      <c r="BV57" t="inlineStr"/>
+      <c r="BW57" t="inlineStr"/>
+      <c r="BX57" t="inlineStr"/>
+      <c r="BY57" t="inlineStr"/>
+      <c r="BZ57" t="inlineStr"/>
+      <c r="CA57" t="inlineStr"/>
+      <c r="CB57" t="inlineStr"/>
+      <c r="CC57" t="inlineStr"/>
+      <c r="CD57" t="inlineStr"/>
+      <c r="CE57" t="inlineStr"/>
+      <c r="CF57" t="inlineStr"/>
+      <c r="CG57" t="inlineStr"/>
+      <c r="CH57" t="inlineStr"/>
+      <c r="CI57" t="inlineStr"/>
+      <c r="CJ57" t="inlineStr"/>
+      <c r="CK57" t="inlineStr"/>
+      <c r="CL57" t="inlineStr"/>
+      <c r="CM57" t="inlineStr"/>
+      <c r="CN57" t="inlineStr"/>
+      <c r="CO57" t="inlineStr"/>
+      <c r="CP57" t="inlineStr"/>
+      <c r="CQ57" t="inlineStr"/>
+      <c r="CR57" t="inlineStr"/>
+      <c r="CS57" t="inlineStr"/>
+      <c r="CT57" t="inlineStr"/>
+      <c r="CU57" t="inlineStr"/>
+      <c r="CV57" t="inlineStr"/>
+      <c r="CW57" t="inlineStr"/>
+      <c r="CX57" t="inlineStr"/>
+      <c r="CY57" t="inlineStr"/>
+      <c r="CZ57" t="inlineStr"/>
+      <c r="DA57" t="inlineStr"/>
+      <c r="DB57" t="inlineStr"/>
+      <c r="DC57" t="inlineStr"/>
+      <c r="DD57" t="inlineStr"/>
+      <c r="DE57" t="inlineStr"/>
+      <c r="DF57" t="inlineStr"/>
+      <c r="DG57" t="inlineStr"/>
+      <c r="DH57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -13359,6 +16409,56 @@
       <c r="BJ58" t="n">
         <v>9.712984233463661e-06</v>
       </c>
+      <c r="BK58" t="inlineStr"/>
+      <c r="BL58" t="inlineStr"/>
+      <c r="BM58" t="inlineStr"/>
+      <c r="BN58" t="inlineStr"/>
+      <c r="BO58" t="inlineStr"/>
+      <c r="BP58" t="inlineStr"/>
+      <c r="BQ58" t="inlineStr"/>
+      <c r="BR58" t="inlineStr"/>
+      <c r="BS58" t="inlineStr"/>
+      <c r="BT58" t="inlineStr"/>
+      <c r="BU58" t="inlineStr"/>
+      <c r="BV58" t="inlineStr"/>
+      <c r="BW58" t="inlineStr"/>
+      <c r="BX58" t="inlineStr"/>
+      <c r="BY58" t="inlineStr"/>
+      <c r="BZ58" t="inlineStr"/>
+      <c r="CA58" t="inlineStr"/>
+      <c r="CB58" t="inlineStr"/>
+      <c r="CC58" t="inlineStr"/>
+      <c r="CD58" t="inlineStr"/>
+      <c r="CE58" t="inlineStr"/>
+      <c r="CF58" t="inlineStr"/>
+      <c r="CG58" t="inlineStr"/>
+      <c r="CH58" t="inlineStr"/>
+      <c r="CI58" t="inlineStr"/>
+      <c r="CJ58" t="inlineStr"/>
+      <c r="CK58" t="inlineStr"/>
+      <c r="CL58" t="inlineStr"/>
+      <c r="CM58" t="inlineStr"/>
+      <c r="CN58" t="inlineStr"/>
+      <c r="CO58" t="inlineStr"/>
+      <c r="CP58" t="inlineStr"/>
+      <c r="CQ58" t="inlineStr"/>
+      <c r="CR58" t="inlineStr"/>
+      <c r="CS58" t="inlineStr"/>
+      <c r="CT58" t="inlineStr"/>
+      <c r="CU58" t="inlineStr"/>
+      <c r="CV58" t="inlineStr"/>
+      <c r="CW58" t="inlineStr"/>
+      <c r="CX58" t="inlineStr"/>
+      <c r="CY58" t="inlineStr"/>
+      <c r="CZ58" t="inlineStr"/>
+      <c r="DA58" t="inlineStr"/>
+      <c r="DB58" t="inlineStr"/>
+      <c r="DC58" t="inlineStr"/>
+      <c r="DD58" t="inlineStr"/>
+      <c r="DE58" t="inlineStr"/>
+      <c r="DF58" t="inlineStr"/>
+      <c r="DG58" t="inlineStr"/>
+      <c r="DH58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -13578,6 +16678,446 @@
       </c>
       <c r="BJ59" t="n">
         <v>0</v>
+      </c>
+      <c r="BK59" t="inlineStr"/>
+      <c r="BL59" t="inlineStr"/>
+      <c r="BM59" t="inlineStr"/>
+      <c r="BN59" t="inlineStr"/>
+      <c r="BO59" t="inlineStr"/>
+      <c r="BP59" t="inlineStr"/>
+      <c r="BQ59" t="inlineStr"/>
+      <c r="BR59" t="inlineStr"/>
+      <c r="BS59" t="inlineStr"/>
+      <c r="BT59" t="inlineStr"/>
+      <c r="BU59" t="inlineStr"/>
+      <c r="BV59" t="inlineStr"/>
+      <c r="BW59" t="inlineStr"/>
+      <c r="BX59" t="inlineStr"/>
+      <c r="BY59" t="inlineStr"/>
+      <c r="BZ59" t="inlineStr"/>
+      <c r="CA59" t="inlineStr"/>
+      <c r="CB59" t="inlineStr"/>
+      <c r="CC59" t="inlineStr"/>
+      <c r="CD59" t="inlineStr"/>
+      <c r="CE59" t="inlineStr"/>
+      <c r="CF59" t="inlineStr"/>
+      <c r="CG59" t="inlineStr"/>
+      <c r="CH59" t="inlineStr"/>
+      <c r="CI59" t="inlineStr"/>
+      <c r="CJ59" t="inlineStr"/>
+      <c r="CK59" t="inlineStr"/>
+      <c r="CL59" t="inlineStr"/>
+      <c r="CM59" t="inlineStr"/>
+      <c r="CN59" t="inlineStr"/>
+      <c r="CO59" t="inlineStr"/>
+      <c r="CP59" t="inlineStr"/>
+      <c r="CQ59" t="inlineStr"/>
+      <c r="CR59" t="inlineStr"/>
+      <c r="CS59" t="inlineStr"/>
+      <c r="CT59" t="inlineStr"/>
+      <c r="CU59" t="inlineStr"/>
+      <c r="CV59" t="inlineStr"/>
+      <c r="CW59" t="inlineStr"/>
+      <c r="CX59" t="inlineStr"/>
+      <c r="CY59" t="inlineStr"/>
+      <c r="CZ59" t="inlineStr"/>
+      <c r="DA59" t="inlineStr"/>
+      <c r="DB59" t="inlineStr"/>
+      <c r="DC59" t="inlineStr"/>
+      <c r="DD59" t="inlineStr"/>
+      <c r="DE59" t="inlineStr"/>
+      <c r="DF59" t="inlineStr"/>
+      <c r="DG59" t="inlineStr"/>
+      <c r="DH59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Logit_splashing</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>{'estimator': StatsModelsEstimator(model_class=&lt;class 'statsmodels.discrete.discrete_model.Logit'&gt;), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'sign_sedimentation_Stk', 'particle_liquid_density_ratio', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0.7866666666666666</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.836734693877551</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.8765432098765433</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.7710437710437711</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.8604651162790697</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.7708333333333334</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.8131868131868132</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.9022569444444445</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>0.0, 0.00415349006652832, 0.00912928581237793, 0.004217624664306641, 0.005815267562866211, 0.007185220718383789, 0.004125356674194336</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>0.004946606499808175</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0.004217624664306641</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.002660950078103845</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>0.026595115661621094, 0.012632131576538086, 0.009029865264892578, 0.013502836227416992, 0.009662866592407227, 0.009221792221069336, 0.012566566467285156</t>
+        </is>
+      </c>
+      <c r="T60" t="n">
+        <v>0.01331588200160435</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0.01256656646728516</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0.005680518324840078</v>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.6981132075471698, 0.8301886792452831, 0.7547169811320755, 0.7924528301886793, 0.7735849056603774, 0.7358490566037735</t>
+        </is>
+      </c>
+      <c r="X60" t="n">
+        <v>0.7819706498951782</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0.7735849056603774</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0.05835693062027481</v>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>0.9166666666666667, 0.75, 0.8656716417910447, 0.7936507936507937, 0.819672131147541, 0.8125, 0.7999999999999999</t>
+        </is>
+      </c>
+      <c r="AB60" t="n">
+        <v>0.8225944618937209</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.0499054289258703</v>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>0.8918918918918919, 0.8275862068965517, 0.8787878787878788, 0.8620689655172413, 0.9259259259259259, 0.8666666666666667, 0.7777777777777778</t>
+        </is>
+      </c>
+      <c r="AF60" t="n">
+        <v>0.8615293304948477</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>0.04401266989323341</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.6857142857142857, 0.8529411764705882, 0.7352941176470589, 0.7352941176470589, 0.7647058823529411, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="AJ60" t="n">
+        <v>0.7914765906362545</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>0.08100848875408138</v>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>0.9533834586466166, 0.8190476190476191, 0.9040247678018576, 0.8993808049535603, 0.9179566563467492, 0.8080495356037152, 0.8622291021671827</t>
+        </is>
+      </c>
+      <c r="AN60" t="n">
+        <v>0.8805817063667573</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>0.8993808049535603</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>0.04925754914855442</v>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>0.7704402515723271, 0.7931034482758621, 0.7962382445141066, 0.7931034482758621, 0.7931034482758621, 0.7931034482758621, 0.8119122257053292</t>
+        </is>
+      </c>
+      <c r="AR60" t="n">
+        <v>0.7930006449850302</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>0.7931034482758621</v>
+      </c>
+      <c r="AT60" t="n">
+        <v>0.01119402621971342</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>0.8142493638676844, 0.8333333333333334, 0.8354430379746836, 0.8333333333333333, 0.83248730964467, 0.8341708542713568, 0.8492462311557789</t>
+        </is>
+      </c>
+      <c r="AV60" t="n">
+        <v>0.833180494797263</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>0.009434910412352306</v>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>0.851063829787234, 0.8638743455497382, 0.873015873015873, 0.868421052631579, 0.8723404255319149, 0.8645833333333334, 0.8802083333333334</t>
+        </is>
+      </c>
+      <c r="AZ60" t="n">
+        <v>0.8676438847404293</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>0.868421052631579</v>
+      </c>
+      <c r="BB60" t="n">
+        <v>0.008517710412420229</v>
+      </c>
+      <c r="BC60" t="inlineStr">
+        <is>
+          <t>0.7804878048780488, 0.8048780487804879, 0.8009708737864077, 0.8009708737864077, 0.7961165048543689, 0.8058252427184466, 0.8203883495145631</t>
+        </is>
+      </c>
+      <c r="BD60" t="n">
+        <v>0.801376814045533</v>
+      </c>
+      <c r="BE60" t="n">
+        <v>0.8009708737864077</v>
+      </c>
+      <c r="BF60" t="n">
+        <v>0.01107014501770598</v>
+      </c>
+      <c r="BG60" t="inlineStr">
+        <is>
+          <t>0.8888625080941075, 0.9075738125802311, 0.8931824039865969, 0.8986381991580032, 0.8930535269353038, 0.9099149411461466, 0.9015594123206461</t>
+        </is>
+      </c>
+      <c r="BH60" t="n">
+        <v>0.8989692577458621</v>
+      </c>
+      <c r="BI60" t="n">
+        <v>0.8986381991580032</v>
+      </c>
+      <c r="BJ60" t="n">
+        <v>0.007283001593575346</v>
+      </c>
+      <c r="BK60" t="n">
+        <v>0.7645211930926217</v>
+      </c>
+      <c r="BL60" t="n">
+        <v>0.7604166666666666</v>
+      </c>
+      <c r="BM60" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BN60" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BO60" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="BP60" t="n">
+        <v>0.7587673196368849</v>
+      </c>
+      <c r="BQ60" t="n">
+        <v>0.7711309523809524</v>
+      </c>
+      <c r="BR60" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="BS60" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="BT60" t="n">
+        <v>0.7043478260869566</v>
+      </c>
+      <c r="BU60" t="inlineStr">
+        <is>
+          <t>0.8661654135338346, 0.7039682539682539, 0.8212074303405572, 0.7623839009287926, 0.8150154798761611, 0.7770897832817337, 0.7012383900928792</t>
+        </is>
+      </c>
+      <c r="BV60" t="n">
+        <v>0.7781526645746017</v>
+      </c>
+      <c r="BW60" t="n">
+        <v>0.7770897832817337</v>
+      </c>
+      <c r="BX60" t="n">
+        <v>0.05685538045414647</v>
+      </c>
+      <c r="BY60" t="inlineStr">
+        <is>
+          <t>0.8333333333333333, 0.619047619047619, 0.7692307692307692, 0.6976744186046512, 0.7555555555555555, 0.7142857142857143, 0.6111111111111113</t>
+        </is>
+      </c>
+      <c r="BZ60" t="n">
+        <v>0.7143197887383934</v>
+      </c>
+      <c r="CA60" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CB60" t="n">
+        <v>0.07453255760672911</v>
+      </c>
+      <c r="CC60" t="inlineStr">
+        <is>
+          <t>0.875, 0.6845238095238095, 0.8174512055109069, 0.7456626061277225, 0.7876138433515483, 0.7633928571428572, 0.7055555555555556</t>
+        </is>
+      </c>
+      <c r="CD60" t="n">
+        <v>0.7684571253160571</v>
+      </c>
+      <c r="CE60" t="n">
+        <v>0.7633928571428572</v>
+      </c>
+      <c r="CF60" t="n">
+        <v>0.06055154802943036</v>
+      </c>
+      <c r="CG60" t="inlineStr">
+        <is>
+          <t>0.8823529411764706, 0.5416666666666666, 0.75, 0.625, 0.6538461538461539, 0.6521739130434783, 0.6470588235294118</t>
+        </is>
+      </c>
+      <c r="CH60" t="n">
+        <v>0.6788712140374544</v>
+      </c>
+      <c r="CI60" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="CJ60" t="n">
+        <v>0.1003866387672127</v>
+      </c>
+      <c r="CK60" t="inlineStr">
+        <is>
+          <t>0.7894736842105263, 0.7222222222222222, 0.7894736842105263, 0.7894736842105263, 0.8947368421052632, 0.7894736842105263, 0.5789473684210527</t>
+        </is>
+      </c>
+      <c r="CL60" t="n">
+        <v>0.764828738512949</v>
+      </c>
+      <c r="CM60" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="CN60" t="n">
+        <v>0.08918104198792963</v>
+      </c>
+      <c r="CO60" t="inlineStr">
+        <is>
+          <t>0.7663500971292898, 0.7884039366709457, 0.7942907466277171, 0.7898659678666552, 0.7918635621616977, 0.7878683735716127, 0.8084242632528568</t>
+        </is>
+      </c>
+      <c r="CP60" t="n">
+        <v>0.7895809924686821</v>
+      </c>
+      <c r="CQ60" t="n">
+        <v>0.7898659678666552</v>
+      </c>
+      <c r="CR60" t="n">
+        <v>0.0115048747157305</v>
+      </c>
+      <c r="CS60" t="inlineStr">
+        <is>
+          <t>0.6995884773662552, 0.7272727272727273, 0.7325102880658437, 0.7272727272727273, 0.7295081967213114, 0.725, 0.7499999999999999</t>
+        </is>
+      </c>
+      <c r="CT60" t="n">
+        <v>0.7273074880998377</v>
+      </c>
+      <c r="CU60" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="CV60" t="n">
+        <v>0.01373490244529015</v>
+      </c>
+      <c r="CW60" t="inlineStr">
+        <is>
+          <t>0.7569189206169697, 0.7803030303030303, 0.7839766630202636, 0.7803030303030303, 0.7809977531829907, 0.7795854271356784, 0.7996231155778895</t>
+        </is>
+      </c>
+      <c r="CX60" t="n">
+        <v>0.7802439914485504</v>
+      </c>
+      <c r="CY60" t="n">
+        <v>0.7803030303030303</v>
+      </c>
+      <c r="CZ60" t="n">
+        <v>0.01155453561692818</v>
+      </c>
+      <c r="DA60" t="inlineStr">
+        <is>
+          <t>0.6538461538461539, 0.6875, 0.6846153846153846, 0.6821705426356589, 0.6793893129770993, 0.6850393700787402, 0.7086614173228346</t>
+        </is>
+      </c>
+      <c r="DB60" t="n">
+        <v>0.6830317402108387</v>
+      </c>
+      <c r="DC60" t="n">
+        <v>0.6846153846153846</v>
+      </c>
+      <c r="DD60" t="n">
+        <v>0.01487659518727417</v>
+      </c>
+      <c r="DE60" t="inlineStr">
+        <is>
+          <t>0.7522123893805309, 0.7719298245614035, 0.7876106194690266, 0.7787610619469026, 0.7876106194690266, 0.7699115044247787, 0.7964601769911505</t>
+        </is>
+      </c>
+      <c r="DF60" t="n">
+        <v>0.7777851708918313</v>
+      </c>
+      <c r="DG60" t="n">
+        <v>0.7787610619469026</v>
+      </c>
+      <c r="DH60" t="n">
+        <v>0.01359114183238239</v>
       </c>
     </row>
   </sheetData>

--- a/results/metrics_modelling3.xlsx
+++ b/results/metrics_modelling3.xlsx
@@ -14583,211 +14583,211 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DecisionStump_splashing_greater_or_equal_kl</t>
+          <t>AdaBoostClassifier_splashing_Stk_diam</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>{'estimator': DecisionStumpEstimator(less_sign=False), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'inclination', 'Re', 'We'), 'log_features': (), 'minmax_features': (), 'passthrough_features': ('K', 'relative_roughness'), 'std_features': (), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': AdaBoostClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8780487804878049</v>
+        <v>0.84</v>
       </c>
       <c r="G52" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="H52" t="n">
-        <v>0.8089887640449439</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7824074074074074</v>
+        <v>0.8815586419753086</v>
       </c>
       <c r="J52" t="n">
-        <v>0.7744107744107744</v>
+        <v>0.9629629629629629</v>
       </c>
       <c r="K52" t="n">
-        <v>0.8930817610062893</v>
+        <v>0.9593908629441624</v>
       </c>
       <c r="L52" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.984375</v>
       </c>
       <c r="M52" t="n">
-        <v>0.8091168091168093</v>
+        <v>0.9717223650385605</v>
       </c>
       <c r="N52" t="n">
-        <v>0.7888392857142857</v>
+        <v>0.9953621031746032</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>0.0009999275207519531, 0.0009720325469970703, 0.001028299331665039, 0.001001119613647461, 0.0009963512420654297, 0.0009982585906982422, 0.0010044574737548828</t>
+          <t>0.04229545593261719, 0.04643964767456055, 0.04575991630554199, 0.04851102828979492, 0.04134535789489746, 0.04512667655944824, 0.040598392486572266</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0.001000063759940011</v>
+        <v>0.04429663930620466</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.0009999275207519531</v>
+        <v>0.04512667655944824</v>
       </c>
       <c r="R52" t="n">
-        <v>1.521501112110338e-05</v>
+        <v>0.002714393570599508</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>0.00299835205078125, 0.003001689910888672, 0.004131317138671875, 0.00299835205078125, 0.0030028820037841797, 0.004002094268798828, 0.0029954910278320312</t>
+          <t>0.01538991928100586, 0.015076637268066406, 0.010388374328613281, 0.01736736297607422, 0.013797998428344727, 0.012734413146972656, 0.014501333236694336</t>
         </is>
       </c>
       <c r="T52" t="n">
-        <v>0.003304311207362584</v>
+        <v>0.01417943409511021</v>
       </c>
       <c r="U52" t="n">
-        <v>0.003001689910888672</v>
+        <v>0.01450133323669434</v>
       </c>
       <c r="V52" t="n">
-        <v>0.000483421014286239</v>
+        <v>0.002040394583262948</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>0.8888888888888888, 0.7169811320754716, 0.7735849056603774, 0.7924528301886793, 0.7547169811320755, 0.7735849056603774, 0.7169811320754716</t>
+          <t>0.8888888888888888, 0.8113207547169812, 0.9056603773584906, 0.7924528301886793, 0.9245283018867925, 0.8113207547169812, 0.8301886792452831</t>
         </is>
       </c>
       <c r="X52" t="n">
-        <v>0.773884396525906</v>
+        <v>0.852051512428871</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.7735849056603774</v>
+        <v>0.8301886792452831</v>
       </c>
       <c r="Z52" t="n">
-        <v>0.05400311129267731</v>
+        <v>0.04903608490660909</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>0.9117647058823529, 0.7619047619047619, 0.8000000000000002, 0.8358208955223881, 0.7719298245614036, 0.8000000000000002, 0.7692307692307693</t>
+          <t>0.9210526315789475, 0.8571428571428571, 0.9315068493150686, 0.8405797101449276, 0.9411764705882353, 0.84375, 0.8656716417910447</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>0.8072358510145251</v>
+        <v>0.8858400229372974</v>
       </c>
       <c r="AC52" t="n">
-        <v>0.8000000000000002</v>
+        <v>0.8656716417910447</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.04868838338201792</v>
+        <v>0.04042252933524638</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>0.9393939393939394, 0.8571428571428571, 0.9230769230769231, 0.8484848484848485, 0.9565217391304348, 0.9230769230769231, 0.8064516129032258</t>
+          <t>0.8536585365853658, 0.8571428571428571, 0.8717948717948718, 0.8285714285714286, 0.9411764705882353, 0.9, 0.8787878787878788</t>
         </is>
       </c>
       <c r="AF52" t="n">
-        <v>0.8934498347441646</v>
+        <v>0.8758760062100911</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.8717948717948718</v>
       </c>
       <c r="AH52" t="n">
-        <v>0.05175932188844546</v>
+        <v>0.03370782503572691</v>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>0.8857142857142857, 0.6857142857142857, 0.7058823529411765, 0.8235294117647058, 0.6470588235294118, 0.7058823529411765, 0.7352941176470589</t>
+          <t>1.0, 0.8571428571428571, 1.0, 0.8529411764705882, 0.9411764705882353, 0.7941176470588235, 0.8529411764705882</t>
         </is>
       </c>
       <c r="AJ52" t="n">
-        <v>0.7412965186074428</v>
+        <v>0.8997599039615846</v>
       </c>
       <c r="AK52" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AL52" t="n">
-        <v>0.07758241980271595</v>
+        <v>0.07480638944209077</v>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>0.8902255639097744, 0.7317460317460317, 0.8003095975232198, 0.780185758513932, 0.7972136222910217, 0.8003095975232198, 0.7097523219814242</t>
+          <t>0.9353383458646617, 0.8714285714285714, 0.9226006191950464, 0.9009287925696594, 0.9411764705882353, 0.836687306501548, 0.8978328173374613</t>
         </is>
       </c>
       <c r="AN52" t="n">
-        <v>0.7871060704983749</v>
+        <v>0.9008561319264548</v>
       </c>
       <c r="AO52" t="n">
-        <v>0.7972136222910217</v>
+        <v>0.9009287925696594</v>
       </c>
       <c r="AP52" t="n">
-        <v>0.05369315704565144</v>
+        <v>0.03439339782656949</v>
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>0.7547169811320755, 0.7836990595611285, 0.774294670846395, 0.7711598746081505, 0.7774294670846394, 0.774294670846395, 0.7836990595611285</t>
+          <t>0.9276729559748428, 0.9247648902821317, 0.9278996865203761, 0.9247648902821317, 0.9153605015673981, 0.9498432601880877, 0.9310344827586207</t>
         </is>
       </c>
       <c r="AR52" t="n">
-        <v>0.7741848262342733</v>
+        <v>0.9287629525105128</v>
       </c>
       <c r="AS52" t="n">
-        <v>0.774294670846395</v>
+        <v>0.9276729559748428</v>
       </c>
       <c r="AT52" t="n">
-        <v>0.009100552752323209</v>
+        <v>0.009732619941746736</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>0.7903225806451611, 0.8169761273209549, 0.8105263157894737, 0.804289544235925, 0.814621409921671, 0.8105263157894737, 0.8160000000000001</t>
+          <t>0.9440389294403893, 0.9411764705882352, 0.943765281173594, 0.9423076923076923, 0.9346246973365618, 0.9611650485436893, 0.9473684210526316</t>
         </is>
       </c>
       <c r="AV52" t="n">
-        <v>0.8090374705289513</v>
+        <v>0.9449209343489706</v>
       </c>
       <c r="AW52" t="n">
-        <v>0.8105263157894737</v>
+        <v>0.943765281173594</v>
       </c>
       <c r="AX52" t="n">
-        <v>0.008618109631169334</v>
+        <v>0.007548296340363749</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>0.8802395209580839, 0.8953488372093024, 0.8850574712643678, 0.8982035928143712, 0.8813559322033898, 0.8850574712643678, 0.9053254437869822</t>
+          <t>0.941747572815534, 0.9458128078817734, 0.9507389162561576, 0.9333333333333333, 0.9323671497584541, 0.9611650485436893, 0.9339622641509434</t>
         </is>
       </c>
       <c r="AZ52" t="n">
-        <v>0.8900840385001236</v>
+        <v>0.9427324418199835</v>
       </c>
       <c r="BA52" t="n">
-        <v>0.8850574712643678</v>
+        <v>0.941747572815534</v>
       </c>
       <c r="BB52" t="n">
-        <v>0.008860609656082421</v>
+        <v>0.009906864732307152</v>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>0.7170731707317073, 0.751219512195122, 0.7475728155339806, 0.7281553398058253, 0.7572815533980582, 0.7475728155339806, 0.7427184466019418</t>
+          <t>0.9463414634146341, 0.9365853658536586, 0.9368932038834952, 0.9514563106796117, 0.9368932038834952, 0.9611650485436893, 0.9611650485436893</t>
         </is>
       </c>
       <c r="BD52" t="n">
-        <v>0.7416562362572309</v>
+        <v>0.9472142349717533</v>
       </c>
       <c r="BE52" t="n">
-        <v>0.7475728155339806</v>
+        <v>0.9463414634146341</v>
       </c>
       <c r="BF52" t="n">
-        <v>0.01305673449402361</v>
+        <v>0.0102401699157158</v>
       </c>
       <c r="BG52" t="inlineStr">
         <is>
-          <t>0.7700410101446147, 0.7966623876765083, 0.7852908325457513, 0.7888564309648596, 0.7857204227167283, 0.7852908325457513, 0.8005627631239797</t>
+          <t>0.9849341679257501, 0.9855370132648695, 0.9842984792507947, 0.9883366268579775, 0.9821934874130079, 0.9935991064524444, 0.9862960735458373</t>
         </is>
       </c>
       <c r="BH52" t="n">
-        <v>0.7874892399597417</v>
+        <v>0.986456422101526</v>
       </c>
       <c r="BI52" t="n">
-        <v>0.7857204227167283</v>
+        <v>0.9855370132648695</v>
       </c>
       <c r="BJ52" t="n">
-        <v>0.009056712480178981</v>
+        <v>0.00339265427510108</v>
       </c>
       <c r="BK52" t="inlineStr"/>
       <c r="BL52" t="inlineStr"/>
@@ -14853,211 +14853,211 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DecisionStump_no_fragmentation_less_kl</t>
+          <t>AdaBoostClassifier_no_fragmentation_Stk_diam</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{'estimator': DecisionStumpEstimator(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'inclination', 'Re', 'We'), 'log_features': (), 'minmax_features': (), 'passthrough_features': ('K', 'relative_roughness'), 'std_features': (), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': AdaBoostClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="F53" t="n">
-        <v>0.5</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="G53" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H53" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.761904761904762</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7863636363636364</v>
+        <v>0.8945454545454545</v>
       </c>
       <c r="J53" t="n">
-        <v>0.7407407407407407</v>
+        <v>0.9764309764309764</v>
       </c>
       <c r="K53" t="n">
-        <v>0.5073529411764706</v>
+        <v>0.9615384615384616</v>
       </c>
       <c r="L53" t="n">
-        <v>0.8734177215189873</v>
+        <v>0.9493670886075949</v>
       </c>
       <c r="M53" t="n">
-        <v>0.641860465116279</v>
+        <v>0.9554140127388535</v>
       </c>
       <c r="N53" t="n">
-        <v>0.7830391359888513</v>
+        <v>0.9983451399372896</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>0.0009992122650146484, 0.0, 0.001001119613647461, 0.0009984970092773438, 0.0010001659393310547, 0.0010004043579101562, 0.001001596450805664</t>
+          <t>0.04655003547668457, 0.043056488037109375, 0.04389595985412598, 0.0430448055267334, 0.042558908462524414, 0.04320216178894043, 0.043022871017456055</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0.0008572850908551897</v>
+        <v>0.04361874716622489</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.001000165939331055</v>
+        <v>0.04305648803710938</v>
       </c>
       <c r="R53" t="n">
-        <v>0.0003499865417194363</v>
+        <v>0.001251668155833141</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>0.0030050277709960938, 0.003998279571533203, 0.0040051937103271484, 0.003999471664428711, 0.004006385803222656, 0.002999544143676758, 0.0030057430267333984</t>
+          <t>0.011513233184814453, 0.012504100799560547, 0.012018680572509766, 0.010513067245483398, 0.012743234634399414, 0.012613534927368164, 0.010503053665161133</t>
         </is>
       </c>
       <c r="T53" t="n">
-        <v>0.003574235098702567</v>
+        <v>0.01177270071847098</v>
       </c>
       <c r="U53" t="n">
-        <v>0.003998279571533203</v>
+        <v>0.01201868057250977</v>
       </c>
       <c r="V53" t="n">
-        <v>0.0004943349529150095</v>
+        <v>0.0008872424329106799</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>0.7592592592592593, 0.6792452830188679, 0.6792452830188679, 0.6792452830188679, 0.7735849056603774, 0.8113207547169812, 0.7924528301886793</t>
+          <t>0.8518518518518519, 0.7924528301886793, 0.9245283018867925, 0.8113207547169812, 0.9056603773584906, 0.8679245283018868, 0.9056603773584906</t>
         </is>
       </c>
       <c r="X53" t="n">
-        <v>0.7391933712688429</v>
+        <v>0.8656284316661675</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.7592592592592593</v>
+        <v>0.8679245283018868</v>
       </c>
       <c r="Z53" t="n">
-        <v>0.05399162204934726</v>
+        <v>0.04655774709538191</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>0.6486486486486486, 0.5853658536585367, 0.6046511627906977, 0.6046511627906977, 0.6470588235294117, 0.7058823529411764, 0.717948717948718</t>
+          <t>0.7333333333333333, 0.5925925925925927, 0.8461538461538461, 0.6875000000000001, 0.8148148148148148, 0.7407407407407408, 0.8275862068965518</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>0.6448866746154124</v>
+        <v>0.7489602192188399</v>
       </c>
       <c r="AC53" t="n">
-        <v>0.6470588235294117</v>
+        <v>0.7407407407407408</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.04759640829931121</v>
+        <v>0.08324269801375989</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>0.5454545454545454, 0.4444444444444444, 0.4482758620689655, 0.4482758620689655, 0.55, 0.6, 0.56</t>
+          <t>0.7333333333333333, 0.6153846153846154, 0.9166666666666666, 0.6111111111111112, 0.8461538461538461, 0.7692307692307693, 0.8</t>
         </is>
       </c>
       <c r="AF53" t="n">
-        <v>0.5137786734338459</v>
+        <v>0.755982905982906</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="AH53" t="n">
-        <v>0.06008844131041598</v>
+        <v>0.1051066120353698</v>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>0.8, 0.8571428571428571, 0.9285714285714286, 0.9285714285714286, 0.7857142857142857, 0.8571428571428571, 1.0</t>
+          <t>0.7333333333333333, 0.5714285714285714, 0.7857142857142857, 0.7857142857142857, 0.7857142857142857, 0.7142857142857143, 0.8571428571428571</t>
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>0.8795918367346938</v>
+        <v>0.7476190476190475</v>
       </c>
       <c r="AK53" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="AL53" t="n">
-        <v>0.07116569703739875</v>
+        <v>0.08341589690323446</v>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>0.7717948717948718, 0.7362637362637363, 0.7591575091575091, 0.7591575091575091, 0.7774725274725274, 0.8260073260073261, 0.858974358974359</t>
+          <t>0.876923076923077, 0.8699633699633699, 0.9725274725274725, 0.8965201465201466, 0.946886446886447, 0.9120879120879121, 0.9413919413919414</t>
         </is>
       </c>
       <c r="AN53" t="n">
-        <v>0.7841182626896911</v>
+        <v>0.9166143380429095</v>
       </c>
       <c r="AO53" t="n">
-        <v>0.7717948717948718</v>
+        <v>0.9120879120879121</v>
       </c>
       <c r="AP53" t="n">
-        <v>0.03980361553852785</v>
+        <v>0.03552178990496289</v>
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>0.7358490566037735, 0.7492163009404389, 0.7492163009404389, 0.7492163009404389, 0.7335423197492164, 0.7272727272727273, 0.7304075235109718</t>
+          <t>0.9842767295597484, 0.9843260188087775, 0.9686520376175548, 0.9749216300940439, 0.9749216300940439, 0.9811912225705329, 0.9749216300940439</t>
         </is>
       </c>
       <c r="AR53" t="n">
-        <v>0.7392457899940009</v>
+        <v>0.9776015569769635</v>
       </c>
       <c r="AS53" t="n">
-        <v>0.7358490566037735</v>
+        <v>0.9749216300940439</v>
       </c>
       <c r="AT53" t="n">
-        <v>0.008974327046072948</v>
+        <v>0.005402406025743921</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>0.6410256410256411, 0.6521739130434783, 0.6491228070175439, 0.6491228070175439, 0.6413502109704642, 0.6329113924050632, 0.6293103448275862</t>
+          <t>0.970059880239521, 0.9710982658959537, 0.941860465116279, 0.9523809523809523, 0.9534883720930232, 0.9651162790697674, 0.9534883720930232</t>
         </is>
       </c>
       <c r="AV53" t="n">
-        <v>0.6421453023296173</v>
+        <v>0.9582132266983601</v>
       </c>
       <c r="AW53" t="n">
-        <v>0.6413502109704642</v>
+        <v>0.9534883720930232</v>
       </c>
       <c r="AX53" t="n">
-        <v>0.008016333455327197</v>
+        <v>0.01000068786525098</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>0.5, 0.5172413793103449, 0.5174825174825175, 0.5174825174825175, 0.5, 0.4934210526315789, 0.4965986394557823</t>
+          <t>0.9759036144578314, 0.9545454545454546, 0.9310344827586207, 0.963855421686747, 0.9425287356321839, 0.9540229885057471, 0.9425287356321839</t>
         </is>
       </c>
       <c r="AZ53" t="n">
-        <v>0.506032300908963</v>
+        <v>0.9520599190312525</v>
       </c>
       <c r="BA53" t="n">
-        <v>0.5</v>
+        <v>0.9540229885057471</v>
       </c>
       <c r="BB53" t="n">
-        <v>0.0100617608357479</v>
+        <v>0.01384321962691562</v>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>0.8928571428571429, 0.8823529411764706, 0.8705882352941177, 0.8705882352941177, 0.8941176470588236, 0.8823529411764706, 0.8588235294117647</t>
+          <t>0.9642857142857143, 0.9882352941176471, 0.9529411764705882, 0.9411764705882353, 0.9647058823529412, 0.9764705882352941, 0.9647058823529412</t>
         </is>
       </c>
       <c r="BD53" t="n">
-        <v>0.8788115246098439</v>
+        <v>0.9646458583433375</v>
       </c>
       <c r="BE53" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.9647058823529412</v>
       </c>
       <c r="BF53" t="n">
-        <v>0.01190081008855812</v>
+        <v>0.01406228169870084</v>
       </c>
       <c r="BG53" t="inlineStr">
         <is>
-          <t>0.7861721611721613, 0.7916038210155857, 0.7878582202111614, 0.7878582202111614, 0.7846656611362495, 0.7766465560583209, 0.7712921065862243</t>
+          <t>0.9983465608465608, 0.998340874811463, 0.9959276018099548, 0.998265460030166, 0.9964303670186023, 0.9974358974358974, 0.9966817496229261</t>
         </is>
       </c>
       <c r="BH53" t="n">
-        <v>0.7837281066272662</v>
+        <v>0.9973469302250815</v>
       </c>
       <c r="BI53" t="n">
-        <v>0.7861721611721613</v>
+        <v>0.9974358974358974</v>
       </c>
       <c r="BJ53" t="n">
-        <v>0.006631067788558371</v>
+        <v>0.000936242175825913</v>
       </c>
       <c r="BK53" t="inlineStr"/>
       <c r="BL53" t="inlineStr"/>
@@ -15123,211 +15123,211 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AdaBoostClassifier_splashing_Stk_diam</t>
+          <t>RandomForestClassifier_splashing_Stk_diam</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{'estimator': AdaBoostClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': RandomForestClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="F54" t="n">
-        <v>0.84</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="G54" t="n">
-        <v>0.875</v>
+        <v>0.9583333333333334</v>
       </c>
       <c r="H54" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.9019607843137256</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8815586419753086</v>
+        <v>0.9540895061728395</v>
       </c>
       <c r="J54" t="n">
-        <v>0.9629629629629629</v>
+        <v>0.9966329966329966</v>
       </c>
       <c r="K54" t="n">
-        <v>0.9593908629441624</v>
+        <v>0.9948186528497409</v>
       </c>
       <c r="L54" t="n">
-        <v>0.984375</v>
+        <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>0.9717223650385605</v>
+        <v>0.9974025974025974</v>
       </c>
       <c r="N54" t="n">
-        <v>0.9953621031746032</v>
+        <v>0.9999751984126984</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>0.04229545593261719, 0.04643964767456055, 0.04575991630554199, 0.04851102828979492, 0.04134535789489746, 0.04512667655944824, 0.040598392486572266</t>
+          <t>0.08300065994262695, 0.08986687660217285, 0.08384990692138672, 0.0838019847869873, 0.08411645889282227, 0.08526420593261719, 0.08512067794799805</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0.04429663930620466</v>
+        <v>0.08500296728951591</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.04512667655944824</v>
+        <v>0.08411645889282227</v>
       </c>
       <c r="R54" t="n">
-        <v>0.002714393570599508</v>
+        <v>0.002114803410730603</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>0.01538991928100586, 0.015076637268066406, 0.010388374328613281, 0.01736736297607422, 0.013797998428344727, 0.012734413146972656, 0.014501333236694336</t>
+          <t>0.01667308807373047, 0.014289140701293945, 0.012070417404174805, 0.012803792953491211, 0.011937856674194336, 0.012521743774414062, 0.01160287857055664</t>
         </is>
       </c>
       <c r="T54" t="n">
-        <v>0.01417943409511021</v>
+        <v>0.0131284168788365</v>
       </c>
       <c r="U54" t="n">
-        <v>0.01450133323669434</v>
+        <v>0.01252174377441406</v>
       </c>
       <c r="V54" t="n">
-        <v>0.002040394583262948</v>
+        <v>0.00165828957663176</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>0.8888888888888888, 0.8113207547169812, 0.9056603773584906, 0.7924528301886793, 0.9245283018867925, 0.8113207547169812, 0.8301886792452831</t>
+          <t>0.9444444444444444, 0.9056603773584906, 0.9056603773584906, 0.8490566037735849, 0.9245283018867925, 0.8490566037735849, 0.8113207547169812</t>
         </is>
       </c>
       <c r="X54" t="n">
-        <v>0.852051512428871</v>
+        <v>0.8842467804731956</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.8301886792452831</v>
+        <v>0.9056603773584906</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.04903608490660909</v>
+        <v>0.04465478103184949</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>0.9210526315789475, 0.8571428571428571, 0.9315068493150686, 0.8405797101449276, 0.9411764705882353, 0.84375, 0.8656716417910447</t>
+          <t>0.958904109589041, 0.9275362318840579, 0.9295774647887325, 0.8787878787878787, 0.9411764705882353, 0.8709677419354839, 0.861111111111111</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>0.8858400229372974</v>
+        <v>0.9097230012406486</v>
       </c>
       <c r="AC54" t="n">
-        <v>0.8656716417910447</v>
+        <v>0.9275362318840579</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.04042252933524638</v>
+        <v>0.03574049493633244</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>0.8536585365853658, 0.8571428571428571, 0.8717948717948718, 0.8285714285714286, 0.9411764705882353, 0.9, 0.8787878787878788</t>
+          <t>0.9210526315789473, 0.9411764705882353, 0.8918918918918919, 0.90625, 0.9411764705882353, 0.9642857142857143, 0.8157894736842105</t>
         </is>
       </c>
       <c r="AF54" t="n">
-        <v>0.8758760062100911</v>
+        <v>0.9116603789453193</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.8717948717948718</v>
+        <v>0.9210526315789473</v>
       </c>
       <c r="AH54" t="n">
-        <v>0.03370782503572691</v>
+        <v>0.04505763835239565</v>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>1.0, 0.8571428571428571, 1.0, 0.8529411764705882, 0.9411764705882353, 0.7941176470588235, 0.8529411764705882</t>
+          <t>1.0, 0.9142857142857143, 0.9705882352941176, 0.8529411764705882, 0.9411764705882353, 0.7941176470588235, 0.9117647058823529</t>
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>0.8997599039615846</v>
+        <v>0.912124849939976</v>
       </c>
       <c r="AK54" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.9142857142857143</v>
       </c>
       <c r="AL54" t="n">
-        <v>0.07480638944209077</v>
+        <v>0.06482637499291748</v>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>0.9353383458646617, 0.8714285714285714, 0.9226006191950464, 0.9009287925696594, 0.9411764705882353, 0.836687306501548, 0.8978328173374613</t>
+          <t>0.9962406015037594, 0.9531746031746031, 0.9876160990712075, 0.9210526315789473, 0.9396284829721362, 0.93343653250774, 0.9303405572755418</t>
         </is>
       </c>
       <c r="AN54" t="n">
-        <v>0.9008561319264548</v>
+        <v>0.9516413582977049</v>
       </c>
       <c r="AO54" t="n">
-        <v>0.9009287925696594</v>
+        <v>0.9396284829721362</v>
       </c>
       <c r="AP54" t="n">
-        <v>0.03439339782656949</v>
+        <v>0.02712601410933079</v>
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>0.9276729559748428, 0.9247648902821317, 0.9278996865203761, 0.9247648902821317, 0.9153605015673981, 0.9498432601880877, 0.9310344827586207</t>
+          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
         </is>
       </c>
       <c r="AR54" t="n">
-        <v>0.9287629525105128</v>
+        <v>0.9977594515655674</v>
       </c>
       <c r="AS54" t="n">
-        <v>0.9276729559748428</v>
+        <v>0.9968652037617555</v>
       </c>
       <c r="AT54" t="n">
-        <v>0.009732619941746736</v>
+        <v>0.001417051170840857</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>0.9440389294403893, 0.9411764705882352, 0.943765281173594, 0.9423076923076923, 0.9346246973365618, 0.9611650485436893, 0.9473684210526316</t>
+          <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
         </is>
       </c>
       <c r="AV54" t="n">
-        <v>0.9449209343489706</v>
+        <v>0.9982688114216364</v>
       </c>
       <c r="AW54" t="n">
-        <v>0.943765281173594</v>
+        <v>0.9975786924939467</v>
       </c>
       <c r="AX54" t="n">
-        <v>0.007548296340363749</v>
+        <v>0.001094907038779773</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>0.941747572815534, 0.9458128078817734, 0.9507389162561576, 0.9333333333333333, 0.9323671497584541, 0.9611650485436893, 0.9339622641509434</t>
+          <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
         </is>
       </c>
       <c r="AZ54" t="n">
-        <v>0.9427324418199835</v>
+        <v>0.9965459942243395</v>
       </c>
       <c r="BA54" t="n">
-        <v>0.941747572815534</v>
+        <v>0.9951690821256038</v>
       </c>
       <c r="BB54" t="n">
-        <v>0.009906864732307152</v>
+        <v>0.002184519446236978</v>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>0.9463414634146341, 0.9365853658536586, 0.9368932038834952, 0.9514563106796117, 0.9368932038834952, 0.9611650485436893, 0.9611650485436893</t>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
         </is>
       </c>
       <c r="BD54" t="n">
-        <v>0.9472142349717533</v>
+        <v>1</v>
       </c>
       <c r="BE54" t="n">
-        <v>0.9463414634146341</v>
+        <v>1</v>
       </c>
       <c r="BF54" t="n">
-        <v>0.0102401699157158</v>
+        <v>0</v>
       </c>
       <c r="BG54" t="inlineStr">
         <is>
-          <t>0.9849341679257501, 0.9855370132648695, 0.9842984792507947, 0.9883366268579775, 0.9821934874130079, 0.9935991064524444, 0.9862960735458373</t>
+          <t>0.9999784157133607, 0.9999999999999999, 0.9999785204914512, 0.9999785204914511, 0.9999785204914512, 1.0, 0.9999785204914512</t>
         </is>
       </c>
       <c r="BH54" t="n">
-        <v>0.986456422101526</v>
+        <v>0.999984642525595</v>
       </c>
       <c r="BI54" t="n">
-        <v>0.9855370132648695</v>
+        <v>0.9999785204914512</v>
       </c>
       <c r="BJ54" t="n">
-        <v>0.00339265427510108</v>
+        <v>9.712984233428587e-06</v>
       </c>
       <c r="BK54" t="inlineStr"/>
       <c r="BL54" t="inlineStr"/>
@@ -15393,211 +15393,211 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AdaBoostClassifier_no_fragmentation_Stk_diam</t>
+          <t>RandomForestClassifier_no_fragmentation_Stk_diam</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>{'estimator': AdaBoostClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': RandomForestClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9466666666666667</v>
       </c>
       <c r="F55" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.9</v>
       </c>
       <c r="G55" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H55" t="n">
-        <v>0.761904761904762</v>
+        <v>0.9</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8945454545454545</v>
+        <v>0.9836363636363636</v>
       </c>
       <c r="J55" t="n">
-        <v>0.9764309764309764</v>
+        <v>1</v>
       </c>
       <c r="K55" t="n">
-        <v>0.9615384615384616</v>
+        <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>0.9493670886075949</v>
+        <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>0.9554140127388535</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>0.9983451399372896</v>
+        <v>1</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>0.04655003547668457, 0.043056488037109375, 0.04389595985412598, 0.0430448055267334, 0.042558908462524414, 0.04320216178894043, 0.043022871017456055</t>
+          <t>0.07860326766967773, 0.07773756980895996, 0.07647180557250977, 0.08232712745666504, 0.08237171173095703, 0.0821986198425293, 0.07474780082702637</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0.04361874716622489</v>
+        <v>0.07920827184404645</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.04305648803710938</v>
+        <v>0.07860326766967773</v>
       </c>
       <c r="R55" t="n">
-        <v>0.001251668155833141</v>
+        <v>0.002893091210809317</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>0.011513233184814453, 0.012504100799560547, 0.012018680572509766, 0.010513067245483398, 0.012743234634399414, 0.012613534927368164, 0.010503053665161133</t>
+          <t>0.009609460830688477, 0.012346744537353516, 0.01396632194519043, 0.009385347366333008, 0.011641263961791992, 0.011887550354003906, 0.013554096221923828</t>
         </is>
       </c>
       <c r="T55" t="n">
-        <v>0.01177270071847098</v>
+        <v>0.01177011217389788</v>
       </c>
       <c r="U55" t="n">
-        <v>0.01201868057250977</v>
+        <v>0.01188755035400391</v>
       </c>
       <c r="V55" t="n">
-        <v>0.0008872424329106799</v>
+        <v>0.001635514437545498</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>0.8518518518518519, 0.7924528301886793, 0.9245283018867925, 0.8113207547169812, 0.9056603773584906, 0.8679245283018868, 0.9056603773584906</t>
+          <t>0.8333333333333334, 0.7924528301886793, 0.9056603773584906, 0.8113207547169812, 0.9433962264150944, 0.9433962264150944, 0.9433962264150944</t>
         </is>
       </c>
       <c r="X55" t="n">
-        <v>0.8656284316661675</v>
+        <v>0.8818508535489668</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.8679245283018868</v>
+        <v>0.9056603773584906</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.04655774709538191</v>
+        <v>0.06239373065756213</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>0.7333333333333333, 0.5925925925925927, 0.8461538461538461, 0.6875000000000001, 0.8148148148148148, 0.7407407407407408, 0.8275862068965518</t>
+          <t>0.6666666666666665, 0.6206896551724138, 0.8148148148148148, 0.6428571428571429, 0.88, 0.888888888888889, 0.896551724137931</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>0.7489602192188399</v>
+        <v>0.7729241275054084</v>
       </c>
       <c r="AC55" t="n">
-        <v>0.7407407407407408</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.08324269801375989</v>
+        <v>0.1154711366108976</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>0.7333333333333333, 0.6153846153846154, 0.9166666666666666, 0.6111111111111112, 0.8461538461538461, 0.7692307692307693, 0.8</t>
+          <t>0.75, 0.6, 0.8461538461538461, 0.6428571428571429, 1.0, 0.9230769230769231, 0.8666666666666667</t>
         </is>
       </c>
       <c r="AF55" t="n">
-        <v>0.755982905982906</v>
+        <v>0.8041077969649398</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="AH55" t="n">
-        <v>0.1051066120353698</v>
+        <v>0.1356457100227356</v>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>0.7333333333333333, 0.5714285714285714, 0.7857142857142857, 0.7857142857142857, 0.7857142857142857, 0.7142857142857143, 0.8571428571428571</t>
+          <t>0.6, 0.6428571428571429, 0.7857142857142857, 0.6428571428571429, 0.7857142857142857, 0.8571428571428571, 0.9285714285714286</t>
         </is>
       </c>
       <c r="AJ55" t="n">
-        <v>0.7476190476190475</v>
+        <v>0.7489795918367347</v>
       </c>
       <c r="AK55" t="n">
         <v>0.7857142857142857</v>
       </c>
       <c r="AL55" t="n">
-        <v>0.08341589690323446</v>
+        <v>0.1142492653247217</v>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>0.876923076923077, 0.8699633699633699, 0.9725274725274725, 0.8965201465201466, 0.946886446886447, 0.9120879120879121, 0.9413919413919414</t>
+          <t>0.9521367521367521, 0.8589743589743589, 0.9752747252747253, 0.9175824175824177, 0.9908424908424909, 0.9093406593406593, 0.9871794871794871</t>
         </is>
       </c>
       <c r="AN55" t="n">
-        <v>0.9166143380429095</v>
+        <v>0.941618698761556</v>
       </c>
       <c r="AO55" t="n">
-        <v>0.9120879120879121</v>
+        <v>0.9521367521367521</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.03552178990496289</v>
+        <v>0.04502670042190914</v>
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>0.9842767295597484, 0.9843260188087775, 0.9686520376175548, 0.9749216300940439, 0.9749216300940439, 0.9811912225705329, 0.9749216300940439</t>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
         </is>
       </c>
       <c r="AR55" t="n">
-        <v>0.9776015569769635</v>
+        <v>1</v>
       </c>
       <c r="AS55" t="n">
-        <v>0.9749216300940439</v>
+        <v>1</v>
       </c>
       <c r="AT55" t="n">
-        <v>0.005402406025743921</v>
+        <v>0</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>0.970059880239521, 0.9710982658959537, 0.941860465116279, 0.9523809523809523, 0.9534883720930232, 0.9651162790697674, 0.9534883720930232</t>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
         </is>
       </c>
       <c r="AV55" t="n">
-        <v>0.9582132266983601</v>
+        <v>1</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.9534883720930232</v>
+        <v>1</v>
       </c>
       <c r="AX55" t="n">
-        <v>0.01000068786525098</v>
+        <v>0</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>0.9759036144578314, 0.9545454545454546, 0.9310344827586207, 0.963855421686747, 0.9425287356321839, 0.9540229885057471, 0.9425287356321839</t>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
         </is>
       </c>
       <c r="AZ55" t="n">
-        <v>0.9520599190312525</v>
+        <v>1</v>
       </c>
       <c r="BA55" t="n">
-        <v>0.9540229885057471</v>
+        <v>1</v>
       </c>
       <c r="BB55" t="n">
-        <v>0.01384321962691562</v>
+        <v>0</v>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>0.9642857142857143, 0.9882352941176471, 0.9529411764705882, 0.9411764705882353, 0.9647058823529412, 0.9764705882352941, 0.9647058823529412</t>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
         </is>
       </c>
       <c r="BD55" t="n">
-        <v>0.9646458583433375</v>
+        <v>1</v>
       </c>
       <c r="BE55" t="n">
-        <v>0.9647058823529412</v>
+        <v>1</v>
       </c>
       <c r="BF55" t="n">
-        <v>0.01406228169870084</v>
+        <v>0</v>
       </c>
       <c r="BG55" t="inlineStr">
         <is>
-          <t>0.9983465608465608, 0.998340874811463, 0.9959276018099548, 0.998265460030166, 0.9964303670186023, 0.9974358974358974, 0.9966817496229261</t>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
         </is>
       </c>
       <c r="BH55" t="n">
-        <v>0.9973469302250815</v>
+        <v>1</v>
       </c>
       <c r="BI55" t="n">
-        <v>0.9974358974358974</v>
+        <v>1</v>
       </c>
       <c r="BJ55" t="n">
-        <v>0.000936242175825913</v>
+        <v>0</v>
       </c>
       <c r="BK55" t="inlineStr"/>
       <c r="BL55" t="inlineStr"/>
@@ -15663,28 +15663,28 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RandomForestClassifier_splashing_Stk_diam</t>
+          <t>LGBMClassifier_splashing_Stk_diam</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>{'estimator': RandomForestClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': LGBMClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.88</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8518518518518519</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="G56" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.9375</v>
       </c>
       <c r="H56" t="n">
-        <v>0.9019607843137256</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="I56" t="n">
-        <v>0.9540895061728395</v>
+        <v>0.9517746913580247</v>
       </c>
       <c r="J56" t="n">
         <v>0.9966329966329966</v>
@@ -15703,101 +15703,101 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>0.08300065994262695, 0.08986687660217285, 0.08384990692138672, 0.0838019847869873, 0.08411645889282227, 0.08526420593261719, 0.08512067794799805</t>
+          <t>0.13146328926086426, 0.01901865005493164, 0.020598173141479492, 0.01701521873474121, 0.0210115909576416, 0.022017240524291992, 0.018513917922973633</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0.08500296728951591</v>
+        <v>0.03566258294241769</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.08411645889282227</v>
+        <v>0.02059817314147949</v>
       </c>
       <c r="R56" t="n">
-        <v>0.002114803410730603</v>
+        <v>0.03914146525364429</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>0.01667308807373047, 0.014289140701293945, 0.012070417404174805, 0.012803792953491211, 0.011937856674194336, 0.012521743774414062, 0.01160287857055664</t>
+          <t>0.011510848999023438, 0.010015487670898438, 0.011011838912963867, 0.009507179260253906, 0.008506298065185547, 0.010508298873901367, 0.01151418685913086</t>
         </is>
       </c>
       <c r="T56" t="n">
-        <v>0.0131284168788365</v>
+        <v>0.01036773409162249</v>
       </c>
       <c r="U56" t="n">
-        <v>0.01252174377441406</v>
+        <v>0.01050829887390137</v>
       </c>
       <c r="V56" t="n">
-        <v>0.00165828957663176</v>
+        <v>0.00102715079973434</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>0.9444444444444444, 0.9056603773584906, 0.9056603773584906, 0.8490566037735849, 0.9245283018867925, 0.8490566037735849, 0.8113207547169812</t>
+          <t>0.9629629629629629, 0.8490566037735849, 0.9433962264150944, 0.8490566037735849, 0.9056603773584906, 0.8679245283018868, 0.8867924528301887</t>
         </is>
       </c>
       <c r="X56" t="n">
-        <v>0.8842467804731956</v>
+        <v>0.8949785364879705</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.9056603773584906</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.04465478103184949</v>
+        <v>0.04157065551294201</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>0.958904109589041, 0.9275362318840579, 0.9295774647887325, 0.8787878787878787, 0.9411764705882353, 0.8709677419354839, 0.861111111111111</t>
+          <t>0.9722222222222222, 0.888888888888889, 0.9565217391304348, 0.8823529411764706, 0.9253731343283583, 0.8923076923076922, 0.9142857142857143</t>
         </is>
       </c>
       <c r="AB56" t="n">
-        <v>0.9097230012406486</v>
+        <v>0.9188503331913973</v>
       </c>
       <c r="AC56" t="n">
-        <v>0.9275362318840579</v>
+        <v>0.9142857142857143</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.03574049493633244</v>
+        <v>0.03221653434902594</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>0.9210526315789473, 0.9411764705882353, 0.8918918918918919, 0.90625, 0.9411764705882353, 0.9642857142857143, 0.8157894736842105</t>
+          <t>0.9459459459459459, 0.8648648648648649, 0.9428571428571428, 0.8823529411764706, 0.9393939393939394, 0.9354838709677419, 0.8888888888888888</t>
         </is>
       </c>
       <c r="AF56" t="n">
-        <v>0.9116603789453193</v>
+        <v>0.9142553705849993</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.9210526315789473</v>
+        <v>0.9354838709677419</v>
       </c>
       <c r="AH56" t="n">
-        <v>0.04505763835239565</v>
+        <v>0.03163541475077126</v>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>1.0, 0.9142857142857143, 0.9705882352941176, 0.8529411764705882, 0.9411764705882353, 0.7941176470588235, 0.9117647058823529</t>
+          <t>1.0, 0.9142857142857143, 0.9705882352941176, 0.8823529411764706, 0.9117647058823529, 0.8529411764705882, 0.9411764705882353</t>
         </is>
       </c>
       <c r="AJ56" t="n">
-        <v>0.912124849939976</v>
+        <v>0.9247298919567827</v>
       </c>
       <c r="AK56" t="n">
         <v>0.9142857142857143</v>
       </c>
       <c r="AL56" t="n">
-        <v>0.06482637499291748</v>
+        <v>0.04669914237959417</v>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>0.9962406015037594, 0.9531746031746031, 0.9876160990712075, 0.9210526315789473, 0.9396284829721362, 0.93343653250774, 0.9303405572755418</t>
+          <t>0.9954887218045113, 0.9523809523809523, 0.9845201238390093, 0.9458204334365325, 0.9427244582043344, 0.9202786377708978, 0.9256965944272446</t>
         </is>
       </c>
       <c r="AN56" t="n">
-        <v>0.9516413582977049</v>
+        <v>0.9524157031233546</v>
       </c>
       <c r="AO56" t="n">
-        <v>0.9396284829721362</v>
+        <v>0.9458204334365325</v>
       </c>
       <c r="AP56" t="n">
-        <v>0.02712601410933079</v>
+        <v>0.02610445918315244</v>
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
       </c>
       <c r="BG56" t="inlineStr">
         <is>
-          <t>0.9999784157133607, 0.9999999999999999, 0.9999785204914512, 0.9999785204914511, 0.9999785204914512, 1.0, 0.9999785204914512</t>
+          <t>0.9999784157133607, 1.0, 0.9999785204914512, 0.9999785204914512, 0.9999785204914511, 1.0, 0.9999785204914511</t>
         </is>
       </c>
       <c r="BH56" t="n">
@@ -15867,7 +15867,7 @@
         <v>0.9999785204914512</v>
       </c>
       <c r="BJ56" t="n">
-        <v>9.712984233428587e-06</v>
+        <v>9.712984233463661e-06</v>
       </c>
       <c r="BK56" t="inlineStr"/>
       <c r="BL56" t="inlineStr"/>
@@ -15933,28 +15933,28 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>RandomForestClassifier_no_fragmentation_Stk_diam</t>
+          <t>LGBMClassifier_no_fragmentation_Stk_diam</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{'estimator': RandomForestClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': LGBMClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G57" t="n">
         <v>0.9</v>
       </c>
       <c r="H57" t="n">
-        <v>0.9</v>
+        <v>0.8780487804878048</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9836363636363636</v>
+        <v>0.9854545454545455</v>
       </c>
       <c r="J57" t="n">
         <v>1</v>
@@ -15973,101 +15973,101 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>0.07860326766967773, 0.07773756980895996, 0.07647180557250977, 0.08232712745666504, 0.08237171173095703, 0.0821986198425293, 0.07474780082702637</t>
+          <t>0.019602537155151367, 0.014482259750366211, 0.02073359489440918, 0.01558375358581543, 0.014885902404785156, 0.013393163681030273, 0.015613317489624023</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0.07920827184404645</v>
+        <v>0.01632778985159738</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.07860326766967773</v>
+        <v>0.01558375358581543</v>
       </c>
       <c r="R57" t="n">
-        <v>0.002893091210809317</v>
+        <v>0.002543793573807909</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>0.009609460830688477, 0.012346744537353516, 0.01396632194519043, 0.009385347366333008, 0.011641263961791992, 0.011887550354003906, 0.013554096221923828</t>
+          <t>0.009006738662719727, 0.006963491439819336, 0.007121086120605469, 0.00627446174621582, 0.012955904006958008, 0.0137939453125, 0.010265588760375977</t>
         </is>
       </c>
       <c r="T57" t="n">
-        <v>0.01177011217389788</v>
+        <v>0.009483030864170619</v>
       </c>
       <c r="U57" t="n">
-        <v>0.01188755035400391</v>
+        <v>0.009006738662719727</v>
       </c>
       <c r="V57" t="n">
-        <v>0.001635514437545498</v>
+        <v>0.002769885506555768</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>0.8333333333333334, 0.7924528301886793, 0.9056603773584906, 0.8113207547169812, 0.9433962264150944, 0.9433962264150944, 0.9433962264150944</t>
+          <t>0.8518518518518519, 0.9056603773584906, 0.9433962264150944, 0.8867924528301887, 0.9245283018867925, 0.9245283018867925, 0.9433962264150944</t>
         </is>
       </c>
       <c r="X57" t="n">
-        <v>0.8818508535489668</v>
+        <v>0.9114505340920437</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.9056603773584906</v>
+        <v>0.9245283018867925</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.06239373065756213</v>
+        <v>0.03065163791537664</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>0.6666666666666665, 0.6206896551724138, 0.8148148148148148, 0.6428571428571429, 0.88, 0.888888888888889, 0.896551724137931</t>
+          <t>0.6666666666666667, 0.8275862068965518, 0.88, 0.7999999999999999, 0.8461538461538461, 0.8571428571428571, 0.896551724137931</t>
         </is>
       </c>
       <c r="AB57" t="n">
-        <v>0.7729241275054084</v>
+        <v>0.8248716144282646</v>
       </c>
       <c r="AC57" t="n">
-        <v>0.8148148148148148</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.1154711366108976</v>
+        <v>0.07103954153456497</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>0.75, 0.6, 0.8461538461538461, 0.6428571428571429, 1.0, 0.9230769230769231, 0.8666666666666667</t>
+          <t>0.8888888888888888, 0.8, 1.0, 0.75, 0.9166666666666666, 0.8571428571428571, 0.8666666666666667</t>
         </is>
       </c>
       <c r="AF57" t="n">
-        <v>0.8041077969649398</v>
+        <v>0.8684807256235827</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="AH57" t="n">
-        <v>0.1356457100227356</v>
+        <v>0.07454129035294924</v>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>0.6, 0.6428571428571429, 0.7857142857142857, 0.6428571428571429, 0.7857142857142857, 0.8571428571428571, 0.9285714285714286</t>
+          <t>0.5333333333333333, 0.8571428571428571, 0.7857142857142857, 0.8571428571428571, 0.7857142857142857, 0.8571428571428571, 0.9285714285714286</t>
         </is>
       </c>
       <c r="AJ57" t="n">
-        <v>0.7489795918367347</v>
+        <v>0.8006802721088435</v>
       </c>
       <c r="AK57" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AL57" t="n">
-        <v>0.1142492653247217</v>
+        <v>0.1182265172078387</v>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>0.9521367521367521, 0.8589743589743589, 0.9752747252747253, 0.9175824175824177, 0.9908424908424909, 0.9093406593406593, 0.9871794871794871</t>
+          <t>0.958974358974359, 0.9322344322344323, 0.990842490842491, 0.9377289377289377, 0.9816849816849818, 0.9139194139194139, 0.9816849816849818</t>
         </is>
       </c>
       <c r="AN57" t="n">
-        <v>0.941618698761556</v>
+        <v>0.9567242281527996</v>
       </c>
       <c r="AO57" t="n">
-        <v>0.9521367521367521</v>
+        <v>0.958974358974359</v>
       </c>
       <c r="AP57" t="n">
-        <v>0.04502670042190914</v>
+        <v>0.02727641748426234</v>
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
@@ -16203,262 +16203,382 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LGBMClassifier_splashing_Stk_diam</t>
+          <t>Logit_splashing</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>{'estimator': LGBMClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': StatsModelsEstimator(model_class=&lt;class 'statsmodels.discrete.discrete_model.Logit'&gt;), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'sign_sedimentation_Stk', 'particle_liquid_density_ratio', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.88</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="F58" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.82</v>
       </c>
       <c r="G58" t="n">
-        <v>0.9375</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="H58" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.836734693877551</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9517746913580247</v>
+        <v>0.8765432098765433</v>
       </c>
       <c r="J58" t="n">
-        <v>0.9966329966329966</v>
+        <v>0.7710437710437711</v>
       </c>
       <c r="K58" t="n">
-        <v>0.9948186528497409</v>
+        <v>0.8604651162790697</v>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="M58" t="n">
-        <v>0.9974025974025974</v>
+        <v>0.8131868131868132</v>
       </c>
       <c r="N58" t="n">
-        <v>0.9999751984126984</v>
+        <v>0.9022569444444445</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>0.13146328926086426, 0.01901865005493164, 0.020598173141479492, 0.01701521873474121, 0.0210115909576416, 0.022017240524291992, 0.018513917922973633</t>
+          <t>0.0, 0.00415349006652832, 0.00912928581237793, 0.004217624664306641, 0.005815267562866211, 0.007185220718383789, 0.004125356674194336</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0.03566258294241769</v>
+        <v>0.004946606499808175</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.02059817314147949</v>
+        <v>0.004217624664306641</v>
       </c>
       <c r="R58" t="n">
-        <v>0.03914146525364429</v>
+        <v>0.002660950078103845</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>0.011510848999023438, 0.010015487670898438, 0.011011838912963867, 0.009507179260253906, 0.008506298065185547, 0.010508298873901367, 0.01151418685913086</t>
+          <t>0.026595115661621094, 0.012632131576538086, 0.009029865264892578, 0.013502836227416992, 0.009662866592407227, 0.009221792221069336, 0.012566566467285156</t>
         </is>
       </c>
       <c r="T58" t="n">
-        <v>0.01036773409162249</v>
+        <v>0.01331588200160435</v>
       </c>
       <c r="U58" t="n">
-        <v>0.01050829887390137</v>
+        <v>0.01256656646728516</v>
       </c>
       <c r="V58" t="n">
-        <v>0.00102715079973434</v>
+        <v>0.005680518324840078</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>0.9629629629629629, 0.8490566037735849, 0.9433962264150944, 0.8490566037735849, 0.9056603773584906, 0.8679245283018868, 0.8867924528301887</t>
+          <t>0.8888888888888888, 0.6981132075471698, 0.8301886792452831, 0.7547169811320755, 0.7924528301886793, 0.7735849056603774, 0.7358490566037735</t>
         </is>
       </c>
       <c r="X58" t="n">
-        <v>0.8949785364879705</v>
+        <v>0.7819706498951782</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.8867924528301887</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.04157065551294201</v>
+        <v>0.05835693062027481</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>0.9722222222222222, 0.888888888888889, 0.9565217391304348, 0.8823529411764706, 0.9253731343283583, 0.8923076923076922, 0.9142857142857143</t>
+          <t>0.9166666666666667, 0.75, 0.8656716417910447, 0.7936507936507937, 0.819672131147541, 0.8125, 0.7999999999999999</t>
         </is>
       </c>
       <c r="AB58" t="n">
-        <v>0.9188503331913973</v>
+        <v>0.8225944618937209</v>
       </c>
       <c r="AC58" t="n">
-        <v>0.9142857142857143</v>
+        <v>0.8125</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.03221653434902594</v>
+        <v>0.0499054289258703</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>0.9459459459459459, 0.8648648648648649, 0.9428571428571428, 0.8823529411764706, 0.9393939393939394, 0.9354838709677419, 0.8888888888888888</t>
+          <t>0.8918918918918919, 0.8275862068965517, 0.8787878787878788, 0.8620689655172413, 0.9259259259259259, 0.8666666666666667, 0.7777777777777778</t>
         </is>
       </c>
       <c r="AF58" t="n">
-        <v>0.9142553705849993</v>
+        <v>0.8615293304948477</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.9354838709677419</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="AH58" t="n">
-        <v>0.03163541475077126</v>
+        <v>0.04401266989323341</v>
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>1.0, 0.9142857142857143, 0.9705882352941176, 0.8823529411764706, 0.9117647058823529, 0.8529411764705882, 0.9411764705882353</t>
+          <t>0.9428571428571428, 0.6857142857142857, 0.8529411764705882, 0.7352941176470589, 0.7352941176470589, 0.7647058823529411, 0.8235294117647058</t>
         </is>
       </c>
       <c r="AJ58" t="n">
-        <v>0.9247298919567827</v>
+        <v>0.7914765906362545</v>
       </c>
       <c r="AK58" t="n">
-        <v>0.9142857142857143</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="AL58" t="n">
-        <v>0.04669914237959417</v>
+        <v>0.08100848875408138</v>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>0.9954887218045113, 0.9523809523809523, 0.9845201238390093, 0.9458204334365325, 0.9427244582043344, 0.9202786377708978, 0.9256965944272446</t>
+          <t>0.9533834586466166, 0.8190476190476191, 0.9040247678018576, 0.8993808049535603, 0.9179566563467492, 0.8080495356037152, 0.8622291021671827</t>
         </is>
       </c>
       <c r="AN58" t="n">
-        <v>0.9524157031233546</v>
+        <v>0.8805817063667573</v>
       </c>
       <c r="AO58" t="n">
-        <v>0.9458204334365325</v>
+        <v>0.8993808049535603</v>
       </c>
       <c r="AP58" t="n">
-        <v>0.02610445918315244</v>
+        <v>0.04925754914855442</v>
       </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+          <t>0.7704402515723271, 0.7931034482758621, 0.7962382445141066, 0.7931034482758621, 0.7931034482758621, 0.7931034482758621, 0.8119122257053292</t>
         </is>
       </c>
       <c r="AR58" t="n">
-        <v>0.9977594515655674</v>
+        <v>0.7930006449850302</v>
       </c>
       <c r="AS58" t="n">
-        <v>0.9968652037617555</v>
+        <v>0.7931034482758621</v>
       </c>
       <c r="AT58" t="n">
-        <v>0.001417051170840857</v>
+        <v>0.01119402621971342</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+          <t>0.8142493638676844, 0.8333333333333334, 0.8354430379746836, 0.8333333333333333, 0.83248730964467, 0.8341708542713568, 0.8492462311557789</t>
         </is>
       </c>
       <c r="AV58" t="n">
-        <v>0.9982688114216364</v>
+        <v>0.833180494797263</v>
       </c>
       <c r="AW58" t="n">
-        <v>0.9975786924939467</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AX58" t="n">
-        <v>0.001094907038779773</v>
+        <v>0.009434910412352306</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+          <t>0.851063829787234, 0.8638743455497382, 0.873015873015873, 0.868421052631579, 0.8723404255319149, 0.8645833333333334, 0.8802083333333334</t>
         </is>
       </c>
       <c r="AZ58" t="n">
-        <v>0.9965459942243395</v>
+        <v>0.8676438847404293</v>
       </c>
       <c r="BA58" t="n">
-        <v>0.9951690821256038</v>
+        <v>0.868421052631579</v>
       </c>
       <c r="BB58" t="n">
-        <v>0.002184519446236978</v>
+        <v>0.008517710412420229</v>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+          <t>0.7804878048780488, 0.8048780487804879, 0.8009708737864077, 0.8009708737864077, 0.7961165048543689, 0.8058252427184466, 0.8203883495145631</t>
         </is>
       </c>
       <c r="BD58" t="n">
-        <v>1</v>
+        <v>0.801376814045533</v>
       </c>
       <c r="BE58" t="n">
-        <v>1</v>
+        <v>0.8009708737864077</v>
       </c>
       <c r="BF58" t="n">
-        <v>0</v>
+        <v>0.01107014501770598</v>
       </c>
       <c r="BG58" t="inlineStr">
         <is>
-          <t>0.9999784157133607, 1.0, 0.9999785204914512, 0.9999785204914512, 0.9999785204914511, 1.0, 0.9999785204914511</t>
+          <t>0.8888625080941075, 0.9075738125802311, 0.8931824039865969, 0.8986381991580032, 0.8930535269353038, 0.9099149411461466, 0.9015594123206461</t>
         </is>
       </c>
       <c r="BH58" t="n">
-        <v>0.999984642525595</v>
+        <v>0.8989692577458621</v>
       </c>
       <c r="BI58" t="n">
-        <v>0.9999785204914512</v>
+        <v>0.8986381991580032</v>
       </c>
       <c r="BJ58" t="n">
-        <v>9.712984233463661e-06</v>
-      </c>
-      <c r="BK58" t="inlineStr"/>
-      <c r="BL58" t="inlineStr"/>
-      <c r="BM58" t="inlineStr"/>
-      <c r="BN58" t="inlineStr"/>
-      <c r="BO58" t="inlineStr"/>
-      <c r="BP58" t="inlineStr"/>
-      <c r="BQ58" t="inlineStr"/>
-      <c r="BR58" t="inlineStr"/>
-      <c r="BS58" t="inlineStr"/>
-      <c r="BT58" t="inlineStr"/>
-      <c r="BU58" t="inlineStr"/>
-      <c r="BV58" t="inlineStr"/>
-      <c r="BW58" t="inlineStr"/>
-      <c r="BX58" t="inlineStr"/>
-      <c r="BY58" t="inlineStr"/>
-      <c r="BZ58" t="inlineStr"/>
-      <c r="CA58" t="inlineStr"/>
-      <c r="CB58" t="inlineStr"/>
-      <c r="CC58" t="inlineStr"/>
-      <c r="CD58" t="inlineStr"/>
-      <c r="CE58" t="inlineStr"/>
-      <c r="CF58" t="inlineStr"/>
-      <c r="CG58" t="inlineStr"/>
-      <c r="CH58" t="inlineStr"/>
-      <c r="CI58" t="inlineStr"/>
-      <c r="CJ58" t="inlineStr"/>
-      <c r="CK58" t="inlineStr"/>
-      <c r="CL58" t="inlineStr"/>
-      <c r="CM58" t="inlineStr"/>
-      <c r="CN58" t="inlineStr"/>
-      <c r="CO58" t="inlineStr"/>
-      <c r="CP58" t="inlineStr"/>
-      <c r="CQ58" t="inlineStr"/>
-      <c r="CR58" t="inlineStr"/>
-      <c r="CS58" t="inlineStr"/>
-      <c r="CT58" t="inlineStr"/>
-      <c r="CU58" t="inlineStr"/>
-      <c r="CV58" t="inlineStr"/>
-      <c r="CW58" t="inlineStr"/>
-      <c r="CX58" t="inlineStr"/>
-      <c r="CY58" t="inlineStr"/>
-      <c r="CZ58" t="inlineStr"/>
-      <c r="DA58" t="inlineStr"/>
-      <c r="DB58" t="inlineStr"/>
-      <c r="DC58" t="inlineStr"/>
-      <c r="DD58" t="inlineStr"/>
-      <c r="DE58" t="inlineStr"/>
-      <c r="DF58" t="inlineStr"/>
-      <c r="DG58" t="inlineStr"/>
-      <c r="DH58" t="inlineStr"/>
+        <v>0.007283001593575346</v>
+      </c>
+      <c r="BK58" t="n">
+        <v>0.7645211930926217</v>
+      </c>
+      <c r="BL58" t="n">
+        <v>0.7604166666666666</v>
+      </c>
+      <c r="BM58" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BN58" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BO58" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="BP58" t="n">
+        <v>0.7587673196368849</v>
+      </c>
+      <c r="BQ58" t="n">
+        <v>0.7711309523809524</v>
+      </c>
+      <c r="BR58" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="BS58" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="BT58" t="n">
+        <v>0.7043478260869566</v>
+      </c>
+      <c r="BU58" t="inlineStr">
+        <is>
+          <t>0.8661654135338346, 0.7039682539682539, 0.8212074303405572, 0.7623839009287926, 0.8150154798761611, 0.7770897832817337, 0.7012383900928792</t>
+        </is>
+      </c>
+      <c r="BV58" t="n">
+        <v>0.7781526645746017</v>
+      </c>
+      <c r="BW58" t="n">
+        <v>0.7770897832817337</v>
+      </c>
+      <c r="BX58" t="n">
+        <v>0.05685538045414647</v>
+      </c>
+      <c r="BY58" t="inlineStr">
+        <is>
+          <t>0.8333333333333333, 0.619047619047619, 0.7692307692307692, 0.6976744186046512, 0.7555555555555555, 0.7142857142857143, 0.6111111111111113</t>
+        </is>
+      </c>
+      <c r="BZ58" t="n">
+        <v>0.7143197887383934</v>
+      </c>
+      <c r="CA58" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CB58" t="n">
+        <v>0.07453255760672911</v>
+      </c>
+      <c r="CC58" t="inlineStr">
+        <is>
+          <t>0.875, 0.6845238095238095, 0.8174512055109069, 0.7456626061277225, 0.7876138433515483, 0.7633928571428572, 0.7055555555555556</t>
+        </is>
+      </c>
+      <c r="CD58" t="n">
+        <v>0.7684571253160571</v>
+      </c>
+      <c r="CE58" t="n">
+        <v>0.7633928571428572</v>
+      </c>
+      <c r="CF58" t="n">
+        <v>0.06055154802943036</v>
+      </c>
+      <c r="CG58" t="inlineStr">
+        <is>
+          <t>0.8823529411764706, 0.5416666666666666, 0.75, 0.625, 0.6538461538461539, 0.6521739130434783, 0.6470588235294118</t>
+        </is>
+      </c>
+      <c r="CH58" t="n">
+        <v>0.6788712140374544</v>
+      </c>
+      <c r="CI58" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="CJ58" t="n">
+        <v>0.1003866387672127</v>
+      </c>
+      <c r="CK58" t="inlineStr">
+        <is>
+          <t>0.7894736842105263, 0.7222222222222222, 0.7894736842105263, 0.7894736842105263, 0.8947368421052632, 0.7894736842105263, 0.5789473684210527</t>
+        </is>
+      </c>
+      <c r="CL58" t="n">
+        <v>0.764828738512949</v>
+      </c>
+      <c r="CM58" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="CN58" t="n">
+        <v>0.08918104198792963</v>
+      </c>
+      <c r="CO58" t="inlineStr">
+        <is>
+          <t>0.7663500971292898, 0.7884039366709457, 0.7942907466277171, 0.7898659678666552, 0.7918635621616977, 0.7878683735716127, 0.8084242632528568</t>
+        </is>
+      </c>
+      <c r="CP58" t="n">
+        <v>0.7895809924686821</v>
+      </c>
+      <c r="CQ58" t="n">
+        <v>0.7898659678666552</v>
+      </c>
+      <c r="CR58" t="n">
+        <v>0.0115048747157305</v>
+      </c>
+      <c r="CS58" t="inlineStr">
+        <is>
+          <t>0.6995884773662552, 0.7272727272727273, 0.7325102880658437, 0.7272727272727273, 0.7295081967213114, 0.725, 0.7499999999999999</t>
+        </is>
+      </c>
+      <c r="CT58" t="n">
+        <v>0.7273074880998377</v>
+      </c>
+      <c r="CU58" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="CV58" t="n">
+        <v>0.01373490244529015</v>
+      </c>
+      <c r="CW58" t="inlineStr">
+        <is>
+          <t>0.7569189206169697, 0.7803030303030303, 0.7839766630202636, 0.7803030303030303, 0.7809977531829907, 0.7795854271356784, 0.7996231155778895</t>
+        </is>
+      </c>
+      <c r="CX58" t="n">
+        <v>0.7802439914485504</v>
+      </c>
+      <c r="CY58" t="n">
+        <v>0.7803030303030303</v>
+      </c>
+      <c r="CZ58" t="n">
+        <v>0.01155453561692818</v>
+      </c>
+      <c r="DA58" t="inlineStr">
+        <is>
+          <t>0.6538461538461539, 0.6875, 0.6846153846153846, 0.6821705426356589, 0.6793893129770993, 0.6850393700787402, 0.7086614173228346</t>
+        </is>
+      </c>
+      <c r="DB58" t="n">
+        <v>0.6830317402108387</v>
+      </c>
+      <c r="DC58" t="n">
+        <v>0.6846153846153846</v>
+      </c>
+      <c r="DD58" t="n">
+        <v>0.01487659518727417</v>
+      </c>
+      <c r="DE58" t="inlineStr">
+        <is>
+          <t>0.7522123893805309, 0.7719298245614035, 0.7876106194690266, 0.7787610619469026, 0.7876106194690266, 0.7699115044247787, 0.7964601769911505</t>
+        </is>
+      </c>
+      <c r="DF58" t="n">
+        <v>0.7777851708918313</v>
+      </c>
+      <c r="DG58" t="n">
+        <v>0.7787610619469026</v>
+      </c>
+      <c r="DH58" t="n">
+        <v>0.01359114183238239</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -16468,267 +16588,387 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>no_fragmentation</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LGBMClassifier_no_fragmentation_Stk_diam</t>
+          <t>DecisionStump_splashing_greater_or_equal_kl</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>{'estimator': LGBMClassifier(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Stk', 'Re', 'We', 'init_volume_fraction', 'sedimentation_Re', 'particle_liquid_density_ratio', 'sign_sedimentation_Re'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': DecisionStumpEstimator(less_sign=False), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'inclination', 'Re', 'We'), 'log_features': (), 'minmax_features': (), 'passthrough_features': ('K', 'relative_roughness'), 'std_features': (), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="F59" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8780487804878049</v>
       </c>
       <c r="G59" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="H59" t="n">
-        <v>0.8780487804878048</v>
+        <v>0.8089887640449439</v>
       </c>
       <c r="I59" t="n">
-        <v>0.9854545454545455</v>
+        <v>0.7824074074074074</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>0.7744107744107744</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>0.8930817610062893</v>
       </c>
       <c r="L59" t="n">
-        <v>1</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="M59" t="n">
-        <v>1</v>
+        <v>0.8091168091168093</v>
       </c>
       <c r="N59" t="n">
-        <v>1</v>
+        <v>0.7888392857142857</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>0.019602537155151367, 0.014482259750366211, 0.02073359489440918, 0.01558375358581543, 0.014885902404785156, 0.013393163681030273, 0.015613317489624023</t>
+          <t>0.0, 0.002619028091430664, 0.0020058155059814453, 0.0, 0.006714582443237305, 0.002017498016357422, 0.0</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0.01632778985159738</v>
+        <v>0.001908132008143834</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.01558375358581543</v>
+        <v>0.002005815505981445</v>
       </c>
       <c r="R59" t="n">
-        <v>0.002543793573807909</v>
+        <v>0.002221702863547117</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>0.009006738662719727, 0.006963491439819336, 0.007121086120605469, 0.00627446174621582, 0.012955904006958008, 0.0137939453125, 0.010265588760375977</t>
+          <t>0.008840560913085938, 0.006383657455444336, 0.0055353641510009766, 0.007167816162109375, 0.005301713943481445, 0.0014159679412841797, 0.009717702865600586</t>
         </is>
       </c>
       <c r="T59" t="n">
-        <v>0.009483030864170619</v>
+        <v>0.006337540490286691</v>
       </c>
       <c r="U59" t="n">
-        <v>0.009006738662719727</v>
+        <v>0.006383657455444336</v>
       </c>
       <c r="V59" t="n">
-        <v>0.002769885506555768</v>
+        <v>0.002516244175512531</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>0.8518518518518519, 0.9056603773584906, 0.9433962264150944, 0.8867924528301887, 0.9245283018867925, 0.9245283018867925, 0.9433962264150944</t>
+          <t>0.8888888888888888, 0.7169811320754716, 0.7735849056603774, 0.7924528301886793, 0.7547169811320755, 0.7735849056603774, 0.7169811320754716</t>
         </is>
       </c>
       <c r="X59" t="n">
-        <v>0.9114505340920437</v>
+        <v>0.773884396525906</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.9245283018867925</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.03065163791537664</v>
+        <v>0.05400311129267731</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>0.6666666666666667, 0.8275862068965518, 0.88, 0.7999999999999999, 0.8461538461538461, 0.8571428571428571, 0.896551724137931</t>
+          <t>0.9117647058823529, 0.7619047619047619, 0.8000000000000002, 0.8358208955223881, 0.7719298245614036, 0.8000000000000002, 0.7692307692307693</t>
         </is>
       </c>
       <c r="AB59" t="n">
-        <v>0.8248716144282646</v>
+        <v>0.8072358510145251</v>
       </c>
       <c r="AC59" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.07103954153456497</v>
+        <v>0.04868838338201792</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>0.8888888888888888, 0.8, 1.0, 0.75, 0.9166666666666666, 0.8571428571428571, 0.8666666666666667</t>
+          <t>0.9393939393939394, 0.8571428571428571, 0.9230769230769231, 0.8484848484848485, 0.9565217391304348, 0.9230769230769231, 0.8064516129032258</t>
         </is>
       </c>
       <c r="AF59" t="n">
-        <v>0.8684807256235827</v>
+        <v>0.8934498347441646</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="AH59" t="n">
-        <v>0.07454129035294924</v>
+        <v>0.05175932188844546</v>
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>0.5333333333333333, 0.8571428571428571, 0.7857142857142857, 0.8571428571428571, 0.7857142857142857, 0.8571428571428571, 0.9285714285714286</t>
+          <t>0.8857142857142857, 0.6857142857142857, 0.7058823529411765, 0.8235294117647058, 0.6470588235294118, 0.7058823529411765, 0.7352941176470589</t>
         </is>
       </c>
       <c r="AJ59" t="n">
-        <v>0.8006802721088435</v>
+        <v>0.7412965186074428</v>
       </c>
       <c r="AK59" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="AL59" t="n">
-        <v>0.1182265172078387</v>
+        <v>0.07758241980271595</v>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>0.958974358974359, 0.9322344322344323, 0.990842490842491, 0.9377289377289377, 0.9816849816849818, 0.9139194139194139, 0.9816849816849818</t>
+          <t>0.8902255639097744, 0.7317460317460317, 0.8003095975232198, 0.780185758513932, 0.7972136222910217, 0.8003095975232198, 0.7097523219814242</t>
         </is>
       </c>
       <c r="AN59" t="n">
-        <v>0.9567242281527996</v>
+        <v>0.7871060704983749</v>
       </c>
       <c r="AO59" t="n">
-        <v>0.958974358974359</v>
+        <v>0.7972136222910217</v>
       </c>
       <c r="AP59" t="n">
-        <v>0.02727641748426234</v>
+        <v>0.05369315704565144</v>
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+          <t>0.7547169811320755, 0.7836990595611285, 0.774294670846395, 0.7711598746081505, 0.7774294670846394, 0.774294670846395, 0.7836990595611285</t>
         </is>
       </c>
       <c r="AR59" t="n">
-        <v>1</v>
+        <v>0.7741848262342733</v>
       </c>
       <c r="AS59" t="n">
-        <v>1</v>
+        <v>0.774294670846395</v>
       </c>
       <c r="AT59" t="n">
-        <v>0</v>
+        <v>0.009100552752323209</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+          <t>0.7903225806451611, 0.8169761273209549, 0.8105263157894737, 0.804289544235925, 0.814621409921671, 0.8105263157894737, 0.8160000000000001</t>
         </is>
       </c>
       <c r="AV59" t="n">
-        <v>1</v>
+        <v>0.8090374705289513</v>
       </c>
       <c r="AW59" t="n">
-        <v>1</v>
+        <v>0.8105263157894737</v>
       </c>
       <c r="AX59" t="n">
-        <v>0</v>
+        <v>0.008618109631169334</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+          <t>0.8802395209580839, 0.8953488372093024, 0.8850574712643678, 0.8982035928143712, 0.8813559322033898, 0.8850574712643678, 0.9053254437869822</t>
         </is>
       </c>
       <c r="AZ59" t="n">
-        <v>1</v>
+        <v>0.8900840385001236</v>
       </c>
       <c r="BA59" t="n">
-        <v>1</v>
+        <v>0.8850574712643678</v>
       </c>
       <c r="BB59" t="n">
-        <v>0</v>
+        <v>0.008860609656082421</v>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+          <t>0.7170731707317073, 0.751219512195122, 0.7475728155339806, 0.7281553398058253, 0.7572815533980582, 0.7475728155339806, 0.7427184466019418</t>
         </is>
       </c>
       <c r="BD59" t="n">
-        <v>1</v>
+        <v>0.7416562362572309</v>
       </c>
       <c r="BE59" t="n">
-        <v>1</v>
+        <v>0.7475728155339806</v>
       </c>
       <c r="BF59" t="n">
-        <v>0</v>
+        <v>0.01305673449402361</v>
       </c>
       <c r="BG59" t="inlineStr">
         <is>
-          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+          <t>0.7700410101446147, 0.7966623876765083, 0.7852908325457513, 0.7888564309648596, 0.7857204227167283, 0.7852908325457513, 0.8005627631239797</t>
         </is>
       </c>
       <c r="BH59" t="n">
-        <v>1</v>
+        <v>0.7874892399597417</v>
       </c>
       <c r="BI59" t="n">
-        <v>1</v>
+        <v>0.7857204227167283</v>
       </c>
       <c r="BJ59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK59" t="inlineStr"/>
-      <c r="BL59" t="inlineStr"/>
-      <c r="BM59" t="inlineStr"/>
-      <c r="BN59" t="inlineStr"/>
-      <c r="BO59" t="inlineStr"/>
-      <c r="BP59" t="inlineStr"/>
-      <c r="BQ59" t="inlineStr"/>
-      <c r="BR59" t="inlineStr"/>
-      <c r="BS59" t="inlineStr"/>
-      <c r="BT59" t="inlineStr"/>
-      <c r="BU59" t="inlineStr"/>
-      <c r="BV59" t="inlineStr"/>
-      <c r="BW59" t="inlineStr"/>
-      <c r="BX59" t="inlineStr"/>
-      <c r="BY59" t="inlineStr"/>
-      <c r="BZ59" t="inlineStr"/>
-      <c r="CA59" t="inlineStr"/>
-      <c r="CB59" t="inlineStr"/>
-      <c r="CC59" t="inlineStr"/>
-      <c r="CD59" t="inlineStr"/>
-      <c r="CE59" t="inlineStr"/>
-      <c r="CF59" t="inlineStr"/>
-      <c r="CG59" t="inlineStr"/>
-      <c r="CH59" t="inlineStr"/>
-      <c r="CI59" t="inlineStr"/>
-      <c r="CJ59" t="inlineStr"/>
-      <c r="CK59" t="inlineStr"/>
-      <c r="CL59" t="inlineStr"/>
-      <c r="CM59" t="inlineStr"/>
-      <c r="CN59" t="inlineStr"/>
-      <c r="CO59" t="inlineStr"/>
-      <c r="CP59" t="inlineStr"/>
-      <c r="CQ59" t="inlineStr"/>
-      <c r="CR59" t="inlineStr"/>
-      <c r="CS59" t="inlineStr"/>
-      <c r="CT59" t="inlineStr"/>
-      <c r="CU59" t="inlineStr"/>
-      <c r="CV59" t="inlineStr"/>
-      <c r="CW59" t="inlineStr"/>
-      <c r="CX59" t="inlineStr"/>
-      <c r="CY59" t="inlineStr"/>
-      <c r="CZ59" t="inlineStr"/>
-      <c r="DA59" t="inlineStr"/>
-      <c r="DB59" t="inlineStr"/>
-      <c r="DC59" t="inlineStr"/>
-      <c r="DD59" t="inlineStr"/>
-      <c r="DE59" t="inlineStr"/>
-      <c r="DF59" t="inlineStr"/>
-      <c r="DG59" t="inlineStr"/>
-      <c r="DH59" t="inlineStr"/>
+        <v>0.009056712480178981</v>
+      </c>
+      <c r="BK59" t="n">
+        <v>0.76515011972739</v>
+      </c>
+      <c r="BL59" t="n">
+        <v>0.7824074074074074</v>
+      </c>
+      <c r="BM59" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="BN59" t="n">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="BO59" t="n">
+        <v>0.7213114754098361</v>
+      </c>
+      <c r="BP59" t="n">
+        <v>0.7666983222538779</v>
+      </c>
+      <c r="BQ59" t="n">
+        <v>0.7888392857142857</v>
+      </c>
+      <c r="BR59" t="n">
+        <v>0.6376811594202898</v>
+      </c>
+      <c r="BS59" t="n">
+        <v>0.8380952380952381</v>
+      </c>
+      <c r="BT59" t="n">
+        <v>0.7242798353909465</v>
+      </c>
+      <c r="BU59" t="inlineStr">
+        <is>
+          <t>0.8902255639097745, 0.7317460317460318, 0.8003095975232198, 0.7801857585139318, 0.7972136222910217, 0.8003095975232198, 0.7097523219814241</t>
+        </is>
+      </c>
+      <c r="BV59" t="n">
+        <v>0.7871060704983748</v>
+      </c>
+      <c r="BW59" t="n">
+        <v>0.7972136222910217</v>
+      </c>
+      <c r="BX59" t="n">
+        <v>0.05369315704565149</v>
+      </c>
+      <c r="BY59" t="inlineStr">
+        <is>
+          <t>0.8500000000000001, 0.6511627906976745, 0.7391304347826088, 0.717948717948718, 0.7346938775510204, 0.7391304347826088, 0.6341463414634148</t>
+        </is>
+      </c>
+      <c r="BZ59" t="n">
+        <v>0.7237446567465778</v>
+      </c>
+      <c r="CA59" t="n">
+        <v>0.7346938775510204</v>
+      </c>
+      <c r="CB59" t="n">
+        <v>0.06531606644953722</v>
+      </c>
+      <c r="CC59" t="inlineStr">
+        <is>
+          <t>0.8808823529411764, 0.7065337763012182, 0.7695652173913045, 0.776884806735553, 0.753311851056212, 0.7695652173913045, 0.701688555347092</t>
+        </is>
+      </c>
+      <c r="CD59" t="n">
+        <v>0.7654902538805514</v>
+      </c>
+      <c r="CE59" t="n">
+        <v>0.7695652173913045</v>
+      </c>
+      <c r="CF59" t="n">
+        <v>0.05499768760759623</v>
+      </c>
+      <c r="CG59" t="inlineStr">
+        <is>
+          <t>0.8095238095238095, 0.56, 0.6296296296296297, 0.7, 0.6, 0.6296296296296297, 0.5909090909090909</t>
+        </is>
+      </c>
+      <c r="CH59" t="n">
+        <v>0.6456703085274514</v>
+      </c>
+      <c r="CI59" t="n">
+        <v>0.6296296296296297</v>
+      </c>
+      <c r="CJ59" t="n">
+        <v>0.07813748114929832</v>
+      </c>
+      <c r="CK59" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.7777777777777778, 0.8947368421052632, 0.7368421052631579, 0.9473684210526315, 0.8947368421052632, 0.6842105263157895</t>
+        </is>
+      </c>
+      <c r="CL59" t="n">
+        <v>0.8329156223893065</v>
+      </c>
+      <c r="CM59" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="CN59" t="n">
+        <v>0.0917672062052365</v>
+      </c>
+      <c r="CO59" t="inlineStr">
+        <is>
+          <t>0.7700410101446147, 0.7966623876765083, 0.7852908325457513, 0.7888564309648596, 0.7857204227167283, 0.7852908325457513, 0.8005627631239798</t>
+        </is>
+      </c>
+      <c r="CP59" t="n">
+        <v>0.7874892399597417</v>
+      </c>
+      <c r="CQ59" t="n">
+        <v>0.7857204227167283</v>
+      </c>
+      <c r="CR59" t="n">
+        <v>0.009056712480179004</v>
+      </c>
+      <c r="CS59" t="inlineStr">
+        <is>
+          <t>0.7045454545454545, 0.735632183908046, 0.7209302325581395, 0.7245283018867924, 0.7215686274509804, 0.7209302325581395, 0.7376425855513308</t>
+        </is>
+      </c>
+      <c r="CT59" t="n">
+        <v>0.7236825169226976</v>
+      </c>
+      <c r="CU59" t="n">
+        <v>0.7215686274509804</v>
+      </c>
+      <c r="CV59" t="n">
+        <v>0.01017166395264157</v>
+      </c>
+      <c r="CW59" t="inlineStr">
+        <is>
+          <t>0.7474340175953078, 0.7763041556145005, 0.7657282741738065, 0.7644089230613587, 0.7680950186863257, 0.7657282741738065, 0.7768212927756655</t>
+        </is>
+      </c>
+      <c r="CX59" t="n">
+        <v>0.7663599937258242</v>
+      </c>
+      <c r="CY59" t="n">
+        <v>0.7657282741738065</v>
+      </c>
+      <c r="CZ59" t="n">
+        <v>0.009056432863735135</v>
+      </c>
+      <c r="DA59" t="inlineStr">
+        <is>
+          <t>0.6158940397350994, 0.6530612244897959, 0.6413793103448275, 0.631578947368421, 0.647887323943662, 0.6413793103448275, 0.6466666666666666</t>
+        </is>
+      </c>
+      <c r="DB59" t="n">
+        <v>0.6396924032704714</v>
+      </c>
+      <c r="DC59" t="n">
+        <v>0.6413793103448275</v>
+      </c>
+      <c r="DD59" t="n">
+        <v>0.01154125544139632</v>
+      </c>
+      <c r="DE59" t="inlineStr">
+        <is>
+          <t>0.8230088495575221, 0.8421052631578947, 0.8230088495575221, 0.8495575221238938, 0.8141592920353983, 0.8230088495575221, 0.8584070796460177</t>
+        </is>
+      </c>
+      <c r="DF59" t="n">
+        <v>0.8333222436622529</v>
+      </c>
+      <c r="DG59" t="n">
+        <v>0.8230088495575221</v>
+      </c>
+      <c r="DH59" t="n">
+        <v>0.01538223327391464</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -16738,386 +16978,386 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>no_fragmentation</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Logit_splashing</t>
+          <t>DecisionStump_no_fragmentation_less_kl</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>{'estimator': StatsModelsEstimator(model_class=&lt;class 'statsmodels.discrete.discrete_model.Logit'&gt;), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_droplet_diameter_ratio', 'sedimentation_Re', 'sedimentation_Stk'), 'log_features': ('relative_roughness',), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sign_sedimentation_Re', 'sign_sedimentation_Stk', 'particle_liquid_density_ratio', 'sign_particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
+          <t>{'estimator': DecisionStumpEstimator(), 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'inclination', 'Re', 'We'), 'log_features': (), 'minmax_features': (), 'passthrough_features': ('K', 'relative_roughness'), 'std_features': (), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False}</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="F60" t="n">
-        <v>0.82</v>
+        <v>0.5</v>
       </c>
       <c r="G60" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.9</v>
       </c>
       <c r="H60" t="n">
-        <v>0.836734693877551</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8765432098765433</v>
+        <v>0.7863636363636364</v>
       </c>
       <c r="J60" t="n">
-        <v>0.7710437710437711</v>
+        <v>0.7407407407407407</v>
       </c>
       <c r="K60" t="n">
-        <v>0.8604651162790697</v>
+        <v>0.5073529411764706</v>
       </c>
       <c r="L60" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.8734177215189873</v>
       </c>
       <c r="M60" t="n">
-        <v>0.8131868131868132</v>
+        <v>0.641860465116279</v>
       </c>
       <c r="N60" t="n">
-        <v>0.9022569444444445</v>
+        <v>0.7830391359888513</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>0.0, 0.00415349006652832, 0.00912928581237793, 0.004217624664306641, 0.005815267562866211, 0.007185220718383789, 0.004125356674194336</t>
+          <t>0.0, 0.0031027793884277344, 0.0020055770874023438, 0.0, 0.00501561164855957, 0.0, 0.003765106201171875</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0.004946606499808175</v>
+        <v>0.001984153475080218</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.004217624664306641</v>
+        <v>0.002005577087402344</v>
       </c>
       <c r="R60" t="n">
-        <v>0.002660950078103845</v>
+        <v>0.001905777277248026</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>0.026595115661621094, 0.012632131576538086, 0.009029865264892578, 0.013502836227416992, 0.009662866592407227, 0.009221792221069336, 0.012566566467285156</t>
+          <t>0.0064258575439453125, 0.006303310394287109, 0.0058591365814208984, 0.0053255558013916016, 0.004686117172241211, 0.007936477661132812, 0.0032172203063964844</t>
         </is>
       </c>
       <c r="T60" t="n">
-        <v>0.01331588200160435</v>
+        <v>0.005679096494402204</v>
       </c>
       <c r="U60" t="n">
-        <v>0.01256656646728516</v>
+        <v>0.005859136581420898</v>
       </c>
       <c r="V60" t="n">
-        <v>0.005680518324840078</v>
+        <v>0.001375671916020432</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>0.8888888888888888, 0.6981132075471698, 0.8301886792452831, 0.7547169811320755, 0.7924528301886793, 0.7735849056603774, 0.7358490566037735</t>
+          <t>0.7592592592592593, 0.6792452830188679, 0.6792452830188679, 0.6792452830188679, 0.7735849056603774, 0.8113207547169812, 0.7924528301886793</t>
         </is>
       </c>
       <c r="X60" t="n">
-        <v>0.7819706498951782</v>
+        <v>0.7391933712688429</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.7735849056603774</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.05835693062027481</v>
+        <v>0.05399162204934726</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>0.9166666666666667, 0.75, 0.8656716417910447, 0.7936507936507937, 0.819672131147541, 0.8125, 0.7999999999999999</t>
+          <t>0.6486486486486486, 0.5853658536585367, 0.6046511627906977, 0.6046511627906977, 0.6470588235294117, 0.7058823529411764, 0.717948717948718</t>
         </is>
       </c>
       <c r="AB60" t="n">
-        <v>0.8225944618937209</v>
+        <v>0.6448866746154124</v>
       </c>
       <c r="AC60" t="n">
-        <v>0.8125</v>
+        <v>0.6470588235294117</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.0499054289258703</v>
+        <v>0.04759640829931121</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>0.8918918918918919, 0.8275862068965517, 0.8787878787878788, 0.8620689655172413, 0.9259259259259259, 0.8666666666666667, 0.7777777777777778</t>
+          <t>0.5454545454545454, 0.4444444444444444, 0.4482758620689655, 0.4482758620689655, 0.55, 0.6, 0.56</t>
         </is>
       </c>
       <c r="AF60" t="n">
-        <v>0.8615293304948477</v>
+        <v>0.5137786734338459</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="AH60" t="n">
-        <v>0.04401266989323341</v>
+        <v>0.06008844131041598</v>
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>0.9428571428571428, 0.6857142857142857, 0.8529411764705882, 0.7352941176470589, 0.7352941176470589, 0.7647058823529411, 0.8235294117647058</t>
+          <t>0.8, 0.8571428571428571, 0.9285714285714286, 0.9285714285714286, 0.7857142857142857, 0.8571428571428571, 1.0</t>
         </is>
       </c>
       <c r="AJ60" t="n">
-        <v>0.7914765906362545</v>
+        <v>0.8795918367346938</v>
       </c>
       <c r="AK60" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AL60" t="n">
-        <v>0.08100848875408138</v>
+        <v>0.07116569703739875</v>
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>0.9533834586466166, 0.8190476190476191, 0.9040247678018576, 0.8993808049535603, 0.9179566563467492, 0.8080495356037152, 0.8622291021671827</t>
+          <t>0.7717948717948718, 0.7362637362637363, 0.7591575091575091, 0.7591575091575091, 0.7774725274725274, 0.8260073260073261, 0.858974358974359</t>
         </is>
       </c>
       <c r="AN60" t="n">
-        <v>0.8805817063667573</v>
+        <v>0.7841182626896911</v>
       </c>
       <c r="AO60" t="n">
-        <v>0.8993808049535603</v>
+        <v>0.7717948717948718</v>
       </c>
       <c r="AP60" t="n">
-        <v>0.04925754914855442</v>
+        <v>0.03980361553852785</v>
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>0.7704402515723271, 0.7931034482758621, 0.7962382445141066, 0.7931034482758621, 0.7931034482758621, 0.7931034482758621, 0.8119122257053292</t>
+          <t>0.7358490566037735, 0.7492163009404389, 0.7492163009404389, 0.7492163009404389, 0.7335423197492164, 0.7272727272727273, 0.7304075235109718</t>
         </is>
       </c>
       <c r="AR60" t="n">
-        <v>0.7930006449850302</v>
+        <v>0.7392457899940009</v>
       </c>
       <c r="AS60" t="n">
-        <v>0.7931034482758621</v>
+        <v>0.7358490566037735</v>
       </c>
       <c r="AT60" t="n">
-        <v>0.01119402621971342</v>
+        <v>0.008974327046072948</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>0.8142493638676844, 0.8333333333333334, 0.8354430379746836, 0.8333333333333333, 0.83248730964467, 0.8341708542713568, 0.8492462311557789</t>
+          <t>0.6410256410256411, 0.6521739130434783, 0.6491228070175439, 0.6491228070175439, 0.6413502109704642, 0.6329113924050632, 0.6293103448275862</t>
         </is>
       </c>
       <c r="AV60" t="n">
-        <v>0.833180494797263</v>
+        <v>0.6421453023296173</v>
       </c>
       <c r="AW60" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6413502109704642</v>
       </c>
       <c r="AX60" t="n">
-        <v>0.009434910412352306</v>
+        <v>0.008016333455327197</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>0.851063829787234, 0.8638743455497382, 0.873015873015873, 0.868421052631579, 0.8723404255319149, 0.8645833333333334, 0.8802083333333334</t>
+          <t>0.5, 0.5172413793103449, 0.5174825174825175, 0.5174825174825175, 0.5, 0.4934210526315789, 0.4965986394557823</t>
         </is>
       </c>
       <c r="AZ60" t="n">
-        <v>0.8676438847404293</v>
+        <v>0.506032300908963</v>
       </c>
       <c r="BA60" t="n">
-        <v>0.868421052631579</v>
+        <v>0.5</v>
       </c>
       <c r="BB60" t="n">
-        <v>0.008517710412420229</v>
+        <v>0.0100617608357479</v>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>0.7804878048780488, 0.8048780487804879, 0.8009708737864077, 0.8009708737864077, 0.7961165048543689, 0.8058252427184466, 0.8203883495145631</t>
+          <t>0.8928571428571429, 0.8823529411764706, 0.8705882352941177, 0.8705882352941177, 0.8941176470588236, 0.8823529411764706, 0.8588235294117647</t>
         </is>
       </c>
       <c r="BD60" t="n">
-        <v>0.801376814045533</v>
+        <v>0.8788115246098439</v>
       </c>
       <c r="BE60" t="n">
-        <v>0.8009708737864077</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="BF60" t="n">
-        <v>0.01107014501770598</v>
+        <v>0.01190081008855812</v>
       </c>
       <c r="BG60" t="inlineStr">
         <is>
-          <t>0.8888625080941075, 0.9075738125802311, 0.8931824039865969, 0.8986381991580032, 0.8930535269353038, 0.9099149411461466, 0.9015594123206461</t>
+          <t>0.7861721611721613, 0.7916038210155857, 0.7878582202111614, 0.7878582202111614, 0.7846656611362495, 0.7766465560583209, 0.7712921065862243</t>
         </is>
       </c>
       <c r="BH60" t="n">
-        <v>0.8989692577458621</v>
+        <v>0.7837281066272662</v>
       </c>
       <c r="BI60" t="n">
-        <v>0.8986381991580032</v>
+        <v>0.7861721611721613</v>
       </c>
       <c r="BJ60" t="n">
-        <v>0.007283001593575346</v>
+        <v>0.006631067788558371</v>
       </c>
       <c r="BK60" t="n">
-        <v>0.7645211930926217</v>
+        <v>0.7150455927051672</v>
       </c>
       <c r="BL60" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7863636363636364</v>
       </c>
       <c r="BM60" t="n">
-        <v>0.72</v>
+        <v>0.9487179487179487</v>
       </c>
       <c r="BN60" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6727272727272727</v>
       </c>
       <c r="BO60" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.7872340425531915</v>
       </c>
       <c r="BP60" t="n">
-        <v>0.7587673196368849</v>
+        <v>0.719347119101675</v>
       </c>
       <c r="BQ60" t="n">
-        <v>0.7711309523809524</v>
+        <v>0.7830391359888514</v>
       </c>
       <c r="BR60" t="n">
-        <v>0.648</v>
+        <v>0.937888198757764</v>
       </c>
       <c r="BS60" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.6926605504587156</v>
       </c>
       <c r="BT60" t="n">
-        <v>0.7043478260869566</v>
+        <v>0.796833773087071</v>
       </c>
       <c r="BU60" t="inlineStr">
         <is>
-          <t>0.8661654135338346, 0.7039682539682539, 0.8212074303405572, 0.7623839009287926, 0.8150154798761611, 0.7770897832817337, 0.7012383900928792</t>
+          <t>0.7717948717948718, 0.7362637362637363, 0.7591575091575091, 0.7591575091575091, 0.7774725274725275, 0.826007326007326, 0.858974358974359</t>
         </is>
       </c>
       <c r="BV60" t="n">
-        <v>0.7781526645746017</v>
+        <v>0.7841182626896911</v>
       </c>
       <c r="BW60" t="n">
-        <v>0.7770897832817337</v>
+        <v>0.7717948717948718</v>
       </c>
       <c r="BX60" t="n">
-        <v>0.05685538045414647</v>
+        <v>0.03980361553852783</v>
       </c>
       <c r="BY60" t="inlineStr">
         <is>
-          <t>0.8333333333333333, 0.619047619047619, 0.7692307692307692, 0.6976744186046512, 0.7555555555555555, 0.7142857142857143, 0.6111111111111113</t>
+          <t>0.8169014084507042, 0.7384615384615384, 0.7301587301587301, 0.7301587301587301, 0.8333333333333333, 0.8611111111111112, 0.835820895522388</t>
         </is>
       </c>
       <c r="BZ60" t="n">
-        <v>0.7143197887383934</v>
+        <v>0.7922779638852192</v>
       </c>
       <c r="CA60" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.8169014084507042</v>
       </c>
       <c r="CB60" t="n">
-        <v>0.07453255760672911</v>
+        <v>0.05283350192320627</v>
       </c>
       <c r="CC60" t="inlineStr">
         <is>
-          <t>0.875, 0.6845238095238095, 0.8174512055109069, 0.7456626061277225, 0.7876138433515483, 0.7633928571428572, 0.7055555555555556</t>
+          <t>0.7327750285496764, 0.6619136960600376, 0.6674049464747139, 0.6674049464747139, 0.7401960784313725, 0.7834967320261438, 0.7768848067355529</t>
         </is>
       </c>
       <c r="CD60" t="n">
-        <v>0.7684571253160571</v>
+        <v>0.7185823192503159</v>
       </c>
       <c r="CE60" t="n">
-        <v>0.7633928571428572</v>
+        <v>0.7327750285496764</v>
       </c>
       <c r="CF60" t="n">
-        <v>0.06055154802943036</v>
+        <v>0.04888942105682</v>
       </c>
       <c r="CG60" t="inlineStr">
         <is>
-          <t>0.8823529411764706, 0.5416666666666666, 0.75, 0.625, 0.6538461538461539, 0.6521739130434783, 0.6470588235294118</t>
+          <t>0.90625, 0.9230769230769231, 0.9583333333333334, 0.9583333333333334, 0.9090909090909091, 0.9393939393939394, 1.0</t>
         </is>
       </c>
       <c r="CH60" t="n">
-        <v>0.6788712140374544</v>
+        <v>0.9420683483183483</v>
       </c>
       <c r="CI60" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.9393939393939394</v>
       </c>
       <c r="CJ60" t="n">
-        <v>0.1003866387672127</v>
+        <v>0.03076052203646088</v>
       </c>
       <c r="CK60" t="inlineStr">
         <is>
-          <t>0.7894736842105263, 0.7222222222222222, 0.7894736842105263, 0.7894736842105263, 0.8947368421052632, 0.7894736842105263, 0.5789473684210527</t>
+          <t>0.7435897435897436, 0.6153846153846154, 0.5897435897435898, 0.5897435897435898, 0.7692307692307693, 0.7948717948717948, 0.717948717948718</t>
         </is>
       </c>
       <c r="CL60" t="n">
-        <v>0.764828738512949</v>
+        <v>0.6886446886446888</v>
       </c>
       <c r="CM60" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.717948717948718</v>
       </c>
       <c r="CN60" t="n">
-        <v>0.08918104198792963</v>
+        <v>0.0815789650231505</v>
       </c>
       <c r="CO60" t="inlineStr">
         <is>
-          <t>0.7663500971292898, 0.7884039366709457, 0.7942907466277171, 0.7898659678666552, 0.7918635621616977, 0.7878683735716127, 0.8084242632528568</t>
+          <t>0.7861721611721613, 0.7916038210155857, 0.7878582202111615, 0.7878582202111615, 0.7846656611362495, 0.7766465560583207, 0.7712921065862242</t>
         </is>
       </c>
       <c r="CP60" t="n">
-        <v>0.7895809924686821</v>
+        <v>0.7837281066272662</v>
       </c>
       <c r="CQ60" t="n">
-        <v>0.7898659678666552</v>
+        <v>0.7861721611721613</v>
       </c>
       <c r="CR60" t="n">
-        <v>0.0115048747157305</v>
+        <v>0.006631067788558456</v>
       </c>
       <c r="CS60" t="inlineStr">
         <is>
-          <t>0.6995884773662552, 0.7272727272727273, 0.7325102880658437, 0.7272727272727273, 0.7295081967213114, 0.725, 0.7499999999999999</t>
+          <t>0.791044776119403, 0.8039215686274509, 0.8048780487804879, 0.8048780487804879, 0.7880299251870325, 0.7830423940149625, 0.7881773399014778</t>
         </is>
       </c>
       <c r="CT60" t="n">
-        <v>0.7273074880998377</v>
+        <v>0.7948531573444718</v>
       </c>
       <c r="CU60" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.791044776119403</v>
       </c>
       <c r="CV60" t="n">
-        <v>0.01373490244529015</v>
+        <v>0.008687872609832255</v>
       </c>
       <c r="CW60" t="inlineStr">
         <is>
-          <t>0.7569189206169697, 0.7803030303030303, 0.7839766630202636, 0.7803030303030303, 0.7809977531829907, 0.7795854271356784, 0.7996231155778895</t>
+          <t>0.7160352085725221, 0.7280477408354646, 0.7270004278990159, 0.7270004278990159, 0.7146900680787484, 0.7079768932100128, 0.708743842364532</t>
         </is>
       </c>
       <c r="CX60" t="n">
-        <v>0.7802439914485504</v>
+        <v>0.7184992298370446</v>
       </c>
       <c r="CY60" t="n">
-        <v>0.7803030303030303</v>
+        <v>0.7160352085725221</v>
       </c>
       <c r="CZ60" t="n">
-        <v>0.01155453561692818</v>
+        <v>0.008125647808803507</v>
       </c>
       <c r="DA60" t="inlineStr">
         <is>
-          <t>0.6538461538461539, 0.6875, 0.6846153846153846, 0.6821705426356589, 0.6793893129770993, 0.6850393700787402, 0.7086614173228346</t>
+          <t>0.9464285714285714, 0.9425287356321839, 0.9375, 0.9375, 0.9461077844311377, 0.9401197604790419, 0.9302325581395349</t>
         </is>
       </c>
       <c r="DB60" t="n">
-        <v>0.6830317402108387</v>
+        <v>0.9400596300157813</v>
       </c>
       <c r="DC60" t="n">
-        <v>0.6846153846153846</v>
+        <v>0.9401197604790419</v>
       </c>
       <c r="DD60" t="n">
-        <v>0.01487659518727417</v>
+        <v>0.005249740647544977</v>
       </c>
       <c r="DE60" t="inlineStr">
         <is>
-          <t>0.7522123893805309, 0.7719298245614035, 0.7876106194690266, 0.7787610619469026, 0.7876106194690266, 0.7699115044247787, 0.7964601769911505</t>
+          <t>0.6794871794871795, 0.7008547008547008, 0.7051282051282052, 0.7051282051282052, 0.6752136752136753, 0.6709401709401709, 0.6837606837606838</t>
         </is>
       </c>
       <c r="DF60" t="n">
-        <v>0.7777851708918313</v>
+        <v>0.6886446886446888</v>
       </c>
       <c r="DG60" t="n">
-        <v>0.7787610619469026</v>
+        <v>0.6837606837606838</v>
       </c>
       <c r="DH60" t="n">
-        <v>0.01359114183238239</v>
+        <v>0.01359649417052509</v>
       </c>
     </row>
   </sheetData>
